--- a/songs/DancingOnMyOwn_v1/quelle/struktur.xlsx
+++ b/songs/DancingOnMyOwn_v1/quelle/struktur.xlsx
@@ -436,15 +436,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,7 @@
       <c r="C2" s="2" t="n">
         <v>8</v>
       </c>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -478,6 +480,7 @@
       <c r="C3" s="2" t="n">
         <v>122</v>
       </c>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -488,6 +491,7 @@
       <c r="C4" s="2" t="n">
         <v>0.125</v>
       </c>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -502,20 +506,25 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Effektidee</t>
+          <t>Effekt (füllt KI)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -530,13 +539,20 @@
           <t>black</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+pause (ab 0:00.000): [SCROLLMATRIX] progBlack(2673, 1); [GITBOARD] progScrollText("Dancing On My Own by Robyn", 15984, 90, getRandomColor(), 2); [sonst] progBlack(5656, 5); [SCROLLMATRIX]
+   Start-MIDI: alle Geräte schwarz</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>progBlack(5655, 5)</t>
         </is>
@@ -551,13 +567,20 @@
           <t>bass</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+bass (ab 0:05.656): setColorScheme(SCHEME_ICE); scene(SCENE_CALM, 15737, 10, 122);
+   nur Synth-Bass, dunkel und kühl anfangen</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>progPalette(15740, 8, 10)   (Matrix: progScrollText("Dancing on my own by Robyn", 18500, 90, getRandomColor(), 10))</t>
         </is>
@@ -572,13 +595,20 @@
           <t>somebody</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+verse 1 (ab 0:21.393): setColorScheme(SCHEME_ICE); scene(SCENE_VERSE, 15738, 15, 122);
+   Gesang setzt ein, Puls auf allen Geräten, noch kalt</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>progPalette(15735, 4, 15)</t>
         </is>
@@ -593,13 +623,20 @@
           <t>git steigt ein</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+verse 1b (ab 0:37.131): setColorScheme(SCHEME_ROYAL); [ANDRESGIT] progSymmetricVU(15738, 20, 122); [GUITAR] progZoneBeat(15738, 20, 122); [sonst] scene(SCENE_VERSE, 15738, 20, 122);
+   Gitarre steigt ein und bekommt ein eigenes VU, Rest bleibt im Verse-Puls</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>progPalette(15740, 6, 20)</t>
         </is>
@@ -614,13 +651,20 @@
           <t>yeah i knwo ist stupid</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+pre-chorus (ab 0:52.869): setColorScheme(SCHEME_SUNSET); scene(SCENE_BUILDUP, 7869, 25, 122);
+   lädt sich über 4 Takte auf und entlädt sich genau in den Chorus</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>progPalette(7870, 11, 25)</t>
         </is>
@@ -635,13 +679,20 @@
           <t>chorus 1</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+chorus 1 (ab 1:00.738): setColorScheme(SCHEME_NEON); scene(SCENE_DROP, 15737, 30, 122);
+   erster Chorus, volle Energie im Beat</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(15735, 30, 26)</t>
         </is>
@@ -656,13 +707,20 @@
           <t>chorus 1b</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+chorus 1b (ab 1:16.475): scene(SCENE_WAVE_LR, 7869, 35, 122);
+   Bühnenbewegung als Variation</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(7870, 490, 35, 5, 26, 5, false, 4)</t>
         </is>
@@ -677,13 +735,21 @@
           <t>i keep dancing</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+hook 1 (ab 1:24.344): scene(SCENE_PINGPONG, 6886, 40, 122);
+   'on my own' springt von Gerät zu Gerät, kurzer Strobo als Absprung in den Stopp
+hook 1 (tail) (ab 1:31.230): progStrobo(983, 45, 75, getRandomCRGB());</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(7870, 4, 40)</t>
         </is>
@@ -698,13 +764,19 @@
           <t>pause vor verse 2a</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+stop (ab 1:32.213): progBlack(3935, 50);</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>progBlack(3935, 45)</t>
         </is>
@@ -719,13 +791,20 @@
           <t>verse 2b</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+verse 2 (ab 1:36.148): setColorScheme(SCHEME_ROYAL); scene(SCENE_VERSE, 19672, 55, 122);
+   zurück in den Puls, eine Stufe wärmer als Verse 1</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(19670, 55, 3000)
 ! im alten Code ein einziger Part mit den folgenden 1</t>
@@ -741,13 +820,20 @@
           <t>bridge</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F16" s="6" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+verse 2 (ab 1:36.148): setColorScheme(SCHEME_ROYAL); scene(SCENE_VERSE, 19672, 55, 122);
+   zurück in den Puls, eine Stufe wärmer als Verse 1</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -758,13 +844,19 @@
           <t>chorus 1</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+chorus 2 (ab 1:55.820): scene(SCENE_DROP, 15737, 60, 122);</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(15735, 60, 26)</t>
         </is>
@@ -779,13 +871,20 @@
           <t>chorus 1b</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+chorus 2b (ab 2:11.557): scene(SCENE_WAVE_RL, 7869, 65, 122);
+   Welle diesmal andersrum</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(7870, 490, 65, 5, 26, 5, true, 3)</t>
         </is>
@@ -800,13 +899,19 @@
           <t>i keep dancing</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+hook 2 (ab 2:19.426): scene(SCENE_PINGPONG, 7869, 70, 122);</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(7870, 4, 70)</t>
         </is>
@@ -821,13 +926,20 @@
           <t>instrumental</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+instrumental (ab 2:27.295): setColorScheme(SCHEME_RETRO); scene(SCENE_SOLO_GIT, 15738, 75, 122);
+   Gitarre im Spotlight, rot/weiß/blau wie im Original</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>progPalette(15740, 9, 75)</t>
         </is>
@@ -842,13 +954,20 @@
           <t>so far away</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+bridge (ab 2:43.033): setColorScheme(SCHEME_ICE); [MATRIX] matrixMovieFX(15737, 80, 100, 6); [sonst] scene(SCENE_CALM, 15737, 80, 122);
+   alles zieht sich zurück, Matrix-Film wie im Original</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>matrixMovieFX(15735, 80, 100, 6)</t>
         </is>
@@ -863,13 +982,20 @@
           <t>im in the corner</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+corner (ab 2:58.770): progBlack(5902, 85);
+   Stille vor dem Finale</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>progBlack(5900, 85)</t>
         </is>
@@ -884,13 +1010,20 @@
           <t>snarewirbel</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+snare roll (ab 3:04.672): setColorScheme(SCHEME_WHITE); scene(SCENE_BUILDUP, 1967, 90, 122);
+   1 Takt Aufladen, Blast genau auf den Einsatz</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1970, 90, 50, getRandomCRGB())</t>
         </is>
@@ -905,13 +1038,20 @@
           <t>chorus 1</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+chorus 3 (ab 3:06.639): setColorScheme(SCHEME_FIRE); scene(SCENE_FIRE, 7869, 95, 122);
+   Finale beginnt, Farbwechsel auf Feuer</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(7870, 95, 50, true, true)</t>
         </is>
@@ -926,13 +1066,19 @@
           <t>i keep dancing</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+hook 3 (ab 3:14.508): setColorScheme(SCHEME_FIRE); scene(SCENE_WAVE_OUT, 7869, 100, 122);</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(7865, 4, 100)</t>
         </is>
@@ -947,13 +1093,19 @@
           <t>chorus 1</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+chorus 4 (ab 3:22.377): setColorScheme(SCHEME_SUNSET); scene(SCENE_DROP, 15738, 105, 122);</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(15740, 490, 105, 5, 26, 5, false, 4)</t>
         </is>
@@ -968,13 +1120,19 @@
           <t>chorus 1b</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+chorus 4b (ab 3:38.115): setColorScheme(SCHEME_SUNSET); scene(SCENE_PINGPONG, 7869, 110, 122);</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(7870, 4, 110)</t>
         </is>
@@ -989,13 +1147,19 @@
           <t>i keep dancing</t>
         </is>
       </c>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+hook 4 (ab 3:45.984): setColorScheme(SCHEME_SUNSET); scene(SCENE_WAVE_LR, 7868, 115, 122);</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(7865, 490, 115, 5, 26, 5, true, 3)</t>
         </is>
@@ -1010,13 +1174,21 @@
           <t>i keep dancing</t>
         </is>
       </c>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+hook 5 (ab 3:53.852): setColorScheme(SCHEME_FIRE); scene(SCENE_FIRE, 13771, 120, 122);
+   Höhepunkt, letzter Takt weißer Strobo
+hook 5 (tail) (ab 4:07.623): setColorScheme(SCHEME_FIRE); progStrobo(1967, 125, 65, CRGB::White);</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(15740, 8, 120)</t>
         </is>
@@ -1031,13 +1203,20 @@
           <t>instrumental</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+outro (ab 4:09.590): setColorScheme(SCHEME_SUNSET); scene(SCENE_CALM, 15738, 130, 122);
+   ausatmen</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(15740, 127, 50, true, true)</t>
         </is>
@@ -1052,13 +1231,19 @@
           <t>outro</t>
         </is>
       </c>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+zu dieser Zeit ist der generierte Code schon zu Ende (schwarz, dann Pausen-Loop)</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>! nur im Excel - der alte Code geht hier schon in Schwarz</t>
         </is>
@@ -1078,10 +1263,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>0</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/DancingOnMyOwn_v1/quelle/struktur.xlsx
+++ b/songs/DancingOnMyOwn_v1/quelle/struktur.xlsx
@@ -532,7 +532,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>

--- a/songs/DancingOnMyOwn_v1/quelle/struktur.xlsx
+++ b/songs/DancingOnMyOwn_v1/quelle/struktur.xlsx
@@ -433,10 +433,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -530,7 +530,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" collapsed="1">
       <c r="A6" s="4" t="n">
         <v>1</v>
       </c>
@@ -558,324 +558,141 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="1" outlineLevel="2">
       <c r="A7" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="n"/>
+    </row>
+    <row r="8" hidden="1" outlineLevel="2">
+      <c r="A8" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="n"/>
+    </row>
+    <row r="9" hidden="1" outlineLevel="2">
+      <c r="A9" s="4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="n"/>
+    </row>
+    <row r="10" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="n"/>
+    </row>
+    <row r="11" hidden="1" outlineLevel="2">
+      <c r="A11" s="4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="n"/>
+    </row>
+    <row r="12" hidden="1" outlineLevel="2">
+      <c r="A12" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="6" t="n"/>
+    </row>
+    <row r="13" hidden="1" outlineLevel="2">
+      <c r="A13" s="4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="n"/>
+    </row>
+    <row r="14" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="n"/>
+    </row>
+    <row r="15" hidden="1" outlineLevel="2">
+      <c r="A15" s="4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="n"/>
+    </row>
+    <row r="16" hidden="1" outlineLevel="2">
+      <c r="A16" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="n"/>
+    </row>
+    <row r="17" hidden="1" outlineLevel="2">
+      <c r="A17" s="4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="6" t="n"/>
+    </row>
+    <row r="18" collapsed="1">
+      <c r="A18" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>bass</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>generierter Code (eingefroren, ohne show.yaml):
 bass (ab 0:05.656): setColorScheme(SCHEME_ICE); scene(SCENE_CALM, 15737, 10, 122);
    nur Synth-Bass, dunkel und kühl anfangen</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>progPalette(15740, 8, 10)   (Matrix: progScrollText("Dancing on my own by Robyn", 18500, 90, getRandomColor(), 10))</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>somebody</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-verse 1 (ab 0:21.393): setColorScheme(SCHEME_ICE); scene(SCENE_VERSE, 15738, 15, 122);
-   Gesang setzt ein, Puls auf allen Geräten, noch kalt</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>progPalette(15735, 4, 15)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>git steigt ein</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-verse 1b (ab 0:37.131): setColorScheme(SCHEME_ROYAL); [ANDRESGIT] progSymmetricVU(15738, 20, 122); [GUITAR] progZoneBeat(15738, 20, 122); [sonst] scene(SCENE_VERSE, 15738, 20, 122);
-   Gitarre steigt ein und bekommt ein eigenes VU, Rest bleibt im Verse-Puls</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>progPalette(15740, 6, 20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>yeah i knwo ist stupid</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-pre-chorus (ab 0:52.869): setColorScheme(SCHEME_SUNSET); scene(SCENE_BUILDUP, 7869, 25, 122);
-   lädt sich über 4 Takte auf und entlädt sich genau in den Chorus</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>progPalette(7870, 11, 25)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>chorus 1</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-chorus 1 (ab 1:00.738): setColorScheme(SCHEME_NEON); scene(SCENE_DROP, 15737, 30, 122);
-   erster Chorus, volle Energie im Beat</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>progMatrixScanner(15735, 30, 26)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>chorus 1b</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-chorus 1b (ab 1:16.475): scene(SCENE_WAVE_LR, 7869, 35, 122);
-   Bühnenbewegung als Variation</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>progSternNeu(7870, 490, 35, 5, 26, 5, false, 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>i keep dancing</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-hook 1 (ab 1:24.344): scene(SCENE_PINGPONG, 6886, 40, 122);
-   'on my own' springt von Gerät zu Gerät, kurzer Strobo als Absprung in den Stopp
-hook 1 (tail) (ab 1:31.230): progStrobo(983, 45, 75, getRandomCRGB());</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>progFastBlingBling(7870, 4, 40)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>pause vor verse 2a</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-stop (ab 1:32.213): progBlack(3935, 50);</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>progBlack(3935, 45)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>verse 2b</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-verse 2 (ab 1:36.148): setColorScheme(SCHEME_ROYAL); scene(SCENE_VERSE, 19672, 55, 122);
-   zurück in den Puls, eine Stufe wärmer als Verse 1</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>progBlingBlingColoring(19670, 55, 3000)
-! im alten Code ein einziger Part mit den folgenden 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>bridge</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-verse 2 (ab 1:36.148): setColorScheme(SCHEME_ROYAL); scene(SCENE_VERSE, 19672, 55, 122);
-   zurück in den Puls, eine Stufe wärmer als Verse 1</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G16" s="6" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>chorus 1</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-chorus 2 (ab 1:55.820): scene(SCENE_DROP, 15737, 60, 122);</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>progMatrixScanner(15735, 60, 26)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>chorus 1b</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-chorus 2b (ab 2:11.557): scene(SCENE_WAVE_RL, 7869, 65, 122);
-   Welle diesmal andersrum</t>
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
@@ -886,295 +703,5461 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
+          <t>progPalette(15740, 8, 10)   (Matrix: progScrollText("Dancing on my own by Robyn", 18500, 90, getRandomColor(), 10))</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" hidden="1" outlineLevel="2">
+      <c r="A19" s="4" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="6" t="n"/>
+    </row>
+    <row r="20" hidden="1" outlineLevel="2">
+      <c r="A20" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="6" t="n"/>
+    </row>
+    <row r="21" hidden="1" outlineLevel="2">
+      <c r="A21" s="4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="6" t="n"/>
+    </row>
+    <row r="22" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A22" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="6" t="n"/>
+    </row>
+    <row r="23" hidden="1" outlineLevel="2">
+      <c r="A23" s="4" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="6" t="n"/>
+    </row>
+    <row r="24" hidden="1" outlineLevel="2">
+      <c r="A24" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="6" t="n"/>
+    </row>
+    <row r="25" hidden="1" outlineLevel="2">
+      <c r="A25" s="4" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="6" t="n"/>
+    </row>
+    <row r="26" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A26" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="6" t="n"/>
+    </row>
+    <row r="27" hidden="1" outlineLevel="2">
+      <c r="A27" s="4" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="6" t="n"/>
+    </row>
+    <row r="28" hidden="1" outlineLevel="2">
+      <c r="A28" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="6" t="n"/>
+    </row>
+    <row r="29" hidden="1" outlineLevel="2">
+      <c r="A29" s="4" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="6" t="n"/>
+    </row>
+    <row r="30" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A30" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="6" t="n"/>
+    </row>
+    <row r="31" hidden="1" outlineLevel="2">
+      <c r="A31" s="4" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="6" t="n"/>
+    </row>
+    <row r="32" hidden="1" outlineLevel="2">
+      <c r="A32" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="6" t="n"/>
+    </row>
+    <row r="33" hidden="1" outlineLevel="2">
+      <c r="A33" s="4" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="6" t="n"/>
+    </row>
+    <row r="34" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A34" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="6" t="n"/>
+    </row>
+    <row r="35" hidden="1" outlineLevel="2">
+      <c r="A35" s="4" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="6" t="n"/>
+    </row>
+    <row r="36" hidden="1" outlineLevel="2">
+      <c r="A36" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="6" t="n"/>
+    </row>
+    <row r="37" hidden="1" outlineLevel="2">
+      <c r="A37" s="4" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="6" t="n"/>
+    </row>
+    <row r="38" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A38" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="6" t="n"/>
+    </row>
+    <row r="39" hidden="1" outlineLevel="2">
+      <c r="A39" s="4" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="6" t="n"/>
+    </row>
+    <row r="40" hidden="1" outlineLevel="2">
+      <c r="A40" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="6" t="n"/>
+    </row>
+    <row r="41" hidden="1" outlineLevel="2">
+      <c r="A41" s="4" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="6" t="n"/>
+    </row>
+    <row r="42" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A42" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="6" t="n"/>
+    </row>
+    <row r="43" hidden="1" outlineLevel="2">
+      <c r="A43" s="4" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="6" t="n"/>
+    </row>
+    <row r="44" hidden="1" outlineLevel="2">
+      <c r="A44" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="6" t="n"/>
+    </row>
+    <row r="45" hidden="1" outlineLevel="2">
+      <c r="A45" s="4" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="6" t="n"/>
+    </row>
+    <row r="46" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A46" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="6" t="n"/>
+    </row>
+    <row r="47" hidden="1" outlineLevel="2">
+      <c r="A47" s="4" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="6" t="n"/>
+    </row>
+    <row r="48" hidden="1" outlineLevel="2">
+      <c r="A48" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="6" t="n"/>
+    </row>
+    <row r="49" hidden="1" outlineLevel="2">
+      <c r="A49" s="4" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="B49" s="5" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="6" t="n"/>
+    </row>
+    <row r="50" collapsed="1">
+      <c r="A50" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>somebody</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+verse 1 (ab 0:21.393): setColorScheme(SCHEME_ICE); scene(SCENE_VERSE, 15738, 15, 122);
+   Gesang setzt ein, Puls auf allen Geräten, noch kalt</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>progPalette(15735, 4, 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" hidden="1" outlineLevel="2">
+      <c r="A51" s="4" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="6" t="n"/>
+    </row>
+    <row r="52" hidden="1" outlineLevel="2">
+      <c r="A52" s="4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="6" t="n"/>
+    </row>
+    <row r="53" hidden="1" outlineLevel="2">
+      <c r="A53" s="4" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="B53" s="5" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="6" t="n"/>
+    </row>
+    <row r="54" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A54" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="6" t="n"/>
+    </row>
+    <row r="55" hidden="1" outlineLevel="2">
+      <c r="A55" s="4" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="6" t="n"/>
+    </row>
+    <row r="56" hidden="1" outlineLevel="2">
+      <c r="A56" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="6" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="6" t="n"/>
+    </row>
+    <row r="57" hidden="1" outlineLevel="2">
+      <c r="A57" s="4" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="6" t="n"/>
+    </row>
+    <row r="58" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A58" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="6" t="n"/>
+    </row>
+    <row r="59" hidden="1" outlineLevel="2">
+      <c r="A59" s="4" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="B59" s="5" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="6" t="n"/>
+    </row>
+    <row r="60" hidden="1" outlineLevel="2">
+      <c r="A60" s="4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="B60" s="5" t="n"/>
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="6" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="6" t="n"/>
+    </row>
+    <row r="61" hidden="1" outlineLevel="2">
+      <c r="A61" s="4" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="B61" s="5" t="n"/>
+      <c r="C61" s="6" t="n"/>
+      <c r="D61" s="6" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="6" t="n"/>
+    </row>
+    <row r="62" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A62" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B62" s="5" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="n"/>
+      <c r="G62" s="6" t="n"/>
+    </row>
+    <row r="63" hidden="1" outlineLevel="2">
+      <c r="A63" s="4" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="B63" s="5" t="n"/>
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="6" t="n"/>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="n"/>
+      <c r="G63" s="6" t="n"/>
+    </row>
+    <row r="64" hidden="1" outlineLevel="2">
+      <c r="A64" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="B64" s="5" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="n"/>
+      <c r="G64" s="6" t="n"/>
+    </row>
+    <row r="65" hidden="1" outlineLevel="2">
+      <c r="A65" s="4" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="B65" s="5" t="n"/>
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="6" t="n"/>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="n"/>
+      <c r="G65" s="6" t="n"/>
+    </row>
+    <row r="66" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A66" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B66" s="5" t="n"/>
+      <c r="C66" s="6" t="n"/>
+      <c r="D66" s="6" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="6" t="n"/>
+    </row>
+    <row r="67" hidden="1" outlineLevel="2">
+      <c r="A67" s="4" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="B67" s="5" t="n"/>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="6" t="n"/>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="n"/>
+      <c r="G67" s="6" t="n"/>
+    </row>
+    <row r="68" hidden="1" outlineLevel="2">
+      <c r="A68" s="4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="B68" s="5" t="n"/>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="n"/>
+      <c r="G68" s="6" t="n"/>
+    </row>
+    <row r="69" hidden="1" outlineLevel="2">
+      <c r="A69" s="4" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="B69" s="5" t="n"/>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="6" t="n"/>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="n"/>
+      <c r="G69" s="6" t="n"/>
+    </row>
+    <row r="70" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A70" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B70" s="5" t="n"/>
+      <c r="C70" s="6" t="n"/>
+      <c r="D70" s="6" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="n"/>
+      <c r="G70" s="6" t="n"/>
+    </row>
+    <row r="71" hidden="1" outlineLevel="2">
+      <c r="A71" s="4" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="6" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="n"/>
+      <c r="G71" s="6" t="n"/>
+    </row>
+    <row r="72" hidden="1" outlineLevel="2">
+      <c r="A72" s="4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="6" t="n"/>
+      <c r="D72" s="6" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="n"/>
+      <c r="G72" s="6" t="n"/>
+    </row>
+    <row r="73" hidden="1" outlineLevel="2">
+      <c r="A73" s="4" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="B73" s="5" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="6" t="n"/>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="5" t="n"/>
+      <c r="G73" s="6" t="n"/>
+    </row>
+    <row r="74" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A74" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B74" s="5" t="n"/>
+      <c r="C74" s="6" t="n"/>
+      <c r="D74" s="6" t="n"/>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="n"/>
+      <c r="G74" s="6" t="n"/>
+    </row>
+    <row r="75" hidden="1" outlineLevel="2">
+      <c r="A75" s="4" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="B75" s="5" t="n"/>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="6" t="n"/>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="5" t="n"/>
+      <c r="G75" s="6" t="n"/>
+    </row>
+    <row r="76" hidden="1" outlineLevel="2">
+      <c r="A76" s="4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="B76" s="5" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="n"/>
+      <c r="G76" s="6" t="n"/>
+    </row>
+    <row r="77" hidden="1" outlineLevel="2">
+      <c r="A77" s="4" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="B77" s="5" t="n"/>
+      <c r="C77" s="6" t="n"/>
+      <c r="D77" s="6" t="n"/>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="n"/>
+      <c r="G77" s="6" t="n"/>
+    </row>
+    <row r="78" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A78" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B78" s="5" t="n"/>
+      <c r="C78" s="6" t="n"/>
+      <c r="D78" s="6" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="6" t="n"/>
+    </row>
+    <row r="79" hidden="1" outlineLevel="2">
+      <c r="A79" s="4" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="B79" s="5" t="n"/>
+      <c r="C79" s="6" t="n"/>
+      <c r="D79" s="6" t="n"/>
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="5" t="n"/>
+      <c r="G79" s="6" t="n"/>
+    </row>
+    <row r="80" hidden="1" outlineLevel="2">
+      <c r="A80" s="4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="B80" s="5" t="n"/>
+      <c r="C80" s="6" t="n"/>
+      <c r="D80" s="6" t="n"/>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="5" t="n"/>
+      <c r="G80" s="6" t="n"/>
+    </row>
+    <row r="81" hidden="1" outlineLevel="2">
+      <c r="A81" s="4" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="B81" s="5" t="n"/>
+      <c r="C81" s="6" t="n"/>
+      <c r="D81" s="6" t="n"/>
+      <c r="E81" s="5" t="n"/>
+      <c r="F81" s="5" t="n"/>
+      <c r="G81" s="6" t="n"/>
+    </row>
+    <row r="82" collapsed="1">
+      <c r="A82" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>git steigt ein</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+verse 1b (ab 0:37.131): setColorScheme(SCHEME_ROYAL); [ANDRESGIT] progSymmetricVU(15738, 20, 122); [GUITAR] progZoneBeat(15738, 20, 122); [sonst] scene(SCENE_VERSE, 15738, 20, 122);
+   Gitarre steigt ein und bekommt ein eigenes VU, Rest bleibt im Verse-Puls</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="n"/>
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>progPalette(15740, 6, 20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" hidden="1" outlineLevel="2">
+      <c r="A83" s="4" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="B83" s="5" t="n"/>
+      <c r="C83" s="6" t="n"/>
+      <c r="D83" s="6" t="n"/>
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="5" t="n"/>
+      <c r="G83" s="6" t="n"/>
+    </row>
+    <row r="84" hidden="1" outlineLevel="2">
+      <c r="A84" s="4" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="B84" s="5" t="n"/>
+      <c r="C84" s="6" t="n"/>
+      <c r="D84" s="6" t="n"/>
+      <c r="E84" s="5" t="n"/>
+      <c r="F84" s="5" t="n"/>
+      <c r="G84" s="6" t="n"/>
+    </row>
+    <row r="85" hidden="1" outlineLevel="2">
+      <c r="A85" s="4" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="B85" s="5" t="n"/>
+      <c r="C85" s="6" t="n"/>
+      <c r="D85" s="6" t="n"/>
+      <c r="E85" s="5" t="n"/>
+      <c r="F85" s="5" t="n"/>
+      <c r="G85" s="6" t="n"/>
+    </row>
+    <row r="86" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A86" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B86" s="5" t="n"/>
+      <c r="C86" s="6" t="n"/>
+      <c r="D86" s="6" t="n"/>
+      <c r="E86" s="5" t="n"/>
+      <c r="F86" s="5" t="n"/>
+      <c r="G86" s="6" t="n"/>
+    </row>
+    <row r="87" hidden="1" outlineLevel="2">
+      <c r="A87" s="4" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="B87" s="5" t="n"/>
+      <c r="C87" s="6" t="n"/>
+      <c r="D87" s="6" t="n"/>
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="5" t="n"/>
+      <c r="G87" s="6" t="n"/>
+    </row>
+    <row r="88" hidden="1" outlineLevel="2">
+      <c r="A88" s="4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="B88" s="5" t="n"/>
+      <c r="C88" s="6" t="n"/>
+      <c r="D88" s="6" t="n"/>
+      <c r="E88" s="5" t="n"/>
+      <c r="F88" s="5" t="n"/>
+      <c r="G88" s="6" t="n"/>
+    </row>
+    <row r="89" hidden="1" outlineLevel="2">
+      <c r="A89" s="4" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="B89" s="5" t="n"/>
+      <c r="C89" s="6" t="n"/>
+      <c r="D89" s="6" t="n"/>
+      <c r="E89" s="5" t="n"/>
+      <c r="F89" s="5" t="n"/>
+      <c r="G89" s="6" t="n"/>
+    </row>
+    <row r="90" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A90" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B90" s="5" t="n"/>
+      <c r="C90" s="6" t="n"/>
+      <c r="D90" s="6" t="n"/>
+      <c r="E90" s="5" t="n"/>
+      <c r="F90" s="5" t="n"/>
+      <c r="G90" s="6" t="n"/>
+    </row>
+    <row r="91" hidden="1" outlineLevel="2">
+      <c r="A91" s="4" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="B91" s="5" t="n"/>
+      <c r="C91" s="6" t="n"/>
+      <c r="D91" s="6" t="n"/>
+      <c r="E91" s="5" t="n"/>
+      <c r="F91" s="5" t="n"/>
+      <c r="G91" s="6" t="n"/>
+    </row>
+    <row r="92" hidden="1" outlineLevel="2">
+      <c r="A92" s="4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="B92" s="5" t="n"/>
+      <c r="C92" s="6" t="n"/>
+      <c r="D92" s="6" t="n"/>
+      <c r="E92" s="5" t="n"/>
+      <c r="F92" s="5" t="n"/>
+      <c r="G92" s="6" t="n"/>
+    </row>
+    <row r="93" hidden="1" outlineLevel="2">
+      <c r="A93" s="4" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="B93" s="5" t="n"/>
+      <c r="C93" s="6" t="n"/>
+      <c r="D93" s="6" t="n"/>
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="5" t="n"/>
+      <c r="G93" s="6" t="n"/>
+    </row>
+    <row r="94" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A94" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B94" s="5" t="n"/>
+      <c r="C94" s="6" t="n"/>
+      <c r="D94" s="6" t="n"/>
+      <c r="E94" s="5" t="n"/>
+      <c r="F94" s="5" t="n"/>
+      <c r="G94" s="6" t="n"/>
+    </row>
+    <row r="95" hidden="1" outlineLevel="2">
+      <c r="A95" s="4" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="B95" s="5" t="n"/>
+      <c r="C95" s="6" t="n"/>
+      <c r="D95" s="6" t="n"/>
+      <c r="E95" s="5" t="n"/>
+      <c r="F95" s="5" t="n"/>
+      <c r="G95" s="6" t="n"/>
+    </row>
+    <row r="96" hidden="1" outlineLevel="2">
+      <c r="A96" s="4" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="B96" s="5" t="n"/>
+      <c r="C96" s="6" t="n"/>
+      <c r="D96" s="6" t="n"/>
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="5" t="n"/>
+      <c r="G96" s="6" t="n"/>
+    </row>
+    <row r="97" hidden="1" outlineLevel="2">
+      <c r="A97" s="4" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="B97" s="5" t="n"/>
+      <c r="C97" s="6" t="n"/>
+      <c r="D97" s="6" t="n"/>
+      <c r="E97" s="5" t="n"/>
+      <c r="F97" s="5" t="n"/>
+      <c r="G97" s="6" t="n"/>
+    </row>
+    <row r="98" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A98" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B98" s="5" t="n"/>
+      <c r="C98" s="6" t="n"/>
+      <c r="D98" s="6" t="n"/>
+      <c r="E98" s="5" t="n"/>
+      <c r="F98" s="5" t="n"/>
+      <c r="G98" s="6" t="n"/>
+    </row>
+    <row r="99" hidden="1" outlineLevel="2">
+      <c r="A99" s="4" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="B99" s="5" t="n"/>
+      <c r="C99" s="6" t="n"/>
+      <c r="D99" s="6" t="n"/>
+      <c r="E99" s="5" t="n"/>
+      <c r="F99" s="5" t="n"/>
+      <c r="G99" s="6" t="n"/>
+    </row>
+    <row r="100" hidden="1" outlineLevel="2">
+      <c r="A100" s="4" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="B100" s="5" t="n"/>
+      <c r="C100" s="6" t="n"/>
+      <c r="D100" s="6" t="n"/>
+      <c r="E100" s="5" t="n"/>
+      <c r="F100" s="5" t="n"/>
+      <c r="G100" s="6" t="n"/>
+    </row>
+    <row r="101" hidden="1" outlineLevel="2">
+      <c r="A101" s="4" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="B101" s="5" t="n"/>
+      <c r="C101" s="6" t="n"/>
+      <c r="D101" s="6" t="n"/>
+      <c r="E101" s="5" t="n"/>
+      <c r="F101" s="5" t="n"/>
+      <c r="G101" s="6" t="n"/>
+    </row>
+    <row r="102" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A102" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B102" s="5" t="n"/>
+      <c r="C102" s="6" t="n"/>
+      <c r="D102" s="6" t="n"/>
+      <c r="E102" s="5" t="n"/>
+      <c r="F102" s="5" t="n"/>
+      <c r="G102" s="6" t="n"/>
+    </row>
+    <row r="103" hidden="1" outlineLevel="2">
+      <c r="A103" s="4" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="B103" s="5" t="n"/>
+      <c r="C103" s="6" t="n"/>
+      <c r="D103" s="6" t="n"/>
+      <c r="E103" s="5" t="n"/>
+      <c r="F103" s="5" t="n"/>
+      <c r="G103" s="6" t="n"/>
+    </row>
+    <row r="104" hidden="1" outlineLevel="2">
+      <c r="A104" s="4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="B104" s="5" t="n"/>
+      <c r="C104" s="6" t="n"/>
+      <c r="D104" s="6" t="n"/>
+      <c r="E104" s="5" t="n"/>
+      <c r="F104" s="5" t="n"/>
+      <c r="G104" s="6" t="n"/>
+    </row>
+    <row r="105" hidden="1" outlineLevel="2">
+      <c r="A105" s="4" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="B105" s="5" t="n"/>
+      <c r="C105" s="6" t="n"/>
+      <c r="D105" s="6" t="n"/>
+      <c r="E105" s="5" t="n"/>
+      <c r="F105" s="5" t="n"/>
+      <c r="G105" s="6" t="n"/>
+    </row>
+    <row r="106" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A106" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B106" s="5" t="n"/>
+      <c r="C106" s="6" t="n"/>
+      <c r="D106" s="6" t="n"/>
+      <c r="E106" s="5" t="n"/>
+      <c r="F106" s="5" t="n"/>
+      <c r="G106" s="6" t="n"/>
+    </row>
+    <row r="107" hidden="1" outlineLevel="2">
+      <c r="A107" s="4" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="B107" s="5" t="n"/>
+      <c r="C107" s="6" t="n"/>
+      <c r="D107" s="6" t="n"/>
+      <c r="E107" s="5" t="n"/>
+      <c r="F107" s="5" t="n"/>
+      <c r="G107" s="6" t="n"/>
+    </row>
+    <row r="108" hidden="1" outlineLevel="2">
+      <c r="A108" s="4" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="B108" s="5" t="n"/>
+      <c r="C108" s="6" t="n"/>
+      <c r="D108" s="6" t="n"/>
+      <c r="E108" s="5" t="n"/>
+      <c r="F108" s="5" t="n"/>
+      <c r="G108" s="6" t="n"/>
+    </row>
+    <row r="109" hidden="1" outlineLevel="2">
+      <c r="A109" s="4" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="B109" s="5" t="n"/>
+      <c r="C109" s="6" t="n"/>
+      <c r="D109" s="6" t="n"/>
+      <c r="E109" s="5" t="n"/>
+      <c r="F109" s="5" t="n"/>
+      <c r="G109" s="6" t="n"/>
+    </row>
+    <row r="110" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A110" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B110" s="5" t="n"/>
+      <c r="C110" s="6" t="n"/>
+      <c r="D110" s="6" t="n"/>
+      <c r="E110" s="5" t="n"/>
+      <c r="F110" s="5" t="n"/>
+      <c r="G110" s="6" t="n"/>
+    </row>
+    <row r="111" hidden="1" outlineLevel="2">
+      <c r="A111" s="4" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="B111" s="5" t="n"/>
+      <c r="C111" s="6" t="n"/>
+      <c r="D111" s="6" t="n"/>
+      <c r="E111" s="5" t="n"/>
+      <c r="F111" s="5" t="n"/>
+      <c r="G111" s="6" t="n"/>
+    </row>
+    <row r="112" hidden="1" outlineLevel="2">
+      <c r="A112" s="4" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="B112" s="5" t="n"/>
+      <c r="C112" s="6" t="n"/>
+      <c r="D112" s="6" t="n"/>
+      <c r="E112" s="5" t="n"/>
+      <c r="F112" s="5" t="n"/>
+      <c r="G112" s="6" t="n"/>
+    </row>
+    <row r="113" hidden="1" outlineLevel="2">
+      <c r="A113" s="4" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="B113" s="5" t="n"/>
+      <c r="C113" s="6" t="n"/>
+      <c r="D113" s="6" t="n"/>
+      <c r="E113" s="5" t="n"/>
+      <c r="F113" s="5" t="n"/>
+      <c r="G113" s="6" t="n"/>
+    </row>
+    <row r="114" collapsed="1">
+      <c r="A114" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>yeah i knwo ist stupid</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+pre-chorus (ab 0:52.869): setColorScheme(SCHEME_SUNSET); scene(SCENE_BUILDUP, 7869, 25, 122);
+   lädt sich über 4 Takte auf und entlädt sich genau in den Chorus</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="n"/>
+      <c r="E114" s="5" t="n"/>
+      <c r="F114" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>progPalette(7870, 11, 25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" hidden="1" outlineLevel="2">
+      <c r="A115" s="4" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="B115" s="5" t="n"/>
+      <c r="C115" s="6" t="n"/>
+      <c r="D115" s="6" t="n"/>
+      <c r="E115" s="5" t="n"/>
+      <c r="F115" s="5" t="n"/>
+      <c r="G115" s="6" t="n"/>
+    </row>
+    <row r="116" hidden="1" outlineLevel="2">
+      <c r="A116" s="4" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="B116" s="5" t="n"/>
+      <c r="C116" s="6" t="n"/>
+      <c r="D116" s="6" t="n"/>
+      <c r="E116" s="5" t="n"/>
+      <c r="F116" s="5" t="n"/>
+      <c r="G116" s="6" t="n"/>
+    </row>
+    <row r="117" hidden="1" outlineLevel="2">
+      <c r="A117" s="4" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="B117" s="5" t="n"/>
+      <c r="C117" s="6" t="n"/>
+      <c r="D117" s="6" t="n"/>
+      <c r="E117" s="5" t="n"/>
+      <c r="F117" s="5" t="n"/>
+      <c r="G117" s="6" t="n"/>
+    </row>
+    <row r="118" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A118" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B118" s="5" t="n"/>
+      <c r="C118" s="6" t="n"/>
+      <c r="D118" s="6" t="n"/>
+      <c r="E118" s="5" t="n"/>
+      <c r="F118" s="5" t="n"/>
+      <c r="G118" s="6" t="n"/>
+    </row>
+    <row r="119" hidden="1" outlineLevel="2">
+      <c r="A119" s="4" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="B119" s="5" t="n"/>
+      <c r="C119" s="6" t="n"/>
+      <c r="D119" s="6" t="n"/>
+      <c r="E119" s="5" t="n"/>
+      <c r="F119" s="5" t="n"/>
+      <c r="G119" s="6" t="n"/>
+    </row>
+    <row r="120" hidden="1" outlineLevel="2">
+      <c r="A120" s="4" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="B120" s="5" t="n"/>
+      <c r="C120" s="6" t="n"/>
+      <c r="D120" s="6" t="n"/>
+      <c r="E120" s="5" t="n"/>
+      <c r="F120" s="5" t="n"/>
+      <c r="G120" s="6" t="n"/>
+    </row>
+    <row r="121" hidden="1" outlineLevel="2">
+      <c r="A121" s="4" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="B121" s="5" t="n"/>
+      <c r="C121" s="6" t="n"/>
+      <c r="D121" s="6" t="n"/>
+      <c r="E121" s="5" t="n"/>
+      <c r="F121" s="5" t="n"/>
+      <c r="G121" s="6" t="n"/>
+    </row>
+    <row r="122" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A122" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B122" s="5" t="n"/>
+      <c r="C122" s="6" t="n"/>
+      <c r="D122" s="6" t="n"/>
+      <c r="E122" s="5" t="n"/>
+      <c r="F122" s="5" t="n"/>
+      <c r="G122" s="6" t="n"/>
+    </row>
+    <row r="123" hidden="1" outlineLevel="2">
+      <c r="A123" s="4" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="B123" s="5" t="n"/>
+      <c r="C123" s="6" t="n"/>
+      <c r="D123" s="6" t="n"/>
+      <c r="E123" s="5" t="n"/>
+      <c r="F123" s="5" t="n"/>
+      <c r="G123" s="6" t="n"/>
+    </row>
+    <row r="124" hidden="1" outlineLevel="2">
+      <c r="A124" s="4" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="B124" s="5" t="n"/>
+      <c r="C124" s="6" t="n"/>
+      <c r="D124" s="6" t="n"/>
+      <c r="E124" s="5" t="n"/>
+      <c r="F124" s="5" t="n"/>
+      <c r="G124" s="6" t="n"/>
+    </row>
+    <row r="125" hidden="1" outlineLevel="2">
+      <c r="A125" s="4" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="B125" s="5" t="n"/>
+      <c r="C125" s="6" t="n"/>
+      <c r="D125" s="6" t="n"/>
+      <c r="E125" s="5" t="n"/>
+      <c r="F125" s="5" t="n"/>
+      <c r="G125" s="6" t="n"/>
+    </row>
+    <row r="126" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A126" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B126" s="5" t="n"/>
+      <c r="C126" s="6" t="n"/>
+      <c r="D126" s="6" t="n"/>
+      <c r="E126" s="5" t="n"/>
+      <c r="F126" s="5" t="n"/>
+      <c r="G126" s="6" t="n"/>
+    </row>
+    <row r="127" hidden="1" outlineLevel="2">
+      <c r="A127" s="4" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="B127" s="5" t="n"/>
+      <c r="C127" s="6" t="n"/>
+      <c r="D127" s="6" t="n"/>
+      <c r="E127" s="5" t="n"/>
+      <c r="F127" s="5" t="n"/>
+      <c r="G127" s="6" t="n"/>
+    </row>
+    <row r="128" hidden="1" outlineLevel="2">
+      <c r="A128" s="4" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="B128" s="5" t="n"/>
+      <c r="C128" s="6" t="n"/>
+      <c r="D128" s="6" t="n"/>
+      <c r="E128" s="5" t="n"/>
+      <c r="F128" s="5" t="n"/>
+      <c r="G128" s="6" t="n"/>
+    </row>
+    <row r="129" hidden="1" outlineLevel="2">
+      <c r="A129" s="4" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="B129" s="5" t="n"/>
+      <c r="C129" s="6" t="n"/>
+      <c r="D129" s="6" t="n"/>
+      <c r="E129" s="5" t="n"/>
+      <c r="F129" s="5" t="n"/>
+      <c r="G129" s="6" t="n"/>
+    </row>
+    <row r="130" collapsed="1">
+      <c r="A130" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>chorus 1</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+chorus 1 (ab 1:00.738): setColorScheme(SCHEME_NEON); scene(SCENE_DROP, 15737, 30, 122);
+   erster Chorus, volle Energie im Beat</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="n"/>
+      <c r="E130" s="5" t="n"/>
+      <c r="F130" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>progMatrixScanner(15735, 30, 26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" hidden="1" outlineLevel="2">
+      <c r="A131" s="4" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="B131" s="5" t="n"/>
+      <c r="C131" s="6" t="n"/>
+      <c r="D131" s="6" t="n"/>
+      <c r="E131" s="5" t="n"/>
+      <c r="F131" s="5" t="n"/>
+      <c r="G131" s="6" t="n"/>
+    </row>
+    <row r="132" hidden="1" outlineLevel="2">
+      <c r="A132" s="4" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="B132" s="5" t="n"/>
+      <c r="C132" s="6" t="n"/>
+      <c r="D132" s="6" t="n"/>
+      <c r="E132" s="5" t="n"/>
+      <c r="F132" s="5" t="n"/>
+      <c r="G132" s="6" t="n"/>
+    </row>
+    <row r="133" hidden="1" outlineLevel="2">
+      <c r="A133" s="4" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="B133" s="5" t="n"/>
+      <c r="C133" s="6" t="n"/>
+      <c r="D133" s="6" t="n"/>
+      <c r="E133" s="5" t="n"/>
+      <c r="F133" s="5" t="n"/>
+      <c r="G133" s="6" t="n"/>
+    </row>
+    <row r="134" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A134" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B134" s="5" t="n"/>
+      <c r="C134" s="6" t="n"/>
+      <c r="D134" s="6" t="n"/>
+      <c r="E134" s="5" t="n"/>
+      <c r="F134" s="5" t="n"/>
+      <c r="G134" s="6" t="n"/>
+    </row>
+    <row r="135" hidden="1" outlineLevel="2">
+      <c r="A135" s="4" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="B135" s="5" t="n"/>
+      <c r="C135" s="6" t="n"/>
+      <c r="D135" s="6" t="n"/>
+      <c r="E135" s="5" t="n"/>
+      <c r="F135" s="5" t="n"/>
+      <c r="G135" s="6" t="n"/>
+    </row>
+    <row r="136" hidden="1" outlineLevel="2">
+      <c r="A136" s="4" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="B136" s="5" t="n"/>
+      <c r="C136" s="6" t="n"/>
+      <c r="D136" s="6" t="n"/>
+      <c r="E136" s="5" t="n"/>
+      <c r="F136" s="5" t="n"/>
+      <c r="G136" s="6" t="n"/>
+    </row>
+    <row r="137" hidden="1" outlineLevel="2">
+      <c r="A137" s="4" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="B137" s="5" t="n"/>
+      <c r="C137" s="6" t="n"/>
+      <c r="D137" s="6" t="n"/>
+      <c r="E137" s="5" t="n"/>
+      <c r="F137" s="5" t="n"/>
+      <c r="G137" s="6" t="n"/>
+    </row>
+    <row r="138" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A138" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B138" s="5" t="n"/>
+      <c r="C138" s="6" t="n"/>
+      <c r="D138" s="6" t="n"/>
+      <c r="E138" s="5" t="n"/>
+      <c r="F138" s="5" t="n"/>
+      <c r="G138" s="6" t="n"/>
+    </row>
+    <row r="139" hidden="1" outlineLevel="2">
+      <c r="A139" s="4" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="B139" s="5" t="n"/>
+      <c r="C139" s="6" t="n"/>
+      <c r="D139" s="6" t="n"/>
+      <c r="E139" s="5" t="n"/>
+      <c r="F139" s="5" t="n"/>
+      <c r="G139" s="6" t="n"/>
+    </row>
+    <row r="140" hidden="1" outlineLevel="2">
+      <c r="A140" s="4" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="B140" s="5" t="n"/>
+      <c r="C140" s="6" t="n"/>
+      <c r="D140" s="6" t="n"/>
+      <c r="E140" s="5" t="n"/>
+      <c r="F140" s="5" t="n"/>
+      <c r="G140" s="6" t="n"/>
+    </row>
+    <row r="141" hidden="1" outlineLevel="2">
+      <c r="A141" s="4" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="B141" s="5" t="n"/>
+      <c r="C141" s="6" t="n"/>
+      <c r="D141" s="6" t="n"/>
+      <c r="E141" s="5" t="n"/>
+      <c r="F141" s="5" t="n"/>
+      <c r="G141" s="6" t="n"/>
+    </row>
+    <row r="142" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A142" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B142" s="5" t="n"/>
+      <c r="C142" s="6" t="n"/>
+      <c r="D142" s="6" t="n"/>
+      <c r="E142" s="5" t="n"/>
+      <c r="F142" s="5" t="n"/>
+      <c r="G142" s="6" t="n"/>
+    </row>
+    <row r="143" hidden="1" outlineLevel="2">
+      <c r="A143" s="4" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="B143" s="5" t="n"/>
+      <c r="C143" s="6" t="n"/>
+      <c r="D143" s="6" t="n"/>
+      <c r="E143" s="5" t="n"/>
+      <c r="F143" s="5" t="n"/>
+      <c r="G143" s="6" t="n"/>
+    </row>
+    <row r="144" hidden="1" outlineLevel="2">
+      <c r="A144" s="4" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="B144" s="5" t="n"/>
+      <c r="C144" s="6" t="n"/>
+      <c r="D144" s="6" t="n"/>
+      <c r="E144" s="5" t="n"/>
+      <c r="F144" s="5" t="n"/>
+      <c r="G144" s="6" t="n"/>
+    </row>
+    <row r="145" hidden="1" outlineLevel="2">
+      <c r="A145" s="4" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="B145" s="5" t="n"/>
+      <c r="C145" s="6" t="n"/>
+      <c r="D145" s="6" t="n"/>
+      <c r="E145" s="5" t="n"/>
+      <c r="F145" s="5" t="n"/>
+      <c r="G145" s="6" t="n"/>
+    </row>
+    <row r="146" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A146" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B146" s="5" t="n"/>
+      <c r="C146" s="6" t="n"/>
+      <c r="D146" s="6" t="n"/>
+      <c r="E146" s="5" t="n"/>
+      <c r="F146" s="5" t="n"/>
+      <c r="G146" s="6" t="n"/>
+    </row>
+    <row r="147" hidden="1" outlineLevel="2">
+      <c r="A147" s="4" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="B147" s="5" t="n"/>
+      <c r="C147" s="6" t="n"/>
+      <c r="D147" s="6" t="n"/>
+      <c r="E147" s="5" t="n"/>
+      <c r="F147" s="5" t="n"/>
+      <c r="G147" s="6" t="n"/>
+    </row>
+    <row r="148" hidden="1" outlineLevel="2">
+      <c r="A148" s="4" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="B148" s="5" t="n"/>
+      <c r="C148" s="6" t="n"/>
+      <c r="D148" s="6" t="n"/>
+      <c r="E148" s="5" t="n"/>
+      <c r="F148" s="5" t="n"/>
+      <c r="G148" s="6" t="n"/>
+    </row>
+    <row r="149" hidden="1" outlineLevel="2">
+      <c r="A149" s="4" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="B149" s="5" t="n"/>
+      <c r="C149" s="6" t="n"/>
+      <c r="D149" s="6" t="n"/>
+      <c r="E149" s="5" t="n"/>
+      <c r="F149" s="5" t="n"/>
+      <c r="G149" s="6" t="n"/>
+    </row>
+    <row r="150" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A150" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B150" s="5" t="n"/>
+      <c r="C150" s="6" t="n"/>
+      <c r="D150" s="6" t="n"/>
+      <c r="E150" s="5" t="n"/>
+      <c r="F150" s="5" t="n"/>
+      <c r="G150" s="6" t="n"/>
+    </row>
+    <row r="151" hidden="1" outlineLevel="2">
+      <c r="A151" s="4" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="B151" s="5" t="n"/>
+      <c r="C151" s="6" t="n"/>
+      <c r="D151" s="6" t="n"/>
+      <c r="E151" s="5" t="n"/>
+      <c r="F151" s="5" t="n"/>
+      <c r="G151" s="6" t="n"/>
+    </row>
+    <row r="152" hidden="1" outlineLevel="2">
+      <c r="A152" s="4" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="B152" s="5" t="n"/>
+      <c r="C152" s="6" t="n"/>
+      <c r="D152" s="6" t="n"/>
+      <c r="E152" s="5" t="n"/>
+      <c r="F152" s="5" t="n"/>
+      <c r="G152" s="6" t="n"/>
+    </row>
+    <row r="153" hidden="1" outlineLevel="2">
+      <c r="A153" s="4" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="B153" s="5" t="n"/>
+      <c r="C153" s="6" t="n"/>
+      <c r="D153" s="6" t="n"/>
+      <c r="E153" s="5" t="n"/>
+      <c r="F153" s="5" t="n"/>
+      <c r="G153" s="6" t="n"/>
+    </row>
+    <row r="154" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A154" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B154" s="5" t="n"/>
+      <c r="C154" s="6" t="n"/>
+      <c r="D154" s="6" t="n"/>
+      <c r="E154" s="5" t="n"/>
+      <c r="F154" s="5" t="n"/>
+      <c r="G154" s="6" t="n"/>
+    </row>
+    <row r="155" hidden="1" outlineLevel="2">
+      <c r="A155" s="4" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="B155" s="5" t="n"/>
+      <c r="C155" s="6" t="n"/>
+      <c r="D155" s="6" t="n"/>
+      <c r="E155" s="5" t="n"/>
+      <c r="F155" s="5" t="n"/>
+      <c r="G155" s="6" t="n"/>
+    </row>
+    <row r="156" hidden="1" outlineLevel="2">
+      <c r="A156" s="4" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="B156" s="5" t="n"/>
+      <c r="C156" s="6" t="n"/>
+      <c r="D156" s="6" t="n"/>
+      <c r="E156" s="5" t="n"/>
+      <c r="F156" s="5" t="n"/>
+      <c r="G156" s="6" t="n"/>
+    </row>
+    <row r="157" hidden="1" outlineLevel="2">
+      <c r="A157" s="4" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="B157" s="5" t="n"/>
+      <c r="C157" s="6" t="n"/>
+      <c r="D157" s="6" t="n"/>
+      <c r="E157" s="5" t="n"/>
+      <c r="F157" s="5" t="n"/>
+      <c r="G157" s="6" t="n"/>
+    </row>
+    <row r="158" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A158" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B158" s="5" t="n"/>
+      <c r="C158" s="6" t="n"/>
+      <c r="D158" s="6" t="n"/>
+      <c r="E158" s="5" t="n"/>
+      <c r="F158" s="5" t="n"/>
+      <c r="G158" s="6" t="n"/>
+    </row>
+    <row r="159" hidden="1" outlineLevel="2">
+      <c r="A159" s="4" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="B159" s="5" t="n"/>
+      <c r="C159" s="6" t="n"/>
+      <c r="D159" s="6" t="n"/>
+      <c r="E159" s="5" t="n"/>
+      <c r="F159" s="5" t="n"/>
+      <c r="G159" s="6" t="n"/>
+    </row>
+    <row r="160" hidden="1" outlineLevel="2">
+      <c r="A160" s="4" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="B160" s="5" t="n"/>
+      <c r="C160" s="6" t="n"/>
+      <c r="D160" s="6" t="n"/>
+      <c r="E160" s="5" t="n"/>
+      <c r="F160" s="5" t="n"/>
+      <c r="G160" s="6" t="n"/>
+    </row>
+    <row r="161" hidden="1" outlineLevel="2">
+      <c r="A161" s="4" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="B161" s="5" t="n"/>
+      <c r="C161" s="6" t="n"/>
+      <c r="D161" s="6" t="n"/>
+      <c r="E161" s="5" t="n"/>
+      <c r="F161" s="5" t="n"/>
+      <c r="G161" s="6" t="n"/>
+    </row>
+    <row r="162" collapsed="1">
+      <c r="A162" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>chorus 1b</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+chorus 1b (ab 1:16.475): scene(SCENE_WAVE_LR, 7869, 35, 122);
+   Bühnenbewegung als Variation</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="n"/>
+      <c r="E162" s="5" t="n"/>
+      <c r="F162" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>progSternNeu(7870, 490, 35, 5, 26, 5, false, 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" hidden="1" outlineLevel="2">
+      <c r="A163" s="4" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="B163" s="5" t="n"/>
+      <c r="C163" s="6" t="n"/>
+      <c r="D163" s="6" t="n"/>
+      <c r="E163" s="5" t="n"/>
+      <c r="F163" s="5" t="n"/>
+      <c r="G163" s="6" t="n"/>
+    </row>
+    <row r="164" hidden="1" outlineLevel="2">
+      <c r="A164" s="4" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="B164" s="5" t="n"/>
+      <c r="C164" s="6" t="n"/>
+      <c r="D164" s="6" t="n"/>
+      <c r="E164" s="5" t="n"/>
+      <c r="F164" s="5" t="n"/>
+      <c r="G164" s="6" t="n"/>
+    </row>
+    <row r="165" hidden="1" outlineLevel="2">
+      <c r="A165" s="4" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="B165" s="5" t="n"/>
+      <c r="C165" s="6" t="n"/>
+      <c r="D165" s="6" t="n"/>
+      <c r="E165" s="5" t="n"/>
+      <c r="F165" s="5" t="n"/>
+      <c r="G165" s="6" t="n"/>
+    </row>
+    <row r="166" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A166" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B166" s="5" t="n"/>
+      <c r="C166" s="6" t="n"/>
+      <c r="D166" s="6" t="n"/>
+      <c r="E166" s="5" t="n"/>
+      <c r="F166" s="5" t="n"/>
+      <c r="G166" s="6" t="n"/>
+    </row>
+    <row r="167" hidden="1" outlineLevel="2">
+      <c r="A167" s="4" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="B167" s="5" t="n"/>
+      <c r="C167" s="6" t="n"/>
+      <c r="D167" s="6" t="n"/>
+      <c r="E167" s="5" t="n"/>
+      <c r="F167" s="5" t="n"/>
+      <c r="G167" s="6" t="n"/>
+    </row>
+    <row r="168" hidden="1" outlineLevel="2">
+      <c r="A168" s="4" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="B168" s="5" t="n"/>
+      <c r="C168" s="6" t="n"/>
+      <c r="D168" s="6" t="n"/>
+      <c r="E168" s="5" t="n"/>
+      <c r="F168" s="5" t="n"/>
+      <c r="G168" s="6" t="n"/>
+    </row>
+    <row r="169" hidden="1" outlineLevel="2">
+      <c r="A169" s="4" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="B169" s="5" t="n"/>
+      <c r="C169" s="6" t="n"/>
+      <c r="D169" s="6" t="n"/>
+      <c r="E169" s="5" t="n"/>
+      <c r="F169" s="5" t="n"/>
+      <c r="G169" s="6" t="n"/>
+    </row>
+    <row r="170" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A170" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B170" s="5" t="n"/>
+      <c r="C170" s="6" t="n"/>
+      <c r="D170" s="6" t="n"/>
+      <c r="E170" s="5" t="n"/>
+      <c r="F170" s="5" t="n"/>
+      <c r="G170" s="6" t="n"/>
+    </row>
+    <row r="171" hidden="1" outlineLevel="2">
+      <c r="A171" s="4" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="B171" s="5" t="n"/>
+      <c r="C171" s="6" t="n"/>
+      <c r="D171" s="6" t="n"/>
+      <c r="E171" s="5" t="n"/>
+      <c r="F171" s="5" t="n"/>
+      <c r="G171" s="6" t="n"/>
+    </row>
+    <row r="172" hidden="1" outlineLevel="2">
+      <c r="A172" s="4" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="B172" s="5" t="n"/>
+      <c r="C172" s="6" t="n"/>
+      <c r="D172" s="6" t="n"/>
+      <c r="E172" s="5" t="n"/>
+      <c r="F172" s="5" t="n"/>
+      <c r="G172" s="6" t="n"/>
+    </row>
+    <row r="173" hidden="1" outlineLevel="2">
+      <c r="A173" s="4" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="B173" s="5" t="n"/>
+      <c r="C173" s="6" t="n"/>
+      <c r="D173" s="6" t="n"/>
+      <c r="E173" s="5" t="n"/>
+      <c r="F173" s="5" t="n"/>
+      <c r="G173" s="6" t="n"/>
+    </row>
+    <row r="174" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A174" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B174" s="5" t="n"/>
+      <c r="C174" s="6" t="n"/>
+      <c r="D174" s="6" t="n"/>
+      <c r="E174" s="5" t="n"/>
+      <c r="F174" s="5" t="n"/>
+      <c r="G174" s="6" t="n"/>
+    </row>
+    <row r="175" hidden="1" outlineLevel="2">
+      <c r="A175" s="4" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="B175" s="5" t="n"/>
+      <c r="C175" s="6" t="n"/>
+      <c r="D175" s="6" t="n"/>
+      <c r="E175" s="5" t="n"/>
+      <c r="F175" s="5" t="n"/>
+      <c r="G175" s="6" t="n"/>
+    </row>
+    <row r="176" hidden="1" outlineLevel="2">
+      <c r="A176" s="4" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="B176" s="5" t="n"/>
+      <c r="C176" s="6" t="n"/>
+      <c r="D176" s="6" t="n"/>
+      <c r="E176" s="5" t="n"/>
+      <c r="F176" s="5" t="n"/>
+      <c r="G176" s="6" t="n"/>
+    </row>
+    <row r="177" hidden="1" outlineLevel="2">
+      <c r="A177" s="4" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="B177" s="5" t="n"/>
+      <c r="C177" s="6" t="n"/>
+      <c r="D177" s="6" t="n"/>
+      <c r="E177" s="5" t="n"/>
+      <c r="F177" s="5" t="n"/>
+      <c r="G177" s="6" t="n"/>
+    </row>
+    <row r="178" collapsed="1">
+      <c r="A178" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
+          <t>i keep dancing</t>
+        </is>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+hook 1 (ab 1:24.344): scene(SCENE_PINGPONG, 6886, 40, 122);
+   'on my own' springt von Gerät zu Gerät, kurzer Strobo als Absprung in den Stopp
+hook 1 (tail) (ab 1:31.230): progStrobo(983, 45, 75, getRandomCRGB());</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="n"/>
+      <c r="E178" s="5" t="n"/>
+      <c r="F178" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>progFastBlingBling(7870, 4, 40)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" hidden="1" outlineLevel="2">
+      <c r="A179" s="4" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="B179" s="5" t="n"/>
+      <c r="C179" s="6" t="n"/>
+      <c r="D179" s="6" t="n"/>
+      <c r="E179" s="5" t="n"/>
+      <c r="F179" s="5" t="n"/>
+      <c r="G179" s="6" t="n"/>
+    </row>
+    <row r="180" hidden="1" outlineLevel="2">
+      <c r="A180" s="4" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="B180" s="5" t="n"/>
+      <c r="C180" s="6" t="n"/>
+      <c r="D180" s="6" t="n"/>
+      <c r="E180" s="5" t="n"/>
+      <c r="F180" s="5" t="n"/>
+      <c r="G180" s="6" t="n"/>
+    </row>
+    <row r="181" hidden="1" outlineLevel="2">
+      <c r="A181" s="4" t="n">
+        <v>44.75</v>
+      </c>
+      <c r="B181" s="5" t="n"/>
+      <c r="C181" s="6" t="n"/>
+      <c r="D181" s="6" t="n"/>
+      <c r="E181" s="5" t="n"/>
+      <c r="F181" s="5" t="n"/>
+      <c r="G181" s="6" t="n"/>
+    </row>
+    <row r="182" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A182" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B182" s="5" t="n"/>
+      <c r="C182" s="6" t="n"/>
+      <c r="D182" s="6" t="n"/>
+      <c r="E182" s="5" t="n"/>
+      <c r="F182" s="5" t="n"/>
+      <c r="G182" s="6" t="n"/>
+    </row>
+    <row r="183" hidden="1" outlineLevel="2">
+      <c r="A183" s="4" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="B183" s="5" t="n"/>
+      <c r="C183" s="6" t="n"/>
+      <c r="D183" s="6" t="n"/>
+      <c r="E183" s="5" t="n"/>
+      <c r="F183" s="5" t="n"/>
+      <c r="G183" s="6" t="n"/>
+    </row>
+    <row r="184" hidden="1" outlineLevel="2">
+      <c r="A184" s="4" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="B184" s="5" t="n"/>
+      <c r="C184" s="6" t="n"/>
+      <c r="D184" s="6" t="n"/>
+      <c r="E184" s="5" t="n"/>
+      <c r="F184" s="5" t="n"/>
+      <c r="G184" s="6" t="n"/>
+    </row>
+    <row r="185" hidden="1" outlineLevel="2">
+      <c r="A185" s="4" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="B185" s="5" t="n"/>
+      <c r="C185" s="6" t="n"/>
+      <c r="D185" s="6" t="n"/>
+      <c r="E185" s="5" t="n"/>
+      <c r="F185" s="5" t="n"/>
+      <c r="G185" s="6" t="n"/>
+    </row>
+    <row r="186" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A186" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B186" s="5" t="n"/>
+      <c r="C186" s="6" t="n"/>
+      <c r="D186" s="6" t="n"/>
+      <c r="E186" s="5" t="n"/>
+      <c r="F186" s="5" t="n"/>
+      <c r="G186" s="6" t="n"/>
+    </row>
+    <row r="187" hidden="1" outlineLevel="2">
+      <c r="A187" s="4" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="B187" s="5" t="n"/>
+      <c r="C187" s="6" t="n"/>
+      <c r="D187" s="6" t="n"/>
+      <c r="E187" s="5" t="n"/>
+      <c r="F187" s="5" t="n"/>
+      <c r="G187" s="6" t="n"/>
+    </row>
+    <row r="188" hidden="1" outlineLevel="2">
+      <c r="A188" s="4" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="B188" s="5" t="n"/>
+      <c r="C188" s="6" t="n"/>
+      <c r="D188" s="6" t="n"/>
+      <c r="E188" s="5" t="n"/>
+      <c r="F188" s="5" t="n"/>
+      <c r="G188" s="6" t="n"/>
+    </row>
+    <row r="189" hidden="1" outlineLevel="2">
+      <c r="A189" s="4" t="n">
+        <v>46.75</v>
+      </c>
+      <c r="B189" s="5" t="n"/>
+      <c r="C189" s="6" t="n"/>
+      <c r="D189" s="6" t="n"/>
+      <c r="E189" s="5" t="n"/>
+      <c r="F189" s="5" t="n"/>
+      <c r="G189" s="6" t="n"/>
+    </row>
+    <row r="190" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A190" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B190" s="5" t="n"/>
+      <c r="C190" s="6" t="n"/>
+      <c r="D190" s="6" t="n"/>
+      <c r="E190" s="5" t="n"/>
+      <c r="F190" s="5" t="n"/>
+      <c r="G190" s="6" t="n"/>
+    </row>
+    <row r="191" hidden="1" outlineLevel="2">
+      <c r="A191" s="4" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="B191" s="5" t="n"/>
+      <c r="C191" s="6" t="n"/>
+      <c r="D191" s="6" t="n"/>
+      <c r="E191" s="5" t="n"/>
+      <c r="F191" s="5" t="n"/>
+      <c r="G191" s="6" t="n"/>
+    </row>
+    <row r="192" hidden="1" outlineLevel="2">
+      <c r="A192" s="4" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="B192" s="5" t="n"/>
+      <c r="C192" s="6" t="n"/>
+      <c r="D192" s="6" t="n"/>
+      <c r="E192" s="5" t="n"/>
+      <c r="F192" s="5" t="n"/>
+      <c r="G192" s="6" t="n"/>
+    </row>
+    <row r="193" hidden="1" outlineLevel="2">
+      <c r="A193" s="4" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="B193" s="5" t="n"/>
+      <c r="C193" s="6" t="n"/>
+      <c r="D193" s="6" t="n"/>
+      <c r="E193" s="5" t="n"/>
+      <c r="F193" s="5" t="n"/>
+      <c r="G193" s="6" t="n"/>
+    </row>
+    <row r="194" collapsed="1">
+      <c r="A194" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B194" s="5" t="inlineStr">
+        <is>
+          <t>pause vor verse 2a</t>
+        </is>
+      </c>
+      <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+stop (ab 1:32.213): progBlack(3935, 50);</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="n"/>
+      <c r="E194" s="5" t="n"/>
+      <c r="F194" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G194" s="6" t="inlineStr">
+        <is>
+          <t>progBlack(3935, 45)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" hidden="1" outlineLevel="2">
+      <c r="A195" s="4" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="B195" s="5" t="n"/>
+      <c r="C195" s="6" t="n"/>
+      <c r="D195" s="6" t="n"/>
+      <c r="E195" s="5" t="n"/>
+      <c r="F195" s="5" t="n"/>
+      <c r="G195" s="6" t="n"/>
+    </row>
+    <row r="196" hidden="1" outlineLevel="2">
+      <c r="A196" s="4" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="B196" s="5" t="n"/>
+      <c r="C196" s="6" t="n"/>
+      <c r="D196" s="6" t="n"/>
+      <c r="E196" s="5" t="n"/>
+      <c r="F196" s="5" t="n"/>
+      <c r="G196" s="6" t="n"/>
+    </row>
+    <row r="197" hidden="1" outlineLevel="2">
+      <c r="A197" s="4" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="B197" s="5" t="n"/>
+      <c r="C197" s="6" t="n"/>
+      <c r="D197" s="6" t="n"/>
+      <c r="E197" s="5" t="n"/>
+      <c r="F197" s="5" t="n"/>
+      <c r="G197" s="6" t="n"/>
+    </row>
+    <row r="198" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A198" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B198" s="5" t="n"/>
+      <c r="C198" s="6" t="n"/>
+      <c r="D198" s="6" t="n"/>
+      <c r="E198" s="5" t="n"/>
+      <c r="F198" s="5" t="n"/>
+      <c r="G198" s="6" t="n"/>
+    </row>
+    <row r="199" hidden="1" outlineLevel="2">
+      <c r="A199" s="4" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="B199" s="5" t="n"/>
+      <c r="C199" s="6" t="n"/>
+      <c r="D199" s="6" t="n"/>
+      <c r="E199" s="5" t="n"/>
+      <c r="F199" s="5" t="n"/>
+      <c r="G199" s="6" t="n"/>
+    </row>
+    <row r="200" hidden="1" outlineLevel="2">
+      <c r="A200" s="4" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="B200" s="5" t="n"/>
+      <c r="C200" s="6" t="n"/>
+      <c r="D200" s="6" t="n"/>
+      <c r="E200" s="5" t="n"/>
+      <c r="F200" s="5" t="n"/>
+      <c r="G200" s="6" t="n"/>
+    </row>
+    <row r="201" hidden="1" outlineLevel="2">
+      <c r="A201" s="4" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="B201" s="5" t="n"/>
+      <c r="C201" s="6" t="n"/>
+      <c r="D201" s="6" t="n"/>
+      <c r="E201" s="5" t="n"/>
+      <c r="F201" s="5" t="n"/>
+      <c r="G201" s="6" t="n"/>
+    </row>
+    <row r="202" collapsed="1">
+      <c r="A202" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B202" s="5" t="inlineStr">
+        <is>
+          <t>verse 2b</t>
+        </is>
+      </c>
+      <c r="C202" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+verse 2 (ab 1:36.148): setColorScheme(SCHEME_ROYAL); scene(SCENE_VERSE, 19672, 55, 122);
+   zurück in den Puls, eine Stufe wärmer als Verse 1</t>
+        </is>
+      </c>
+      <c r="D202" s="6" t="n"/>
+      <c r="E202" s="5" t="n"/>
+      <c r="F202" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G202" s="6" t="inlineStr">
+        <is>
+          <t>progBlingBlingColoring(19670, 55, 3000)
+! im alten Code ein einziger Part mit den folgenden 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" hidden="1" outlineLevel="2">
+      <c r="A203" s="4" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="B203" s="5" t="n"/>
+      <c r="C203" s="6" t="n"/>
+      <c r="D203" s="6" t="n"/>
+      <c r="E203" s="5" t="n"/>
+      <c r="F203" s="5" t="n"/>
+      <c r="G203" s="6" t="n"/>
+    </row>
+    <row r="204" hidden="1" outlineLevel="2">
+      <c r="A204" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="B204" s="5" t="n"/>
+      <c r="C204" s="6" t="n"/>
+      <c r="D204" s="6" t="n"/>
+      <c r="E204" s="5" t="n"/>
+      <c r="F204" s="5" t="n"/>
+      <c r="G204" s="6" t="n"/>
+    </row>
+    <row r="205" hidden="1" outlineLevel="2">
+      <c r="A205" s="4" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="B205" s="5" t="n"/>
+      <c r="C205" s="6" t="n"/>
+      <c r="D205" s="6" t="n"/>
+      <c r="E205" s="5" t="n"/>
+      <c r="F205" s="5" t="n"/>
+      <c r="G205" s="6" t="n"/>
+    </row>
+    <row r="206" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A206" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B206" s="5" t="n"/>
+      <c r="C206" s="6" t="n"/>
+      <c r="D206" s="6" t="n"/>
+      <c r="E206" s="5" t="n"/>
+      <c r="F206" s="5" t="n"/>
+      <c r="G206" s="6" t="n"/>
+    </row>
+    <row r="207" hidden="1" outlineLevel="2">
+      <c r="A207" s="4" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="B207" s="5" t="n"/>
+      <c r="C207" s="6" t="n"/>
+      <c r="D207" s="6" t="n"/>
+      <c r="E207" s="5" t="n"/>
+      <c r="F207" s="5" t="n"/>
+      <c r="G207" s="6" t="n"/>
+    </row>
+    <row r="208" hidden="1" outlineLevel="2">
+      <c r="A208" s="4" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="B208" s="5" t="n"/>
+      <c r="C208" s="6" t="n"/>
+      <c r="D208" s="6" t="n"/>
+      <c r="E208" s="5" t="n"/>
+      <c r="F208" s="5" t="n"/>
+      <c r="G208" s="6" t="n"/>
+    </row>
+    <row r="209" hidden="1" outlineLevel="2">
+      <c r="A209" s="4" t="n">
+        <v>51.75</v>
+      </c>
+      <c r="B209" s="5" t="n"/>
+      <c r="C209" s="6" t="n"/>
+      <c r="D209" s="6" t="n"/>
+      <c r="E209" s="5" t="n"/>
+      <c r="F209" s="5" t="n"/>
+      <c r="G209" s="6" t="n"/>
+    </row>
+    <row r="210" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A210" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B210" s="5" t="n"/>
+      <c r="C210" s="6" t="n"/>
+      <c r="D210" s="6" t="n"/>
+      <c r="E210" s="5" t="n"/>
+      <c r="F210" s="5" t="n"/>
+      <c r="G210" s="6" t="n"/>
+    </row>
+    <row r="211" hidden="1" outlineLevel="2">
+      <c r="A211" s="4" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="B211" s="5" t="n"/>
+      <c r="C211" s="6" t="n"/>
+      <c r="D211" s="6" t="n"/>
+      <c r="E211" s="5" t="n"/>
+      <c r="F211" s="5" t="n"/>
+      <c r="G211" s="6" t="n"/>
+    </row>
+    <row r="212" hidden="1" outlineLevel="2">
+      <c r="A212" s="4" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="B212" s="5" t="n"/>
+      <c r="C212" s="6" t="n"/>
+      <c r="D212" s="6" t="n"/>
+      <c r="E212" s="5" t="n"/>
+      <c r="F212" s="5" t="n"/>
+      <c r="G212" s="6" t="n"/>
+    </row>
+    <row r="213" hidden="1" outlineLevel="2">
+      <c r="A213" s="4" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="B213" s="5" t="n"/>
+      <c r="C213" s="6" t="n"/>
+      <c r="D213" s="6" t="n"/>
+      <c r="E213" s="5" t="n"/>
+      <c r="F213" s="5" t="n"/>
+      <c r="G213" s="6" t="n"/>
+    </row>
+    <row r="214" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A214" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B214" s="5" t="n"/>
+      <c r="C214" s="6" t="n"/>
+      <c r="D214" s="6" t="n"/>
+      <c r="E214" s="5" t="n"/>
+      <c r="F214" s="5" t="n"/>
+      <c r="G214" s="6" t="n"/>
+    </row>
+    <row r="215" hidden="1" outlineLevel="2">
+      <c r="A215" s="4" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="B215" s="5" t="n"/>
+      <c r="C215" s="6" t="n"/>
+      <c r="D215" s="6" t="n"/>
+      <c r="E215" s="5" t="n"/>
+      <c r="F215" s="5" t="n"/>
+      <c r="G215" s="6" t="n"/>
+    </row>
+    <row r="216" hidden="1" outlineLevel="2">
+      <c r="A216" s="4" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="B216" s="5" t="n"/>
+      <c r="C216" s="6" t="n"/>
+      <c r="D216" s="6" t="n"/>
+      <c r="E216" s="5" t="n"/>
+      <c r="F216" s="5" t="n"/>
+      <c r="G216" s="6" t="n"/>
+    </row>
+    <row r="217" hidden="1" outlineLevel="2">
+      <c r="A217" s="4" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="B217" s="5" t="n"/>
+      <c r="C217" s="6" t="n"/>
+      <c r="D217" s="6" t="n"/>
+      <c r="E217" s="5" t="n"/>
+      <c r="F217" s="5" t="n"/>
+      <c r="G217" s="6" t="n"/>
+    </row>
+    <row r="218" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A218" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B218" s="5" t="n"/>
+      <c r="C218" s="6" t="n"/>
+      <c r="D218" s="6" t="n"/>
+      <c r="E218" s="5" t="n"/>
+      <c r="F218" s="5" t="n"/>
+      <c r="G218" s="6" t="n"/>
+    </row>
+    <row r="219" hidden="1" outlineLevel="2">
+      <c r="A219" s="4" t="n">
+        <v>54.25</v>
+      </c>
+      <c r="B219" s="5" t="n"/>
+      <c r="C219" s="6" t="n"/>
+      <c r="D219" s="6" t="n"/>
+      <c r="E219" s="5" t="n"/>
+      <c r="F219" s="5" t="n"/>
+      <c r="G219" s="6" t="n"/>
+    </row>
+    <row r="220" hidden="1" outlineLevel="2">
+      <c r="A220" s="4" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="B220" s="5" t="n"/>
+      <c r="C220" s="6" t="n"/>
+      <c r="D220" s="6" t="n"/>
+      <c r="E220" s="5" t="n"/>
+      <c r="F220" s="5" t="n"/>
+      <c r="G220" s="6" t="n"/>
+    </row>
+    <row r="221" hidden="1" outlineLevel="2">
+      <c r="A221" s="4" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="B221" s="5" t="n"/>
+      <c r="C221" s="6" t="n"/>
+      <c r="D221" s="6" t="n"/>
+      <c r="E221" s="5" t="n"/>
+      <c r="F221" s="5" t="n"/>
+      <c r="G221" s="6" t="n"/>
+    </row>
+    <row r="222" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A222" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B222" s="5" t="n"/>
+      <c r="C222" s="6" t="n"/>
+      <c r="D222" s="6" t="n"/>
+      <c r="E222" s="5" t="n"/>
+      <c r="F222" s="5" t="n"/>
+      <c r="G222" s="6" t="n"/>
+    </row>
+    <row r="223" hidden="1" outlineLevel="2">
+      <c r="A223" s="4" t="n">
+        <v>55.25</v>
+      </c>
+      <c r="B223" s="5" t="n"/>
+      <c r="C223" s="6" t="n"/>
+      <c r="D223" s="6" t="n"/>
+      <c r="E223" s="5" t="n"/>
+      <c r="F223" s="5" t="n"/>
+      <c r="G223" s="6" t="n"/>
+    </row>
+    <row r="224" hidden="1" outlineLevel="2">
+      <c r="A224" s="4" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="B224" s="5" t="n"/>
+      <c r="C224" s="6" t="n"/>
+      <c r="D224" s="6" t="n"/>
+      <c r="E224" s="5" t="n"/>
+      <c r="F224" s="5" t="n"/>
+      <c r="G224" s="6" t="n"/>
+    </row>
+    <row r="225" hidden="1" outlineLevel="2">
+      <c r="A225" s="4" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="B225" s="5" t="n"/>
+      <c r="C225" s="6" t="n"/>
+      <c r="D225" s="6" t="n"/>
+      <c r="E225" s="5" t="n"/>
+      <c r="F225" s="5" t="n"/>
+      <c r="G225" s="6" t="n"/>
+    </row>
+    <row r="226" collapsed="1">
+      <c r="A226" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B226" s="5" t="inlineStr">
+        <is>
+          <t>bridge</t>
+        </is>
+      </c>
+      <c r="C226" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+verse 2 (ab 1:36.148): setColorScheme(SCHEME_ROYAL); scene(SCENE_VERSE, 19672, 55, 122);
+   zurück in den Puls, eine Stufe wärmer als Verse 1</t>
+        </is>
+      </c>
+      <c r="D226" s="6" t="n"/>
+      <c r="E226" s="5" t="n"/>
+      <c r="F226" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G226" s="6" t="n"/>
+    </row>
+    <row r="227" hidden="1" outlineLevel="2">
+      <c r="A227" s="4" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="B227" s="5" t="n"/>
+      <c r="C227" s="6" t="n"/>
+      <c r="D227" s="6" t="n"/>
+      <c r="E227" s="5" t="n"/>
+      <c r="F227" s="5" t="n"/>
+      <c r="G227" s="6" t="n"/>
+    </row>
+    <row r="228" hidden="1" outlineLevel="2">
+      <c r="A228" s="4" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="B228" s="5" t="n"/>
+      <c r="C228" s="6" t="n"/>
+      <c r="D228" s="6" t="n"/>
+      <c r="E228" s="5" t="n"/>
+      <c r="F228" s="5" t="n"/>
+      <c r="G228" s="6" t="n"/>
+    </row>
+    <row r="229" hidden="1" outlineLevel="2">
+      <c r="A229" s="4" t="n">
+        <v>56.75</v>
+      </c>
+      <c r="B229" s="5" t="n"/>
+      <c r="C229" s="6" t="n"/>
+      <c r="D229" s="6" t="n"/>
+      <c r="E229" s="5" t="n"/>
+      <c r="F229" s="5" t="n"/>
+      <c r="G229" s="6" t="n"/>
+    </row>
+    <row r="230" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A230" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B230" s="5" t="n"/>
+      <c r="C230" s="6" t="n"/>
+      <c r="D230" s="6" t="n"/>
+      <c r="E230" s="5" t="n"/>
+      <c r="F230" s="5" t="n"/>
+      <c r="G230" s="6" t="n"/>
+    </row>
+    <row r="231" hidden="1" outlineLevel="2">
+      <c r="A231" s="4" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="B231" s="5" t="n"/>
+      <c r="C231" s="6" t="n"/>
+      <c r="D231" s="6" t="n"/>
+      <c r="E231" s="5" t="n"/>
+      <c r="F231" s="5" t="n"/>
+      <c r="G231" s="6" t="n"/>
+    </row>
+    <row r="232" hidden="1" outlineLevel="2">
+      <c r="A232" s="4" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="B232" s="5" t="n"/>
+      <c r="C232" s="6" t="n"/>
+      <c r="D232" s="6" t="n"/>
+      <c r="E232" s="5" t="n"/>
+      <c r="F232" s="5" t="n"/>
+      <c r="G232" s="6" t="n"/>
+    </row>
+    <row r="233" hidden="1" outlineLevel="2">
+      <c r="A233" s="4" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="B233" s="5" t="n"/>
+      <c r="C233" s="6" t="n"/>
+      <c r="D233" s="6" t="n"/>
+      <c r="E233" s="5" t="n"/>
+      <c r="F233" s="5" t="n"/>
+      <c r="G233" s="6" t="n"/>
+    </row>
+    <row r="234" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A234" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B234" s="5" t="n"/>
+      <c r="C234" s="6" t="n"/>
+      <c r="D234" s="6" t="n"/>
+      <c r="E234" s="5" t="n"/>
+      <c r="F234" s="5" t="n"/>
+      <c r="G234" s="6" t="n"/>
+    </row>
+    <row r="235" hidden="1" outlineLevel="2">
+      <c r="A235" s="4" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="B235" s="5" t="n"/>
+      <c r="C235" s="6" t="n"/>
+      <c r="D235" s="6" t="n"/>
+      <c r="E235" s="5" t="n"/>
+      <c r="F235" s="5" t="n"/>
+      <c r="G235" s="6" t="n"/>
+    </row>
+    <row r="236" hidden="1" outlineLevel="2">
+      <c r="A236" s="4" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="B236" s="5" t="n"/>
+      <c r="C236" s="6" t="n"/>
+      <c r="D236" s="6" t="n"/>
+      <c r="E236" s="5" t="n"/>
+      <c r="F236" s="5" t="n"/>
+      <c r="G236" s="6" t="n"/>
+    </row>
+    <row r="237" hidden="1" outlineLevel="2">
+      <c r="A237" s="4" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="B237" s="5" t="n"/>
+      <c r="C237" s="6" t="n"/>
+      <c r="D237" s="6" t="n"/>
+      <c r="E237" s="5" t="n"/>
+      <c r="F237" s="5" t="n"/>
+      <c r="G237" s="6" t="n"/>
+    </row>
+    <row r="238" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A238" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B238" s="5" t="n"/>
+      <c r="C238" s="6" t="n"/>
+      <c r="D238" s="6" t="n"/>
+      <c r="E238" s="5" t="n"/>
+      <c r="F238" s="5" t="n"/>
+      <c r="G238" s="6" t="n"/>
+    </row>
+    <row r="239" hidden="1" outlineLevel="2">
+      <c r="A239" s="4" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="B239" s="5" t="n"/>
+      <c r="C239" s="6" t="n"/>
+      <c r="D239" s="6" t="n"/>
+      <c r="E239" s="5" t="n"/>
+      <c r="F239" s="5" t="n"/>
+      <c r="G239" s="6" t="n"/>
+    </row>
+    <row r="240" hidden="1" outlineLevel="2">
+      <c r="A240" s="4" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="B240" s="5" t="n"/>
+      <c r="C240" s="6" t="n"/>
+      <c r="D240" s="6" t="n"/>
+      <c r="E240" s="5" t="n"/>
+      <c r="F240" s="5" t="n"/>
+      <c r="G240" s="6" t="n"/>
+    </row>
+    <row r="241" hidden="1" outlineLevel="2">
+      <c r="A241" s="4" t="n">
+        <v>59.75</v>
+      </c>
+      <c r="B241" s="5" t="n"/>
+      <c r="C241" s="6" t="n"/>
+      <c r="D241" s="6" t="n"/>
+      <c r="E241" s="5" t="n"/>
+      <c r="F241" s="5" t="n"/>
+      <c r="G241" s="6" t="n"/>
+    </row>
+    <row r="242" collapsed="1">
+      <c r="A242" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
+        <is>
+          <t>chorus 1</t>
+        </is>
+      </c>
+      <c r="C242" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+chorus 2 (ab 1:55.820): scene(SCENE_DROP, 15737, 60, 122);</t>
+        </is>
+      </c>
+      <c r="D242" s="6" t="n"/>
+      <c r="E242" s="5" t="n"/>
+      <c r="F242" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G242" s="6" t="inlineStr">
+        <is>
+          <t>progMatrixScanner(15735, 60, 26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" hidden="1" outlineLevel="2">
+      <c r="A243" s="4" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="B243" s="5" t="n"/>
+      <c r="C243" s="6" t="n"/>
+      <c r="D243" s="6" t="n"/>
+      <c r="E243" s="5" t="n"/>
+      <c r="F243" s="5" t="n"/>
+      <c r="G243" s="6" t="n"/>
+    </row>
+    <row r="244" hidden="1" outlineLevel="2">
+      <c r="A244" s="4" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="B244" s="5" t="n"/>
+      <c r="C244" s="6" t="n"/>
+      <c r="D244" s="6" t="n"/>
+      <c r="E244" s="5" t="n"/>
+      <c r="F244" s="5" t="n"/>
+      <c r="G244" s="6" t="n"/>
+    </row>
+    <row r="245" hidden="1" outlineLevel="2">
+      <c r="A245" s="4" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="B245" s="5" t="n"/>
+      <c r="C245" s="6" t="n"/>
+      <c r="D245" s="6" t="n"/>
+      <c r="E245" s="5" t="n"/>
+      <c r="F245" s="5" t="n"/>
+      <c r="G245" s="6" t="n"/>
+    </row>
+    <row r="246" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A246" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B246" s="5" t="n"/>
+      <c r="C246" s="6" t="n"/>
+      <c r="D246" s="6" t="n"/>
+      <c r="E246" s="5" t="n"/>
+      <c r="F246" s="5" t="n"/>
+      <c r="G246" s="6" t="n"/>
+    </row>
+    <row r="247" hidden="1" outlineLevel="2">
+      <c r="A247" s="4" t="n">
+        <v>61.25</v>
+      </c>
+      <c r="B247" s="5" t="n"/>
+      <c r="C247" s="6" t="n"/>
+      <c r="D247" s="6" t="n"/>
+      <c r="E247" s="5" t="n"/>
+      <c r="F247" s="5" t="n"/>
+      <c r="G247" s="6" t="n"/>
+    </row>
+    <row r="248" hidden="1" outlineLevel="2">
+      <c r="A248" s="4" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="B248" s="5" t="n"/>
+      <c r="C248" s="6" t="n"/>
+      <c r="D248" s="6" t="n"/>
+      <c r="E248" s="5" t="n"/>
+      <c r="F248" s="5" t="n"/>
+      <c r="G248" s="6" t="n"/>
+    </row>
+    <row r="249" hidden="1" outlineLevel="2">
+      <c r="A249" s="4" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="B249" s="5" t="n"/>
+      <c r="C249" s="6" t="n"/>
+      <c r="D249" s="6" t="n"/>
+      <c r="E249" s="5" t="n"/>
+      <c r="F249" s="5" t="n"/>
+      <c r="G249" s="6" t="n"/>
+    </row>
+    <row r="250" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A250" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B250" s="5" t="n"/>
+      <c r="C250" s="6" t="n"/>
+      <c r="D250" s="6" t="n"/>
+      <c r="E250" s="5" t="n"/>
+      <c r="F250" s="5" t="n"/>
+      <c r="G250" s="6" t="n"/>
+    </row>
+    <row r="251" hidden="1" outlineLevel="2">
+      <c r="A251" s="4" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="B251" s="5" t="n"/>
+      <c r="C251" s="6" t="n"/>
+      <c r="D251" s="6" t="n"/>
+      <c r="E251" s="5" t="n"/>
+      <c r="F251" s="5" t="n"/>
+      <c r="G251" s="6" t="n"/>
+    </row>
+    <row r="252" hidden="1" outlineLevel="2">
+      <c r="A252" s="4" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="B252" s="5" t="n"/>
+      <c r="C252" s="6" t="n"/>
+      <c r="D252" s="6" t="n"/>
+      <c r="E252" s="5" t="n"/>
+      <c r="F252" s="5" t="n"/>
+      <c r="G252" s="6" t="n"/>
+    </row>
+    <row r="253" hidden="1" outlineLevel="2">
+      <c r="A253" s="4" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="B253" s="5" t="n"/>
+      <c r="C253" s="6" t="n"/>
+      <c r="D253" s="6" t="n"/>
+      <c r="E253" s="5" t="n"/>
+      <c r="F253" s="5" t="n"/>
+      <c r="G253" s="6" t="n"/>
+    </row>
+    <row r="254" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A254" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="B254" s="5" t="n"/>
+      <c r="C254" s="6" t="n"/>
+      <c r="D254" s="6" t="n"/>
+      <c r="E254" s="5" t="n"/>
+      <c r="F254" s="5" t="n"/>
+      <c r="G254" s="6" t="n"/>
+    </row>
+    <row r="255" hidden="1" outlineLevel="2">
+      <c r="A255" s="4" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="B255" s="5" t="n"/>
+      <c r="C255" s="6" t="n"/>
+      <c r="D255" s="6" t="n"/>
+      <c r="E255" s="5" t="n"/>
+      <c r="F255" s="5" t="n"/>
+      <c r="G255" s="6" t="n"/>
+    </row>
+    <row r="256" hidden="1" outlineLevel="2">
+      <c r="A256" s="4" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="B256" s="5" t="n"/>
+      <c r="C256" s="6" t="n"/>
+      <c r="D256" s="6" t="n"/>
+      <c r="E256" s="5" t="n"/>
+      <c r="F256" s="5" t="n"/>
+      <c r="G256" s="6" t="n"/>
+    </row>
+    <row r="257" hidden="1" outlineLevel="2">
+      <c r="A257" s="4" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="B257" s="5" t="n"/>
+      <c r="C257" s="6" t="n"/>
+      <c r="D257" s="6" t="n"/>
+      <c r="E257" s="5" t="n"/>
+      <c r="F257" s="5" t="n"/>
+      <c r="G257" s="6" t="n"/>
+    </row>
+    <row r="258" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A258" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B258" s="5" t="n"/>
+      <c r="C258" s="6" t="n"/>
+      <c r="D258" s="6" t="n"/>
+      <c r="E258" s="5" t="n"/>
+      <c r="F258" s="5" t="n"/>
+      <c r="G258" s="6" t="n"/>
+    </row>
+    <row r="259" hidden="1" outlineLevel="2">
+      <c r="A259" s="4" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="B259" s="5" t="n"/>
+      <c r="C259" s="6" t="n"/>
+      <c r="D259" s="6" t="n"/>
+      <c r="E259" s="5" t="n"/>
+      <c r="F259" s="5" t="n"/>
+      <c r="G259" s="6" t="n"/>
+    </row>
+    <row r="260" hidden="1" outlineLevel="2">
+      <c r="A260" s="4" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="B260" s="5" t="n"/>
+      <c r="C260" s="6" t="n"/>
+      <c r="D260" s="6" t="n"/>
+      <c r="E260" s="5" t="n"/>
+      <c r="F260" s="5" t="n"/>
+      <c r="G260" s="6" t="n"/>
+    </row>
+    <row r="261" hidden="1" outlineLevel="2">
+      <c r="A261" s="4" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="B261" s="5" t="n"/>
+      <c r="C261" s="6" t="n"/>
+      <c r="D261" s="6" t="n"/>
+      <c r="E261" s="5" t="n"/>
+      <c r="F261" s="5" t="n"/>
+      <c r="G261" s="6" t="n"/>
+    </row>
+    <row r="262" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A262" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="B262" s="5" t="n"/>
+      <c r="C262" s="6" t="n"/>
+      <c r="D262" s="6" t="n"/>
+      <c r="E262" s="5" t="n"/>
+      <c r="F262" s="5" t="n"/>
+      <c r="G262" s="6" t="n"/>
+    </row>
+    <row r="263" hidden="1" outlineLevel="2">
+      <c r="A263" s="4" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="B263" s="5" t="n"/>
+      <c r="C263" s="6" t="n"/>
+      <c r="D263" s="6" t="n"/>
+      <c r="E263" s="5" t="n"/>
+      <c r="F263" s="5" t="n"/>
+      <c r="G263" s="6" t="n"/>
+    </row>
+    <row r="264" hidden="1" outlineLevel="2">
+      <c r="A264" s="4" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="B264" s="5" t="n"/>
+      <c r="C264" s="6" t="n"/>
+      <c r="D264" s="6" t="n"/>
+      <c r="E264" s="5" t="n"/>
+      <c r="F264" s="5" t="n"/>
+      <c r="G264" s="6" t="n"/>
+    </row>
+    <row r="265" hidden="1" outlineLevel="2">
+      <c r="A265" s="4" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="B265" s="5" t="n"/>
+      <c r="C265" s="6" t="n"/>
+      <c r="D265" s="6" t="n"/>
+      <c r="E265" s="5" t="n"/>
+      <c r="F265" s="5" t="n"/>
+      <c r="G265" s="6" t="n"/>
+    </row>
+    <row r="266" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A266" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="B266" s="5" t="n"/>
+      <c r="C266" s="6" t="n"/>
+      <c r="D266" s="6" t="n"/>
+      <c r="E266" s="5" t="n"/>
+      <c r="F266" s="5" t="n"/>
+      <c r="G266" s="6" t="n"/>
+    </row>
+    <row r="267" hidden="1" outlineLevel="2">
+      <c r="A267" s="4" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="B267" s="5" t="n"/>
+      <c r="C267" s="6" t="n"/>
+      <c r="D267" s="6" t="n"/>
+      <c r="E267" s="5" t="n"/>
+      <c r="F267" s="5" t="n"/>
+      <c r="G267" s="6" t="n"/>
+    </row>
+    <row r="268" hidden="1" outlineLevel="2">
+      <c r="A268" s="4" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="B268" s="5" t="n"/>
+      <c r="C268" s="6" t="n"/>
+      <c r="D268" s="6" t="n"/>
+      <c r="E268" s="5" t="n"/>
+      <c r="F268" s="5" t="n"/>
+      <c r="G268" s="6" t="n"/>
+    </row>
+    <row r="269" hidden="1" outlineLevel="2">
+      <c r="A269" s="4" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="B269" s="5" t="n"/>
+      <c r="C269" s="6" t="n"/>
+      <c r="D269" s="6" t="n"/>
+      <c r="E269" s="5" t="n"/>
+      <c r="F269" s="5" t="n"/>
+      <c r="G269" s="6" t="n"/>
+    </row>
+    <row r="270" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A270" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="B270" s="5" t="n"/>
+      <c r="C270" s="6" t="n"/>
+      <c r="D270" s="6" t="n"/>
+      <c r="E270" s="5" t="n"/>
+      <c r="F270" s="5" t="n"/>
+      <c r="G270" s="6" t="n"/>
+    </row>
+    <row r="271" hidden="1" outlineLevel="2">
+      <c r="A271" s="4" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="B271" s="5" t="n"/>
+      <c r="C271" s="6" t="n"/>
+      <c r="D271" s="6" t="n"/>
+      <c r="E271" s="5" t="n"/>
+      <c r="F271" s="5" t="n"/>
+      <c r="G271" s="6" t="n"/>
+    </row>
+    <row r="272" hidden="1" outlineLevel="2">
+      <c r="A272" s="4" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="B272" s="5" t="n"/>
+      <c r="C272" s="6" t="n"/>
+      <c r="D272" s="6" t="n"/>
+      <c r="E272" s="5" t="n"/>
+      <c r="F272" s="5" t="n"/>
+      <c r="G272" s="6" t="n"/>
+    </row>
+    <row r="273" hidden="1" outlineLevel="2">
+      <c r="A273" s="4" t="n">
+        <v>67.75</v>
+      </c>
+      <c r="B273" s="5" t="n"/>
+      <c r="C273" s="6" t="n"/>
+      <c r="D273" s="6" t="n"/>
+      <c r="E273" s="5" t="n"/>
+      <c r="F273" s="5" t="n"/>
+      <c r="G273" s="6" t="n"/>
+    </row>
+    <row r="274" collapsed="1">
+      <c r="A274" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="B274" s="5" t="inlineStr">
+        <is>
+          <t>chorus 1b</t>
+        </is>
+      </c>
+      <c r="C274" s="6" t="inlineStr">
+        <is>
+          <t>generierter Code (eingefroren, ohne show.yaml):
+chorus 2b (ab 2:11.557): scene(SCENE_WAVE_RL, 7869, 65, 122);
+   Welle diesmal andersrum</t>
+        </is>
+      </c>
+      <c r="D274" s="6" t="n"/>
+      <c r="E274" s="5" t="n"/>
+      <c r="F274" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G274" s="6" t="inlineStr">
+        <is>
           <t>progSternNeu(7870, 490, 65, 5, 26, 5, true, 3)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
+    <row r="275" hidden="1" outlineLevel="2">
+      <c r="A275" s="4" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="B275" s="5" t="n"/>
+      <c r="C275" s="6" t="n"/>
+      <c r="D275" s="6" t="n"/>
+      <c r="E275" s="5" t="n"/>
+      <c r="F275" s="5" t="n"/>
+      <c r="G275" s="6" t="n"/>
+    </row>
+    <row r="276" hidden="1" outlineLevel="2">
+      <c r="A276" s="4" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="B276" s="5" t="n"/>
+      <c r="C276" s="6" t="n"/>
+      <c r="D276" s="6" t="n"/>
+      <c r="E276" s="5" t="n"/>
+      <c r="F276" s="5" t="n"/>
+      <c r="G276" s="6" t="n"/>
+    </row>
+    <row r="277" hidden="1" outlineLevel="2">
+      <c r="A277" s="4" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="B277" s="5" t="n"/>
+      <c r="C277" s="6" t="n"/>
+      <c r="D277" s="6" t="n"/>
+      <c r="E277" s="5" t="n"/>
+      <c r="F277" s="5" t="n"/>
+      <c r="G277" s="6" t="n"/>
+    </row>
+    <row r="278" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A278" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="B278" s="5" t="n"/>
+      <c r="C278" s="6" t="n"/>
+      <c r="D278" s="6" t="n"/>
+      <c r="E278" s="5" t="n"/>
+      <c r="F278" s="5" t="n"/>
+      <c r="G278" s="6" t="n"/>
+    </row>
+    <row r="279" hidden="1" outlineLevel="2">
+      <c r="A279" s="4" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="B279" s="5" t="n"/>
+      <c r="C279" s="6" t="n"/>
+      <c r="D279" s="6" t="n"/>
+      <c r="E279" s="5" t="n"/>
+      <c r="F279" s="5" t="n"/>
+      <c r="G279" s="6" t="n"/>
+    </row>
+    <row r="280" hidden="1" outlineLevel="2">
+      <c r="A280" s="4" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="B280" s="5" t="n"/>
+      <c r="C280" s="6" t="n"/>
+      <c r="D280" s="6" t="n"/>
+      <c r="E280" s="5" t="n"/>
+      <c r="F280" s="5" t="n"/>
+      <c r="G280" s="6" t="n"/>
+    </row>
+    <row r="281" hidden="1" outlineLevel="2">
+      <c r="A281" s="4" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="B281" s="5" t="n"/>
+      <c r="C281" s="6" t="n"/>
+      <c r="D281" s="6" t="n"/>
+      <c r="E281" s="5" t="n"/>
+      <c r="F281" s="5" t="n"/>
+      <c r="G281" s="6" t="n"/>
+    </row>
+    <row r="282" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A282" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B282" s="5" t="n"/>
+      <c r="C282" s="6" t="n"/>
+      <c r="D282" s="6" t="n"/>
+      <c r="E282" s="5" t="n"/>
+      <c r="F282" s="5" t="n"/>
+      <c r="G282" s="6" t="n"/>
+    </row>
+    <row r="283" hidden="1" outlineLevel="2">
+      <c r="A283" s="4" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="B283" s="5" t="n"/>
+      <c r="C283" s="6" t="n"/>
+      <c r="D283" s="6" t="n"/>
+      <c r="E283" s="5" t="n"/>
+      <c r="F283" s="5" t="n"/>
+      <c r="G283" s="6" t="n"/>
+    </row>
+    <row r="284" hidden="1" outlineLevel="2">
+      <c r="A284" s="4" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="B284" s="5" t="n"/>
+      <c r="C284" s="6" t="n"/>
+      <c r="D284" s="6" t="n"/>
+      <c r="E284" s="5" t="n"/>
+      <c r="F284" s="5" t="n"/>
+      <c r="G284" s="6" t="n"/>
+    </row>
+    <row r="285" hidden="1" outlineLevel="2">
+      <c r="A285" s="4" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="B285" s="5" t="n"/>
+      <c r="C285" s="6" t="n"/>
+      <c r="D285" s="6" t="n"/>
+      <c r="E285" s="5" t="n"/>
+      <c r="F285" s="5" t="n"/>
+      <c r="G285" s="6" t="n"/>
+    </row>
+    <row r="286" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A286" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B286" s="5" t="n"/>
+      <c r="C286" s="6" t="n"/>
+      <c r="D286" s="6" t="n"/>
+      <c r="E286" s="5" t="n"/>
+      <c r="F286" s="5" t="n"/>
+      <c r="G286" s="6" t="n"/>
+    </row>
+    <row r="287" hidden="1" outlineLevel="2">
+      <c r="A287" s="4" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="B287" s="5" t="n"/>
+      <c r="C287" s="6" t="n"/>
+      <c r="D287" s="6" t="n"/>
+      <c r="E287" s="5" t="n"/>
+      <c r="F287" s="5" t="n"/>
+      <c r="G287" s="6" t="n"/>
+    </row>
+    <row r="288" hidden="1" outlineLevel="2">
+      <c r="A288" s="4" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="B288" s="5" t="n"/>
+      <c r="C288" s="6" t="n"/>
+      <c r="D288" s="6" t="n"/>
+      <c r="E288" s="5" t="n"/>
+      <c r="F288" s="5" t="n"/>
+      <c r="G288" s="6" t="n"/>
+    </row>
+    <row r="289" hidden="1" outlineLevel="2">
+      <c r="A289" s="4" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="B289" s="5" t="n"/>
+      <c r="C289" s="6" t="n"/>
+      <c r="D289" s="6" t="n"/>
+      <c r="E289" s="5" t="n"/>
+      <c r="F289" s="5" t="n"/>
+      <c r="G289" s="6" t="n"/>
+    </row>
+    <row r="290" collapsed="1">
+      <c r="A290" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B290" s="5" t="inlineStr">
         <is>
           <t>i keep dancing</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C290" s="6" t="inlineStr">
         <is>
           <t>generierter Code (eingefroren, ohne show.yaml):
 hook 2 (ab 2:19.426): scene(SCENE_PINGPONG, 7869, 70, 122);</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5">
+      <c r="D290" s="6" t="n"/>
+      <c r="E290" s="5" t="n"/>
+      <c r="F290" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G290" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(7870, 4, 70)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
+    <row r="291" hidden="1" outlineLevel="2">
+      <c r="A291" s="4" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="B291" s="5" t="n"/>
+      <c r="C291" s="6" t="n"/>
+      <c r="D291" s="6" t="n"/>
+      <c r="E291" s="5" t="n"/>
+      <c r="F291" s="5" t="n"/>
+      <c r="G291" s="6" t="n"/>
+    </row>
+    <row r="292" hidden="1" outlineLevel="2">
+      <c r="A292" s="4" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="B292" s="5" t="n"/>
+      <c r="C292" s="6" t="n"/>
+      <c r="D292" s="6" t="n"/>
+      <c r="E292" s="5" t="n"/>
+      <c r="F292" s="5" t="n"/>
+      <c r="G292" s="6" t="n"/>
+    </row>
+    <row r="293" hidden="1" outlineLevel="2">
+      <c r="A293" s="4" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="B293" s="5" t="n"/>
+      <c r="C293" s="6" t="n"/>
+      <c r="D293" s="6" t="n"/>
+      <c r="E293" s="5" t="n"/>
+      <c r="F293" s="5" t="n"/>
+      <c r="G293" s="6" t="n"/>
+    </row>
+    <row r="294" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A294" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="B294" s="5" t="n"/>
+      <c r="C294" s="6" t="n"/>
+      <c r="D294" s="6" t="n"/>
+      <c r="E294" s="5" t="n"/>
+      <c r="F294" s="5" t="n"/>
+      <c r="G294" s="6" t="n"/>
+    </row>
+    <row r="295" hidden="1" outlineLevel="2">
+      <c r="A295" s="4" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="B295" s="5" t="n"/>
+      <c r="C295" s="6" t="n"/>
+      <c r="D295" s="6" t="n"/>
+      <c r="E295" s="5" t="n"/>
+      <c r="F295" s="5" t="n"/>
+      <c r="G295" s="6" t="n"/>
+    </row>
+    <row r="296" hidden="1" outlineLevel="2">
+      <c r="A296" s="4" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="B296" s="5" t="n"/>
+      <c r="C296" s="6" t="n"/>
+      <c r="D296" s="6" t="n"/>
+      <c r="E296" s="5" t="n"/>
+      <c r="F296" s="5" t="n"/>
+      <c r="G296" s="6" t="n"/>
+    </row>
+    <row r="297" hidden="1" outlineLevel="2">
+      <c r="A297" s="4" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="B297" s="5" t="n"/>
+      <c r="C297" s="6" t="n"/>
+      <c r="D297" s="6" t="n"/>
+      <c r="E297" s="5" t="n"/>
+      <c r="F297" s="5" t="n"/>
+      <c r="G297" s="6" t="n"/>
+    </row>
+    <row r="298" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A298" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="B298" s="5" t="n"/>
+      <c r="C298" s="6" t="n"/>
+      <c r="D298" s="6" t="n"/>
+      <c r="E298" s="5" t="n"/>
+      <c r="F298" s="5" t="n"/>
+      <c r="G298" s="6" t="n"/>
+    </row>
+    <row r="299" hidden="1" outlineLevel="2">
+      <c r="A299" s="4" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="B299" s="5" t="n"/>
+      <c r="C299" s="6" t="n"/>
+      <c r="D299" s="6" t="n"/>
+      <c r="E299" s="5" t="n"/>
+      <c r="F299" s="5" t="n"/>
+      <c r="G299" s="6" t="n"/>
+    </row>
+    <row r="300" hidden="1" outlineLevel="2">
+      <c r="A300" s="4" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="B300" s="5" t="n"/>
+      <c r="C300" s="6" t="n"/>
+      <c r="D300" s="6" t="n"/>
+      <c r="E300" s="5" t="n"/>
+      <c r="F300" s="5" t="n"/>
+      <c r="G300" s="6" t="n"/>
+    </row>
+    <row r="301" hidden="1" outlineLevel="2">
+      <c r="A301" s="4" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="B301" s="5" t="n"/>
+      <c r="C301" s="6" t="n"/>
+      <c r="D301" s="6" t="n"/>
+      <c r="E301" s="5" t="n"/>
+      <c r="F301" s="5" t="n"/>
+      <c r="G301" s="6" t="n"/>
+    </row>
+    <row r="302" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A302" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="B302" s="5" t="n"/>
+      <c r="C302" s="6" t="n"/>
+      <c r="D302" s="6" t="n"/>
+      <c r="E302" s="5" t="n"/>
+      <c r="F302" s="5" t="n"/>
+      <c r="G302" s="6" t="n"/>
+    </row>
+    <row r="303" hidden="1" outlineLevel="2">
+      <c r="A303" s="4" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="B303" s="5" t="n"/>
+      <c r="C303" s="6" t="n"/>
+      <c r="D303" s="6" t="n"/>
+      <c r="E303" s="5" t="n"/>
+      <c r="F303" s="5" t="n"/>
+      <c r="G303" s="6" t="n"/>
+    </row>
+    <row r="304" hidden="1" outlineLevel="2">
+      <c r="A304" s="4" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="B304" s="5" t="n"/>
+      <c r="C304" s="6" t="n"/>
+      <c r="D304" s="6" t="n"/>
+      <c r="E304" s="5" t="n"/>
+      <c r="F304" s="5" t="n"/>
+      <c r="G304" s="6" t="n"/>
+    </row>
+    <row r="305" hidden="1" outlineLevel="2">
+      <c r="A305" s="4" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="B305" s="5" t="n"/>
+      <c r="C305" s="6" t="n"/>
+      <c r="D305" s="6" t="n"/>
+      <c r="E305" s="5" t="n"/>
+      <c r="F305" s="5" t="n"/>
+      <c r="G305" s="6" t="n"/>
+    </row>
+    <row r="306" collapsed="1">
+      <c r="A306" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B306" s="5" t="inlineStr">
         <is>
           <t>instrumental</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C306" s="6" t="inlineStr">
         <is>
           <t>generierter Code (eingefroren, ohne show.yaml):
 instrumental (ab 2:27.295): setColorScheme(SCHEME_RETRO); scene(SCENE_SOLO_GIT, 15738, 75, 122);
    Gitarre im Spotlight, rot/weiß/blau wie im Original</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5">
+      <c r="D306" s="6" t="n"/>
+      <c r="E306" s="5" t="n"/>
+      <c r="F306" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G306" s="6" t="inlineStr">
         <is>
           <t>progPalette(15740, 9, 75)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
+    <row r="307" hidden="1" outlineLevel="2">
+      <c r="A307" s="4" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="B307" s="5" t="n"/>
+      <c r="C307" s="6" t="n"/>
+      <c r="D307" s="6" t="n"/>
+      <c r="E307" s="5" t="n"/>
+      <c r="F307" s="5" t="n"/>
+      <c r="G307" s="6" t="n"/>
+    </row>
+    <row r="308" hidden="1" outlineLevel="2">
+      <c r="A308" s="4" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="B308" s="5" t="n"/>
+      <c r="C308" s="6" t="n"/>
+      <c r="D308" s="6" t="n"/>
+      <c r="E308" s="5" t="n"/>
+      <c r="F308" s="5" t="n"/>
+      <c r="G308" s="6" t="n"/>
+    </row>
+    <row r="309" hidden="1" outlineLevel="2">
+      <c r="A309" s="4" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="B309" s="5" t="n"/>
+      <c r="C309" s="6" t="n"/>
+      <c r="D309" s="6" t="n"/>
+      <c r="E309" s="5" t="n"/>
+      <c r="F309" s="5" t="n"/>
+      <c r="G309" s="6" t="n"/>
+    </row>
+    <row r="310" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A310" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="B310" s="5" t="n"/>
+      <c r="C310" s="6" t="n"/>
+      <c r="D310" s="6" t="n"/>
+      <c r="E310" s="5" t="n"/>
+      <c r="F310" s="5" t="n"/>
+      <c r="G310" s="6" t="n"/>
+    </row>
+    <row r="311" hidden="1" outlineLevel="2">
+      <c r="A311" s="4" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="B311" s="5" t="n"/>
+      <c r="C311" s="6" t="n"/>
+      <c r="D311" s="6" t="n"/>
+      <c r="E311" s="5" t="n"/>
+      <c r="F311" s="5" t="n"/>
+      <c r="G311" s="6" t="n"/>
+    </row>
+    <row r="312" hidden="1" outlineLevel="2">
+      <c r="A312" s="4" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="B312" s="5" t="n"/>
+      <c r="C312" s="6" t="n"/>
+      <c r="D312" s="6" t="n"/>
+      <c r="E312" s="5" t="n"/>
+      <c r="F312" s="5" t="n"/>
+      <c r="G312" s="6" t="n"/>
+    </row>
+    <row r="313" hidden="1" outlineLevel="2">
+      <c r="A313" s="4" t="n">
+        <v>77.75</v>
+      </c>
+      <c r="B313" s="5" t="n"/>
+      <c r="C313" s="6" t="n"/>
+      <c r="D313" s="6" t="n"/>
+      <c r="E313" s="5" t="n"/>
+      <c r="F313" s="5" t="n"/>
+      <c r="G313" s="6" t="n"/>
+    </row>
+    <row r="314" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A314" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="B314" s="5" t="n"/>
+      <c r="C314" s="6" t="n"/>
+      <c r="D314" s="6" t="n"/>
+      <c r="E314" s="5" t="n"/>
+      <c r="F314" s="5" t="n"/>
+      <c r="G314" s="6" t="n"/>
+    </row>
+    <row r="315" hidden="1" outlineLevel="2">
+      <c r="A315" s="4" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="B315" s="5" t="n"/>
+      <c r="C315" s="6" t="n"/>
+      <c r="D315" s="6" t="n"/>
+      <c r="E315" s="5" t="n"/>
+      <c r="F315" s="5" t="n"/>
+      <c r="G315" s="6" t="n"/>
+    </row>
+    <row r="316" hidden="1" outlineLevel="2">
+      <c r="A316" s="4" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="B316" s="5" t="n"/>
+      <c r="C316" s="6" t="n"/>
+      <c r="D316" s="6" t="n"/>
+      <c r="E316" s="5" t="n"/>
+      <c r="F316" s="5" t="n"/>
+      <c r="G316" s="6" t="n"/>
+    </row>
+    <row r="317" hidden="1" outlineLevel="2">
+      <c r="A317" s="4" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="B317" s="5" t="n"/>
+      <c r="C317" s="6" t="n"/>
+      <c r="D317" s="6" t="n"/>
+      <c r="E317" s="5" t="n"/>
+      <c r="F317" s="5" t="n"/>
+      <c r="G317" s="6" t="n"/>
+    </row>
+    <row r="318" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A318" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="B318" s="5" t="n"/>
+      <c r="C318" s="6" t="n"/>
+      <c r="D318" s="6" t="n"/>
+      <c r="E318" s="5" t="n"/>
+      <c r="F318" s="5" t="n"/>
+      <c r="G318" s="6" t="n"/>
+    </row>
+    <row r="319" hidden="1" outlineLevel="2">
+      <c r="A319" s="4" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="B319" s="5" t="n"/>
+      <c r="C319" s="6" t="n"/>
+      <c r="D319" s="6" t="n"/>
+      <c r="E319" s="5" t="n"/>
+      <c r="F319" s="5" t="n"/>
+      <c r="G319" s="6" t="n"/>
+    </row>
+    <row r="320" hidden="1" outlineLevel="2">
+      <c r="A320" s="4" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="B320" s="5" t="n"/>
+      <c r="C320" s="6" t="n"/>
+      <c r="D320" s="6" t="n"/>
+      <c r="E320" s="5" t="n"/>
+      <c r="F320" s="5" t="n"/>
+      <c r="G320" s="6" t="n"/>
+    </row>
+    <row r="321" hidden="1" outlineLevel="2">
+      <c r="A321" s="4" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="B321" s="5" t="n"/>
+      <c r="C321" s="6" t="n"/>
+      <c r="D321" s="6" t="n"/>
+      <c r="E321" s="5" t="n"/>
+      <c r="F321" s="5" t="n"/>
+      <c r="G321" s="6" t="n"/>
+    </row>
+    <row r="322" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A322" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="B322" s="5" t="n"/>
+      <c r="C322" s="6" t="n"/>
+      <c r="D322" s="6" t="n"/>
+      <c r="E322" s="5" t="n"/>
+      <c r="F322" s="5" t="n"/>
+      <c r="G322" s="6" t="n"/>
+    </row>
+    <row r="323" hidden="1" outlineLevel="2">
+      <c r="A323" s="4" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="B323" s="5" t="n"/>
+      <c r="C323" s="6" t="n"/>
+      <c r="D323" s="6" t="n"/>
+      <c r="E323" s="5" t="n"/>
+      <c r="F323" s="5" t="n"/>
+      <c r="G323" s="6" t="n"/>
+    </row>
+    <row r="324" hidden="1" outlineLevel="2">
+      <c r="A324" s="4" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="B324" s="5" t="n"/>
+      <c r="C324" s="6" t="n"/>
+      <c r="D324" s="6" t="n"/>
+      <c r="E324" s="5" t="n"/>
+      <c r="F324" s="5" t="n"/>
+      <c r="G324" s="6" t="n"/>
+    </row>
+    <row r="325" hidden="1" outlineLevel="2">
+      <c r="A325" s="4" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="B325" s="5" t="n"/>
+      <c r="C325" s="6" t="n"/>
+      <c r="D325" s="6" t="n"/>
+      <c r="E325" s="5" t="n"/>
+      <c r="F325" s="5" t="n"/>
+      <c r="G325" s="6" t="n"/>
+    </row>
+    <row r="326" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A326" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B326" s="5" t="n"/>
+      <c r="C326" s="6" t="n"/>
+      <c r="D326" s="6" t="n"/>
+      <c r="E326" s="5" t="n"/>
+      <c r="F326" s="5" t="n"/>
+      <c r="G326" s="6" t="n"/>
+    </row>
+    <row r="327" hidden="1" outlineLevel="2">
+      <c r="A327" s="4" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="B327" s="5" t="n"/>
+      <c r="C327" s="6" t="n"/>
+      <c r="D327" s="6" t="n"/>
+      <c r="E327" s="5" t="n"/>
+      <c r="F327" s="5" t="n"/>
+      <c r="G327" s="6" t="n"/>
+    </row>
+    <row r="328" hidden="1" outlineLevel="2">
+      <c r="A328" s="4" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="B328" s="5" t="n"/>
+      <c r="C328" s="6" t="n"/>
+      <c r="D328" s="6" t="n"/>
+      <c r="E328" s="5" t="n"/>
+      <c r="F328" s="5" t="n"/>
+      <c r="G328" s="6" t="n"/>
+    </row>
+    <row r="329" hidden="1" outlineLevel="2">
+      <c r="A329" s="4" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="B329" s="5" t="n"/>
+      <c r="C329" s="6" t="n"/>
+      <c r="D329" s="6" t="n"/>
+      <c r="E329" s="5" t="n"/>
+      <c r="F329" s="5" t="n"/>
+      <c r="G329" s="6" t="n"/>
+    </row>
+    <row r="330" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A330" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="B330" s="5" t="n"/>
+      <c r="C330" s="6" t="n"/>
+      <c r="D330" s="6" t="n"/>
+      <c r="E330" s="5" t="n"/>
+      <c r="F330" s="5" t="n"/>
+      <c r="G330" s="6" t="n"/>
+    </row>
+    <row r="331" hidden="1" outlineLevel="2">
+      <c r="A331" s="4" t="n">
+        <v>82.25</v>
+      </c>
+      <c r="B331" s="5" t="n"/>
+      <c r="C331" s="6" t="n"/>
+      <c r="D331" s="6" t="n"/>
+      <c r="E331" s="5" t="n"/>
+      <c r="F331" s="5" t="n"/>
+      <c r="G331" s="6" t="n"/>
+    </row>
+    <row r="332" hidden="1" outlineLevel="2">
+      <c r="A332" s="4" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="B332" s="5" t="n"/>
+      <c r="C332" s="6" t="n"/>
+      <c r="D332" s="6" t="n"/>
+      <c r="E332" s="5" t="n"/>
+      <c r="F332" s="5" t="n"/>
+      <c r="G332" s="6" t="n"/>
+    </row>
+    <row r="333" hidden="1" outlineLevel="2">
+      <c r="A333" s="4" t="n">
+        <v>82.75</v>
+      </c>
+      <c r="B333" s="5" t="n"/>
+      <c r="C333" s="6" t="n"/>
+      <c r="D333" s="6" t="n"/>
+      <c r="E333" s="5" t="n"/>
+      <c r="F333" s="5" t="n"/>
+      <c r="G333" s="6" t="n"/>
+    </row>
+    <row r="334" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A334" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="B334" s="5" t="n"/>
+      <c r="C334" s="6" t="n"/>
+      <c r="D334" s="6" t="n"/>
+      <c r="E334" s="5" t="n"/>
+      <c r="F334" s="5" t="n"/>
+      <c r="G334" s="6" t="n"/>
+    </row>
+    <row r="335" hidden="1" outlineLevel="2">
+      <c r="A335" s="4" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="B335" s="5" t="n"/>
+      <c r="C335" s="6" t="n"/>
+      <c r="D335" s="6" t="n"/>
+      <c r="E335" s="5" t="n"/>
+      <c r="F335" s="5" t="n"/>
+      <c r="G335" s="6" t="n"/>
+    </row>
+    <row r="336" hidden="1" outlineLevel="2">
+      <c r="A336" s="4" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="B336" s="5" t="n"/>
+      <c r="C336" s="6" t="n"/>
+      <c r="D336" s="6" t="n"/>
+      <c r="E336" s="5" t="n"/>
+      <c r="F336" s="5" t="n"/>
+      <c r="G336" s="6" t="n"/>
+    </row>
+    <row r="337" hidden="1" outlineLevel="2">
+      <c r="A337" s="4" t="n">
+        <v>83.75</v>
+      </c>
+      <c r="B337" s="5" t="n"/>
+      <c r="C337" s="6" t="n"/>
+      <c r="D337" s="6" t="n"/>
+      <c r="E337" s="5" t="n"/>
+      <c r="F337" s="5" t="n"/>
+      <c r="G337" s="6" t="n"/>
+    </row>
+    <row r="338" collapsed="1">
+      <c r="A338" s="4" t="n">
         <v>84</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B338" s="5" t="inlineStr">
         <is>
           <t>so far away</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C338" s="6" t="inlineStr">
         <is>
           <t>generierter Code (eingefroren, ohne show.yaml):
 bridge (ab 2:43.033): setColorScheme(SCHEME_ICE); [MATRIX] matrixMovieFX(15737, 80, 100, 6); [sonst] scene(SCENE_CALM, 15737, 80, 122);
    alles zieht sich zurück, Matrix-Film wie im Original</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5">
+      <c r="D338" s="6" t="n"/>
+      <c r="E338" s="5" t="n"/>
+      <c r="F338" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G338" s="6" t="inlineStr">
         <is>
           <t>matrixMovieFX(15735, 80, 100, 6)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
+    <row r="339" hidden="1" outlineLevel="2">
+      <c r="A339" s="4" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="B339" s="5" t="n"/>
+      <c r="C339" s="6" t="n"/>
+      <c r="D339" s="6" t="n"/>
+      <c r="E339" s="5" t="n"/>
+      <c r="F339" s="5" t="n"/>
+      <c r="G339" s="6" t="n"/>
+    </row>
+    <row r="340" hidden="1" outlineLevel="2">
+      <c r="A340" s="4" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="B340" s="5" t="n"/>
+      <c r="C340" s="6" t="n"/>
+      <c r="D340" s="6" t="n"/>
+      <c r="E340" s="5" t="n"/>
+      <c r="F340" s="5" t="n"/>
+      <c r="G340" s="6" t="n"/>
+    </row>
+    <row r="341" hidden="1" outlineLevel="2">
+      <c r="A341" s="4" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="B341" s="5" t="n"/>
+      <c r="C341" s="6" t="n"/>
+      <c r="D341" s="6" t="n"/>
+      <c r="E341" s="5" t="n"/>
+      <c r="F341" s="5" t="n"/>
+      <c r="G341" s="6" t="n"/>
+    </row>
+    <row r="342" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A342" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="B342" s="5" t="n"/>
+      <c r="C342" s="6" t="n"/>
+      <c r="D342" s="6" t="n"/>
+      <c r="E342" s="5" t="n"/>
+      <c r="F342" s="5" t="n"/>
+      <c r="G342" s="6" t="n"/>
+    </row>
+    <row r="343" hidden="1" outlineLevel="2">
+      <c r="A343" s="4" t="n">
+        <v>85.25</v>
+      </c>
+      <c r="B343" s="5" t="n"/>
+      <c r="C343" s="6" t="n"/>
+      <c r="D343" s="6" t="n"/>
+      <c r="E343" s="5" t="n"/>
+      <c r="F343" s="5" t="n"/>
+      <c r="G343" s="6" t="n"/>
+    </row>
+    <row r="344" hidden="1" outlineLevel="2">
+      <c r="A344" s="4" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="B344" s="5" t="n"/>
+      <c r="C344" s="6" t="n"/>
+      <c r="D344" s="6" t="n"/>
+      <c r="E344" s="5" t="n"/>
+      <c r="F344" s="5" t="n"/>
+      <c r="G344" s="6" t="n"/>
+    </row>
+    <row r="345" hidden="1" outlineLevel="2">
+      <c r="A345" s="4" t="n">
+        <v>85.75</v>
+      </c>
+      <c r="B345" s="5" t="n"/>
+      <c r="C345" s="6" t="n"/>
+      <c r="D345" s="6" t="n"/>
+      <c r="E345" s="5" t="n"/>
+      <c r="F345" s="5" t="n"/>
+      <c r="G345" s="6" t="n"/>
+    </row>
+    <row r="346" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A346" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="B346" s="5" t="n"/>
+      <c r="C346" s="6" t="n"/>
+      <c r="D346" s="6" t="n"/>
+      <c r="E346" s="5" t="n"/>
+      <c r="F346" s="5" t="n"/>
+      <c r="G346" s="6" t="n"/>
+    </row>
+    <row r="347" hidden="1" outlineLevel="2">
+      <c r="A347" s="4" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="B347" s="5" t="n"/>
+      <c r="C347" s="6" t="n"/>
+      <c r="D347" s="6" t="n"/>
+      <c r="E347" s="5" t="n"/>
+      <c r="F347" s="5" t="n"/>
+      <c r="G347" s="6" t="n"/>
+    </row>
+    <row r="348" hidden="1" outlineLevel="2">
+      <c r="A348" s="4" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="B348" s="5" t="n"/>
+      <c r="C348" s="6" t="n"/>
+      <c r="D348" s="6" t="n"/>
+      <c r="E348" s="5" t="n"/>
+      <c r="F348" s="5" t="n"/>
+      <c r="G348" s="6" t="n"/>
+    </row>
+    <row r="349" hidden="1" outlineLevel="2">
+      <c r="A349" s="4" t="n">
+        <v>86.75</v>
+      </c>
+      <c r="B349" s="5" t="n"/>
+      <c r="C349" s="6" t="n"/>
+      <c r="D349" s="6" t="n"/>
+      <c r="E349" s="5" t="n"/>
+      <c r="F349" s="5" t="n"/>
+      <c r="G349" s="6" t="n"/>
+    </row>
+    <row r="350" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A350" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="B350" s="5" t="n"/>
+      <c r="C350" s="6" t="n"/>
+      <c r="D350" s="6" t="n"/>
+      <c r="E350" s="5" t="n"/>
+      <c r="F350" s="5" t="n"/>
+      <c r="G350" s="6" t="n"/>
+    </row>
+    <row r="351" hidden="1" outlineLevel="2">
+      <c r="A351" s="4" t="n">
+        <v>87.25</v>
+      </c>
+      <c r="B351" s="5" t="n"/>
+      <c r="C351" s="6" t="n"/>
+      <c r="D351" s="6" t="n"/>
+      <c r="E351" s="5" t="n"/>
+      <c r="F351" s="5" t="n"/>
+      <c r="G351" s="6" t="n"/>
+    </row>
+    <row r="352" hidden="1" outlineLevel="2">
+      <c r="A352" s="4" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="B352" s="5" t="n"/>
+      <c r="C352" s="6" t="n"/>
+      <c r="D352" s="6" t="n"/>
+      <c r="E352" s="5" t="n"/>
+      <c r="F352" s="5" t="n"/>
+      <c r="G352" s="6" t="n"/>
+    </row>
+    <row r="353" hidden="1" outlineLevel="2">
+      <c r="A353" s="4" t="n">
+        <v>87.75</v>
+      </c>
+      <c r="B353" s="5" t="n"/>
+      <c r="C353" s="6" t="n"/>
+      <c r="D353" s="6" t="n"/>
+      <c r="E353" s="5" t="n"/>
+      <c r="F353" s="5" t="n"/>
+      <c r="G353" s="6" t="n"/>
+    </row>
+    <row r="354" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A354" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="B354" s="5" t="n"/>
+      <c r="C354" s="6" t="n"/>
+      <c r="D354" s="6" t="n"/>
+      <c r="E354" s="5" t="n"/>
+      <c r="F354" s="5" t="n"/>
+      <c r="G354" s="6" t="n"/>
+    </row>
+    <row r="355" hidden="1" outlineLevel="2">
+      <c r="A355" s="4" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="B355" s="5" t="n"/>
+      <c r="C355" s="6" t="n"/>
+      <c r="D355" s="6" t="n"/>
+      <c r="E355" s="5" t="n"/>
+      <c r="F355" s="5" t="n"/>
+      <c r="G355" s="6" t="n"/>
+    </row>
+    <row r="356" hidden="1" outlineLevel="2">
+      <c r="A356" s="4" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="B356" s="5" t="n"/>
+      <c r="C356" s="6" t="n"/>
+      <c r="D356" s="6" t="n"/>
+      <c r="E356" s="5" t="n"/>
+      <c r="F356" s="5" t="n"/>
+      <c r="G356" s="6" t="n"/>
+    </row>
+    <row r="357" hidden="1" outlineLevel="2">
+      <c r="A357" s="4" t="n">
+        <v>88.75</v>
+      </c>
+      <c r="B357" s="5" t="n"/>
+      <c r="C357" s="6" t="n"/>
+      <c r="D357" s="6" t="n"/>
+      <c r="E357" s="5" t="n"/>
+      <c r="F357" s="5" t="n"/>
+      <c r="G357" s="6" t="n"/>
+    </row>
+    <row r="358" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A358" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="B358" s="5" t="n"/>
+      <c r="C358" s="6" t="n"/>
+      <c r="D358" s="6" t="n"/>
+      <c r="E358" s="5" t="n"/>
+      <c r="F358" s="5" t="n"/>
+      <c r="G358" s="6" t="n"/>
+    </row>
+    <row r="359" hidden="1" outlineLevel="2">
+      <c r="A359" s="4" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="B359" s="5" t="n"/>
+      <c r="C359" s="6" t="n"/>
+      <c r="D359" s="6" t="n"/>
+      <c r="E359" s="5" t="n"/>
+      <c r="F359" s="5" t="n"/>
+      <c r="G359" s="6" t="n"/>
+    </row>
+    <row r="360" hidden="1" outlineLevel="2">
+      <c r="A360" s="4" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="B360" s="5" t="n"/>
+      <c r="C360" s="6" t="n"/>
+      <c r="D360" s="6" t="n"/>
+      <c r="E360" s="5" t="n"/>
+      <c r="F360" s="5" t="n"/>
+      <c r="G360" s="6" t="n"/>
+    </row>
+    <row r="361" hidden="1" outlineLevel="2">
+      <c r="A361" s="4" t="n">
+        <v>89.75</v>
+      </c>
+      <c r="B361" s="5" t="n"/>
+      <c r="C361" s="6" t="n"/>
+      <c r="D361" s="6" t="n"/>
+      <c r="E361" s="5" t="n"/>
+      <c r="F361" s="5" t="n"/>
+      <c r="G361" s="6" t="n"/>
+    </row>
+    <row r="362" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A362" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="B362" s="5" t="n"/>
+      <c r="C362" s="6" t="n"/>
+      <c r="D362" s="6" t="n"/>
+      <c r="E362" s="5" t="n"/>
+      <c r="F362" s="5" t="n"/>
+      <c r="G362" s="6" t="n"/>
+    </row>
+    <row r="363" hidden="1" outlineLevel="2">
+      <c r="A363" s="4" t="n">
+        <v>90.25</v>
+      </c>
+      <c r="B363" s="5" t="n"/>
+      <c r="C363" s="6" t="n"/>
+      <c r="D363" s="6" t="n"/>
+      <c r="E363" s="5" t="n"/>
+      <c r="F363" s="5" t="n"/>
+      <c r="G363" s="6" t="n"/>
+    </row>
+    <row r="364" hidden="1" outlineLevel="2">
+      <c r="A364" s="4" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="B364" s="5" t="n"/>
+      <c r="C364" s="6" t="n"/>
+      <c r="D364" s="6" t="n"/>
+      <c r="E364" s="5" t="n"/>
+      <c r="F364" s="5" t="n"/>
+      <c r="G364" s="6" t="n"/>
+    </row>
+    <row r="365" hidden="1" outlineLevel="2">
+      <c r="A365" s="4" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="B365" s="5" t="n"/>
+      <c r="C365" s="6" t="n"/>
+      <c r="D365" s="6" t="n"/>
+      <c r="E365" s="5" t="n"/>
+      <c r="F365" s="5" t="n"/>
+      <c r="G365" s="6" t="n"/>
+    </row>
+    <row r="366" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A366" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="B366" s="5" t="n"/>
+      <c r="C366" s="6" t="n"/>
+      <c r="D366" s="6" t="n"/>
+      <c r="E366" s="5" t="n"/>
+      <c r="F366" s="5" t="n"/>
+      <c r="G366" s="6" t="n"/>
+    </row>
+    <row r="367" hidden="1" outlineLevel="2">
+      <c r="A367" s="4" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="B367" s="5" t="n"/>
+      <c r="C367" s="6" t="n"/>
+      <c r="D367" s="6" t="n"/>
+      <c r="E367" s="5" t="n"/>
+      <c r="F367" s="5" t="n"/>
+      <c r="G367" s="6" t="n"/>
+    </row>
+    <row r="368" hidden="1" outlineLevel="2">
+      <c r="A368" s="4" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="B368" s="5" t="n"/>
+      <c r="C368" s="6" t="n"/>
+      <c r="D368" s="6" t="n"/>
+      <c r="E368" s="5" t="n"/>
+      <c r="F368" s="5" t="n"/>
+      <c r="G368" s="6" t="n"/>
+    </row>
+    <row r="369" hidden="1" outlineLevel="2">
+      <c r="A369" s="4" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="B369" s="5" t="n"/>
+      <c r="C369" s="6" t="n"/>
+      <c r="D369" s="6" t="n"/>
+      <c r="E369" s="5" t="n"/>
+      <c r="F369" s="5" t="n"/>
+      <c r="G369" s="6" t="n"/>
+    </row>
+    <row r="370" collapsed="1">
+      <c r="A370" s="4" t="n">
         <v>92</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B370" s="5" t="inlineStr">
         <is>
           <t>im in the corner</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C370" s="6" t="inlineStr">
         <is>
           <t>generierter Code (eingefroren, ohne show.yaml):
 corner (ab 2:58.770): progBlack(5902, 85);
    Stille vor dem Finale</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5">
+      <c r="D370" s="6" t="n"/>
+      <c r="E370" s="5" t="n"/>
+      <c r="F370" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G370" s="6" t="inlineStr">
         <is>
           <t>progBlack(5900, 85)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
+    <row r="371" hidden="1" outlineLevel="2">
+      <c r="A371" s="4" t="n">
+        <v>92.25</v>
+      </c>
+      <c r="B371" s="5" t="n"/>
+      <c r="C371" s="6" t="n"/>
+      <c r="D371" s="6" t="n"/>
+      <c r="E371" s="5" t="n"/>
+      <c r="F371" s="5" t="n"/>
+      <c r="G371" s="6" t="n"/>
+    </row>
+    <row r="372" hidden="1" outlineLevel="2">
+      <c r="A372" s="4" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="B372" s="5" t="n"/>
+      <c r="C372" s="6" t="n"/>
+      <c r="D372" s="6" t="n"/>
+      <c r="E372" s="5" t="n"/>
+      <c r="F372" s="5" t="n"/>
+      <c r="G372" s="6" t="n"/>
+    </row>
+    <row r="373" hidden="1" outlineLevel="2">
+      <c r="A373" s="4" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="B373" s="5" t="n"/>
+      <c r="C373" s="6" t="n"/>
+      <c r="D373" s="6" t="n"/>
+      <c r="E373" s="5" t="n"/>
+      <c r="F373" s="5" t="n"/>
+      <c r="G373" s="6" t="n"/>
+    </row>
+    <row r="374" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A374" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="B374" s="5" t="n"/>
+      <c r="C374" s="6" t="n"/>
+      <c r="D374" s="6" t="n"/>
+      <c r="E374" s="5" t="n"/>
+      <c r="F374" s="5" t="n"/>
+      <c r="G374" s="6" t="n"/>
+    </row>
+    <row r="375" hidden="1" outlineLevel="2">
+      <c r="A375" s="4" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="B375" s="5" t="n"/>
+      <c r="C375" s="6" t="n"/>
+      <c r="D375" s="6" t="n"/>
+      <c r="E375" s="5" t="n"/>
+      <c r="F375" s="5" t="n"/>
+      <c r="G375" s="6" t="n"/>
+    </row>
+    <row r="376" hidden="1" outlineLevel="2">
+      <c r="A376" s="4" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="B376" s="5" t="n"/>
+      <c r="C376" s="6" t="n"/>
+      <c r="D376" s="6" t="n"/>
+      <c r="E376" s="5" t="n"/>
+      <c r="F376" s="5" t="n"/>
+      <c r="G376" s="6" t="n"/>
+    </row>
+    <row r="377" hidden="1" outlineLevel="2">
+      <c r="A377" s="4" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="B377" s="5" t="n"/>
+      <c r="C377" s="6" t="n"/>
+      <c r="D377" s="6" t="n"/>
+      <c r="E377" s="5" t="n"/>
+      <c r="F377" s="5" t="n"/>
+      <c r="G377" s="6" t="n"/>
+    </row>
+    <row r="378" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A378" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="B378" s="5" t="n"/>
+      <c r="C378" s="6" t="n"/>
+      <c r="D378" s="6" t="n"/>
+      <c r="E378" s="5" t="n"/>
+      <c r="F378" s="5" t="n"/>
+      <c r="G378" s="6" t="n"/>
+    </row>
+    <row r="379" hidden="1" outlineLevel="2">
+      <c r="A379" s="4" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="B379" s="5" t="n"/>
+      <c r="C379" s="6" t="n"/>
+      <c r="D379" s="6" t="n"/>
+      <c r="E379" s="5" t="n"/>
+      <c r="F379" s="5" t="n"/>
+      <c r="G379" s="6" t="n"/>
+    </row>
+    <row r="380" hidden="1" outlineLevel="2">
+      <c r="A380" s="4" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="B380" s="5" t="n"/>
+      <c r="C380" s="6" t="n"/>
+      <c r="D380" s="6" t="n"/>
+      <c r="E380" s="5" t="n"/>
+      <c r="F380" s="5" t="n"/>
+      <c r="G380" s="6" t="n"/>
+    </row>
+    <row r="381" hidden="1" outlineLevel="2">
+      <c r="A381" s="4" t="n">
+        <v>94.75</v>
+      </c>
+      <c r="B381" s="5" t="n"/>
+      <c r="C381" s="6" t="n"/>
+      <c r="D381" s="6" t="n"/>
+      <c r="E381" s="5" t="n"/>
+      <c r="F381" s="5" t="n"/>
+      <c r="G381" s="6" t="n"/>
+    </row>
+    <row r="382" collapsed="1">
+      <c r="A382" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B382" s="5" t="inlineStr">
         <is>
           <t>snarewirbel</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C382" s="6" t="inlineStr">
         <is>
           <t>generierter Code (eingefroren, ohne show.yaml):
 snare roll (ab 3:04.672): setColorScheme(SCHEME_WHITE); scene(SCENE_BUILDUP, 1967, 90, 122);
    1 Takt Aufladen, Blast genau auf den Einsatz</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5">
+      <c r="D382" s="6" t="n"/>
+      <c r="E382" s="5" t="n"/>
+      <c r="F382" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G382" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1970, 90, 50, getRandomCRGB())</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
+    <row r="383" hidden="1" outlineLevel="2">
+      <c r="A383" s="4" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="B383" s="5" t="n"/>
+      <c r="C383" s="6" t="n"/>
+      <c r="D383" s="6" t="n"/>
+      <c r="E383" s="5" t="n"/>
+      <c r="F383" s="5" t="n"/>
+      <c r="G383" s="6" t="n"/>
+    </row>
+    <row r="384" hidden="1" outlineLevel="2">
+      <c r="A384" s="4" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="B384" s="5" t="n"/>
+      <c r="C384" s="6" t="n"/>
+      <c r="D384" s="6" t="n"/>
+      <c r="E384" s="5" t="n"/>
+      <c r="F384" s="5" t="n"/>
+      <c r="G384" s="6" t="n"/>
+    </row>
+    <row r="385" hidden="1" outlineLevel="2">
+      <c r="A385" s="4" t="n">
+        <v>95.75</v>
+      </c>
+      <c r="B385" s="5" t="n"/>
+      <c r="C385" s="6" t="n"/>
+      <c r="D385" s="6" t="n"/>
+      <c r="E385" s="5" t="n"/>
+      <c r="F385" s="5" t="n"/>
+      <c r="G385" s="6" t="n"/>
+    </row>
+    <row r="386" collapsed="1">
+      <c r="A386" s="4" t="n">
         <v>96</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B386" s="5" t="inlineStr">
         <is>
           <t>chorus 1</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C386" s="6" t="inlineStr">
         <is>
           <t>generierter Code (eingefroren, ohne show.yaml):
 chorus 3 (ab 3:06.639): setColorScheme(SCHEME_FIRE); scene(SCENE_FIRE, 7869, 95, 122);
    Finale beginnt, Farbwechsel auf Feuer</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5">
+      <c r="D386" s="6" t="n"/>
+      <c r="E386" s="5" t="n"/>
+      <c r="F386" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G386" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(7870, 95, 50, true, true)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
+    <row r="387" hidden="1" outlineLevel="2">
+      <c r="A387" s="4" t="n">
+        <v>96.25</v>
+      </c>
+      <c r="B387" s="5" t="n"/>
+      <c r="C387" s="6" t="n"/>
+      <c r="D387" s="6" t="n"/>
+      <c r="E387" s="5" t="n"/>
+      <c r="F387" s="5" t="n"/>
+      <c r="G387" s="6" t="n"/>
+    </row>
+    <row r="388" hidden="1" outlineLevel="2">
+      <c r="A388" s="4" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="B388" s="5" t="n"/>
+      <c r="C388" s="6" t="n"/>
+      <c r="D388" s="6" t="n"/>
+      <c r="E388" s="5" t="n"/>
+      <c r="F388" s="5" t="n"/>
+      <c r="G388" s="6" t="n"/>
+    </row>
+    <row r="389" hidden="1" outlineLevel="2">
+      <c r="A389" s="4" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="B389" s="5" t="n"/>
+      <c r="C389" s="6" t="n"/>
+      <c r="D389" s="6" t="n"/>
+      <c r="E389" s="5" t="n"/>
+      <c r="F389" s="5" t="n"/>
+      <c r="G389" s="6" t="n"/>
+    </row>
+    <row r="390" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A390" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="B390" s="5" t="n"/>
+      <c r="C390" s="6" t="n"/>
+      <c r="D390" s="6" t="n"/>
+      <c r="E390" s="5" t="n"/>
+      <c r="F390" s="5" t="n"/>
+      <c r="G390" s="6" t="n"/>
+    </row>
+    <row r="391" hidden="1" outlineLevel="2">
+      <c r="A391" s="4" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="B391" s="5" t="n"/>
+      <c r="C391" s="6" t="n"/>
+      <c r="D391" s="6" t="n"/>
+      <c r="E391" s="5" t="n"/>
+      <c r="F391" s="5" t="n"/>
+      <c r="G391" s="6" t="n"/>
+    </row>
+    <row r="392" hidden="1" outlineLevel="2">
+      <c r="A392" s="4" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="B392" s="5" t="n"/>
+      <c r="C392" s="6" t="n"/>
+      <c r="D392" s="6" t="n"/>
+      <c r="E392" s="5" t="n"/>
+      <c r="F392" s="5" t="n"/>
+      <c r="G392" s="6" t="n"/>
+    </row>
+    <row r="393" hidden="1" outlineLevel="2">
+      <c r="A393" s="4" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="B393" s="5" t="n"/>
+      <c r="C393" s="6" t="n"/>
+      <c r="D393" s="6" t="n"/>
+      <c r="E393" s="5" t="n"/>
+      <c r="F393" s="5" t="n"/>
+      <c r="G393" s="6" t="n"/>
+    </row>
+    <row r="394" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A394" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="B394" s="5" t="n"/>
+      <c r="C394" s="6" t="n"/>
+      <c r="D394" s="6" t="n"/>
+      <c r="E394" s="5" t="n"/>
+      <c r="F394" s="5" t="n"/>
+      <c r="G394" s="6" t="n"/>
+    </row>
+    <row r="395" hidden="1" outlineLevel="2">
+      <c r="A395" s="4" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="B395" s="5" t="n"/>
+      <c r="C395" s="6" t="n"/>
+      <c r="D395" s="6" t="n"/>
+      <c r="E395" s="5" t="n"/>
+      <c r="F395" s="5" t="n"/>
+      <c r="G395" s="6" t="n"/>
+    </row>
+    <row r="396" hidden="1" outlineLevel="2">
+      <c r="A396" s="4" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="B396" s="5" t="n"/>
+      <c r="C396" s="6" t="n"/>
+      <c r="D396" s="6" t="n"/>
+      <c r="E396" s="5" t="n"/>
+      <c r="F396" s="5" t="n"/>
+      <c r="G396" s="6" t="n"/>
+    </row>
+    <row r="397" hidden="1" outlineLevel="2">
+      <c r="A397" s="4" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="B397" s="5" t="n"/>
+      <c r="C397" s="6" t="n"/>
+      <c r="D397" s="6" t="n"/>
+      <c r="E397" s="5" t="n"/>
+      <c r="F397" s="5" t="n"/>
+      <c r="G397" s="6" t="n"/>
+    </row>
+    <row r="398" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A398" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="B398" s="5" t="n"/>
+      <c r="C398" s="6" t="n"/>
+      <c r="D398" s="6" t="n"/>
+      <c r="E398" s="5" t="n"/>
+      <c r="F398" s="5" t="n"/>
+      <c r="G398" s="6" t="n"/>
+    </row>
+    <row r="399" hidden="1" outlineLevel="2">
+      <c r="A399" s="4" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="B399" s="5" t="n"/>
+      <c r="C399" s="6" t="n"/>
+      <c r="D399" s="6" t="n"/>
+      <c r="E399" s="5" t="n"/>
+      <c r="F399" s="5" t="n"/>
+      <c r="G399" s="6" t="n"/>
+    </row>
+    <row r="400" hidden="1" outlineLevel="2">
+      <c r="A400" s="4" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="B400" s="5" t="n"/>
+      <c r="C400" s="6" t="n"/>
+      <c r="D400" s="6" t="n"/>
+      <c r="E400" s="5" t="n"/>
+      <c r="F400" s="5" t="n"/>
+      <c r="G400" s="6" t="n"/>
+    </row>
+    <row r="401" hidden="1" outlineLevel="2">
+      <c r="A401" s="4" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="B401" s="5" t="n"/>
+      <c r="C401" s="6" t="n"/>
+      <c r="D401" s="6" t="n"/>
+      <c r="E401" s="5" t="n"/>
+      <c r="F401" s="5" t="n"/>
+      <c r="G401" s="6" t="n"/>
+    </row>
+    <row r="402" collapsed="1">
+      <c r="A402" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B402" s="5" t="inlineStr">
         <is>
           <t>i keep dancing</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C402" s="6" t="inlineStr">
         <is>
           <t>generierter Code (eingefroren, ohne show.yaml):
 hook 3 (ab 3:14.508): setColorScheme(SCHEME_FIRE); scene(SCENE_WAVE_OUT, 7869, 100, 122);</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5">
+      <c r="D402" s="6" t="n"/>
+      <c r="E402" s="5" t="n"/>
+      <c r="F402" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G402" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(7865, 4, 100)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="n">
+    <row r="403" hidden="1" outlineLevel="2">
+      <c r="A403" s="4" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="B403" s="5" t="n"/>
+      <c r="C403" s="6" t="n"/>
+      <c r="D403" s="6" t="n"/>
+      <c r="E403" s="5" t="n"/>
+      <c r="F403" s="5" t="n"/>
+      <c r="G403" s="6" t="n"/>
+    </row>
+    <row r="404" hidden="1" outlineLevel="2">
+      <c r="A404" s="4" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="B404" s="5" t="n"/>
+      <c r="C404" s="6" t="n"/>
+      <c r="D404" s="6" t="n"/>
+      <c r="E404" s="5" t="n"/>
+      <c r="F404" s="5" t="n"/>
+      <c r="G404" s="6" t="n"/>
+    </row>
+    <row r="405" hidden="1" outlineLevel="2">
+      <c r="A405" s="4" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="B405" s="5" t="n"/>
+      <c r="C405" s="6" t="n"/>
+      <c r="D405" s="6" t="n"/>
+      <c r="E405" s="5" t="n"/>
+      <c r="F405" s="5" t="n"/>
+      <c r="G405" s="6" t="n"/>
+    </row>
+    <row r="406" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A406" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B406" s="5" t="n"/>
+      <c r="C406" s="6" t="n"/>
+      <c r="D406" s="6" t="n"/>
+      <c r="E406" s="5" t="n"/>
+      <c r="F406" s="5" t="n"/>
+      <c r="G406" s="6" t="n"/>
+    </row>
+    <row r="407" hidden="1" outlineLevel="2">
+      <c r="A407" s="4" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="B407" s="5" t="n"/>
+      <c r="C407" s="6" t="n"/>
+      <c r="D407" s="6" t="n"/>
+      <c r="E407" s="5" t="n"/>
+      <c r="F407" s="5" t="n"/>
+      <c r="G407" s="6" t="n"/>
+    </row>
+    <row r="408" hidden="1" outlineLevel="2">
+      <c r="A408" s="4" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="B408" s="5" t="n"/>
+      <c r="C408" s="6" t="n"/>
+      <c r="D408" s="6" t="n"/>
+      <c r="E408" s="5" t="n"/>
+      <c r="F408" s="5" t="n"/>
+      <c r="G408" s="6" t="n"/>
+    </row>
+    <row r="409" hidden="1" outlineLevel="2">
+      <c r="A409" s="4" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="B409" s="5" t="n"/>
+      <c r="C409" s="6" t="n"/>
+      <c r="D409" s="6" t="n"/>
+      <c r="E409" s="5" t="n"/>
+      <c r="F409" s="5" t="n"/>
+      <c r="G409" s="6" t="n"/>
+    </row>
+    <row r="410" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A410" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="B410" s="5" t="n"/>
+      <c r="C410" s="6" t="n"/>
+      <c r="D410" s="6" t="n"/>
+      <c r="E410" s="5" t="n"/>
+      <c r="F410" s="5" t="n"/>
+      <c r="G410" s="6" t="n"/>
+    </row>
+    <row r="411" hidden="1" outlineLevel="2">
+      <c r="A411" s="4" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="B411" s="5" t="n"/>
+      <c r="C411" s="6" t="n"/>
+      <c r="D411" s="6" t="n"/>
+      <c r="E411" s="5" t="n"/>
+      <c r="F411" s="5" t="n"/>
+      <c r="G411" s="6" t="n"/>
+    </row>
+    <row r="412" hidden="1" outlineLevel="2">
+      <c r="A412" s="4" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="B412" s="5" t="n"/>
+      <c r="C412" s="6" t="n"/>
+      <c r="D412" s="6" t="n"/>
+      <c r="E412" s="5" t="n"/>
+      <c r="F412" s="5" t="n"/>
+      <c r="G412" s="6" t="n"/>
+    </row>
+    <row r="413" hidden="1" outlineLevel="2">
+      <c r="A413" s="4" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="B413" s="5" t="n"/>
+      <c r="C413" s="6" t="n"/>
+      <c r="D413" s="6" t="n"/>
+      <c r="E413" s="5" t="n"/>
+      <c r="F413" s="5" t="n"/>
+      <c r="G413" s="6" t="n"/>
+    </row>
+    <row r="414" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A414" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="B414" s="5" t="n"/>
+      <c r="C414" s="6" t="n"/>
+      <c r="D414" s="6" t="n"/>
+      <c r="E414" s="5" t="n"/>
+      <c r="F414" s="5" t="n"/>
+      <c r="G414" s="6" t="n"/>
+    </row>
+    <row r="415" hidden="1" outlineLevel="2">
+      <c r="A415" s="4" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="B415" s="5" t="n"/>
+      <c r="C415" s="6" t="n"/>
+      <c r="D415" s="6" t="n"/>
+      <c r="E415" s="5" t="n"/>
+      <c r="F415" s="5" t="n"/>
+      <c r="G415" s="6" t="n"/>
+    </row>
+    <row r="416" hidden="1" outlineLevel="2">
+      <c r="A416" s="4" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="B416" s="5" t="n"/>
+      <c r="C416" s="6" t="n"/>
+      <c r="D416" s="6" t="n"/>
+      <c r="E416" s="5" t="n"/>
+      <c r="F416" s="5" t="n"/>
+      <c r="G416" s="6" t="n"/>
+    </row>
+    <row r="417" hidden="1" outlineLevel="2">
+      <c r="A417" s="4" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="B417" s="5" t="n"/>
+      <c r="C417" s="6" t="n"/>
+      <c r="D417" s="6" t="n"/>
+      <c r="E417" s="5" t="n"/>
+      <c r="F417" s="5" t="n"/>
+      <c r="G417" s="6" t="n"/>
+    </row>
+    <row r="418" collapsed="1">
+      <c r="A418" s="4" t="n">
         <v>104</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B418" s="5" t="inlineStr">
         <is>
           <t>chorus 1</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C418" s="6" t="inlineStr">
         <is>
           <t>generierter Code (eingefroren, ohne show.yaml):
 chorus 4 (ab 3:22.377): setColorScheme(SCHEME_SUNSET); scene(SCENE_DROP, 15738, 105, 122);</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5">
+      <c r="D418" s="6" t="n"/>
+      <c r="E418" s="5" t="n"/>
+      <c r="F418" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G418" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(15740, 490, 105, 5, 26, 5, false, 4)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
+    <row r="419" hidden="1" outlineLevel="2">
+      <c r="A419" s="4" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="B419" s="5" t="n"/>
+      <c r="C419" s="6" t="n"/>
+      <c r="D419" s="6" t="n"/>
+      <c r="E419" s="5" t="n"/>
+      <c r="F419" s="5" t="n"/>
+      <c r="G419" s="6" t="n"/>
+    </row>
+    <row r="420" hidden="1" outlineLevel="2">
+      <c r="A420" s="4" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="B420" s="5" t="n"/>
+      <c r="C420" s="6" t="n"/>
+      <c r="D420" s="6" t="n"/>
+      <c r="E420" s="5" t="n"/>
+      <c r="F420" s="5" t="n"/>
+      <c r="G420" s="6" t="n"/>
+    </row>
+    <row r="421" hidden="1" outlineLevel="2">
+      <c r="A421" s="4" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="B421" s="5" t="n"/>
+      <c r="C421" s="6" t="n"/>
+      <c r="D421" s="6" t="n"/>
+      <c r="E421" s="5" t="n"/>
+      <c r="F421" s="5" t="n"/>
+      <c r="G421" s="6" t="n"/>
+    </row>
+    <row r="422" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A422" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="B422" s="5" t="n"/>
+      <c r="C422" s="6" t="n"/>
+      <c r="D422" s="6" t="n"/>
+      <c r="E422" s="5" t="n"/>
+      <c r="F422" s="5" t="n"/>
+      <c r="G422" s="6" t="n"/>
+    </row>
+    <row r="423" hidden="1" outlineLevel="2">
+      <c r="A423" s="4" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="B423" s="5" t="n"/>
+      <c r="C423" s="6" t="n"/>
+      <c r="D423" s="6" t="n"/>
+      <c r="E423" s="5" t="n"/>
+      <c r="F423" s="5" t="n"/>
+      <c r="G423" s="6" t="n"/>
+    </row>
+    <row r="424" hidden="1" outlineLevel="2">
+      <c r="A424" s="4" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="B424" s="5" t="n"/>
+      <c r="C424" s="6" t="n"/>
+      <c r="D424" s="6" t="n"/>
+      <c r="E424" s="5" t="n"/>
+      <c r="F424" s="5" t="n"/>
+      <c r="G424" s="6" t="n"/>
+    </row>
+    <row r="425" hidden="1" outlineLevel="2">
+      <c r="A425" s="4" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="B425" s="5" t="n"/>
+      <c r="C425" s="6" t="n"/>
+      <c r="D425" s="6" t="n"/>
+      <c r="E425" s="5" t="n"/>
+      <c r="F425" s="5" t="n"/>
+      <c r="G425" s="6" t="n"/>
+    </row>
+    <row r="426" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A426" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="B426" s="5" t="n"/>
+      <c r="C426" s="6" t="n"/>
+      <c r="D426" s="6" t="n"/>
+      <c r="E426" s="5" t="n"/>
+      <c r="F426" s="5" t="n"/>
+      <c r="G426" s="6" t="n"/>
+    </row>
+    <row r="427" hidden="1" outlineLevel="2">
+      <c r="A427" s="4" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="B427" s="5" t="n"/>
+      <c r="C427" s="6" t="n"/>
+      <c r="D427" s="6" t="n"/>
+      <c r="E427" s="5" t="n"/>
+      <c r="F427" s="5" t="n"/>
+      <c r="G427" s="6" t="n"/>
+    </row>
+    <row r="428" hidden="1" outlineLevel="2">
+      <c r="A428" s="4" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="B428" s="5" t="n"/>
+      <c r="C428" s="6" t="n"/>
+      <c r="D428" s="6" t="n"/>
+      <c r="E428" s="5" t="n"/>
+      <c r="F428" s="5" t="n"/>
+      <c r="G428" s="6" t="n"/>
+    </row>
+    <row r="429" hidden="1" outlineLevel="2">
+      <c r="A429" s="4" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="B429" s="5" t="n"/>
+      <c r="C429" s="6" t="n"/>
+      <c r="D429" s="6" t="n"/>
+      <c r="E429" s="5" t="n"/>
+      <c r="F429" s="5" t="n"/>
+      <c r="G429" s="6" t="n"/>
+    </row>
+    <row r="430" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A430" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="B430" s="5" t="n"/>
+      <c r="C430" s="6" t="n"/>
+      <c r="D430" s="6" t="n"/>
+      <c r="E430" s="5" t="n"/>
+      <c r="F430" s="5" t="n"/>
+      <c r="G430" s="6" t="n"/>
+    </row>
+    <row r="431" hidden="1" outlineLevel="2">
+      <c r="A431" s="4" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="B431" s="5" t="n"/>
+      <c r="C431" s="6" t="n"/>
+      <c r="D431" s="6" t="n"/>
+      <c r="E431" s="5" t="n"/>
+      <c r="F431" s="5" t="n"/>
+      <c r="G431" s="6" t="n"/>
+    </row>
+    <row r="432" hidden="1" outlineLevel="2">
+      <c r="A432" s="4" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="B432" s="5" t="n"/>
+      <c r="C432" s="6" t="n"/>
+      <c r="D432" s="6" t="n"/>
+      <c r="E432" s="5" t="n"/>
+      <c r="F432" s="5" t="n"/>
+      <c r="G432" s="6" t="n"/>
+    </row>
+    <row r="433" hidden="1" outlineLevel="2">
+      <c r="A433" s="4" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="B433" s="5" t="n"/>
+      <c r="C433" s="6" t="n"/>
+      <c r="D433" s="6" t="n"/>
+      <c r="E433" s="5" t="n"/>
+      <c r="F433" s="5" t="n"/>
+      <c r="G433" s="6" t="n"/>
+    </row>
+    <row r="434" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A434" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="B434" s="5" t="n"/>
+      <c r="C434" s="6" t="n"/>
+      <c r="D434" s="6" t="n"/>
+      <c r="E434" s="5" t="n"/>
+      <c r="F434" s="5" t="n"/>
+      <c r="G434" s="6" t="n"/>
+    </row>
+    <row r="435" hidden="1" outlineLevel="2">
+      <c r="A435" s="4" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="B435" s="5" t="n"/>
+      <c r="C435" s="6" t="n"/>
+      <c r="D435" s="6" t="n"/>
+      <c r="E435" s="5" t="n"/>
+      <c r="F435" s="5" t="n"/>
+      <c r="G435" s="6" t="n"/>
+    </row>
+    <row r="436" hidden="1" outlineLevel="2">
+      <c r="A436" s="4" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="B436" s="5" t="n"/>
+      <c r="C436" s="6" t="n"/>
+      <c r="D436" s="6" t="n"/>
+      <c r="E436" s="5" t="n"/>
+      <c r="F436" s="5" t="n"/>
+      <c r="G436" s="6" t="n"/>
+    </row>
+    <row r="437" hidden="1" outlineLevel="2">
+      <c r="A437" s="4" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="B437" s="5" t="n"/>
+      <c r="C437" s="6" t="n"/>
+      <c r="D437" s="6" t="n"/>
+      <c r="E437" s="5" t="n"/>
+      <c r="F437" s="5" t="n"/>
+      <c r="G437" s="6" t="n"/>
+    </row>
+    <row r="438" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A438" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="B438" s="5" t="n"/>
+      <c r="C438" s="6" t="n"/>
+      <c r="D438" s="6" t="n"/>
+      <c r="E438" s="5" t="n"/>
+      <c r="F438" s="5" t="n"/>
+      <c r="G438" s="6" t="n"/>
+    </row>
+    <row r="439" hidden="1" outlineLevel="2">
+      <c r="A439" s="4" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="B439" s="5" t="n"/>
+      <c r="C439" s="6" t="n"/>
+      <c r="D439" s="6" t="n"/>
+      <c r="E439" s="5" t="n"/>
+      <c r="F439" s="5" t="n"/>
+      <c r="G439" s="6" t="n"/>
+    </row>
+    <row r="440" hidden="1" outlineLevel="2">
+      <c r="A440" s="4" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="B440" s="5" t="n"/>
+      <c r="C440" s="6" t="n"/>
+      <c r="D440" s="6" t="n"/>
+      <c r="E440" s="5" t="n"/>
+      <c r="F440" s="5" t="n"/>
+      <c r="G440" s="6" t="n"/>
+    </row>
+    <row r="441" hidden="1" outlineLevel="2">
+      <c r="A441" s="4" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="B441" s="5" t="n"/>
+      <c r="C441" s="6" t="n"/>
+      <c r="D441" s="6" t="n"/>
+      <c r="E441" s="5" t="n"/>
+      <c r="F441" s="5" t="n"/>
+      <c r="G441" s="6" t="n"/>
+    </row>
+    <row r="442" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A442" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="B442" s="5" t="n"/>
+      <c r="C442" s="6" t="n"/>
+      <c r="D442" s="6" t="n"/>
+      <c r="E442" s="5" t="n"/>
+      <c r="F442" s="5" t="n"/>
+      <c r="G442" s="6" t="n"/>
+    </row>
+    <row r="443" hidden="1" outlineLevel="2">
+      <c r="A443" s="4" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="B443" s="5" t="n"/>
+      <c r="C443" s="6" t="n"/>
+      <c r="D443" s="6" t="n"/>
+      <c r="E443" s="5" t="n"/>
+      <c r="F443" s="5" t="n"/>
+      <c r="G443" s="6" t="n"/>
+    </row>
+    <row r="444" hidden="1" outlineLevel="2">
+      <c r="A444" s="4" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="B444" s="5" t="n"/>
+      <c r="C444" s="6" t="n"/>
+      <c r="D444" s="6" t="n"/>
+      <c r="E444" s="5" t="n"/>
+      <c r="F444" s="5" t="n"/>
+      <c r="G444" s="6" t="n"/>
+    </row>
+    <row r="445" hidden="1" outlineLevel="2">
+      <c r="A445" s="4" t="n">
+        <v>110.75</v>
+      </c>
+      <c r="B445" s="5" t="n"/>
+      <c r="C445" s="6" t="n"/>
+      <c r="D445" s="6" t="n"/>
+      <c r="E445" s="5" t="n"/>
+      <c r="F445" s="5" t="n"/>
+      <c r="G445" s="6" t="n"/>
+    </row>
+    <row r="446" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A446" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="B446" s="5" t="n"/>
+      <c r="C446" s="6" t="n"/>
+      <c r="D446" s="6" t="n"/>
+      <c r="E446" s="5" t="n"/>
+      <c r="F446" s="5" t="n"/>
+      <c r="G446" s="6" t="n"/>
+    </row>
+    <row r="447" hidden="1" outlineLevel="2">
+      <c r="A447" s="4" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="B447" s="5" t="n"/>
+      <c r="C447" s="6" t="n"/>
+      <c r="D447" s="6" t="n"/>
+      <c r="E447" s="5" t="n"/>
+      <c r="F447" s="5" t="n"/>
+      <c r="G447" s="6" t="n"/>
+    </row>
+    <row r="448" hidden="1" outlineLevel="2">
+      <c r="A448" s="4" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="B448" s="5" t="n"/>
+      <c r="C448" s="6" t="n"/>
+      <c r="D448" s="6" t="n"/>
+      <c r="E448" s="5" t="n"/>
+      <c r="F448" s="5" t="n"/>
+      <c r="G448" s="6" t="n"/>
+    </row>
+    <row r="449" hidden="1" outlineLevel="2">
+      <c r="A449" s="4" t="n">
+        <v>111.75</v>
+      </c>
+      <c r="B449" s="5" t="n"/>
+      <c r="C449" s="6" t="n"/>
+      <c r="D449" s="6" t="n"/>
+      <c r="E449" s="5" t="n"/>
+      <c r="F449" s="5" t="n"/>
+      <c r="G449" s="6" t="n"/>
+    </row>
+    <row r="450" collapsed="1">
+      <c r="A450" s="4" t="n">
         <v>112</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B450" s="5" t="inlineStr">
         <is>
           <t>chorus 1b</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C450" s="6" t="inlineStr">
         <is>
           <t>generierter Code (eingefroren, ohne show.yaml):
 chorus 4b (ab 3:38.115): setColorScheme(SCHEME_SUNSET); scene(SCENE_PINGPONG, 7869, 110, 122);</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5">
+      <c r="D450" s="6" t="n"/>
+      <c r="E450" s="5" t="n"/>
+      <c r="F450" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G450" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(7870, 4, 110)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="n">
+    <row r="451" hidden="1" outlineLevel="2">
+      <c r="A451" s="4" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="B451" s="5" t="n"/>
+      <c r="C451" s="6" t="n"/>
+      <c r="D451" s="6" t="n"/>
+      <c r="E451" s="5" t="n"/>
+      <c r="F451" s="5" t="n"/>
+      <c r="G451" s="6" t="n"/>
+    </row>
+    <row r="452" hidden="1" outlineLevel="2">
+      <c r="A452" s="4" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="B452" s="5" t="n"/>
+      <c r="C452" s="6" t="n"/>
+      <c r="D452" s="6" t="n"/>
+      <c r="E452" s="5" t="n"/>
+      <c r="F452" s="5" t="n"/>
+      <c r="G452" s="6" t="n"/>
+    </row>
+    <row r="453" hidden="1" outlineLevel="2">
+      <c r="A453" s="4" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="B453" s="5" t="n"/>
+      <c r="C453" s="6" t="n"/>
+      <c r="D453" s="6" t="n"/>
+      <c r="E453" s="5" t="n"/>
+      <c r="F453" s="5" t="n"/>
+      <c r="G453" s="6" t="n"/>
+    </row>
+    <row r="454" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A454" s="4" t="n">
+        <v>113</v>
+      </c>
+      <c r="B454" s="5" t="n"/>
+      <c r="C454" s="6" t="n"/>
+      <c r="D454" s="6" t="n"/>
+      <c r="E454" s="5" t="n"/>
+      <c r="F454" s="5" t="n"/>
+      <c r="G454" s="6" t="n"/>
+    </row>
+    <row r="455" hidden="1" outlineLevel="2">
+      <c r="A455" s="4" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="B455" s="5" t="n"/>
+      <c r="C455" s="6" t="n"/>
+      <c r="D455" s="6" t="n"/>
+      <c r="E455" s="5" t="n"/>
+      <c r="F455" s="5" t="n"/>
+      <c r="G455" s="6" t="n"/>
+    </row>
+    <row r="456" hidden="1" outlineLevel="2">
+      <c r="A456" s="4" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="B456" s="5" t="n"/>
+      <c r="C456" s="6" t="n"/>
+      <c r="D456" s="6" t="n"/>
+      <c r="E456" s="5" t="n"/>
+      <c r="F456" s="5" t="n"/>
+      <c r="G456" s="6" t="n"/>
+    </row>
+    <row r="457" hidden="1" outlineLevel="2">
+      <c r="A457" s="4" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="B457" s="5" t="n"/>
+      <c r="C457" s="6" t="n"/>
+      <c r="D457" s="6" t="n"/>
+      <c r="E457" s="5" t="n"/>
+      <c r="F457" s="5" t="n"/>
+      <c r="G457" s="6" t="n"/>
+    </row>
+    <row r="458" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A458" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="B458" s="5" t="n"/>
+      <c r="C458" s="6" t="n"/>
+      <c r="D458" s="6" t="n"/>
+      <c r="E458" s="5" t="n"/>
+      <c r="F458" s="5" t="n"/>
+      <c r="G458" s="6" t="n"/>
+    </row>
+    <row r="459" hidden="1" outlineLevel="2">
+      <c r="A459" s="4" t="n">
+        <v>114.25</v>
+      </c>
+      <c r="B459" s="5" t="n"/>
+      <c r="C459" s="6" t="n"/>
+      <c r="D459" s="6" t="n"/>
+      <c r="E459" s="5" t="n"/>
+      <c r="F459" s="5" t="n"/>
+      <c r="G459" s="6" t="n"/>
+    </row>
+    <row r="460" hidden="1" outlineLevel="2">
+      <c r="A460" s="4" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="B460" s="5" t="n"/>
+      <c r="C460" s="6" t="n"/>
+      <c r="D460" s="6" t="n"/>
+      <c r="E460" s="5" t="n"/>
+      <c r="F460" s="5" t="n"/>
+      <c r="G460" s="6" t="n"/>
+    </row>
+    <row r="461" hidden="1" outlineLevel="2">
+      <c r="A461" s="4" t="n">
+        <v>114.75</v>
+      </c>
+      <c r="B461" s="5" t="n"/>
+      <c r="C461" s="6" t="n"/>
+      <c r="D461" s="6" t="n"/>
+      <c r="E461" s="5" t="n"/>
+      <c r="F461" s="5" t="n"/>
+      <c r="G461" s="6" t="n"/>
+    </row>
+    <row r="462" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A462" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="B462" s="5" t="n"/>
+      <c r="C462" s="6" t="n"/>
+      <c r="D462" s="6" t="n"/>
+      <c r="E462" s="5" t="n"/>
+      <c r="F462" s="5" t="n"/>
+      <c r="G462" s="6" t="n"/>
+    </row>
+    <row r="463" hidden="1" outlineLevel="2">
+      <c r="A463" s="4" t="n">
+        <v>115.25</v>
+      </c>
+      <c r="B463" s="5" t="n"/>
+      <c r="C463" s="6" t="n"/>
+      <c r="D463" s="6" t="n"/>
+      <c r="E463" s="5" t="n"/>
+      <c r="F463" s="5" t="n"/>
+      <c r="G463" s="6" t="n"/>
+    </row>
+    <row r="464" hidden="1" outlineLevel="2">
+      <c r="A464" s="4" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="B464" s="5" t="n"/>
+      <c r="C464" s="6" t="n"/>
+      <c r="D464" s="6" t="n"/>
+      <c r="E464" s="5" t="n"/>
+      <c r="F464" s="5" t="n"/>
+      <c r="G464" s="6" t="n"/>
+    </row>
+    <row r="465" hidden="1" outlineLevel="2">
+      <c r="A465" s="4" t="n">
+        <v>115.75</v>
+      </c>
+      <c r="B465" s="5" t="n"/>
+      <c r="C465" s="6" t="n"/>
+      <c r="D465" s="6" t="n"/>
+      <c r="E465" s="5" t="n"/>
+      <c r="F465" s="5" t="n"/>
+      <c r="G465" s="6" t="n"/>
+    </row>
+    <row r="466" collapsed="1">
+      <c r="A466" s="4" t="n">
         <v>116</v>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B466" s="5" t="inlineStr">
         <is>
           <t>i keep dancing</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C466" s="6" t="inlineStr">
         <is>
           <t>generierter Code (eingefroren, ohne show.yaml):
 hook 4 (ab 3:45.984): setColorScheme(SCHEME_SUNSET); scene(SCENE_WAVE_LR, 7868, 115, 122);</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5">
+      <c r="D466" s="6" t="n"/>
+      <c r="E466" s="5" t="n"/>
+      <c r="F466" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G466" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(7865, 490, 115, 5, 26, 5, true, 3)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
+    <row r="467" hidden="1" outlineLevel="2">
+      <c r="A467" s="4" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="B467" s="5" t="n"/>
+      <c r="C467" s="6" t="n"/>
+      <c r="D467" s="6" t="n"/>
+      <c r="E467" s="5" t="n"/>
+      <c r="F467" s="5" t="n"/>
+      <c r="G467" s="6" t="n"/>
+    </row>
+    <row r="468" hidden="1" outlineLevel="2">
+      <c r="A468" s="4" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="B468" s="5" t="n"/>
+      <c r="C468" s="6" t="n"/>
+      <c r="D468" s="6" t="n"/>
+      <c r="E468" s="5" t="n"/>
+      <c r="F468" s="5" t="n"/>
+      <c r="G468" s="6" t="n"/>
+    </row>
+    <row r="469" hidden="1" outlineLevel="2">
+      <c r="A469" s="4" t="n">
+        <v>116.75</v>
+      </c>
+      <c r="B469" s="5" t="n"/>
+      <c r="C469" s="6" t="n"/>
+      <c r="D469" s="6" t="n"/>
+      <c r="E469" s="5" t="n"/>
+      <c r="F469" s="5" t="n"/>
+      <c r="G469" s="6" t="n"/>
+    </row>
+    <row r="470" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A470" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="B470" s="5" t="n"/>
+      <c r="C470" s="6" t="n"/>
+      <c r="D470" s="6" t="n"/>
+      <c r="E470" s="5" t="n"/>
+      <c r="F470" s="5" t="n"/>
+      <c r="G470" s="6" t="n"/>
+    </row>
+    <row r="471" hidden="1" outlineLevel="2">
+      <c r="A471" s="4" t="n">
+        <v>117.25</v>
+      </c>
+      <c r="B471" s="5" t="n"/>
+      <c r="C471" s="6" t="n"/>
+      <c r="D471" s="6" t="n"/>
+      <c r="E471" s="5" t="n"/>
+      <c r="F471" s="5" t="n"/>
+      <c r="G471" s="6" t="n"/>
+    </row>
+    <row r="472" hidden="1" outlineLevel="2">
+      <c r="A472" s="4" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="B472" s="5" t="n"/>
+      <c r="C472" s="6" t="n"/>
+      <c r="D472" s="6" t="n"/>
+      <c r="E472" s="5" t="n"/>
+      <c r="F472" s="5" t="n"/>
+      <c r="G472" s="6" t="n"/>
+    </row>
+    <row r="473" hidden="1" outlineLevel="2">
+      <c r="A473" s="4" t="n">
+        <v>117.75</v>
+      </c>
+      <c r="B473" s="5" t="n"/>
+      <c r="C473" s="6" t="n"/>
+      <c r="D473" s="6" t="n"/>
+      <c r="E473" s="5" t="n"/>
+      <c r="F473" s="5" t="n"/>
+      <c r="G473" s="6" t="n"/>
+    </row>
+    <row r="474" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A474" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="B474" s="5" t="n"/>
+      <c r="C474" s="6" t="n"/>
+      <c r="D474" s="6" t="n"/>
+      <c r="E474" s="5" t="n"/>
+      <c r="F474" s="5" t="n"/>
+      <c r="G474" s="6" t="n"/>
+    </row>
+    <row r="475" hidden="1" outlineLevel="2">
+      <c r="A475" s="4" t="n">
+        <v>118.25</v>
+      </c>
+      <c r="B475" s="5" t="n"/>
+      <c r="C475" s="6" t="n"/>
+      <c r="D475" s="6" t="n"/>
+      <c r="E475" s="5" t="n"/>
+      <c r="F475" s="5" t="n"/>
+      <c r="G475" s="6" t="n"/>
+    </row>
+    <row r="476" hidden="1" outlineLevel="2">
+      <c r="A476" s="4" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="B476" s="5" t="n"/>
+      <c r="C476" s="6" t="n"/>
+      <c r="D476" s="6" t="n"/>
+      <c r="E476" s="5" t="n"/>
+      <c r="F476" s="5" t="n"/>
+      <c r="G476" s="6" t="n"/>
+    </row>
+    <row r="477" hidden="1" outlineLevel="2">
+      <c r="A477" s="4" t="n">
+        <v>118.75</v>
+      </c>
+      <c r="B477" s="5" t="n"/>
+      <c r="C477" s="6" t="n"/>
+      <c r="D477" s="6" t="n"/>
+      <c r="E477" s="5" t="n"/>
+      <c r="F477" s="5" t="n"/>
+      <c r="G477" s="6" t="n"/>
+    </row>
+    <row r="478" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A478" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="B478" s="5" t="n"/>
+      <c r="C478" s="6" t="n"/>
+      <c r="D478" s="6" t="n"/>
+      <c r="E478" s="5" t="n"/>
+      <c r="F478" s="5" t="n"/>
+      <c r="G478" s="6" t="n"/>
+    </row>
+    <row r="479" hidden="1" outlineLevel="2">
+      <c r="A479" s="4" t="n">
+        <v>119.25</v>
+      </c>
+      <c r="B479" s="5" t="n"/>
+      <c r="C479" s="6" t="n"/>
+      <c r="D479" s="6" t="n"/>
+      <c r="E479" s="5" t="n"/>
+      <c r="F479" s="5" t="n"/>
+      <c r="G479" s="6" t="n"/>
+    </row>
+    <row r="480" hidden="1" outlineLevel="2">
+      <c r="A480" s="4" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="B480" s="5" t="n"/>
+      <c r="C480" s="6" t="n"/>
+      <c r="D480" s="6" t="n"/>
+      <c r="E480" s="5" t="n"/>
+      <c r="F480" s="5" t="n"/>
+      <c r="G480" s="6" t="n"/>
+    </row>
+    <row r="481" hidden="1" outlineLevel="2">
+      <c r="A481" s="4" t="n">
+        <v>119.75</v>
+      </c>
+      <c r="B481" s="5" t="n"/>
+      <c r="C481" s="6" t="n"/>
+      <c r="D481" s="6" t="n"/>
+      <c r="E481" s="5" t="n"/>
+      <c r="F481" s="5" t="n"/>
+      <c r="G481" s="6" t="n"/>
+    </row>
+    <row r="482" collapsed="1">
+      <c r="A482" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B482" s="5" t="inlineStr">
         <is>
           <t>i keep dancing</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C482" s="6" t="inlineStr">
         <is>
           <t>generierter Code (eingefroren, ohne show.yaml):
 hook 5 (ab 3:53.852): setColorScheme(SCHEME_FIRE); scene(SCENE_FIRE, 13771, 120, 122);
@@ -1182,91 +6165,850 @@
 hook 5 (tail) (ab 4:07.623): setColorScheme(SCHEME_FIRE); progStrobo(1967, 125, 65, CRGB::White);</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5">
+      <c r="D482" s="6" t="n"/>
+      <c r="E482" s="5" t="n"/>
+      <c r="F482" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G482" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(15740, 8, 120)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="n">
+    <row r="483" hidden="1" outlineLevel="2">
+      <c r="A483" s="4" t="n">
+        <v>120.25</v>
+      </c>
+      <c r="B483" s="5" t="n"/>
+      <c r="C483" s="6" t="n"/>
+      <c r="D483" s="6" t="n"/>
+      <c r="E483" s="5" t="n"/>
+      <c r="F483" s="5" t="n"/>
+      <c r="G483" s="6" t="n"/>
+    </row>
+    <row r="484" hidden="1" outlineLevel="2">
+      <c r="A484" s="4" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="B484" s="5" t="n"/>
+      <c r="C484" s="6" t="n"/>
+      <c r="D484" s="6" t="n"/>
+      <c r="E484" s="5" t="n"/>
+      <c r="F484" s="5" t="n"/>
+      <c r="G484" s="6" t="n"/>
+    </row>
+    <row r="485" hidden="1" outlineLevel="2">
+      <c r="A485" s="4" t="n">
+        <v>120.75</v>
+      </c>
+      <c r="B485" s="5" t="n"/>
+      <c r="C485" s="6" t="n"/>
+      <c r="D485" s="6" t="n"/>
+      <c r="E485" s="5" t="n"/>
+      <c r="F485" s="5" t="n"/>
+      <c r="G485" s="6" t="n"/>
+    </row>
+    <row r="486" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A486" s="4" t="n">
+        <v>121</v>
+      </c>
+      <c r="B486" s="5" t="n"/>
+      <c r="C486" s="6" t="n"/>
+      <c r="D486" s="6" t="n"/>
+      <c r="E486" s="5" t="n"/>
+      <c r="F486" s="5" t="n"/>
+      <c r="G486" s="6" t="n"/>
+    </row>
+    <row r="487" hidden="1" outlineLevel="2">
+      <c r="A487" s="4" t="n">
+        <v>121.25</v>
+      </c>
+      <c r="B487" s="5" t="n"/>
+      <c r="C487" s="6" t="n"/>
+      <c r="D487" s="6" t="n"/>
+      <c r="E487" s="5" t="n"/>
+      <c r="F487" s="5" t="n"/>
+      <c r="G487" s="6" t="n"/>
+    </row>
+    <row r="488" hidden="1" outlineLevel="2">
+      <c r="A488" s="4" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="B488" s="5" t="n"/>
+      <c r="C488" s="6" t="n"/>
+      <c r="D488" s="6" t="n"/>
+      <c r="E488" s="5" t="n"/>
+      <c r="F488" s="5" t="n"/>
+      <c r="G488" s="6" t="n"/>
+    </row>
+    <row r="489" hidden="1" outlineLevel="2">
+      <c r="A489" s="4" t="n">
+        <v>121.75</v>
+      </c>
+      <c r="B489" s="5" t="n"/>
+      <c r="C489" s="6" t="n"/>
+      <c r="D489" s="6" t="n"/>
+      <c r="E489" s="5" t="n"/>
+      <c r="F489" s="5" t="n"/>
+      <c r="G489" s="6" t="n"/>
+    </row>
+    <row r="490" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A490" s="4" t="n">
+        <v>122</v>
+      </c>
+      <c r="B490" s="5" t="n"/>
+      <c r="C490" s="6" t="n"/>
+      <c r="D490" s="6" t="n"/>
+      <c r="E490" s="5" t="n"/>
+      <c r="F490" s="5" t="n"/>
+      <c r="G490" s="6" t="n"/>
+    </row>
+    <row r="491" hidden="1" outlineLevel="2">
+      <c r="A491" s="4" t="n">
+        <v>122.25</v>
+      </c>
+      <c r="B491" s="5" t="n"/>
+      <c r="C491" s="6" t="n"/>
+      <c r="D491" s="6" t="n"/>
+      <c r="E491" s="5" t="n"/>
+      <c r="F491" s="5" t="n"/>
+      <c r="G491" s="6" t="n"/>
+    </row>
+    <row r="492" hidden="1" outlineLevel="2">
+      <c r="A492" s="4" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="B492" s="5" t="n"/>
+      <c r="C492" s="6" t="n"/>
+      <c r="D492" s="6" t="n"/>
+      <c r="E492" s="5" t="n"/>
+      <c r="F492" s="5" t="n"/>
+      <c r="G492" s="6" t="n"/>
+    </row>
+    <row r="493" hidden="1" outlineLevel="2">
+      <c r="A493" s="4" t="n">
+        <v>122.75</v>
+      </c>
+      <c r="B493" s="5" t="n"/>
+      <c r="C493" s="6" t="n"/>
+      <c r="D493" s="6" t="n"/>
+      <c r="E493" s="5" t="n"/>
+      <c r="F493" s="5" t="n"/>
+      <c r="G493" s="6" t="n"/>
+    </row>
+    <row r="494" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A494" s="4" t="n">
+        <v>123</v>
+      </c>
+      <c r="B494" s="5" t="n"/>
+      <c r="C494" s="6" t="n"/>
+      <c r="D494" s="6" t="n"/>
+      <c r="E494" s="5" t="n"/>
+      <c r="F494" s="5" t="n"/>
+      <c r="G494" s="6" t="n"/>
+    </row>
+    <row r="495" hidden="1" outlineLevel="2">
+      <c r="A495" s="4" t="n">
+        <v>123.25</v>
+      </c>
+      <c r="B495" s="5" t="n"/>
+      <c r="C495" s="6" t="n"/>
+      <c r="D495" s="6" t="n"/>
+      <c r="E495" s="5" t="n"/>
+      <c r="F495" s="5" t="n"/>
+      <c r="G495" s="6" t="n"/>
+    </row>
+    <row r="496" hidden="1" outlineLevel="2">
+      <c r="A496" s="4" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="B496" s="5" t="n"/>
+      <c r="C496" s="6" t="n"/>
+      <c r="D496" s="6" t="n"/>
+      <c r="E496" s="5" t="n"/>
+      <c r="F496" s="5" t="n"/>
+      <c r="G496" s="6" t="n"/>
+    </row>
+    <row r="497" hidden="1" outlineLevel="2">
+      <c r="A497" s="4" t="n">
+        <v>123.75</v>
+      </c>
+      <c r="B497" s="5" t="n"/>
+      <c r="C497" s="6" t="n"/>
+      <c r="D497" s="6" t="n"/>
+      <c r="E497" s="5" t="n"/>
+      <c r="F497" s="5" t="n"/>
+      <c r="G497" s="6" t="n"/>
+    </row>
+    <row r="498" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A498" s="4" t="n">
+        <v>124</v>
+      </c>
+      <c r="B498" s="5" t="n"/>
+      <c r="C498" s="6" t="n"/>
+      <c r="D498" s="6" t="n"/>
+      <c r="E498" s="5" t="n"/>
+      <c r="F498" s="5" t="n"/>
+      <c r="G498" s="6" t="n"/>
+    </row>
+    <row r="499" hidden="1" outlineLevel="2">
+      <c r="A499" s="4" t="n">
+        <v>124.25</v>
+      </c>
+      <c r="B499" s="5" t="n"/>
+      <c r="C499" s="6" t="n"/>
+      <c r="D499" s="6" t="n"/>
+      <c r="E499" s="5" t="n"/>
+      <c r="F499" s="5" t="n"/>
+      <c r="G499" s="6" t="n"/>
+    </row>
+    <row r="500" hidden="1" outlineLevel="2">
+      <c r="A500" s="4" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="B500" s="5" t="n"/>
+      <c r="C500" s="6" t="n"/>
+      <c r="D500" s="6" t="n"/>
+      <c r="E500" s="5" t="n"/>
+      <c r="F500" s="5" t="n"/>
+      <c r="G500" s="6" t="n"/>
+    </row>
+    <row r="501" hidden="1" outlineLevel="2">
+      <c r="A501" s="4" t="n">
+        <v>124.75</v>
+      </c>
+      <c r="B501" s="5" t="n"/>
+      <c r="C501" s="6" t="n"/>
+      <c r="D501" s="6" t="n"/>
+      <c r="E501" s="5" t="n"/>
+      <c r="F501" s="5" t="n"/>
+      <c r="G501" s="6" t="n"/>
+    </row>
+    <row r="502" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A502" s="4" t="n">
+        <v>125</v>
+      </c>
+      <c r="B502" s="5" t="n"/>
+      <c r="C502" s="6" t="n"/>
+      <c r="D502" s="6" t="n"/>
+      <c r="E502" s="5" t="n"/>
+      <c r="F502" s="5" t="n"/>
+      <c r="G502" s="6" t="n"/>
+    </row>
+    <row r="503" hidden="1" outlineLevel="2">
+      <c r="A503" s="4" t="n">
+        <v>125.25</v>
+      </c>
+      <c r="B503" s="5" t="n"/>
+      <c r="C503" s="6" t="n"/>
+      <c r="D503" s="6" t="n"/>
+      <c r="E503" s="5" t="n"/>
+      <c r="F503" s="5" t="n"/>
+      <c r="G503" s="6" t="n"/>
+    </row>
+    <row r="504" hidden="1" outlineLevel="2">
+      <c r="A504" s="4" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="B504" s="5" t="n"/>
+      <c r="C504" s="6" t="n"/>
+      <c r="D504" s="6" t="n"/>
+      <c r="E504" s="5" t="n"/>
+      <c r="F504" s="5" t="n"/>
+      <c r="G504" s="6" t="n"/>
+    </row>
+    <row r="505" hidden="1" outlineLevel="2">
+      <c r="A505" s="4" t="n">
+        <v>125.75</v>
+      </c>
+      <c r="B505" s="5" t="n"/>
+      <c r="C505" s="6" t="n"/>
+      <c r="D505" s="6" t="n"/>
+      <c r="E505" s="5" t="n"/>
+      <c r="F505" s="5" t="n"/>
+      <c r="G505" s="6" t="n"/>
+    </row>
+    <row r="506" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A506" s="4" t="n">
+        <v>126</v>
+      </c>
+      <c r="B506" s="5" t="n"/>
+      <c r="C506" s="6" t="n"/>
+      <c r="D506" s="6" t="n"/>
+      <c r="E506" s="5" t="n"/>
+      <c r="F506" s="5" t="n"/>
+      <c r="G506" s="6" t="n"/>
+    </row>
+    <row r="507" hidden="1" outlineLevel="2">
+      <c r="A507" s="4" t="n">
+        <v>126.25</v>
+      </c>
+      <c r="B507" s="5" t="n"/>
+      <c r="C507" s="6" t="n"/>
+      <c r="D507" s="6" t="n"/>
+      <c r="E507" s="5" t="n"/>
+      <c r="F507" s="5" t="n"/>
+      <c r="G507" s="6" t="n"/>
+    </row>
+    <row r="508" hidden="1" outlineLevel="2">
+      <c r="A508" s="4" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="B508" s="5" t="n"/>
+      <c r="C508" s="6" t="n"/>
+      <c r="D508" s="6" t="n"/>
+      <c r="E508" s="5" t="n"/>
+      <c r="F508" s="5" t="n"/>
+      <c r="G508" s="6" t="n"/>
+    </row>
+    <row r="509" hidden="1" outlineLevel="2">
+      <c r="A509" s="4" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="B509" s="5" t="n"/>
+      <c r="C509" s="6" t="n"/>
+      <c r="D509" s="6" t="n"/>
+      <c r="E509" s="5" t="n"/>
+      <c r="F509" s="5" t="n"/>
+      <c r="G509" s="6" t="n"/>
+    </row>
+    <row r="510" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A510" s="4" t="n">
+        <v>127</v>
+      </c>
+      <c r="B510" s="5" t="n"/>
+      <c r="C510" s="6" t="n"/>
+      <c r="D510" s="6" t="n"/>
+      <c r="E510" s="5" t="n"/>
+      <c r="F510" s="5" t="n"/>
+      <c r="G510" s="6" t="n"/>
+    </row>
+    <row r="511" hidden="1" outlineLevel="2">
+      <c r="A511" s="4" t="n">
+        <v>127.25</v>
+      </c>
+      <c r="B511" s="5" t="n"/>
+      <c r="C511" s="6" t="n"/>
+      <c r="D511" s="6" t="n"/>
+      <c r="E511" s="5" t="n"/>
+      <c r="F511" s="5" t="n"/>
+      <c r="G511" s="6" t="n"/>
+    </row>
+    <row r="512" hidden="1" outlineLevel="2">
+      <c r="A512" s="4" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="B512" s="5" t="n"/>
+      <c r="C512" s="6" t="n"/>
+      <c r="D512" s="6" t="n"/>
+      <c r="E512" s="5" t="n"/>
+      <c r="F512" s="5" t="n"/>
+      <c r="G512" s="6" t="n"/>
+    </row>
+    <row r="513" hidden="1" outlineLevel="2">
+      <c r="A513" s="4" t="n">
+        <v>127.75</v>
+      </c>
+      <c r="B513" s="5" t="n"/>
+      <c r="C513" s="6" t="n"/>
+      <c r="D513" s="6" t="n"/>
+      <c r="E513" s="5" t="n"/>
+      <c r="F513" s="5" t="n"/>
+      <c r="G513" s="6" t="n"/>
+    </row>
+    <row r="514" collapsed="1">
+      <c r="A514" s="4" t="n">
         <v>128</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B514" s="5" t="inlineStr">
         <is>
           <t>instrumental</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C514" s="6" t="inlineStr">
         <is>
           <t>generierter Code (eingefroren, ohne show.yaml):
 outro (ab 4:09.590): setColorScheme(SCHEME_SUNSET); scene(SCENE_CALM, 15738, 130, 122);
    ausatmen</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5">
+      <c r="D514" s="6" t="n"/>
+      <c r="E514" s="5" t="n"/>
+      <c r="F514" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G514" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(15740, 127, 50, true, true)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="n">
+    <row r="515" hidden="1" outlineLevel="2">
+      <c r="A515" s="4" t="n">
+        <v>128.25</v>
+      </c>
+      <c r="B515" s="5" t="n"/>
+      <c r="C515" s="6" t="n"/>
+      <c r="D515" s="6" t="n"/>
+      <c r="E515" s="5" t="n"/>
+      <c r="F515" s="5" t="n"/>
+      <c r="G515" s="6" t="n"/>
+    </row>
+    <row r="516" hidden="1" outlineLevel="2">
+      <c r="A516" s="4" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="B516" s="5" t="n"/>
+      <c r="C516" s="6" t="n"/>
+      <c r="D516" s="6" t="n"/>
+      <c r="E516" s="5" t="n"/>
+      <c r="F516" s="5" t="n"/>
+      <c r="G516" s="6" t="n"/>
+    </row>
+    <row r="517" hidden="1" outlineLevel="2">
+      <c r="A517" s="4" t="n">
+        <v>128.75</v>
+      </c>
+      <c r="B517" s="5" t="n"/>
+      <c r="C517" s="6" t="n"/>
+      <c r="D517" s="6" t="n"/>
+      <c r="E517" s="5" t="n"/>
+      <c r="F517" s="5" t="n"/>
+      <c r="G517" s="6" t="n"/>
+    </row>
+    <row r="518" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A518" s="4" t="n">
+        <v>129</v>
+      </c>
+      <c r="B518" s="5" t="n"/>
+      <c r="C518" s="6" t="n"/>
+      <c r="D518" s="6" t="n"/>
+      <c r="E518" s="5" t="n"/>
+      <c r="F518" s="5" t="n"/>
+      <c r="G518" s="6" t="n"/>
+    </row>
+    <row r="519" hidden="1" outlineLevel="2">
+      <c r="A519" s="4" t="n">
+        <v>129.25</v>
+      </c>
+      <c r="B519" s="5" t="n"/>
+      <c r="C519" s="6" t="n"/>
+      <c r="D519" s="6" t="n"/>
+      <c r="E519" s="5" t="n"/>
+      <c r="F519" s="5" t="n"/>
+      <c r="G519" s="6" t="n"/>
+    </row>
+    <row r="520" hidden="1" outlineLevel="2">
+      <c r="A520" s="4" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="B520" s="5" t="n"/>
+      <c r="C520" s="6" t="n"/>
+      <c r="D520" s="6" t="n"/>
+      <c r="E520" s="5" t="n"/>
+      <c r="F520" s="5" t="n"/>
+      <c r="G520" s="6" t="n"/>
+    </row>
+    <row r="521" hidden="1" outlineLevel="2">
+      <c r="A521" s="4" t="n">
+        <v>129.75</v>
+      </c>
+      <c r="B521" s="5" t="n"/>
+      <c r="C521" s="6" t="n"/>
+      <c r="D521" s="6" t="n"/>
+      <c r="E521" s="5" t="n"/>
+      <c r="F521" s="5" t="n"/>
+      <c r="G521" s="6" t="n"/>
+    </row>
+    <row r="522" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A522" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="B522" s="5" t="n"/>
+      <c r="C522" s="6" t="n"/>
+      <c r="D522" s="6" t="n"/>
+      <c r="E522" s="5" t="n"/>
+      <c r="F522" s="5" t="n"/>
+      <c r="G522" s="6" t="n"/>
+    </row>
+    <row r="523" hidden="1" outlineLevel="2">
+      <c r="A523" s="4" t="n">
+        <v>130.25</v>
+      </c>
+      <c r="B523" s="5" t="n"/>
+      <c r="C523" s="6" t="n"/>
+      <c r="D523" s="6" t="n"/>
+      <c r="E523" s="5" t="n"/>
+      <c r="F523" s="5" t="n"/>
+      <c r="G523" s="6" t="n"/>
+    </row>
+    <row r="524" hidden="1" outlineLevel="2">
+      <c r="A524" s="4" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="B524" s="5" t="n"/>
+      <c r="C524" s="6" t="n"/>
+      <c r="D524" s="6" t="n"/>
+      <c r="E524" s="5" t="n"/>
+      <c r="F524" s="5" t="n"/>
+      <c r="G524" s="6" t="n"/>
+    </row>
+    <row r="525" hidden="1" outlineLevel="2">
+      <c r="A525" s="4" t="n">
+        <v>130.75</v>
+      </c>
+      <c r="B525" s="5" t="n"/>
+      <c r="C525" s="6" t="n"/>
+      <c r="D525" s="6" t="n"/>
+      <c r="E525" s="5" t="n"/>
+      <c r="F525" s="5" t="n"/>
+      <c r="G525" s="6" t="n"/>
+    </row>
+    <row r="526" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A526" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="B526" s="5" t="n"/>
+      <c r="C526" s="6" t="n"/>
+      <c r="D526" s="6" t="n"/>
+      <c r="E526" s="5" t="n"/>
+      <c r="F526" s="5" t="n"/>
+      <c r="G526" s="6" t="n"/>
+    </row>
+    <row r="527" hidden="1" outlineLevel="2">
+      <c r="A527" s="4" t="n">
+        <v>131.25</v>
+      </c>
+      <c r="B527" s="5" t="n"/>
+      <c r="C527" s="6" t="n"/>
+      <c r="D527" s="6" t="n"/>
+      <c r="E527" s="5" t="n"/>
+      <c r="F527" s="5" t="n"/>
+      <c r="G527" s="6" t="n"/>
+    </row>
+    <row r="528" hidden="1" outlineLevel="2">
+      <c r="A528" s="4" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="B528" s="5" t="n"/>
+      <c r="C528" s="6" t="n"/>
+      <c r="D528" s="6" t="n"/>
+      <c r="E528" s="5" t="n"/>
+      <c r="F528" s="5" t="n"/>
+      <c r="G528" s="6" t="n"/>
+    </row>
+    <row r="529" hidden="1" outlineLevel="2">
+      <c r="A529" s="4" t="n">
+        <v>131.75</v>
+      </c>
+      <c r="B529" s="5" t="n"/>
+      <c r="C529" s="6" t="n"/>
+      <c r="D529" s="6" t="n"/>
+      <c r="E529" s="5" t="n"/>
+      <c r="F529" s="5" t="n"/>
+      <c r="G529" s="6" t="n"/>
+    </row>
+    <row r="530" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A530" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="B530" s="5" t="n"/>
+      <c r="C530" s="6" t="n"/>
+      <c r="D530" s="6" t="n"/>
+      <c r="E530" s="5" t="n"/>
+      <c r="F530" s="5" t="n"/>
+      <c r="G530" s="6" t="n"/>
+    </row>
+    <row r="531" hidden="1" outlineLevel="2">
+      <c r="A531" s="4" t="n">
+        <v>132.25</v>
+      </c>
+      <c r="B531" s="5" t="n"/>
+      <c r="C531" s="6" t="n"/>
+      <c r="D531" s="6" t="n"/>
+      <c r="E531" s="5" t="n"/>
+      <c r="F531" s="5" t="n"/>
+      <c r="G531" s="6" t="n"/>
+    </row>
+    <row r="532" hidden="1" outlineLevel="2">
+      <c r="A532" s="4" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="B532" s="5" t="n"/>
+      <c r="C532" s="6" t="n"/>
+      <c r="D532" s="6" t="n"/>
+      <c r="E532" s="5" t="n"/>
+      <c r="F532" s="5" t="n"/>
+      <c r="G532" s="6" t="n"/>
+    </row>
+    <row r="533" hidden="1" outlineLevel="2">
+      <c r="A533" s="4" t="n">
+        <v>132.75</v>
+      </c>
+      <c r="B533" s="5" t="n"/>
+      <c r="C533" s="6" t="n"/>
+      <c r="D533" s="6" t="n"/>
+      <c r="E533" s="5" t="n"/>
+      <c r="F533" s="5" t="n"/>
+      <c r="G533" s="6" t="n"/>
+    </row>
+    <row r="534" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A534" s="4" t="n">
+        <v>133</v>
+      </c>
+      <c r="B534" s="5" t="n"/>
+      <c r="C534" s="6" t="n"/>
+      <c r="D534" s="6" t="n"/>
+      <c r="E534" s="5" t="n"/>
+      <c r="F534" s="5" t="n"/>
+      <c r="G534" s="6" t="n"/>
+    </row>
+    <row r="535" hidden="1" outlineLevel="2">
+      <c r="A535" s="4" t="n">
+        <v>133.25</v>
+      </c>
+      <c r="B535" s="5" t="n"/>
+      <c r="C535" s="6" t="n"/>
+      <c r="D535" s="6" t="n"/>
+      <c r="E535" s="5" t="n"/>
+      <c r="F535" s="5" t="n"/>
+      <c r="G535" s="6" t="n"/>
+    </row>
+    <row r="536" hidden="1" outlineLevel="2">
+      <c r="A536" s="4" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="B536" s="5" t="n"/>
+      <c r="C536" s="6" t="n"/>
+      <c r="D536" s="6" t="n"/>
+      <c r="E536" s="5" t="n"/>
+      <c r="F536" s="5" t="n"/>
+      <c r="G536" s="6" t="n"/>
+    </row>
+    <row r="537" hidden="1" outlineLevel="2">
+      <c r="A537" s="4" t="n">
+        <v>133.75</v>
+      </c>
+      <c r="B537" s="5" t="n"/>
+      <c r="C537" s="6" t="n"/>
+      <c r="D537" s="6" t="n"/>
+      <c r="E537" s="5" t="n"/>
+      <c r="F537" s="5" t="n"/>
+      <c r="G537" s="6" t="n"/>
+    </row>
+    <row r="538" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A538" s="4" t="n">
+        <v>134</v>
+      </c>
+      <c r="B538" s="5" t="n"/>
+      <c r="C538" s="6" t="n"/>
+      <c r="D538" s="6" t="n"/>
+      <c r="E538" s="5" t="n"/>
+      <c r="F538" s="5" t="n"/>
+      <c r="G538" s="6" t="n"/>
+    </row>
+    <row r="539" hidden="1" outlineLevel="2">
+      <c r="A539" s="4" t="n">
+        <v>134.25</v>
+      </c>
+      <c r="B539" s="5" t="n"/>
+      <c r="C539" s="6" t="n"/>
+      <c r="D539" s="6" t="n"/>
+      <c r="E539" s="5" t="n"/>
+      <c r="F539" s="5" t="n"/>
+      <c r="G539" s="6" t="n"/>
+    </row>
+    <row r="540" hidden="1" outlineLevel="2">
+      <c r="A540" s="4" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="B540" s="5" t="n"/>
+      <c r="C540" s="6" t="n"/>
+      <c r="D540" s="6" t="n"/>
+      <c r="E540" s="5" t="n"/>
+      <c r="F540" s="5" t="n"/>
+      <c r="G540" s="6" t="n"/>
+    </row>
+    <row r="541" hidden="1" outlineLevel="2">
+      <c r="A541" s="4" t="n">
+        <v>134.75</v>
+      </c>
+      <c r="B541" s="5" t="n"/>
+      <c r="C541" s="6" t="n"/>
+      <c r="D541" s="6" t="n"/>
+      <c r="E541" s="5" t="n"/>
+      <c r="F541" s="5" t="n"/>
+      <c r="G541" s="6" t="n"/>
+    </row>
+    <row r="542" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A542" s="4" t="n">
+        <v>135</v>
+      </c>
+      <c r="B542" s="5" t="n"/>
+      <c r="C542" s="6" t="n"/>
+      <c r="D542" s="6" t="n"/>
+      <c r="E542" s="5" t="n"/>
+      <c r="F542" s="5" t="n"/>
+      <c r="G542" s="6" t="n"/>
+    </row>
+    <row r="543" hidden="1" outlineLevel="2">
+      <c r="A543" s="4" t="n">
+        <v>135.25</v>
+      </c>
+      <c r="B543" s="5" t="n"/>
+      <c r="C543" s="6" t="n"/>
+      <c r="D543" s="6" t="n"/>
+      <c r="E543" s="5" t="n"/>
+      <c r="F543" s="5" t="n"/>
+      <c r="G543" s="6" t="n"/>
+    </row>
+    <row r="544" hidden="1" outlineLevel="2">
+      <c r="A544" s="4" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="B544" s="5" t="n"/>
+      <c r="C544" s="6" t="n"/>
+      <c r="D544" s="6" t="n"/>
+      <c r="E544" s="5" t="n"/>
+      <c r="F544" s="5" t="n"/>
+      <c r="G544" s="6" t="n"/>
+    </row>
+    <row r="545" hidden="1" outlineLevel="2">
+      <c r="A545" s="4" t="n">
+        <v>135.75</v>
+      </c>
+      <c r="B545" s="5" t="n"/>
+      <c r="C545" s="6" t="n"/>
+      <c r="D545" s="6" t="n"/>
+      <c r="E545" s="5" t="n"/>
+      <c r="F545" s="5" t="n"/>
+      <c r="G545" s="6" t="n"/>
+    </row>
+    <row r="546" collapsed="1">
+      <c r="A546" s="4" t="n">
         <v>136</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B546" s="5" t="inlineStr">
         <is>
           <t>outro</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C546" s="6" t="inlineStr">
         <is>
           <t>generierter Code (eingefroren, ohne show.yaml):
 zu dieser Zeit ist der generierte Code schon zu Ende (schwarz, dann Pausen-Loop)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5">
+      <c r="D546" s="6" t="n"/>
+      <c r="E546" s="5" t="n"/>
+      <c r="F546" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G546" s="6" t="inlineStr">
         <is>
           <t>! nur im Excel - der alte Code geht hier schon in Schwarz</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="7" t="n">
+    <row r="547" hidden="1" outlineLevel="2">
+      <c r="A547" s="4" t="n">
+        <v>136.25</v>
+      </c>
+      <c r="B547" s="5" t="n"/>
+      <c r="C547" s="6" t="n"/>
+      <c r="D547" s="6" t="n"/>
+      <c r="E547" s="5" t="n"/>
+      <c r="F547" s="5" t="n"/>
+      <c r="G547" s="6" t="n"/>
+    </row>
+    <row r="548" hidden="1" outlineLevel="2">
+      <c r="A548" s="4" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="B548" s="5" t="n"/>
+      <c r="C548" s="6" t="n"/>
+      <c r="D548" s="6" t="n"/>
+      <c r="E548" s="5" t="n"/>
+      <c r="F548" s="5" t="n"/>
+      <c r="G548" s="6" t="n"/>
+    </row>
+    <row r="549" hidden="1" outlineLevel="2">
+      <c r="A549" s="4" t="n">
+        <v>136.75</v>
+      </c>
+      <c r="B549" s="5" t="n"/>
+      <c r="C549" s="6" t="n"/>
+      <c r="D549" s="6" t="n"/>
+      <c r="E549" s="5" t="n"/>
+      <c r="F549" s="5" t="n"/>
+      <c r="G549" s="6" t="n"/>
+    </row>
+    <row r="550" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A550" s="4" t="n">
+        <v>137</v>
+      </c>
+      <c r="B550" s="5" t="n"/>
+      <c r="C550" s="6" t="n"/>
+      <c r="D550" s="6" t="n"/>
+      <c r="E550" s="5" t="n"/>
+      <c r="F550" s="5" t="n"/>
+      <c r="G550" s="6" t="n"/>
+    </row>
+    <row r="551" hidden="1" outlineLevel="2">
+      <c r="A551" s="4" t="n">
+        <v>137.25</v>
+      </c>
+      <c r="B551" s="5" t="n"/>
+      <c r="C551" s="6" t="n"/>
+      <c r="D551" s="6" t="n"/>
+      <c r="E551" s="5" t="n"/>
+      <c r="F551" s="5" t="n"/>
+      <c r="G551" s="6" t="n"/>
+    </row>
+    <row r="552" hidden="1" outlineLevel="2">
+      <c r="A552" s="4" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="B552" s="5" t="n"/>
+      <c r="C552" s="6" t="n"/>
+      <c r="D552" s="6" t="n"/>
+      <c r="E552" s="5" t="n"/>
+      <c r="F552" s="5" t="n"/>
+      <c r="G552" s="6" t="n"/>
+    </row>
+    <row r="553" hidden="1" outlineLevel="2">
+      <c r="A553" s="4" t="n">
+        <v>137.75</v>
+      </c>
+      <c r="B553" s="5" t="n"/>
+      <c r="C553" s="6" t="n"/>
+      <c r="D553" s="6" t="n"/>
+      <c r="E553" s="5" t="n"/>
+      <c r="F553" s="5" t="n"/>
+      <c r="G553" s="6" t="n"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="7" t="n">
         <v>138</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B554" t="inlineStr">
         <is>
           <t>Ende</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C554" t="inlineStr">
         <is>
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E554" t="n">
         <v>0</v>
       </c>
-      <c r="F32">
+      <c r="F554">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/DancingOnMyOwn_v1/quelle/struktur.xlsx
+++ b/songs/DancingOnMyOwn_v1/quelle/struktur.xlsx
@@ -541,9 +541,8 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-pause (ab 0:00.000): [SCROLLMATRIX] progBlack(2673, 1); [GITBOARD] progScrollText("Dancing On My Own by Robyn", 15984, 90, getRandomColor(), 2); [sonst] progBlack(5656, 5); [SCROLLMATRIX]
-   Start-MIDI: alle Geräte schwarz</t>
+          <t>progBlack(5656, 5), Farben SCHEME_NEON
+Start-MIDI: alle Geräte schwarz</t>
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
@@ -690,9 +689,8 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-bass (ab 0:05.656): setColorScheme(SCHEME_ICE); scene(SCENE_CALM, 15737, 10, 122);
-   nur Synth-Bass, dunkel und kühl anfangen</t>
+          <t>SCENE_CALM, Farben SCHEME_ICE
+nur Synth-Bass: alle Geräte atmen langsam in Blau, dunkel und kühl</t>
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
@@ -1059,9 +1057,8 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-verse 1 (ab 0:21.393): setColorScheme(SCHEME_ICE); scene(SCENE_VERSE, 15738, 15, 122);
-   Gesang setzt ein, Puls auf allen Geräten, noch kalt</t>
+          <t>SCENE_VERSE, Farben SCHEME_ICE
+Gesang setzt ein: Gitarre und Bass leuchten Zone für Zone im Beat, Lampen mit Lichtschuss pro Beat, auf der Matrix farbiger Regen in Blautönen</t>
         </is>
       </c>
       <c r="D50" s="6" t="n"/>
@@ -1428,9 +1425,9 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-verse 1b (ab 0:37.131): setColorScheme(SCHEME_ROYAL); [ANDRESGIT] progSymmetricVU(15738, 20, 122); [GUITAR] progZoneBeat(15738, 20, 122); [sonst] scene(SCENE_VERSE, 15738, 20, 122);
-   Gitarre steigt ein und bekommt ein eigenes VU, Rest bleibt im Verse-Puls</t>
+          <t>SCENE_VERSE, Farben SCHEME_ROYAL
+ANDRESGIT: progSymmetricVU(15738, 20, 122)
+Gitarre steigt ein und bekommt ein eigenes VU, der Rest bleibt im Verse-Puls, Farben Blau/Violett</t>
         </is>
       </c>
       <c r="D82" s="6" t="n"/>
@@ -1797,9 +1794,8 @@
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-pre-chorus (ab 0:52.869): setColorScheme(SCHEME_SUNSET); scene(SCENE_BUILDUP, 7869, 25, 122);
-   lädt sich über 4 Takte auf und entlädt sich genau in den Chorus</t>
+          <t>SCENE_BUILDUP, Farben SCHEME_SUNSET
+Pre-Chorus: lädt sich über 4 Takte in warmen Farben auf und entlädt sich genau auf den Chorus</t>
         </is>
       </c>
       <c r="D114" s="6" t="n"/>
@@ -1990,9 +1986,8 @@
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-chorus 1 (ab 1:00.738): setColorScheme(SCHEME_NEON); scene(SCENE_DROP, 15737, 30, 122);
-   erster Chorus, volle Energie im Beat</t>
+          <t>SCENE_DROP, Farben SCHEME_NEON
+erster Chorus: volle Energie im Beat in Pink, Türkis und Violett</t>
         </is>
       </c>
       <c r="D130" s="6" t="n"/>
@@ -2359,9 +2354,8 @@
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-chorus 1b (ab 1:16.475): scene(SCENE_WAVE_LR, 7869, 35, 122);
-   Bühnenbewegung als Variation</t>
+          <t>SCENE_WAVE_LR, Farben SCHEME_NEON
+Blitz läuft auf jedem Beat von links nach rechts über die Bühne</t>
         </is>
       </c>
       <c r="D162" s="6" t="n"/>
@@ -2552,10 +2546,10 @@
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-hook 1 (ab 1:24.344): scene(SCENE_PINGPONG, 6886, 40, 122);
-   'on my own' springt von Gerät zu Gerät, kurzer Strobo als Absprung in den Stopp
-hook 1 (tail) (ab 1:31.230): progStrobo(983, 45, 75, getRandomCRGB());</t>
+          <t>SCENE_PINGPONG, Farben SCHEME_NEON
+Schluss (2 Beats): SCENE_COLORS, Farben SCHEME_NEON
+   Ausgabe: Tor 4x pro Beat, 50 % hell
+'on my own' springt pro Beat von Gerät zu Gerät; die letzten 2 Beats Strobo im Takt als Absprung in den Stopp</t>
         </is>
       </c>
       <c r="D178" s="6" t="n"/>
@@ -2746,8 +2740,8 @@
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-stop (ab 1:32.213): progBlack(3935, 50);</t>
+          <t>progBlack(3935, 50), Farben SCHEME_NEON
+Stopp: alles dunkel</t>
         </is>
       </c>
       <c r="D194" s="6" t="n"/>
@@ -2850,9 +2844,8 @@
       </c>
       <c r="C202" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-verse 2 (ab 1:36.148): setColorScheme(SCHEME_ROYAL); scene(SCENE_VERSE, 19672, 55, 122);
-   zurück in den Puls, eine Stufe wärmer als Verse 1</t>
+          <t>SCENE_VERSE, Farben SCHEME_ROYAL
+zurück in den Puls, eine Stufe wärmer als Verse 1 (Blau/Violett), auf der Matrix farbiger Regen</t>
         </is>
       </c>
       <c r="D202" s="6" t="n"/>
@@ -3132,9 +3125,8 @@
       </c>
       <c r="C226" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-verse 2 (ab 1:36.148): setColorScheme(SCHEME_ROYAL); scene(SCENE_VERSE, 19672, 55, 122);
-   zurück in den Puls, eine Stufe wärmer als Verse 1</t>
+          <t>SCENE_BUILDUP, Farben SCHEME_SUNSET
+wie der erste Pre-Chorus: lädt sich über 4 Takte in warmen Farben auf und entlädt sich genau auf den Chorus</t>
         </is>
       </c>
       <c r="D226" s="6" t="n"/>
@@ -3321,8 +3313,8 @@
       </c>
       <c r="C242" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-chorus 2 (ab 1:55.820): scene(SCENE_DROP, 15737, 60, 122);</t>
+          <t>SCENE_DROP, Farben SCHEME_NEON
+zweiter Chorus wie der erste: volle Energie im Beat in Neonfarben</t>
         </is>
       </c>
       <c r="D242" s="6" t="n"/>
@@ -3689,9 +3681,8 @@
       </c>
       <c r="C274" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-chorus 2b (ab 2:11.557): scene(SCENE_WAVE_RL, 7869, 65, 122);
-   Welle diesmal andersrum</t>
+          <t>SCENE_WAVE_RL, Farben SCHEME_NEON
+Blitzwelle diesmal von rechts nach links</t>
         </is>
       </c>
       <c r="D274" s="6" t="n"/>
@@ -3882,8 +3873,8 @@
       </c>
       <c r="C290" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-hook 2 (ab 2:19.426): scene(SCENE_PINGPONG, 7869, 70, 122);</t>
+          <t>SCENE_PINGPONG, Farben SCHEME_NEON
+'on my own' springt pro Beat von Gerät zu Gerät</t>
         </is>
       </c>
       <c r="D290" s="6" t="n"/>
@@ -4074,9 +4065,8 @@
       </c>
       <c r="C306" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-instrumental (ab 2:27.295): setColorScheme(SCHEME_RETRO); scene(SCENE_SOLO_GIT, 15738, 75, 122);
-   Gitarre im Spotlight, rot/weiß/blau wie im Original</t>
+          <t>SCENE_SOLO_GIT, Farben SCHEME_RETRO
+Gitarre im Spotlight, rot/weiß/blau wie im Original</t>
         </is>
       </c>
       <c r="D306" s="6" t="n"/>
@@ -4443,9 +4433,9 @@
       </c>
       <c r="C338" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-bridge (ab 2:43.033): setColorScheme(SCHEME_ICE); [MATRIX] matrixMovieFX(15737, 80, 100, 6); [sonst] scene(SCENE_CALM, 15737, 80, 122);
-   alles zieht sich zurück, Matrix-Film wie im Original</t>
+          <t>SCENE_CALM, Farben SCHEME_ICE
+matrix: matrixMovieFX(15737, 85, 100, 6)
+alles zieht sich zurück und atmet in Blau, auf der Matrix ein dünner Matrix-Regen (6 Spuren) wie im Original</t>
         </is>
       </c>
       <c r="D338" s="6" t="n"/>
@@ -4812,9 +4802,8 @@
       </c>
       <c r="C370" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-corner (ab 2:58.770): progBlack(5902, 85);
-   Stille vor dem Finale</t>
+          <t>progBlack(5902, 90), Farben SCHEME_NEON
+Stille vor dem Finale</t>
         </is>
       </c>
       <c r="D370" s="6" t="n"/>
@@ -4961,9 +4950,8 @@
       </c>
       <c r="C382" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-snare roll (ab 3:04.672): setColorScheme(SCHEME_WHITE); scene(SCENE_BUILDUP, 1967, 90, 122);
-   1 Takt Aufladen, Blast genau auf den Einsatz</t>
+          <t>SCENE_BUILDUP, Farben SCHEME_WHITE
+1 Takt weißes Aufladen, die Explosion fällt genau auf den Einsatz</t>
         </is>
       </c>
       <c r="D382" s="6" t="n"/>
@@ -5022,9 +5010,8 @@
       </c>
       <c r="C386" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-chorus 3 (ab 3:06.639): setColorScheme(SCHEME_FIRE); scene(SCENE_FIRE, 7869, 95, 122);
-   Finale beginnt, Farbwechsel auf Feuer</t>
+          <t>SCENE_FIRE, Farben SCHEME_FIRE
+Finale beginnt: Feuer auf allen Geräten</t>
         </is>
       </c>
       <c r="D386" s="6" t="n"/>
@@ -5215,8 +5202,8 @@
       </c>
       <c r="C402" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-hook 3 (ab 3:14.508): setColorScheme(SCHEME_FIRE); scene(SCENE_WAVE_OUT, 7869, 100, 122);</t>
+          <t>SCENE_WAVE_OUT, Farben SCHEME_FIRE
+Blitz läuft pro Beat von der Mitte nach außen, in Feuerfarben</t>
         </is>
       </c>
       <c r="D402" s="6" t="n"/>
@@ -5407,8 +5394,8 @@
       </c>
       <c r="C418" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-chorus 4 (ab 3:22.377): setColorScheme(SCHEME_SUNSET); scene(SCENE_DROP, 15738, 105, 122);</t>
+          <t>SCENE_DROP, Farben SCHEME_SUNSET
+volle Energie im Beat in Orange, Pink, Violett und Gold</t>
         </is>
       </c>
       <c r="D418" s="6" t="n"/>
@@ -5775,8 +5762,8 @@
       </c>
       <c r="C450" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-chorus 4b (ab 3:38.115): setColorScheme(SCHEME_SUNSET); scene(SCENE_PINGPONG, 7869, 110, 122);</t>
+          <t>SCENE_PINGPONG, Farben SCHEME_SUNSET
+Licht springt pro Beat von Gerät zu Gerät, Sonnenuntergangsfarben</t>
         </is>
       </c>
       <c r="D450" s="6" t="n"/>
@@ -5967,8 +5954,8 @@
       </c>
       <c r="C466" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-hook 4 (ab 3:45.984): setColorScheme(SCHEME_SUNSET); scene(SCENE_WAVE_LR, 7868, 115, 122);</t>
+          <t>SCENE_WAVE_LR, Farben SCHEME_SUNSET
+Blitzwelle von links nach rechts, Sonnenuntergangsfarben</t>
         </is>
       </c>
       <c r="D466" s="6" t="n"/>
@@ -6159,10 +6146,10 @@
       </c>
       <c r="C482" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-hook 5 (ab 3:53.852): setColorScheme(SCHEME_FIRE); scene(SCENE_FIRE, 13771, 120, 122);
-   Höhepunkt, letzter Takt weißer Strobo
-hook 5 (tail) (ab 4:07.623): setColorScheme(SCHEME_FIRE); progStrobo(1967, 125, 65, CRGB::White);</t>
+          <t>SCENE_FIRE, Farben SCHEME_FIRE
+Schluss (4 Beats): SCENE_COLORS, Farben SCHEME_WHITE
+   Ausgabe: Tor 4x pro Beat, 50 % hell
+Höhepunkt: Feuer auf allen Geräten, der letzte Takt weißer Strobo im Takt</t>
         </is>
       </c>
       <c r="D482" s="6" t="n"/>
@@ -6529,9 +6516,8 @@
       </c>
       <c r="C514" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-outro (ab 4:09.590): setColorScheme(SCHEME_SUNSET); scene(SCENE_CALM, 15738, 130, 122);
-   ausatmen</t>
+          <t>SCENE_CALM, Farben SCHEME_SUNSET
+ausatmen: alle Geräte atmen langsam in warmen Farben</t>
         </is>
       </c>
       <c r="D514" s="6" t="n"/>
@@ -6898,8 +6884,8 @@
       </c>
       <c r="C546" s="6" t="inlineStr">
         <is>
-          <t>generierter Code (eingefroren, ohne show.yaml):
-zu dieser Zeit ist der generierte Code schon zu Ende (schwarz, dann Pausen-Loop)</t>
+          <t>SCENE_FADEOUT, Farben SCHEME_SUNSET
+die letzten 2 Takte blenden weich nach Schwarz</t>
         </is>
       </c>
       <c r="D546" s="6" t="n"/>

--- a/songs/DancingOnMyOwn_v1/quelle/struktur.xlsx
+++ b/songs/DancingOnMyOwn_v1/quelle/struktur.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>progBlack(5656, 5), Farben SCHEME_NEON
+          <t>progBlack(5656, 3), Farben SCHEME_NEON
 Start-MIDI: alle Geräte schwarz</t>
         </is>
       </c>
@@ -1426,7 +1426,7 @@
       <c r="C82" s="6" t="inlineStr">
         <is>
           <t>SCENE_VERSE, Farben SCHEME_ROYAL
-ANDRESGIT: progSymmetricVU(15738, 20, 122)
+ANDRESGIT: progSymmetricVU(15738, 6, 122)
 Gitarre steigt ein und bekommt ein eigenes VU, der Rest bleibt im Verse-Puls, Farben Blau/Violett</t>
         </is>
       </c>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>progBlack(3935, 50), Farben SCHEME_NEON
+          <t>progBlack(3935, 12), Farben SCHEME_NEON
 Stopp: alles dunkel</t>
         </is>
       </c>
@@ -4434,7 +4434,7 @@
       <c r="C338" s="6" t="inlineStr">
         <is>
           <t>SCENE_CALM, Farben SCHEME_ICE
-matrix: matrixMovieFX(15737, 85, 100, 6)
+matrix: matrixMovieFX(15737, 19, 100, 6)
 alles zieht sich zurück und atmet in Blau, auf der Matrix ein dünner Matrix-Regen (6 Spuren) wie im Original</t>
         </is>
       </c>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="C370" s="6" t="inlineStr">
         <is>
-          <t>progBlack(5902, 90), Farben SCHEME_NEON
+          <t>progBlack(5902, 20), Farben SCHEME_NEON
 Stille vor dem Finale</t>
         </is>
       </c>

--- a/songs/DancingOnMyOwn_v1/quelle/struktur.xlsx
+++ b/songs/DancingOnMyOwn_v1/quelle/struktur.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -39,6 +39,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -54,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -71,6 +77,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,16 +445,17 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G554"/>
+  <dimension ref="A1:H554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,6 +480,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -481,6 +492,7 @@
         <v>122</v>
       </c>
       <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -492,6 +504,7 @@
         <v>0.125</v>
       </c>
       <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -511,20 +524,25 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Alter Effekt (temporär)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Änderungswunsch</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -546,12 +564,13 @@
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>progBlack(5655, 5)</t>
         </is>
@@ -564,9 +583,10 @@
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="5" t="n"/>
+      <c r="E7" s="6" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" hidden="1" outlineLevel="2">
       <c r="A8" s="4" t="n">
@@ -575,9 +595,10 @@
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="n"/>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" hidden="1" outlineLevel="2">
       <c r="A9" s="4" t="n">
@@ -586,9 +607,10 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="n"/>
+      <c r="E9" s="6" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="6" t="n"/>
     </row>
     <row r="10" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A10" s="4" t="n">
@@ -597,9 +619,10 @@
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="n"/>
+      <c r="E10" s="6" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="6" t="n"/>
     </row>
     <row r="11" hidden="1" outlineLevel="2">
       <c r="A11" s="4" t="n">
@@ -608,9 +631,10 @@
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="5" t="n"/>
+      <c r="E11" s="6" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" hidden="1" outlineLevel="2">
       <c r="A12" s="4" t="n">
@@ -619,9 +643,10 @@
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="5" t="n"/>
+      <c r="E12" s="6" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" hidden="1" outlineLevel="2">
       <c r="A13" s="4" t="n">
@@ -630,9 +655,10 @@
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="n"/>
+      <c r="E13" s="6" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="6" t="n"/>
     </row>
     <row r="14" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A14" s="4" t="n">
@@ -641,9 +667,10 @@
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="5" t="n"/>
+      <c r="E14" s="6" t="n"/>
       <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" hidden="1" outlineLevel="2">
       <c r="A15" s="4" t="n">
@@ -652,9 +679,10 @@
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="n"/>
+      <c r="E15" s="6" t="n"/>
       <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" hidden="1" outlineLevel="2">
       <c r="A16" s="4" t="n">
@@ -663,9 +691,10 @@
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="n"/>
+      <c r="E16" s="6" t="n"/>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="6" t="n"/>
     </row>
     <row r="17" hidden="1" outlineLevel="2">
       <c r="A17" s="4" t="n">
@@ -674,9 +703,10 @@
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="n"/>
+      <c r="E17" s="6" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="6" t="n"/>
     </row>
     <row r="18" collapsed="1">
       <c r="A18" s="4" t="n">
@@ -694,12 +724,13 @@
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5">
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>progPalette(15740, 8, 10)   (Matrix: progScrollText("Dancing on my own by Robyn", 18500, 90, getRandomColor(), 10))</t>
         </is>
@@ -712,9 +743,10 @@
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="5" t="n"/>
+      <c r="E19" s="6" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="6" t="n"/>
     </row>
     <row r="20" hidden="1" outlineLevel="2">
       <c r="A20" s="4" t="n">
@@ -723,9 +755,10 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="5" t="n"/>
+      <c r="E20" s="6" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="6" t="n"/>
     </row>
     <row r="21" hidden="1" outlineLevel="2">
       <c r="A21" s="4" t="n">
@@ -734,9 +767,10 @@
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="5" t="n"/>
+      <c r="E21" s="6" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A22" s="4" t="n">
@@ -745,9 +779,10 @@
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
-      <c r="E22" s="5" t="n"/>
+      <c r="E22" s="6" t="n"/>
       <c r="F22" s="5" t="n"/>
-      <c r="G22" s="6" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" hidden="1" outlineLevel="2">
       <c r="A23" s="4" t="n">
@@ -756,9 +791,10 @@
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="5" t="n"/>
+      <c r="E23" s="6" t="n"/>
       <c r="F23" s="5" t="n"/>
-      <c r="G23" s="6" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="6" t="n"/>
     </row>
     <row r="24" hidden="1" outlineLevel="2">
       <c r="A24" s="4" t="n">
@@ -767,9 +803,10 @@
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="6" t="n"/>
-      <c r="E24" s="5" t="n"/>
+      <c r="E24" s="6" t="n"/>
       <c r="F24" s="5" t="n"/>
-      <c r="G24" s="6" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="6" t="n"/>
     </row>
     <row r="25" hidden="1" outlineLevel="2">
       <c r="A25" s="4" t="n">
@@ -778,9 +815,10 @@
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="5" t="n"/>
+      <c r="E25" s="6" t="n"/>
       <c r="F25" s="5" t="n"/>
-      <c r="G25" s="6" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="6" t="n"/>
     </row>
     <row r="26" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A26" s="4" t="n">
@@ -789,9 +827,10 @@
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6" t="n"/>
       <c r="D26" s="6" t="n"/>
-      <c r="E26" s="5" t="n"/>
+      <c r="E26" s="6" t="n"/>
       <c r="F26" s="5" t="n"/>
-      <c r="G26" s="6" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="6" t="n"/>
     </row>
     <row r="27" hidden="1" outlineLevel="2">
       <c r="A27" s="4" t="n">
@@ -800,9 +839,10 @@
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="6" t="n"/>
       <c r="D27" s="6" t="n"/>
-      <c r="E27" s="5" t="n"/>
+      <c r="E27" s="6" t="n"/>
       <c r="F27" s="5" t="n"/>
-      <c r="G27" s="6" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="6" t="n"/>
     </row>
     <row r="28" hidden="1" outlineLevel="2">
       <c r="A28" s="4" t="n">
@@ -811,9 +851,10 @@
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6" t="n"/>
       <c r="D28" s="6" t="n"/>
-      <c r="E28" s="5" t="n"/>
+      <c r="E28" s="6" t="n"/>
       <c r="F28" s="5" t="n"/>
-      <c r="G28" s="6" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="6" t="n"/>
     </row>
     <row r="29" hidden="1" outlineLevel="2">
       <c r="A29" s="4" t="n">
@@ -822,9 +863,10 @@
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="6" t="n"/>
       <c r="D29" s="6" t="n"/>
-      <c r="E29" s="5" t="n"/>
+      <c r="E29" s="6" t="n"/>
       <c r="F29" s="5" t="n"/>
-      <c r="G29" s="6" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="6" t="n"/>
     </row>
     <row r="30" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A30" s="4" t="n">
@@ -833,9 +875,10 @@
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6" t="n"/>
       <c r="D30" s="6" t="n"/>
-      <c r="E30" s="5" t="n"/>
+      <c r="E30" s="6" t="n"/>
       <c r="F30" s="5" t="n"/>
-      <c r="G30" s="6" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="6" t="n"/>
     </row>
     <row r="31" hidden="1" outlineLevel="2">
       <c r="A31" s="4" t="n">
@@ -844,9 +887,10 @@
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="6" t="n"/>
       <c r="D31" s="6" t="n"/>
-      <c r="E31" s="5" t="n"/>
+      <c r="E31" s="6" t="n"/>
       <c r="F31" s="5" t="n"/>
-      <c r="G31" s="6" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="6" t="n"/>
     </row>
     <row r="32" hidden="1" outlineLevel="2">
       <c r="A32" s="4" t="n">
@@ -855,9 +899,10 @@
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6" t="n"/>
       <c r="D32" s="6" t="n"/>
-      <c r="E32" s="5" t="n"/>
+      <c r="E32" s="6" t="n"/>
       <c r="F32" s="5" t="n"/>
-      <c r="G32" s="6" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="6" t="n"/>
     </row>
     <row r="33" hidden="1" outlineLevel="2">
       <c r="A33" s="4" t="n">
@@ -866,9 +911,10 @@
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="6" t="n"/>
       <c r="D33" s="6" t="n"/>
-      <c r="E33" s="5" t="n"/>
+      <c r="E33" s="6" t="n"/>
       <c r="F33" s="5" t="n"/>
-      <c r="G33" s="6" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="6" t="n"/>
     </row>
     <row r="34" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A34" s="4" t="n">
@@ -877,9 +923,10 @@
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6" t="n"/>
       <c r="D34" s="6" t="n"/>
-      <c r="E34" s="5" t="n"/>
+      <c r="E34" s="6" t="n"/>
       <c r="F34" s="5" t="n"/>
-      <c r="G34" s="6" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="6" t="n"/>
     </row>
     <row r="35" hidden="1" outlineLevel="2">
       <c r="A35" s="4" t="n">
@@ -888,9 +935,10 @@
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="6" t="n"/>
       <c r="D35" s="6" t="n"/>
-      <c r="E35" s="5" t="n"/>
+      <c r="E35" s="6" t="n"/>
       <c r="F35" s="5" t="n"/>
-      <c r="G35" s="6" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="6" t="n"/>
     </row>
     <row r="36" hidden="1" outlineLevel="2">
       <c r="A36" s="4" t="n">
@@ -899,9 +947,10 @@
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6" t="n"/>
       <c r="D36" s="6" t="n"/>
-      <c r="E36" s="5" t="n"/>
+      <c r="E36" s="6" t="n"/>
       <c r="F36" s="5" t="n"/>
-      <c r="G36" s="6" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="6" t="n"/>
     </row>
     <row r="37" hidden="1" outlineLevel="2">
       <c r="A37" s="4" t="n">
@@ -910,9 +959,10 @@
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="6" t="n"/>
       <c r="D37" s="6" t="n"/>
-      <c r="E37" s="5" t="n"/>
+      <c r="E37" s="6" t="n"/>
       <c r="F37" s="5" t="n"/>
-      <c r="G37" s="6" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="6" t="n"/>
     </row>
     <row r="38" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A38" s="4" t="n">
@@ -921,9 +971,10 @@
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6" t="n"/>
       <c r="D38" s="6" t="n"/>
-      <c r="E38" s="5" t="n"/>
+      <c r="E38" s="6" t="n"/>
       <c r="F38" s="5" t="n"/>
-      <c r="G38" s="6" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="6" t="n"/>
     </row>
     <row r="39" hidden="1" outlineLevel="2">
       <c r="A39" s="4" t="n">
@@ -932,9 +983,10 @@
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="6" t="n"/>
       <c r="D39" s="6" t="n"/>
-      <c r="E39" s="5" t="n"/>
+      <c r="E39" s="6" t="n"/>
       <c r="F39" s="5" t="n"/>
-      <c r="G39" s="6" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="6" t="n"/>
     </row>
     <row r="40" hidden="1" outlineLevel="2">
       <c r="A40" s="4" t="n">
@@ -943,9 +995,10 @@
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6" t="n"/>
       <c r="D40" s="6" t="n"/>
-      <c r="E40" s="5" t="n"/>
+      <c r="E40" s="6" t="n"/>
       <c r="F40" s="5" t="n"/>
-      <c r="G40" s="6" t="n"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="6" t="n"/>
     </row>
     <row r="41" hidden="1" outlineLevel="2">
       <c r="A41" s="4" t="n">
@@ -954,9 +1007,10 @@
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="6" t="n"/>
       <c r="D41" s="6" t="n"/>
-      <c r="E41" s="5" t="n"/>
+      <c r="E41" s="6" t="n"/>
       <c r="F41" s="5" t="n"/>
-      <c r="G41" s="6" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="6" t="n"/>
     </row>
     <row r="42" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A42" s="4" t="n">
@@ -965,9 +1019,10 @@
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="6" t="n"/>
       <c r="D42" s="6" t="n"/>
-      <c r="E42" s="5" t="n"/>
+      <c r="E42" s="6" t="n"/>
       <c r="F42" s="5" t="n"/>
-      <c r="G42" s="6" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="6" t="n"/>
     </row>
     <row r="43" hidden="1" outlineLevel="2">
       <c r="A43" s="4" t="n">
@@ -976,9 +1031,10 @@
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="6" t="n"/>
       <c r="D43" s="6" t="n"/>
-      <c r="E43" s="5" t="n"/>
+      <c r="E43" s="6" t="n"/>
       <c r="F43" s="5" t="n"/>
-      <c r="G43" s="6" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="6" t="n"/>
     </row>
     <row r="44" hidden="1" outlineLevel="2">
       <c r="A44" s="4" t="n">
@@ -987,9 +1043,10 @@
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="6" t="n"/>
       <c r="D44" s="6" t="n"/>
-      <c r="E44" s="5" t="n"/>
+      <c r="E44" s="6" t="n"/>
       <c r="F44" s="5" t="n"/>
-      <c r="G44" s="6" t="n"/>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="6" t="n"/>
     </row>
     <row r="45" hidden="1" outlineLevel="2">
       <c r="A45" s="4" t="n">
@@ -998,9 +1055,10 @@
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="6" t="n"/>
       <c r="D45" s="6" t="n"/>
-      <c r="E45" s="5" t="n"/>
+      <c r="E45" s="6" t="n"/>
       <c r="F45" s="5" t="n"/>
-      <c r="G45" s="6" t="n"/>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="6" t="n"/>
     </row>
     <row r="46" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A46" s="4" t="n">
@@ -1009,9 +1067,10 @@
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="6" t="n"/>
       <c r="D46" s="6" t="n"/>
-      <c r="E46" s="5" t="n"/>
+      <c r="E46" s="6" t="n"/>
       <c r="F46" s="5" t="n"/>
-      <c r="G46" s="6" t="n"/>
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="6" t="n"/>
     </row>
     <row r="47" hidden="1" outlineLevel="2">
       <c r="A47" s="4" t="n">
@@ -1020,9 +1079,10 @@
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="6" t="n"/>
       <c r="D47" s="6" t="n"/>
-      <c r="E47" s="5" t="n"/>
+      <c r="E47" s="6" t="n"/>
       <c r="F47" s="5" t="n"/>
-      <c r="G47" s="6" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="6" t="n"/>
     </row>
     <row r="48" hidden="1" outlineLevel="2">
       <c r="A48" s="4" t="n">
@@ -1031,9 +1091,10 @@
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="6" t="n"/>
       <c r="D48" s="6" t="n"/>
-      <c r="E48" s="5" t="n"/>
+      <c r="E48" s="6" t="n"/>
       <c r="F48" s="5" t="n"/>
-      <c r="G48" s="6" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="6" t="n"/>
     </row>
     <row r="49" hidden="1" outlineLevel="2">
       <c r="A49" s="4" t="n">
@@ -1042,9 +1103,10 @@
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="6" t="n"/>
       <c r="D49" s="6" t="n"/>
-      <c r="E49" s="5" t="n"/>
+      <c r="E49" s="6" t="n"/>
       <c r="F49" s="5" t="n"/>
-      <c r="G49" s="6" t="n"/>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="6" t="n"/>
     </row>
     <row r="50" collapsed="1">
       <c r="A50" s="4" t="n">
@@ -1055,19 +1117,25 @@
           <t>somebody</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE_HEART, Farben SCHEME_ICE
+Gesang setzt ein, noch zurückhaltend: alle Geräte schlagen auf jedem Beat wie ein Herz (lub-dub) in Blautönen, die Matrix zeigt eine Lissajous-Schleife</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>SCENE_VERSE, Farben SCHEME_ICE
 Gesang setzt ein: Gitarre und Bass leuchten Zone für Zone im Beat, Lampen mit Lichtschuss pro Beat, auf der Matrix farbiger Regen in Blautönen</t>
         </is>
       </c>
-      <c r="D50" s="6" t="n"/>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5">
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G50" s="6" t="inlineStr">
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>progPalette(15735, 4, 15)</t>
         </is>
@@ -1080,9 +1148,10 @@
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="6" t="n"/>
       <c r="D51" s="6" t="n"/>
-      <c r="E51" s="5" t="n"/>
+      <c r="E51" s="6" t="n"/>
       <c r="F51" s="5" t="n"/>
-      <c r="G51" s="6" t="n"/>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="6" t="n"/>
     </row>
     <row r="52" hidden="1" outlineLevel="2">
       <c r="A52" s="4" t="n">
@@ -1091,9 +1160,10 @@
       <c r="B52" s="5" t="n"/>
       <c r="C52" s="6" t="n"/>
       <c r="D52" s="6" t="n"/>
-      <c r="E52" s="5" t="n"/>
+      <c r="E52" s="6" t="n"/>
       <c r="F52" s="5" t="n"/>
-      <c r="G52" s="6" t="n"/>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="6" t="n"/>
     </row>
     <row r="53" hidden="1" outlineLevel="2">
       <c r="A53" s="4" t="n">
@@ -1102,9 +1172,10 @@
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="6" t="n"/>
       <c r="D53" s="6" t="n"/>
-      <c r="E53" s="5" t="n"/>
+      <c r="E53" s="6" t="n"/>
       <c r="F53" s="5" t="n"/>
-      <c r="G53" s="6" t="n"/>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="6" t="n"/>
     </row>
     <row r="54" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A54" s="4" t="n">
@@ -1113,9 +1184,10 @@
       <c r="B54" s="5" t="n"/>
       <c r="C54" s="6" t="n"/>
       <c r="D54" s="6" t="n"/>
-      <c r="E54" s="5" t="n"/>
+      <c r="E54" s="6" t="n"/>
       <c r="F54" s="5" t="n"/>
-      <c r="G54" s="6" t="n"/>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="6" t="n"/>
     </row>
     <row r="55" hidden="1" outlineLevel="2">
       <c r="A55" s="4" t="n">
@@ -1124,9 +1196,10 @@
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="6" t="n"/>
       <c r="D55" s="6" t="n"/>
-      <c r="E55" s="5" t="n"/>
+      <c r="E55" s="6" t="n"/>
       <c r="F55" s="5" t="n"/>
-      <c r="G55" s="6" t="n"/>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="6" t="n"/>
     </row>
     <row r="56" hidden="1" outlineLevel="2">
       <c r="A56" s="4" t="n">
@@ -1135,9 +1208,10 @@
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="6" t="n"/>
       <c r="D56" s="6" t="n"/>
-      <c r="E56" s="5" t="n"/>
+      <c r="E56" s="6" t="n"/>
       <c r="F56" s="5" t="n"/>
-      <c r="G56" s="6" t="n"/>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="6" t="n"/>
     </row>
     <row r="57" hidden="1" outlineLevel="2">
       <c r="A57" s="4" t="n">
@@ -1146,9 +1220,10 @@
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="6" t="n"/>
       <c r="D57" s="6" t="n"/>
-      <c r="E57" s="5" t="n"/>
+      <c r="E57" s="6" t="n"/>
       <c r="F57" s="5" t="n"/>
-      <c r="G57" s="6" t="n"/>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="6" t="n"/>
     </row>
     <row r="58" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A58" s="4" t="n">
@@ -1157,9 +1232,10 @@
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="6" t="n"/>
       <c r="D58" s="6" t="n"/>
-      <c r="E58" s="5" t="n"/>
+      <c r="E58" s="6" t="n"/>
       <c r="F58" s="5" t="n"/>
-      <c r="G58" s="6" t="n"/>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="6" t="n"/>
     </row>
     <row r="59" hidden="1" outlineLevel="2">
       <c r="A59" s="4" t="n">
@@ -1168,9 +1244,10 @@
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="6" t="n"/>
       <c r="D59" s="6" t="n"/>
-      <c r="E59" s="5" t="n"/>
+      <c r="E59" s="6" t="n"/>
       <c r="F59" s="5" t="n"/>
-      <c r="G59" s="6" t="n"/>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="6" t="n"/>
     </row>
     <row r="60" hidden="1" outlineLevel="2">
       <c r="A60" s="4" t="n">
@@ -1179,9 +1256,10 @@
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="6" t="n"/>
       <c r="D60" s="6" t="n"/>
-      <c r="E60" s="5" t="n"/>
+      <c r="E60" s="6" t="n"/>
       <c r="F60" s="5" t="n"/>
-      <c r="G60" s="6" t="n"/>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="6" t="n"/>
     </row>
     <row r="61" hidden="1" outlineLevel="2">
       <c r="A61" s="4" t="n">
@@ -1190,9 +1268,10 @@
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="6" t="n"/>
       <c r="D61" s="6" t="n"/>
-      <c r="E61" s="5" t="n"/>
+      <c r="E61" s="6" t="n"/>
       <c r="F61" s="5" t="n"/>
-      <c r="G61" s="6" t="n"/>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="6" t="n"/>
     </row>
     <row r="62" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A62" s="4" t="n">
@@ -1201,9 +1280,10 @@
       <c r="B62" s="5" t="n"/>
       <c r="C62" s="6" t="n"/>
       <c r="D62" s="6" t="n"/>
-      <c r="E62" s="5" t="n"/>
+      <c r="E62" s="6" t="n"/>
       <c r="F62" s="5" t="n"/>
-      <c r="G62" s="6" t="n"/>
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="6" t="n"/>
     </row>
     <row r="63" hidden="1" outlineLevel="2">
       <c r="A63" s="4" t="n">
@@ -1212,9 +1292,10 @@
       <c r="B63" s="5" t="n"/>
       <c r="C63" s="6" t="n"/>
       <c r="D63" s="6" t="n"/>
-      <c r="E63" s="5" t="n"/>
+      <c r="E63" s="6" t="n"/>
       <c r="F63" s="5" t="n"/>
-      <c r="G63" s="6" t="n"/>
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="6" t="n"/>
     </row>
     <row r="64" hidden="1" outlineLevel="2">
       <c r="A64" s="4" t="n">
@@ -1223,9 +1304,10 @@
       <c r="B64" s="5" t="n"/>
       <c r="C64" s="6" t="n"/>
       <c r="D64" s="6" t="n"/>
-      <c r="E64" s="5" t="n"/>
+      <c r="E64" s="6" t="n"/>
       <c r="F64" s="5" t="n"/>
-      <c r="G64" s="6" t="n"/>
+      <c r="G64" s="5" t="n"/>
+      <c r="H64" s="6" t="n"/>
     </row>
     <row r="65" hidden="1" outlineLevel="2">
       <c r="A65" s="4" t="n">
@@ -1234,9 +1316,10 @@
       <c r="B65" s="5" t="n"/>
       <c r="C65" s="6" t="n"/>
       <c r="D65" s="6" t="n"/>
-      <c r="E65" s="5" t="n"/>
+      <c r="E65" s="6" t="n"/>
       <c r="F65" s="5" t="n"/>
-      <c r="G65" s="6" t="n"/>
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="6" t="n"/>
     </row>
     <row r="66" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A66" s="4" t="n">
@@ -1245,9 +1328,10 @@
       <c r="B66" s="5" t="n"/>
       <c r="C66" s="6" t="n"/>
       <c r="D66" s="6" t="n"/>
-      <c r="E66" s="5" t="n"/>
+      <c r="E66" s="6" t="n"/>
       <c r="F66" s="5" t="n"/>
-      <c r="G66" s="6" t="n"/>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="6" t="n"/>
     </row>
     <row r="67" hidden="1" outlineLevel="2">
       <c r="A67" s="4" t="n">
@@ -1256,9 +1340,10 @@
       <c r="B67" s="5" t="n"/>
       <c r="C67" s="6" t="n"/>
       <c r="D67" s="6" t="n"/>
-      <c r="E67" s="5" t="n"/>
+      <c r="E67" s="6" t="n"/>
       <c r="F67" s="5" t="n"/>
-      <c r="G67" s="6" t="n"/>
+      <c r="G67" s="5" t="n"/>
+      <c r="H67" s="6" t="n"/>
     </row>
     <row r="68" hidden="1" outlineLevel="2">
       <c r="A68" s="4" t="n">
@@ -1267,9 +1352,10 @@
       <c r="B68" s="5" t="n"/>
       <c r="C68" s="6" t="n"/>
       <c r="D68" s="6" t="n"/>
-      <c r="E68" s="5" t="n"/>
+      <c r="E68" s="6" t="n"/>
       <c r="F68" s="5" t="n"/>
-      <c r="G68" s="6" t="n"/>
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="6" t="n"/>
     </row>
     <row r="69" hidden="1" outlineLevel="2">
       <c r="A69" s="4" t="n">
@@ -1278,9 +1364,10 @@
       <c r="B69" s="5" t="n"/>
       <c r="C69" s="6" t="n"/>
       <c r="D69" s="6" t="n"/>
-      <c r="E69" s="5" t="n"/>
+      <c r="E69" s="6" t="n"/>
       <c r="F69" s="5" t="n"/>
-      <c r="G69" s="6" t="n"/>
+      <c r="G69" s="5" t="n"/>
+      <c r="H69" s="6" t="n"/>
     </row>
     <row r="70" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A70" s="4" t="n">
@@ -1289,9 +1376,10 @@
       <c r="B70" s="5" t="n"/>
       <c r="C70" s="6" t="n"/>
       <c r="D70" s="6" t="n"/>
-      <c r="E70" s="5" t="n"/>
+      <c r="E70" s="6" t="n"/>
       <c r="F70" s="5" t="n"/>
-      <c r="G70" s="6" t="n"/>
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="6" t="n"/>
     </row>
     <row r="71" hidden="1" outlineLevel="2">
       <c r="A71" s="4" t="n">
@@ -1300,9 +1388,10 @@
       <c r="B71" s="5" t="n"/>
       <c r="C71" s="6" t="n"/>
       <c r="D71" s="6" t="n"/>
-      <c r="E71" s="5" t="n"/>
+      <c r="E71" s="6" t="n"/>
       <c r="F71" s="5" t="n"/>
-      <c r="G71" s="6" t="n"/>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="6" t="n"/>
     </row>
     <row r="72" hidden="1" outlineLevel="2">
       <c r="A72" s="4" t="n">
@@ -1311,9 +1400,10 @@
       <c r="B72" s="5" t="n"/>
       <c r="C72" s="6" t="n"/>
       <c r="D72" s="6" t="n"/>
-      <c r="E72" s="5" t="n"/>
+      <c r="E72" s="6" t="n"/>
       <c r="F72" s="5" t="n"/>
-      <c r="G72" s="6" t="n"/>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="6" t="n"/>
     </row>
     <row r="73" hidden="1" outlineLevel="2">
       <c r="A73" s="4" t="n">
@@ -1322,9 +1412,10 @@
       <c r="B73" s="5" t="n"/>
       <c r="C73" s="6" t="n"/>
       <c r="D73" s="6" t="n"/>
-      <c r="E73" s="5" t="n"/>
+      <c r="E73" s="6" t="n"/>
       <c r="F73" s="5" t="n"/>
-      <c r="G73" s="6" t="n"/>
+      <c r="G73" s="5" t="n"/>
+      <c r="H73" s="6" t="n"/>
     </row>
     <row r="74" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A74" s="4" t="n">
@@ -1333,9 +1424,10 @@
       <c r="B74" s="5" t="n"/>
       <c r="C74" s="6" t="n"/>
       <c r="D74" s="6" t="n"/>
-      <c r="E74" s="5" t="n"/>
+      <c r="E74" s="6" t="n"/>
       <c r="F74" s="5" t="n"/>
-      <c r="G74" s="6" t="n"/>
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="6" t="n"/>
     </row>
     <row r="75" hidden="1" outlineLevel="2">
       <c r="A75" s="4" t="n">
@@ -1344,9 +1436,10 @@
       <c r="B75" s="5" t="n"/>
       <c r="C75" s="6" t="n"/>
       <c r="D75" s="6" t="n"/>
-      <c r="E75" s="5" t="n"/>
+      <c r="E75" s="6" t="n"/>
       <c r="F75" s="5" t="n"/>
-      <c r="G75" s="6" t="n"/>
+      <c r="G75" s="5" t="n"/>
+      <c r="H75" s="6" t="n"/>
     </row>
     <row r="76" hidden="1" outlineLevel="2">
       <c r="A76" s="4" t="n">
@@ -1355,9 +1448,10 @@
       <c r="B76" s="5" t="n"/>
       <c r="C76" s="6" t="n"/>
       <c r="D76" s="6" t="n"/>
-      <c r="E76" s="5" t="n"/>
+      <c r="E76" s="6" t="n"/>
       <c r="F76" s="5" t="n"/>
-      <c r="G76" s="6" t="n"/>
+      <c r="G76" s="5" t="n"/>
+      <c r="H76" s="6" t="n"/>
     </row>
     <row r="77" hidden="1" outlineLevel="2">
       <c r="A77" s="4" t="n">
@@ -1366,9 +1460,10 @@
       <c r="B77" s="5" t="n"/>
       <c r="C77" s="6" t="n"/>
       <c r="D77" s="6" t="n"/>
-      <c r="E77" s="5" t="n"/>
+      <c r="E77" s="6" t="n"/>
       <c r="F77" s="5" t="n"/>
-      <c r="G77" s="6" t="n"/>
+      <c r="G77" s="5" t="n"/>
+      <c r="H77" s="6" t="n"/>
     </row>
     <row r="78" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A78" s="4" t="n">
@@ -1377,9 +1472,10 @@
       <c r="B78" s="5" t="n"/>
       <c r="C78" s="6" t="n"/>
       <c r="D78" s="6" t="n"/>
-      <c r="E78" s="5" t="n"/>
+      <c r="E78" s="6" t="n"/>
       <c r="F78" s="5" t="n"/>
-      <c r="G78" s="6" t="n"/>
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="6" t="n"/>
     </row>
     <row r="79" hidden="1" outlineLevel="2">
       <c r="A79" s="4" t="n">
@@ -1388,9 +1484,10 @@
       <c r="B79" s="5" t="n"/>
       <c r="C79" s="6" t="n"/>
       <c r="D79" s="6" t="n"/>
-      <c r="E79" s="5" t="n"/>
+      <c r="E79" s="6" t="n"/>
       <c r="F79" s="5" t="n"/>
-      <c r="G79" s="6" t="n"/>
+      <c r="G79" s="5" t="n"/>
+      <c r="H79" s="6" t="n"/>
     </row>
     <row r="80" hidden="1" outlineLevel="2">
       <c r="A80" s="4" t="n">
@@ -1399,9 +1496,10 @@
       <c r="B80" s="5" t="n"/>
       <c r="C80" s="6" t="n"/>
       <c r="D80" s="6" t="n"/>
-      <c r="E80" s="5" t="n"/>
+      <c r="E80" s="6" t="n"/>
       <c r="F80" s="5" t="n"/>
-      <c r="G80" s="6" t="n"/>
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="6" t="n"/>
     </row>
     <row r="81" hidden="1" outlineLevel="2">
       <c r="A81" s="4" t="n">
@@ -1410,9 +1508,10 @@
       <c r="B81" s="5" t="n"/>
       <c r="C81" s="6" t="n"/>
       <c r="D81" s="6" t="n"/>
-      <c r="E81" s="5" t="n"/>
+      <c r="E81" s="6" t="n"/>
       <c r="F81" s="5" t="n"/>
-      <c r="G81" s="6" t="n"/>
+      <c r="G81" s="5" t="n"/>
+      <c r="H81" s="6" t="n"/>
     </row>
     <row r="82" collapsed="1">
       <c r="A82" s="4" t="n">
@@ -1431,12 +1530,13 @@
         </is>
       </c>
       <c r="D82" s="6" t="n"/>
-      <c r="E82" s="5" t="n"/>
-      <c r="F82" s="5">
+      <c r="E82" s="6" t="n"/>
+      <c r="F82" s="5" t="n"/>
+      <c r="G82" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G82" s="6" t="inlineStr">
+      <c r="H82" s="6" t="inlineStr">
         <is>
           <t>progPalette(15740, 6, 20)</t>
         </is>
@@ -1449,9 +1549,10 @@
       <c r="B83" s="5" t="n"/>
       <c r="C83" s="6" t="n"/>
       <c r="D83" s="6" t="n"/>
-      <c r="E83" s="5" t="n"/>
+      <c r="E83" s="6" t="n"/>
       <c r="F83" s="5" t="n"/>
-      <c r="G83" s="6" t="n"/>
+      <c r="G83" s="5" t="n"/>
+      <c r="H83" s="6" t="n"/>
     </row>
     <row r="84" hidden="1" outlineLevel="2">
       <c r="A84" s="4" t="n">
@@ -1460,9 +1561,10 @@
       <c r="B84" s="5" t="n"/>
       <c r="C84" s="6" t="n"/>
       <c r="D84" s="6" t="n"/>
-      <c r="E84" s="5" t="n"/>
+      <c r="E84" s="6" t="n"/>
       <c r="F84" s="5" t="n"/>
-      <c r="G84" s="6" t="n"/>
+      <c r="G84" s="5" t="n"/>
+      <c r="H84" s="6" t="n"/>
     </row>
     <row r="85" hidden="1" outlineLevel="2">
       <c r="A85" s="4" t="n">
@@ -1471,9 +1573,10 @@
       <c r="B85" s="5" t="n"/>
       <c r="C85" s="6" t="n"/>
       <c r="D85" s="6" t="n"/>
-      <c r="E85" s="5" t="n"/>
+      <c r="E85" s="6" t="n"/>
       <c r="F85" s="5" t="n"/>
-      <c r="G85" s="6" t="n"/>
+      <c r="G85" s="5" t="n"/>
+      <c r="H85" s="6" t="n"/>
     </row>
     <row r="86" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A86" s="4" t="n">
@@ -1482,9 +1585,10 @@
       <c r="B86" s="5" t="n"/>
       <c r="C86" s="6" t="n"/>
       <c r="D86" s="6" t="n"/>
-      <c r="E86" s="5" t="n"/>
+      <c r="E86" s="6" t="n"/>
       <c r="F86" s="5" t="n"/>
-      <c r="G86" s="6" t="n"/>
+      <c r="G86" s="5" t="n"/>
+      <c r="H86" s="6" t="n"/>
     </row>
     <row r="87" hidden="1" outlineLevel="2">
       <c r="A87" s="4" t="n">
@@ -1493,9 +1597,10 @@
       <c r="B87" s="5" t="n"/>
       <c r="C87" s="6" t="n"/>
       <c r="D87" s="6" t="n"/>
-      <c r="E87" s="5" t="n"/>
+      <c r="E87" s="6" t="n"/>
       <c r="F87" s="5" t="n"/>
-      <c r="G87" s="6" t="n"/>
+      <c r="G87" s="5" t="n"/>
+      <c r="H87" s="6" t="n"/>
     </row>
     <row r="88" hidden="1" outlineLevel="2">
       <c r="A88" s="4" t="n">
@@ -1504,9 +1609,10 @@
       <c r="B88" s="5" t="n"/>
       <c r="C88" s="6" t="n"/>
       <c r="D88" s="6" t="n"/>
-      <c r="E88" s="5" t="n"/>
+      <c r="E88" s="6" t="n"/>
       <c r="F88" s="5" t="n"/>
-      <c r="G88" s="6" t="n"/>
+      <c r="G88" s="5" t="n"/>
+      <c r="H88" s="6" t="n"/>
     </row>
     <row r="89" hidden="1" outlineLevel="2">
       <c r="A89" s="4" t="n">
@@ -1515,9 +1621,10 @@
       <c r="B89" s="5" t="n"/>
       <c r="C89" s="6" t="n"/>
       <c r="D89" s="6" t="n"/>
-      <c r="E89" s="5" t="n"/>
+      <c r="E89" s="6" t="n"/>
       <c r="F89" s="5" t="n"/>
-      <c r="G89" s="6" t="n"/>
+      <c r="G89" s="5" t="n"/>
+      <c r="H89" s="6" t="n"/>
     </row>
     <row r="90" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A90" s="4" t="n">
@@ -1526,9 +1633,10 @@
       <c r="B90" s="5" t="n"/>
       <c r="C90" s="6" t="n"/>
       <c r="D90" s="6" t="n"/>
-      <c r="E90" s="5" t="n"/>
+      <c r="E90" s="6" t="n"/>
       <c r="F90" s="5" t="n"/>
-      <c r="G90" s="6" t="n"/>
+      <c r="G90" s="5" t="n"/>
+      <c r="H90" s="6" t="n"/>
     </row>
     <row r="91" hidden="1" outlineLevel="2">
       <c r="A91" s="4" t="n">
@@ -1537,9 +1645,10 @@
       <c r="B91" s="5" t="n"/>
       <c r="C91" s="6" t="n"/>
       <c r="D91" s="6" t="n"/>
-      <c r="E91" s="5" t="n"/>
+      <c r="E91" s="6" t="n"/>
       <c r="F91" s="5" t="n"/>
-      <c r="G91" s="6" t="n"/>
+      <c r="G91" s="5" t="n"/>
+      <c r="H91" s="6" t="n"/>
     </row>
     <row r="92" hidden="1" outlineLevel="2">
       <c r="A92" s="4" t="n">
@@ -1548,9 +1657,10 @@
       <c r="B92" s="5" t="n"/>
       <c r="C92" s="6" t="n"/>
       <c r="D92" s="6" t="n"/>
-      <c r="E92" s="5" t="n"/>
+      <c r="E92" s="6" t="n"/>
       <c r="F92" s="5" t="n"/>
-      <c r="G92" s="6" t="n"/>
+      <c r="G92" s="5" t="n"/>
+      <c r="H92" s="6" t="n"/>
     </row>
     <row r="93" hidden="1" outlineLevel="2">
       <c r="A93" s="4" t="n">
@@ -1559,9 +1669,10 @@
       <c r="B93" s="5" t="n"/>
       <c r="C93" s="6" t="n"/>
       <c r="D93" s="6" t="n"/>
-      <c r="E93" s="5" t="n"/>
+      <c r="E93" s="6" t="n"/>
       <c r="F93" s="5" t="n"/>
-      <c r="G93" s="6" t="n"/>
+      <c r="G93" s="5" t="n"/>
+      <c r="H93" s="6" t="n"/>
     </row>
     <row r="94" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A94" s="4" t="n">
@@ -1570,9 +1681,10 @@
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="6" t="n"/>
       <c r="D94" s="6" t="n"/>
-      <c r="E94" s="5" t="n"/>
+      <c r="E94" s="6" t="n"/>
       <c r="F94" s="5" t="n"/>
-      <c r="G94" s="6" t="n"/>
+      <c r="G94" s="5" t="n"/>
+      <c r="H94" s="6" t="n"/>
     </row>
     <row r="95" hidden="1" outlineLevel="2">
       <c r="A95" s="4" t="n">
@@ -1581,9 +1693,10 @@
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="6" t="n"/>
       <c r="D95" s="6" t="n"/>
-      <c r="E95" s="5" t="n"/>
+      <c r="E95" s="6" t="n"/>
       <c r="F95" s="5" t="n"/>
-      <c r="G95" s="6" t="n"/>
+      <c r="G95" s="5" t="n"/>
+      <c r="H95" s="6" t="n"/>
     </row>
     <row r="96" hidden="1" outlineLevel="2">
       <c r="A96" s="4" t="n">
@@ -1592,9 +1705,10 @@
       <c r="B96" s="5" t="n"/>
       <c r="C96" s="6" t="n"/>
       <c r="D96" s="6" t="n"/>
-      <c r="E96" s="5" t="n"/>
+      <c r="E96" s="6" t="n"/>
       <c r="F96" s="5" t="n"/>
-      <c r="G96" s="6" t="n"/>
+      <c r="G96" s="5" t="n"/>
+      <c r="H96" s="6" t="n"/>
     </row>
     <row r="97" hidden="1" outlineLevel="2">
       <c r="A97" s="4" t="n">
@@ -1603,9 +1717,10 @@
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="6" t="n"/>
       <c r="D97" s="6" t="n"/>
-      <c r="E97" s="5" t="n"/>
+      <c r="E97" s="6" t="n"/>
       <c r="F97" s="5" t="n"/>
-      <c r="G97" s="6" t="n"/>
+      <c r="G97" s="5" t="n"/>
+      <c r="H97" s="6" t="n"/>
     </row>
     <row r="98" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A98" s="4" t="n">
@@ -1614,9 +1729,10 @@
       <c r="B98" s="5" t="n"/>
       <c r="C98" s="6" t="n"/>
       <c r="D98" s="6" t="n"/>
-      <c r="E98" s="5" t="n"/>
+      <c r="E98" s="6" t="n"/>
       <c r="F98" s="5" t="n"/>
-      <c r="G98" s="6" t="n"/>
+      <c r="G98" s="5" t="n"/>
+      <c r="H98" s="6" t="n"/>
     </row>
     <row r="99" hidden="1" outlineLevel="2">
       <c r="A99" s="4" t="n">
@@ -1625,9 +1741,10 @@
       <c r="B99" s="5" t="n"/>
       <c r="C99" s="6" t="n"/>
       <c r="D99" s="6" t="n"/>
-      <c r="E99" s="5" t="n"/>
+      <c r="E99" s="6" t="n"/>
       <c r="F99" s="5" t="n"/>
-      <c r="G99" s="6" t="n"/>
+      <c r="G99" s="5" t="n"/>
+      <c r="H99" s="6" t="n"/>
     </row>
     <row r="100" hidden="1" outlineLevel="2">
       <c r="A100" s="4" t="n">
@@ -1636,9 +1753,10 @@
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="6" t="n"/>
       <c r="D100" s="6" t="n"/>
-      <c r="E100" s="5" t="n"/>
+      <c r="E100" s="6" t="n"/>
       <c r="F100" s="5" t="n"/>
-      <c r="G100" s="6" t="n"/>
+      <c r="G100" s="5" t="n"/>
+      <c r="H100" s="6" t="n"/>
     </row>
     <row r="101" hidden="1" outlineLevel="2">
       <c r="A101" s="4" t="n">
@@ -1647,9 +1765,10 @@
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="6" t="n"/>
       <c r="D101" s="6" t="n"/>
-      <c r="E101" s="5" t="n"/>
+      <c r="E101" s="6" t="n"/>
       <c r="F101" s="5" t="n"/>
-      <c r="G101" s="6" t="n"/>
+      <c r="G101" s="5" t="n"/>
+      <c r="H101" s="6" t="n"/>
     </row>
     <row r="102" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A102" s="4" t="n">
@@ -1658,9 +1777,10 @@
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="6" t="n"/>
       <c r="D102" s="6" t="n"/>
-      <c r="E102" s="5" t="n"/>
+      <c r="E102" s="6" t="n"/>
       <c r="F102" s="5" t="n"/>
-      <c r="G102" s="6" t="n"/>
+      <c r="G102" s="5" t="n"/>
+      <c r="H102" s="6" t="n"/>
     </row>
     <row r="103" hidden="1" outlineLevel="2">
       <c r="A103" s="4" t="n">
@@ -1669,9 +1789,10 @@
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="6" t="n"/>
       <c r="D103" s="6" t="n"/>
-      <c r="E103" s="5" t="n"/>
+      <c r="E103" s="6" t="n"/>
       <c r="F103" s="5" t="n"/>
-      <c r="G103" s="6" t="n"/>
+      <c r="G103" s="5" t="n"/>
+      <c r="H103" s="6" t="n"/>
     </row>
     <row r="104" hidden="1" outlineLevel="2">
       <c r="A104" s="4" t="n">
@@ -1680,9 +1801,10 @@
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="6" t="n"/>
       <c r="D104" s="6" t="n"/>
-      <c r="E104" s="5" t="n"/>
+      <c r="E104" s="6" t="n"/>
       <c r="F104" s="5" t="n"/>
-      <c r="G104" s="6" t="n"/>
+      <c r="G104" s="5" t="n"/>
+      <c r="H104" s="6" t="n"/>
     </row>
     <row r="105" hidden="1" outlineLevel="2">
       <c r="A105" s="4" t="n">
@@ -1691,9 +1813,10 @@
       <c r="B105" s="5" t="n"/>
       <c r="C105" s="6" t="n"/>
       <c r="D105" s="6" t="n"/>
-      <c r="E105" s="5" t="n"/>
+      <c r="E105" s="6" t="n"/>
       <c r="F105" s="5" t="n"/>
-      <c r="G105" s="6" t="n"/>
+      <c r="G105" s="5" t="n"/>
+      <c r="H105" s="6" t="n"/>
     </row>
     <row r="106" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A106" s="4" t="n">
@@ -1702,9 +1825,10 @@
       <c r="B106" s="5" t="n"/>
       <c r="C106" s="6" t="n"/>
       <c r="D106" s="6" t="n"/>
-      <c r="E106" s="5" t="n"/>
+      <c r="E106" s="6" t="n"/>
       <c r="F106" s="5" t="n"/>
-      <c r="G106" s="6" t="n"/>
+      <c r="G106" s="5" t="n"/>
+      <c r="H106" s="6" t="n"/>
     </row>
     <row r="107" hidden="1" outlineLevel="2">
       <c r="A107" s="4" t="n">
@@ -1713,9 +1837,10 @@
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="6" t="n"/>
       <c r="D107" s="6" t="n"/>
-      <c r="E107" s="5" t="n"/>
+      <c r="E107" s="6" t="n"/>
       <c r="F107" s="5" t="n"/>
-      <c r="G107" s="6" t="n"/>
+      <c r="G107" s="5" t="n"/>
+      <c r="H107" s="6" t="n"/>
     </row>
     <row r="108" hidden="1" outlineLevel="2">
       <c r="A108" s="4" t="n">
@@ -1724,9 +1849,10 @@
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="6" t="n"/>
       <c r="D108" s="6" t="n"/>
-      <c r="E108" s="5" t="n"/>
+      <c r="E108" s="6" t="n"/>
       <c r="F108" s="5" t="n"/>
-      <c r="G108" s="6" t="n"/>
+      <c r="G108" s="5" t="n"/>
+      <c r="H108" s="6" t="n"/>
     </row>
     <row r="109" hidden="1" outlineLevel="2">
       <c r="A109" s="4" t="n">
@@ -1735,9 +1861,10 @@
       <c r="B109" s="5" t="n"/>
       <c r="C109" s="6" t="n"/>
       <c r="D109" s="6" t="n"/>
-      <c r="E109" s="5" t="n"/>
+      <c r="E109" s="6" t="n"/>
       <c r="F109" s="5" t="n"/>
-      <c r="G109" s="6" t="n"/>
+      <c r="G109" s="5" t="n"/>
+      <c r="H109" s="6" t="n"/>
     </row>
     <row r="110" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A110" s="4" t="n">
@@ -1746,9 +1873,10 @@
       <c r="B110" s="5" t="n"/>
       <c r="C110" s="6" t="n"/>
       <c r="D110" s="6" t="n"/>
-      <c r="E110" s="5" t="n"/>
+      <c r="E110" s="6" t="n"/>
       <c r="F110" s="5" t="n"/>
-      <c r="G110" s="6" t="n"/>
+      <c r="G110" s="5" t="n"/>
+      <c r="H110" s="6" t="n"/>
     </row>
     <row r="111" hidden="1" outlineLevel="2">
       <c r="A111" s="4" t="n">
@@ -1757,9 +1885,10 @@
       <c r="B111" s="5" t="n"/>
       <c r="C111" s="6" t="n"/>
       <c r="D111" s="6" t="n"/>
-      <c r="E111" s="5" t="n"/>
+      <c r="E111" s="6" t="n"/>
       <c r="F111" s="5" t="n"/>
-      <c r="G111" s="6" t="n"/>
+      <c r="G111" s="5" t="n"/>
+      <c r="H111" s="6" t="n"/>
     </row>
     <row r="112" hidden="1" outlineLevel="2">
       <c r="A112" s="4" t="n">
@@ -1768,9 +1897,10 @@
       <c r="B112" s="5" t="n"/>
       <c r="C112" s="6" t="n"/>
       <c r="D112" s="6" t="n"/>
-      <c r="E112" s="5" t="n"/>
+      <c r="E112" s="6" t="n"/>
       <c r="F112" s="5" t="n"/>
-      <c r="G112" s="6" t="n"/>
+      <c r="G112" s="5" t="n"/>
+      <c r="H112" s="6" t="n"/>
     </row>
     <row r="113" hidden="1" outlineLevel="2">
       <c r="A113" s="4" t="n">
@@ -1779,9 +1909,10 @@
       <c r="B113" s="5" t="n"/>
       <c r="C113" s="6" t="n"/>
       <c r="D113" s="6" t="n"/>
-      <c r="E113" s="5" t="n"/>
+      <c r="E113" s="6" t="n"/>
       <c r="F113" s="5" t="n"/>
-      <c r="G113" s="6" t="n"/>
+      <c r="G113" s="5" t="n"/>
+      <c r="H113" s="6" t="n"/>
     </row>
     <row r="114" collapsed="1">
       <c r="A114" s="4" t="n">
@@ -1799,12 +1930,13 @@
         </is>
       </c>
       <c r="D114" s="6" t="n"/>
-      <c r="E114" s="5" t="n"/>
-      <c r="F114" s="5">
+      <c r="E114" s="6" t="n"/>
+      <c r="F114" s="5" t="n"/>
+      <c r="G114" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G114" s="6" t="inlineStr">
+      <c r="H114" s="6" t="inlineStr">
         <is>
           <t>progPalette(7870, 11, 25)</t>
         </is>
@@ -1817,9 +1949,10 @@
       <c r="B115" s="5" t="n"/>
       <c r="C115" s="6" t="n"/>
       <c r="D115" s="6" t="n"/>
-      <c r="E115" s="5" t="n"/>
+      <c r="E115" s="6" t="n"/>
       <c r="F115" s="5" t="n"/>
-      <c r="G115" s="6" t="n"/>
+      <c r="G115" s="5" t="n"/>
+      <c r="H115" s="6" t="n"/>
     </row>
     <row r="116" hidden="1" outlineLevel="2">
       <c r="A116" s="4" t="n">
@@ -1828,9 +1961,10 @@
       <c r="B116" s="5" t="n"/>
       <c r="C116" s="6" t="n"/>
       <c r="D116" s="6" t="n"/>
-      <c r="E116" s="5" t="n"/>
+      <c r="E116" s="6" t="n"/>
       <c r="F116" s="5" t="n"/>
-      <c r="G116" s="6" t="n"/>
+      <c r="G116" s="5" t="n"/>
+      <c r="H116" s="6" t="n"/>
     </row>
     <row r="117" hidden="1" outlineLevel="2">
       <c r="A117" s="4" t="n">
@@ -1839,9 +1973,10 @@
       <c r="B117" s="5" t="n"/>
       <c r="C117" s="6" t="n"/>
       <c r="D117" s="6" t="n"/>
-      <c r="E117" s="5" t="n"/>
+      <c r="E117" s="6" t="n"/>
       <c r="F117" s="5" t="n"/>
-      <c r="G117" s="6" t="n"/>
+      <c r="G117" s="5" t="n"/>
+      <c r="H117" s="6" t="n"/>
     </row>
     <row r="118" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A118" s="4" t="n">
@@ -1850,9 +1985,10 @@
       <c r="B118" s="5" t="n"/>
       <c r="C118" s="6" t="n"/>
       <c r="D118" s="6" t="n"/>
-      <c r="E118" s="5" t="n"/>
+      <c r="E118" s="6" t="n"/>
       <c r="F118" s="5" t="n"/>
-      <c r="G118" s="6" t="n"/>
+      <c r="G118" s="5" t="n"/>
+      <c r="H118" s="6" t="n"/>
     </row>
     <row r="119" hidden="1" outlineLevel="2">
       <c r="A119" s="4" t="n">
@@ -1861,9 +1997,10 @@
       <c r="B119" s="5" t="n"/>
       <c r="C119" s="6" t="n"/>
       <c r="D119" s="6" t="n"/>
-      <c r="E119" s="5" t="n"/>
+      <c r="E119" s="6" t="n"/>
       <c r="F119" s="5" t="n"/>
-      <c r="G119" s="6" t="n"/>
+      <c r="G119" s="5" t="n"/>
+      <c r="H119" s="6" t="n"/>
     </row>
     <row r="120" hidden="1" outlineLevel="2">
       <c r="A120" s="4" t="n">
@@ -1872,9 +2009,10 @@
       <c r="B120" s="5" t="n"/>
       <c r="C120" s="6" t="n"/>
       <c r="D120" s="6" t="n"/>
-      <c r="E120" s="5" t="n"/>
+      <c r="E120" s="6" t="n"/>
       <c r="F120" s="5" t="n"/>
-      <c r="G120" s="6" t="n"/>
+      <c r="G120" s="5" t="n"/>
+      <c r="H120" s="6" t="n"/>
     </row>
     <row r="121" hidden="1" outlineLevel="2">
       <c r="A121" s="4" t="n">
@@ -1883,9 +2021,10 @@
       <c r="B121" s="5" t="n"/>
       <c r="C121" s="6" t="n"/>
       <c r="D121" s="6" t="n"/>
-      <c r="E121" s="5" t="n"/>
+      <c r="E121" s="6" t="n"/>
       <c r="F121" s="5" t="n"/>
-      <c r="G121" s="6" t="n"/>
+      <c r="G121" s="5" t="n"/>
+      <c r="H121" s="6" t="n"/>
     </row>
     <row r="122" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A122" s="4" t="n">
@@ -1894,9 +2033,10 @@
       <c r="B122" s="5" t="n"/>
       <c r="C122" s="6" t="n"/>
       <c r="D122" s="6" t="n"/>
-      <c r="E122" s="5" t="n"/>
+      <c r="E122" s="6" t="n"/>
       <c r="F122" s="5" t="n"/>
-      <c r="G122" s="6" t="n"/>
+      <c r="G122" s="5" t="n"/>
+      <c r="H122" s="6" t="n"/>
     </row>
     <row r="123" hidden="1" outlineLevel="2">
       <c r="A123" s="4" t="n">
@@ -1905,9 +2045,10 @@
       <c r="B123" s="5" t="n"/>
       <c r="C123" s="6" t="n"/>
       <c r="D123" s="6" t="n"/>
-      <c r="E123" s="5" t="n"/>
+      <c r="E123" s="6" t="n"/>
       <c r="F123" s="5" t="n"/>
-      <c r="G123" s="6" t="n"/>
+      <c r="G123" s="5" t="n"/>
+      <c r="H123" s="6" t="n"/>
     </row>
     <row r="124" hidden="1" outlineLevel="2">
       <c r="A124" s="4" t="n">
@@ -1916,9 +2057,10 @@
       <c r="B124" s="5" t="n"/>
       <c r="C124" s="6" t="n"/>
       <c r="D124" s="6" t="n"/>
-      <c r="E124" s="5" t="n"/>
+      <c r="E124" s="6" t="n"/>
       <c r="F124" s="5" t="n"/>
-      <c r="G124" s="6" t="n"/>
+      <c r="G124" s="5" t="n"/>
+      <c r="H124" s="6" t="n"/>
     </row>
     <row r="125" hidden="1" outlineLevel="2">
       <c r="A125" s="4" t="n">
@@ -1927,9 +2069,10 @@
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="6" t="n"/>
       <c r="D125" s="6" t="n"/>
-      <c r="E125" s="5" t="n"/>
+      <c r="E125" s="6" t="n"/>
       <c r="F125" s="5" t="n"/>
-      <c r="G125" s="6" t="n"/>
+      <c r="G125" s="5" t="n"/>
+      <c r="H125" s="6" t="n"/>
     </row>
     <row r="126" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A126" s="4" t="n">
@@ -1938,9 +2081,10 @@
       <c r="B126" s="5" t="n"/>
       <c r="C126" s="6" t="n"/>
       <c r="D126" s="6" t="n"/>
-      <c r="E126" s="5" t="n"/>
+      <c r="E126" s="6" t="n"/>
       <c r="F126" s="5" t="n"/>
-      <c r="G126" s="6" t="n"/>
+      <c r="G126" s="5" t="n"/>
+      <c r="H126" s="6" t="n"/>
     </row>
     <row r="127" hidden="1" outlineLevel="2">
       <c r="A127" s="4" t="n">
@@ -1949,9 +2093,10 @@
       <c r="B127" s="5" t="n"/>
       <c r="C127" s="6" t="n"/>
       <c r="D127" s="6" t="n"/>
-      <c r="E127" s="5" t="n"/>
+      <c r="E127" s="6" t="n"/>
       <c r="F127" s="5" t="n"/>
-      <c r="G127" s="6" t="n"/>
+      <c r="G127" s="5" t="n"/>
+      <c r="H127" s="6" t="n"/>
     </row>
     <row r="128" hidden="1" outlineLevel="2">
       <c r="A128" s="4" t="n">
@@ -1960,9 +2105,10 @@
       <c r="B128" s="5" t="n"/>
       <c r="C128" s="6" t="n"/>
       <c r="D128" s="6" t="n"/>
-      <c r="E128" s="5" t="n"/>
+      <c r="E128" s="6" t="n"/>
       <c r="F128" s="5" t="n"/>
-      <c r="G128" s="6" t="n"/>
+      <c r="G128" s="5" t="n"/>
+      <c r="H128" s="6" t="n"/>
     </row>
     <row r="129" hidden="1" outlineLevel="2">
       <c r="A129" s="4" t="n">
@@ -1971,9 +2117,10 @@
       <c r="B129" s="5" t="n"/>
       <c r="C129" s="6" t="n"/>
       <c r="D129" s="6" t="n"/>
-      <c r="E129" s="5" t="n"/>
+      <c r="E129" s="6" t="n"/>
       <c r="F129" s="5" t="n"/>
-      <c r="G129" s="6" t="n"/>
+      <c r="G129" s="5" t="n"/>
+      <c r="H129" s="6" t="n"/>
     </row>
     <row r="130" collapsed="1">
       <c r="A130" s="4" t="n">
@@ -1991,12 +2138,13 @@
         </is>
       </c>
       <c r="D130" s="6" t="n"/>
-      <c r="E130" s="5" t="n"/>
-      <c r="F130" s="5">
+      <c r="E130" s="6" t="n"/>
+      <c r="F130" s="5" t="n"/>
+      <c r="G130" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G130" s="6" t="inlineStr">
+      <c r="H130" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(15735, 30, 26)</t>
         </is>
@@ -2009,9 +2157,10 @@
       <c r="B131" s="5" t="n"/>
       <c r="C131" s="6" t="n"/>
       <c r="D131" s="6" t="n"/>
-      <c r="E131" s="5" t="n"/>
+      <c r="E131" s="6" t="n"/>
       <c r="F131" s="5" t="n"/>
-      <c r="G131" s="6" t="n"/>
+      <c r="G131" s="5" t="n"/>
+      <c r="H131" s="6" t="n"/>
     </row>
     <row r="132" hidden="1" outlineLevel="2">
       <c r="A132" s="4" t="n">
@@ -2020,9 +2169,10 @@
       <c r="B132" s="5" t="n"/>
       <c r="C132" s="6" t="n"/>
       <c r="D132" s="6" t="n"/>
-      <c r="E132" s="5" t="n"/>
+      <c r="E132" s="6" t="n"/>
       <c r="F132" s="5" t="n"/>
-      <c r="G132" s="6" t="n"/>
+      <c r="G132" s="5" t="n"/>
+      <c r="H132" s="6" t="n"/>
     </row>
     <row r="133" hidden="1" outlineLevel="2">
       <c r="A133" s="4" t="n">
@@ -2031,9 +2181,10 @@
       <c r="B133" s="5" t="n"/>
       <c r="C133" s="6" t="n"/>
       <c r="D133" s="6" t="n"/>
-      <c r="E133" s="5" t="n"/>
+      <c r="E133" s="6" t="n"/>
       <c r="F133" s="5" t="n"/>
-      <c r="G133" s="6" t="n"/>
+      <c r="G133" s="5" t="n"/>
+      <c r="H133" s="6" t="n"/>
     </row>
     <row r="134" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A134" s="4" t="n">
@@ -2042,9 +2193,10 @@
       <c r="B134" s="5" t="n"/>
       <c r="C134" s="6" t="n"/>
       <c r="D134" s="6" t="n"/>
-      <c r="E134" s="5" t="n"/>
+      <c r="E134" s="6" t="n"/>
       <c r="F134" s="5" t="n"/>
-      <c r="G134" s="6" t="n"/>
+      <c r="G134" s="5" t="n"/>
+      <c r="H134" s="6" t="n"/>
     </row>
     <row r="135" hidden="1" outlineLevel="2">
       <c r="A135" s="4" t="n">
@@ -2053,9 +2205,10 @@
       <c r="B135" s="5" t="n"/>
       <c r="C135" s="6" t="n"/>
       <c r="D135" s="6" t="n"/>
-      <c r="E135" s="5" t="n"/>
+      <c r="E135" s="6" t="n"/>
       <c r="F135" s="5" t="n"/>
-      <c r="G135" s="6" t="n"/>
+      <c r="G135" s="5" t="n"/>
+      <c r="H135" s="6" t="n"/>
     </row>
     <row r="136" hidden="1" outlineLevel="2">
       <c r="A136" s="4" t="n">
@@ -2064,9 +2217,10 @@
       <c r="B136" s="5" t="n"/>
       <c r="C136" s="6" t="n"/>
       <c r="D136" s="6" t="n"/>
-      <c r="E136" s="5" t="n"/>
+      <c r="E136" s="6" t="n"/>
       <c r="F136" s="5" t="n"/>
-      <c r="G136" s="6" t="n"/>
+      <c r="G136" s="5" t="n"/>
+      <c r="H136" s="6" t="n"/>
     </row>
     <row r="137" hidden="1" outlineLevel="2">
       <c r="A137" s="4" t="n">
@@ -2075,9 +2229,10 @@
       <c r="B137" s="5" t="n"/>
       <c r="C137" s="6" t="n"/>
       <c r="D137" s="6" t="n"/>
-      <c r="E137" s="5" t="n"/>
+      <c r="E137" s="6" t="n"/>
       <c r="F137" s="5" t="n"/>
-      <c r="G137" s="6" t="n"/>
+      <c r="G137" s="5" t="n"/>
+      <c r="H137" s="6" t="n"/>
     </row>
     <row r="138" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A138" s="4" t="n">
@@ -2086,9 +2241,10 @@
       <c r="B138" s="5" t="n"/>
       <c r="C138" s="6" t="n"/>
       <c r="D138" s="6" t="n"/>
-      <c r="E138" s="5" t="n"/>
+      <c r="E138" s="6" t="n"/>
       <c r="F138" s="5" t="n"/>
-      <c r="G138" s="6" t="n"/>
+      <c r="G138" s="5" t="n"/>
+      <c r="H138" s="6" t="n"/>
     </row>
     <row r="139" hidden="1" outlineLevel="2">
       <c r="A139" s="4" t="n">
@@ -2097,9 +2253,10 @@
       <c r="B139" s="5" t="n"/>
       <c r="C139" s="6" t="n"/>
       <c r="D139" s="6" t="n"/>
-      <c r="E139" s="5" t="n"/>
+      <c r="E139" s="6" t="n"/>
       <c r="F139" s="5" t="n"/>
-      <c r="G139" s="6" t="n"/>
+      <c r="G139" s="5" t="n"/>
+      <c r="H139" s="6" t="n"/>
     </row>
     <row r="140" hidden="1" outlineLevel="2">
       <c r="A140" s="4" t="n">
@@ -2108,9 +2265,10 @@
       <c r="B140" s="5" t="n"/>
       <c r="C140" s="6" t="n"/>
       <c r="D140" s="6" t="n"/>
-      <c r="E140" s="5" t="n"/>
+      <c r="E140" s="6" t="n"/>
       <c r="F140" s="5" t="n"/>
-      <c r="G140" s="6" t="n"/>
+      <c r="G140" s="5" t="n"/>
+      <c r="H140" s="6" t="n"/>
     </row>
     <row r="141" hidden="1" outlineLevel="2">
       <c r="A141" s="4" t="n">
@@ -2119,9 +2277,10 @@
       <c r="B141" s="5" t="n"/>
       <c r="C141" s="6" t="n"/>
       <c r="D141" s="6" t="n"/>
-      <c r="E141" s="5" t="n"/>
+      <c r="E141" s="6" t="n"/>
       <c r="F141" s="5" t="n"/>
-      <c r="G141" s="6" t="n"/>
+      <c r="G141" s="5" t="n"/>
+      <c r="H141" s="6" t="n"/>
     </row>
     <row r="142" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A142" s="4" t="n">
@@ -2130,9 +2289,10 @@
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="6" t="n"/>
       <c r="D142" s="6" t="n"/>
-      <c r="E142" s="5" t="n"/>
+      <c r="E142" s="6" t="n"/>
       <c r="F142" s="5" t="n"/>
-      <c r="G142" s="6" t="n"/>
+      <c r="G142" s="5" t="n"/>
+      <c r="H142" s="6" t="n"/>
     </row>
     <row r="143" hidden="1" outlineLevel="2">
       <c r="A143" s="4" t="n">
@@ -2141,9 +2301,10 @@
       <c r="B143" s="5" t="n"/>
       <c r="C143" s="6" t="n"/>
       <c r="D143" s="6" t="n"/>
-      <c r="E143" s="5" t="n"/>
+      <c r="E143" s="6" t="n"/>
       <c r="F143" s="5" t="n"/>
-      <c r="G143" s="6" t="n"/>
+      <c r="G143" s="5" t="n"/>
+      <c r="H143" s="6" t="n"/>
     </row>
     <row r="144" hidden="1" outlineLevel="2">
       <c r="A144" s="4" t="n">
@@ -2152,9 +2313,10 @@
       <c r="B144" s="5" t="n"/>
       <c r="C144" s="6" t="n"/>
       <c r="D144" s="6" t="n"/>
-      <c r="E144" s="5" t="n"/>
+      <c r="E144" s="6" t="n"/>
       <c r="F144" s="5" t="n"/>
-      <c r="G144" s="6" t="n"/>
+      <c r="G144" s="5" t="n"/>
+      <c r="H144" s="6" t="n"/>
     </row>
     <row r="145" hidden="1" outlineLevel="2">
       <c r="A145" s="4" t="n">
@@ -2163,9 +2325,10 @@
       <c r="B145" s="5" t="n"/>
       <c r="C145" s="6" t="n"/>
       <c r="D145" s="6" t="n"/>
-      <c r="E145" s="5" t="n"/>
+      <c r="E145" s="6" t="n"/>
       <c r="F145" s="5" t="n"/>
-      <c r="G145" s="6" t="n"/>
+      <c r="G145" s="5" t="n"/>
+      <c r="H145" s="6" t="n"/>
     </row>
     <row r="146" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A146" s="4" t="n">
@@ -2174,9 +2337,10 @@
       <c r="B146" s="5" t="n"/>
       <c r="C146" s="6" t="n"/>
       <c r="D146" s="6" t="n"/>
-      <c r="E146" s="5" t="n"/>
+      <c r="E146" s="6" t="n"/>
       <c r="F146" s="5" t="n"/>
-      <c r="G146" s="6" t="n"/>
+      <c r="G146" s="5" t="n"/>
+      <c r="H146" s="6" t="n"/>
     </row>
     <row r="147" hidden="1" outlineLevel="2">
       <c r="A147" s="4" t="n">
@@ -2185,9 +2349,10 @@
       <c r="B147" s="5" t="n"/>
       <c r="C147" s="6" t="n"/>
       <c r="D147" s="6" t="n"/>
-      <c r="E147" s="5" t="n"/>
+      <c r="E147" s="6" t="n"/>
       <c r="F147" s="5" t="n"/>
-      <c r="G147" s="6" t="n"/>
+      <c r="G147" s="5" t="n"/>
+      <c r="H147" s="6" t="n"/>
     </row>
     <row r="148" hidden="1" outlineLevel="2">
       <c r="A148" s="4" t="n">
@@ -2196,9 +2361,10 @@
       <c r="B148" s="5" t="n"/>
       <c r="C148" s="6" t="n"/>
       <c r="D148" s="6" t="n"/>
-      <c r="E148" s="5" t="n"/>
+      <c r="E148" s="6" t="n"/>
       <c r="F148" s="5" t="n"/>
-      <c r="G148" s="6" t="n"/>
+      <c r="G148" s="5" t="n"/>
+      <c r="H148" s="6" t="n"/>
     </row>
     <row r="149" hidden="1" outlineLevel="2">
       <c r="A149" s="4" t="n">
@@ -2207,9 +2373,10 @@
       <c r="B149" s="5" t="n"/>
       <c r="C149" s="6" t="n"/>
       <c r="D149" s="6" t="n"/>
-      <c r="E149" s="5" t="n"/>
+      <c r="E149" s="6" t="n"/>
       <c r="F149" s="5" t="n"/>
-      <c r="G149" s="6" t="n"/>
+      <c r="G149" s="5" t="n"/>
+      <c r="H149" s="6" t="n"/>
     </row>
     <row r="150" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A150" s="4" t="n">
@@ -2218,9 +2385,10 @@
       <c r="B150" s="5" t="n"/>
       <c r="C150" s="6" t="n"/>
       <c r="D150" s="6" t="n"/>
-      <c r="E150" s="5" t="n"/>
+      <c r="E150" s="6" t="n"/>
       <c r="F150" s="5" t="n"/>
-      <c r="G150" s="6" t="n"/>
+      <c r="G150" s="5" t="n"/>
+      <c r="H150" s="6" t="n"/>
     </row>
     <row r="151" hidden="1" outlineLevel="2">
       <c r="A151" s="4" t="n">
@@ -2229,9 +2397,10 @@
       <c r="B151" s="5" t="n"/>
       <c r="C151" s="6" t="n"/>
       <c r="D151" s="6" t="n"/>
-      <c r="E151" s="5" t="n"/>
+      <c r="E151" s="6" t="n"/>
       <c r="F151" s="5" t="n"/>
-      <c r="G151" s="6" t="n"/>
+      <c r="G151" s="5" t="n"/>
+      <c r="H151" s="6" t="n"/>
     </row>
     <row r="152" hidden="1" outlineLevel="2">
       <c r="A152" s="4" t="n">
@@ -2240,9 +2409,10 @@
       <c r="B152" s="5" t="n"/>
       <c r="C152" s="6" t="n"/>
       <c r="D152" s="6" t="n"/>
-      <c r="E152" s="5" t="n"/>
+      <c r="E152" s="6" t="n"/>
       <c r="F152" s="5" t="n"/>
-      <c r="G152" s="6" t="n"/>
+      <c r="G152" s="5" t="n"/>
+      <c r="H152" s="6" t="n"/>
     </row>
     <row r="153" hidden="1" outlineLevel="2">
       <c r="A153" s="4" t="n">
@@ -2251,9 +2421,10 @@
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="6" t="n"/>
       <c r="D153" s="6" t="n"/>
-      <c r="E153" s="5" t="n"/>
+      <c r="E153" s="6" t="n"/>
       <c r="F153" s="5" t="n"/>
-      <c r="G153" s="6" t="n"/>
+      <c r="G153" s="5" t="n"/>
+      <c r="H153" s="6" t="n"/>
     </row>
     <row r="154" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A154" s="4" t="n">
@@ -2262,9 +2433,10 @@
       <c r="B154" s="5" t="n"/>
       <c r="C154" s="6" t="n"/>
       <c r="D154" s="6" t="n"/>
-      <c r="E154" s="5" t="n"/>
+      <c r="E154" s="6" t="n"/>
       <c r="F154" s="5" t="n"/>
-      <c r="G154" s="6" t="n"/>
+      <c r="G154" s="5" t="n"/>
+      <c r="H154" s="6" t="n"/>
     </row>
     <row r="155" hidden="1" outlineLevel="2">
       <c r="A155" s="4" t="n">
@@ -2273,9 +2445,10 @@
       <c r="B155" s="5" t="n"/>
       <c r="C155" s="6" t="n"/>
       <c r="D155" s="6" t="n"/>
-      <c r="E155" s="5" t="n"/>
+      <c r="E155" s="6" t="n"/>
       <c r="F155" s="5" t="n"/>
-      <c r="G155" s="6" t="n"/>
+      <c r="G155" s="5" t="n"/>
+      <c r="H155" s="6" t="n"/>
     </row>
     <row r="156" hidden="1" outlineLevel="2">
       <c r="A156" s="4" t="n">
@@ -2284,9 +2457,10 @@
       <c r="B156" s="5" t="n"/>
       <c r="C156" s="6" t="n"/>
       <c r="D156" s="6" t="n"/>
-      <c r="E156" s="5" t="n"/>
+      <c r="E156" s="6" t="n"/>
       <c r="F156" s="5" t="n"/>
-      <c r="G156" s="6" t="n"/>
+      <c r="G156" s="5" t="n"/>
+      <c r="H156" s="6" t="n"/>
     </row>
     <row r="157" hidden="1" outlineLevel="2">
       <c r="A157" s="4" t="n">
@@ -2295,9 +2469,10 @@
       <c r="B157" s="5" t="n"/>
       <c r="C157" s="6" t="n"/>
       <c r="D157" s="6" t="n"/>
-      <c r="E157" s="5" t="n"/>
+      <c r="E157" s="6" t="n"/>
       <c r="F157" s="5" t="n"/>
-      <c r="G157" s="6" t="n"/>
+      <c r="G157" s="5" t="n"/>
+      <c r="H157" s="6" t="n"/>
     </row>
     <row r="158" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A158" s="4" t="n">
@@ -2306,9 +2481,10 @@
       <c r="B158" s="5" t="n"/>
       <c r="C158" s="6" t="n"/>
       <c r="D158" s="6" t="n"/>
-      <c r="E158" s="5" t="n"/>
+      <c r="E158" s="6" t="n"/>
       <c r="F158" s="5" t="n"/>
-      <c r="G158" s="6" t="n"/>
+      <c r="G158" s="5" t="n"/>
+      <c r="H158" s="6" t="n"/>
     </row>
     <row r="159" hidden="1" outlineLevel="2">
       <c r="A159" s="4" t="n">
@@ -2317,9 +2493,10 @@
       <c r="B159" s="5" t="n"/>
       <c r="C159" s="6" t="n"/>
       <c r="D159" s="6" t="n"/>
-      <c r="E159" s="5" t="n"/>
+      <c r="E159" s="6" t="n"/>
       <c r="F159" s="5" t="n"/>
-      <c r="G159" s="6" t="n"/>
+      <c r="G159" s="5" t="n"/>
+      <c r="H159" s="6" t="n"/>
     </row>
     <row r="160" hidden="1" outlineLevel="2">
       <c r="A160" s="4" t="n">
@@ -2328,9 +2505,10 @@
       <c r="B160" s="5" t="n"/>
       <c r="C160" s="6" t="n"/>
       <c r="D160" s="6" t="n"/>
-      <c r="E160" s="5" t="n"/>
+      <c r="E160" s="6" t="n"/>
       <c r="F160" s="5" t="n"/>
-      <c r="G160" s="6" t="n"/>
+      <c r="G160" s="5" t="n"/>
+      <c r="H160" s="6" t="n"/>
     </row>
     <row r="161" hidden="1" outlineLevel="2">
       <c r="A161" s="4" t="n">
@@ -2339,9 +2517,10 @@
       <c r="B161" s="5" t="n"/>
       <c r="C161" s="6" t="n"/>
       <c r="D161" s="6" t="n"/>
-      <c r="E161" s="5" t="n"/>
+      <c r="E161" s="6" t="n"/>
       <c r="F161" s="5" t="n"/>
-      <c r="G161" s="6" t="n"/>
+      <c r="G161" s="5" t="n"/>
+      <c r="H161" s="6" t="n"/>
     </row>
     <row r="162" collapsed="1">
       <c r="A162" s="4" t="n">
@@ -2359,12 +2538,13 @@
         </is>
       </c>
       <c r="D162" s="6" t="n"/>
-      <c r="E162" s="5" t="n"/>
-      <c r="F162" s="5">
+      <c r="E162" s="6" t="n"/>
+      <c r="F162" s="5" t="n"/>
+      <c r="G162" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G162" s="6" t="inlineStr">
+      <c r="H162" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(7870, 490, 35, 5, 26, 5, false, 4)</t>
         </is>
@@ -2377,9 +2557,10 @@
       <c r="B163" s="5" t="n"/>
       <c r="C163" s="6" t="n"/>
       <c r="D163" s="6" t="n"/>
-      <c r="E163" s="5" t="n"/>
+      <c r="E163" s="6" t="n"/>
       <c r="F163" s="5" t="n"/>
-      <c r="G163" s="6" t="n"/>
+      <c r="G163" s="5" t="n"/>
+      <c r="H163" s="6" t="n"/>
     </row>
     <row r="164" hidden="1" outlineLevel="2">
       <c r="A164" s="4" t="n">
@@ -2388,9 +2569,10 @@
       <c r="B164" s="5" t="n"/>
       <c r="C164" s="6" t="n"/>
       <c r="D164" s="6" t="n"/>
-      <c r="E164" s="5" t="n"/>
+      <c r="E164" s="6" t="n"/>
       <c r="F164" s="5" t="n"/>
-      <c r="G164" s="6" t="n"/>
+      <c r="G164" s="5" t="n"/>
+      <c r="H164" s="6" t="n"/>
     </row>
     <row r="165" hidden="1" outlineLevel="2">
       <c r="A165" s="4" t="n">
@@ -2399,9 +2581,10 @@
       <c r="B165" s="5" t="n"/>
       <c r="C165" s="6" t="n"/>
       <c r="D165" s="6" t="n"/>
-      <c r="E165" s="5" t="n"/>
+      <c r="E165" s="6" t="n"/>
       <c r="F165" s="5" t="n"/>
-      <c r="G165" s="6" t="n"/>
+      <c r="G165" s="5" t="n"/>
+      <c r="H165" s="6" t="n"/>
     </row>
     <row r="166" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A166" s="4" t="n">
@@ -2410,9 +2593,10 @@
       <c r="B166" s="5" t="n"/>
       <c r="C166" s="6" t="n"/>
       <c r="D166" s="6" t="n"/>
-      <c r="E166" s="5" t="n"/>
+      <c r="E166" s="6" t="n"/>
       <c r="F166" s="5" t="n"/>
-      <c r="G166" s="6" t="n"/>
+      <c r="G166" s="5" t="n"/>
+      <c r="H166" s="6" t="n"/>
     </row>
     <row r="167" hidden="1" outlineLevel="2">
       <c r="A167" s="4" t="n">
@@ -2421,9 +2605,10 @@
       <c r="B167" s="5" t="n"/>
       <c r="C167" s="6" t="n"/>
       <c r="D167" s="6" t="n"/>
-      <c r="E167" s="5" t="n"/>
+      <c r="E167" s="6" t="n"/>
       <c r="F167" s="5" t="n"/>
-      <c r="G167" s="6" t="n"/>
+      <c r="G167" s="5" t="n"/>
+      <c r="H167" s="6" t="n"/>
     </row>
     <row r="168" hidden="1" outlineLevel="2">
       <c r="A168" s="4" t="n">
@@ -2432,9 +2617,10 @@
       <c r="B168" s="5" t="n"/>
       <c r="C168" s="6" t="n"/>
       <c r="D168" s="6" t="n"/>
-      <c r="E168" s="5" t="n"/>
+      <c r="E168" s="6" t="n"/>
       <c r="F168" s="5" t="n"/>
-      <c r="G168" s="6" t="n"/>
+      <c r="G168" s="5" t="n"/>
+      <c r="H168" s="6" t="n"/>
     </row>
     <row r="169" hidden="1" outlineLevel="2">
       <c r="A169" s="4" t="n">
@@ -2443,9 +2629,10 @@
       <c r="B169" s="5" t="n"/>
       <c r="C169" s="6" t="n"/>
       <c r="D169" s="6" t="n"/>
-      <c r="E169" s="5" t="n"/>
+      <c r="E169" s="6" t="n"/>
       <c r="F169" s="5" t="n"/>
-      <c r="G169" s="6" t="n"/>
+      <c r="G169" s="5" t="n"/>
+      <c r="H169" s="6" t="n"/>
     </row>
     <row r="170" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A170" s="4" t="n">
@@ -2454,9 +2641,10 @@
       <c r="B170" s="5" t="n"/>
       <c r="C170" s="6" t="n"/>
       <c r="D170" s="6" t="n"/>
-      <c r="E170" s="5" t="n"/>
+      <c r="E170" s="6" t="n"/>
       <c r="F170" s="5" t="n"/>
-      <c r="G170" s="6" t="n"/>
+      <c r="G170" s="5" t="n"/>
+      <c r="H170" s="6" t="n"/>
     </row>
     <row r="171" hidden="1" outlineLevel="2">
       <c r="A171" s="4" t="n">
@@ -2465,9 +2653,10 @@
       <c r="B171" s="5" t="n"/>
       <c r="C171" s="6" t="n"/>
       <c r="D171" s="6" t="n"/>
-      <c r="E171" s="5" t="n"/>
+      <c r="E171" s="6" t="n"/>
       <c r="F171" s="5" t="n"/>
-      <c r="G171" s="6" t="n"/>
+      <c r="G171" s="5" t="n"/>
+      <c r="H171" s="6" t="n"/>
     </row>
     <row r="172" hidden="1" outlineLevel="2">
       <c r="A172" s="4" t="n">
@@ -2476,9 +2665,10 @@
       <c r="B172" s="5" t="n"/>
       <c r="C172" s="6" t="n"/>
       <c r="D172" s="6" t="n"/>
-      <c r="E172" s="5" t="n"/>
+      <c r="E172" s="6" t="n"/>
       <c r="F172" s="5" t="n"/>
-      <c r="G172" s="6" t="n"/>
+      <c r="G172" s="5" t="n"/>
+      <c r="H172" s="6" t="n"/>
     </row>
     <row r="173" hidden="1" outlineLevel="2">
       <c r="A173" s="4" t="n">
@@ -2487,9 +2677,10 @@
       <c r="B173" s="5" t="n"/>
       <c r="C173" s="6" t="n"/>
       <c r="D173" s="6" t="n"/>
-      <c r="E173" s="5" t="n"/>
+      <c r="E173" s="6" t="n"/>
       <c r="F173" s="5" t="n"/>
-      <c r="G173" s="6" t="n"/>
+      <c r="G173" s="5" t="n"/>
+      <c r="H173" s="6" t="n"/>
     </row>
     <row r="174" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A174" s="4" t="n">
@@ -2498,9 +2689,10 @@
       <c r="B174" s="5" t="n"/>
       <c r="C174" s="6" t="n"/>
       <c r="D174" s="6" t="n"/>
-      <c r="E174" s="5" t="n"/>
+      <c r="E174" s="6" t="n"/>
       <c r="F174" s="5" t="n"/>
-      <c r="G174" s="6" t="n"/>
+      <c r="G174" s="5" t="n"/>
+      <c r="H174" s="6" t="n"/>
     </row>
     <row r="175" hidden="1" outlineLevel="2">
       <c r="A175" s="4" t="n">
@@ -2509,9 +2701,10 @@
       <c r="B175" s="5" t="n"/>
       <c r="C175" s="6" t="n"/>
       <c r="D175" s="6" t="n"/>
-      <c r="E175" s="5" t="n"/>
+      <c r="E175" s="6" t="n"/>
       <c r="F175" s="5" t="n"/>
-      <c r="G175" s="6" t="n"/>
+      <c r="G175" s="5" t="n"/>
+      <c r="H175" s="6" t="n"/>
     </row>
     <row r="176" hidden="1" outlineLevel="2">
       <c r="A176" s="4" t="n">
@@ -2520,9 +2713,10 @@
       <c r="B176" s="5" t="n"/>
       <c r="C176" s="6" t="n"/>
       <c r="D176" s="6" t="n"/>
-      <c r="E176" s="5" t="n"/>
+      <c r="E176" s="6" t="n"/>
       <c r="F176" s="5" t="n"/>
-      <c r="G176" s="6" t="n"/>
+      <c r="G176" s="5" t="n"/>
+      <c r="H176" s="6" t="n"/>
     </row>
     <row r="177" hidden="1" outlineLevel="2">
       <c r="A177" s="4" t="n">
@@ -2531,9 +2725,10 @@
       <c r="B177" s="5" t="n"/>
       <c r="C177" s="6" t="n"/>
       <c r="D177" s="6" t="n"/>
-      <c r="E177" s="5" t="n"/>
+      <c r="E177" s="6" t="n"/>
       <c r="F177" s="5" t="n"/>
-      <c r="G177" s="6" t="n"/>
+      <c r="G177" s="5" t="n"/>
+      <c r="H177" s="6" t="n"/>
     </row>
     <row r="178" collapsed="1">
       <c r="A178" s="4" t="n">
@@ -2553,12 +2748,13 @@
         </is>
       </c>
       <c r="D178" s="6" t="n"/>
-      <c r="E178" s="5" t="n"/>
-      <c r="F178" s="5">
+      <c r="E178" s="6" t="n"/>
+      <c r="F178" s="5" t="n"/>
+      <c r="G178" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G178" s="6" t="inlineStr">
+      <c r="H178" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(7870, 4, 40)</t>
         </is>
@@ -2571,9 +2767,10 @@
       <c r="B179" s="5" t="n"/>
       <c r="C179" s="6" t="n"/>
       <c r="D179" s="6" t="n"/>
-      <c r="E179" s="5" t="n"/>
+      <c r="E179" s="6" t="n"/>
       <c r="F179" s="5" t="n"/>
-      <c r="G179" s="6" t="n"/>
+      <c r="G179" s="5" t="n"/>
+      <c r="H179" s="6" t="n"/>
     </row>
     <row r="180" hidden="1" outlineLevel="2">
       <c r="A180" s="4" t="n">
@@ -2582,9 +2779,10 @@
       <c r="B180" s="5" t="n"/>
       <c r="C180" s="6" t="n"/>
       <c r="D180" s="6" t="n"/>
-      <c r="E180" s="5" t="n"/>
+      <c r="E180" s="6" t="n"/>
       <c r="F180" s="5" t="n"/>
-      <c r="G180" s="6" t="n"/>
+      <c r="G180" s="5" t="n"/>
+      <c r="H180" s="6" t="n"/>
     </row>
     <row r="181" hidden="1" outlineLevel="2">
       <c r="A181" s="4" t="n">
@@ -2593,9 +2791,10 @@
       <c r="B181" s="5" t="n"/>
       <c r="C181" s="6" t="n"/>
       <c r="D181" s="6" t="n"/>
-      <c r="E181" s="5" t="n"/>
+      <c r="E181" s="6" t="n"/>
       <c r="F181" s="5" t="n"/>
-      <c r="G181" s="6" t="n"/>
+      <c r="G181" s="5" t="n"/>
+      <c r="H181" s="6" t="n"/>
     </row>
     <row r="182" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A182" s="4" t="n">
@@ -2604,9 +2803,10 @@
       <c r="B182" s="5" t="n"/>
       <c r="C182" s="6" t="n"/>
       <c r="D182" s="6" t="n"/>
-      <c r="E182" s="5" t="n"/>
+      <c r="E182" s="6" t="n"/>
       <c r="F182" s="5" t="n"/>
-      <c r="G182" s="6" t="n"/>
+      <c r="G182" s="5" t="n"/>
+      <c r="H182" s="6" t="n"/>
     </row>
     <row r="183" hidden="1" outlineLevel="2">
       <c r="A183" s="4" t="n">
@@ -2615,9 +2815,10 @@
       <c r="B183" s="5" t="n"/>
       <c r="C183" s="6" t="n"/>
       <c r="D183" s="6" t="n"/>
-      <c r="E183" s="5" t="n"/>
+      <c r="E183" s="6" t="n"/>
       <c r="F183" s="5" t="n"/>
-      <c r="G183" s="6" t="n"/>
+      <c r="G183" s="5" t="n"/>
+      <c r="H183" s="6" t="n"/>
     </row>
     <row r="184" hidden="1" outlineLevel="2">
       <c r="A184" s="4" t="n">
@@ -2626,9 +2827,10 @@
       <c r="B184" s="5" t="n"/>
       <c r="C184" s="6" t="n"/>
       <c r="D184" s="6" t="n"/>
-      <c r="E184" s="5" t="n"/>
+      <c r="E184" s="6" t="n"/>
       <c r="F184" s="5" t="n"/>
-      <c r="G184" s="6" t="n"/>
+      <c r="G184" s="5" t="n"/>
+      <c r="H184" s="6" t="n"/>
     </row>
     <row r="185" hidden="1" outlineLevel="2">
       <c r="A185" s="4" t="n">
@@ -2637,9 +2839,10 @@
       <c r="B185" s="5" t="n"/>
       <c r="C185" s="6" t="n"/>
       <c r="D185" s="6" t="n"/>
-      <c r="E185" s="5" t="n"/>
+      <c r="E185" s="6" t="n"/>
       <c r="F185" s="5" t="n"/>
-      <c r="G185" s="6" t="n"/>
+      <c r="G185" s="5" t="n"/>
+      <c r="H185" s="6" t="n"/>
     </row>
     <row r="186" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A186" s="4" t="n">
@@ -2648,9 +2851,10 @@
       <c r="B186" s="5" t="n"/>
       <c r="C186" s="6" t="n"/>
       <c r="D186" s="6" t="n"/>
-      <c r="E186" s="5" t="n"/>
+      <c r="E186" s="6" t="n"/>
       <c r="F186" s="5" t="n"/>
-      <c r="G186" s="6" t="n"/>
+      <c r="G186" s="5" t="n"/>
+      <c r="H186" s="6" t="n"/>
     </row>
     <row r="187" hidden="1" outlineLevel="2">
       <c r="A187" s="4" t="n">
@@ -2659,9 +2863,10 @@
       <c r="B187" s="5" t="n"/>
       <c r="C187" s="6" t="n"/>
       <c r="D187" s="6" t="n"/>
-      <c r="E187" s="5" t="n"/>
+      <c r="E187" s="6" t="n"/>
       <c r="F187" s="5" t="n"/>
-      <c r="G187" s="6" t="n"/>
+      <c r="G187" s="5" t="n"/>
+      <c r="H187" s="6" t="n"/>
     </row>
     <row r="188" hidden="1" outlineLevel="2">
       <c r="A188" s="4" t="n">
@@ -2670,9 +2875,10 @@
       <c r="B188" s="5" t="n"/>
       <c r="C188" s="6" t="n"/>
       <c r="D188" s="6" t="n"/>
-      <c r="E188" s="5" t="n"/>
+      <c r="E188" s="6" t="n"/>
       <c r="F188" s="5" t="n"/>
-      <c r="G188" s="6" t="n"/>
+      <c r="G188" s="5" t="n"/>
+      <c r="H188" s="6" t="n"/>
     </row>
     <row r="189" hidden="1" outlineLevel="2">
       <c r="A189" s="4" t="n">
@@ -2681,9 +2887,10 @@
       <c r="B189" s="5" t="n"/>
       <c r="C189" s="6" t="n"/>
       <c r="D189" s="6" t="n"/>
-      <c r="E189" s="5" t="n"/>
+      <c r="E189" s="6" t="n"/>
       <c r="F189" s="5" t="n"/>
-      <c r="G189" s="6" t="n"/>
+      <c r="G189" s="5" t="n"/>
+      <c r="H189" s="6" t="n"/>
     </row>
     <row r="190" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A190" s="4" t="n">
@@ -2692,9 +2899,10 @@
       <c r="B190" s="5" t="n"/>
       <c r="C190" s="6" t="n"/>
       <c r="D190" s="6" t="n"/>
-      <c r="E190" s="5" t="n"/>
+      <c r="E190" s="6" t="n"/>
       <c r="F190" s="5" t="n"/>
-      <c r="G190" s="6" t="n"/>
+      <c r="G190" s="5" t="n"/>
+      <c r="H190" s="6" t="n"/>
     </row>
     <row r="191" hidden="1" outlineLevel="2">
       <c r="A191" s="4" t="n">
@@ -2703,9 +2911,10 @@
       <c r="B191" s="5" t="n"/>
       <c r="C191" s="6" t="n"/>
       <c r="D191" s="6" t="n"/>
-      <c r="E191" s="5" t="n"/>
+      <c r="E191" s="6" t="n"/>
       <c r="F191" s="5" t="n"/>
-      <c r="G191" s="6" t="n"/>
+      <c r="G191" s="5" t="n"/>
+      <c r="H191" s="6" t="n"/>
     </row>
     <row r="192" hidden="1" outlineLevel="2">
       <c r="A192" s="4" t="n">
@@ -2714,9 +2923,10 @@
       <c r="B192" s="5" t="n"/>
       <c r="C192" s="6" t="n"/>
       <c r="D192" s="6" t="n"/>
-      <c r="E192" s="5" t="n"/>
+      <c r="E192" s="6" t="n"/>
       <c r="F192" s="5" t="n"/>
-      <c r="G192" s="6" t="n"/>
+      <c r="G192" s="5" t="n"/>
+      <c r="H192" s="6" t="n"/>
     </row>
     <row r="193" hidden="1" outlineLevel="2">
       <c r="A193" s="4" t="n">
@@ -2725,9 +2935,10 @@
       <c r="B193" s="5" t="n"/>
       <c r="C193" s="6" t="n"/>
       <c r="D193" s="6" t="n"/>
-      <c r="E193" s="5" t="n"/>
+      <c r="E193" s="6" t="n"/>
       <c r="F193" s="5" t="n"/>
-      <c r="G193" s="6" t="n"/>
+      <c r="G193" s="5" t="n"/>
+      <c r="H193" s="6" t="n"/>
     </row>
     <row r="194" collapsed="1">
       <c r="A194" s="4" t="n">
@@ -2745,12 +2956,13 @@
         </is>
       </c>
       <c r="D194" s="6" t="n"/>
-      <c r="E194" s="5" t="n"/>
-      <c r="F194" s="5">
+      <c r="E194" s="6" t="n"/>
+      <c r="F194" s="5" t="n"/>
+      <c r="G194" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G194" s="6" t="inlineStr">
+      <c r="H194" s="6" t="inlineStr">
         <is>
           <t>progBlack(3935, 45)</t>
         </is>
@@ -2763,9 +2975,10 @@
       <c r="B195" s="5" t="n"/>
       <c r="C195" s="6" t="n"/>
       <c r="D195" s="6" t="n"/>
-      <c r="E195" s="5" t="n"/>
+      <c r="E195" s="6" t="n"/>
       <c r="F195" s="5" t="n"/>
-      <c r="G195" s="6" t="n"/>
+      <c r="G195" s="5" t="n"/>
+      <c r="H195" s="6" t="n"/>
     </row>
     <row r="196" hidden="1" outlineLevel="2">
       <c r="A196" s="4" t="n">
@@ -2774,9 +2987,10 @@
       <c r="B196" s="5" t="n"/>
       <c r="C196" s="6" t="n"/>
       <c r="D196" s="6" t="n"/>
-      <c r="E196" s="5" t="n"/>
+      <c r="E196" s="6" t="n"/>
       <c r="F196" s="5" t="n"/>
-      <c r="G196" s="6" t="n"/>
+      <c r="G196" s="5" t="n"/>
+      <c r="H196" s="6" t="n"/>
     </row>
     <row r="197" hidden="1" outlineLevel="2">
       <c r="A197" s="4" t="n">
@@ -2785,9 +2999,10 @@
       <c r="B197" s="5" t="n"/>
       <c r="C197" s="6" t="n"/>
       <c r="D197" s="6" t="n"/>
-      <c r="E197" s="5" t="n"/>
+      <c r="E197" s="6" t="n"/>
       <c r="F197" s="5" t="n"/>
-      <c r="G197" s="6" t="n"/>
+      <c r="G197" s="5" t="n"/>
+      <c r="H197" s="6" t="n"/>
     </row>
     <row r="198" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A198" s="4" t="n">
@@ -2796,9 +3011,10 @@
       <c r="B198" s="5" t="n"/>
       <c r="C198" s="6" t="n"/>
       <c r="D198" s="6" t="n"/>
-      <c r="E198" s="5" t="n"/>
+      <c r="E198" s="6" t="n"/>
       <c r="F198" s="5" t="n"/>
-      <c r="G198" s="6" t="n"/>
+      <c r="G198" s="5" t="n"/>
+      <c r="H198" s="6" t="n"/>
     </row>
     <row r="199" hidden="1" outlineLevel="2">
       <c r="A199" s="4" t="n">
@@ -2807,9 +3023,10 @@
       <c r="B199" s="5" t="n"/>
       <c r="C199" s="6" t="n"/>
       <c r="D199" s="6" t="n"/>
-      <c r="E199" s="5" t="n"/>
+      <c r="E199" s="6" t="n"/>
       <c r="F199" s="5" t="n"/>
-      <c r="G199" s="6" t="n"/>
+      <c r="G199" s="5" t="n"/>
+      <c r="H199" s="6" t="n"/>
     </row>
     <row r="200" hidden="1" outlineLevel="2">
       <c r="A200" s="4" t="n">
@@ -2818,9 +3035,10 @@
       <c r="B200" s="5" t="n"/>
       <c r="C200" s="6" t="n"/>
       <c r="D200" s="6" t="n"/>
-      <c r="E200" s="5" t="n"/>
+      <c r="E200" s="6" t="n"/>
       <c r="F200" s="5" t="n"/>
-      <c r="G200" s="6" t="n"/>
+      <c r="G200" s="5" t="n"/>
+      <c r="H200" s="6" t="n"/>
     </row>
     <row r="201" hidden="1" outlineLevel="2">
       <c r="A201" s="4" t="n">
@@ -2829,9 +3047,10 @@
       <c r="B201" s="5" t="n"/>
       <c r="C201" s="6" t="n"/>
       <c r="D201" s="6" t="n"/>
-      <c r="E201" s="5" t="n"/>
+      <c r="E201" s="6" t="n"/>
       <c r="F201" s="5" t="n"/>
-      <c r="G201" s="6" t="n"/>
+      <c r="G201" s="5" t="n"/>
+      <c r="H201" s="6" t="n"/>
     </row>
     <row r="202" collapsed="1">
       <c r="A202" s="4" t="n">
@@ -2842,19 +3061,25 @@
           <t>verse 2b</t>
         </is>
       </c>
-      <c r="C202" s="6" t="inlineStr">
+      <c r="C202" s="8" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE_WAVES, Farben SCHEME_ROYAL
+zurück in den Puls, eine Stufe wärmer als Verse 1 (Blau/Violett): Sinuswellen laufen im Takt über die Matrix, eine Lichtebene fährt je Takt über Gitarre und Bass, Lichtschuss in den Lampen</t>
+        </is>
+      </c>
+      <c r="D202" s="6" t="inlineStr">
         <is>
           <t>SCENE_VERSE, Farben SCHEME_ROYAL
 zurück in den Puls, eine Stufe wärmer als Verse 1 (Blau/Violett), auf der Matrix farbiger Regen</t>
         </is>
       </c>
-      <c r="D202" s="6" t="n"/>
-      <c r="E202" s="5" t="n"/>
-      <c r="F202" s="5">
+      <c r="E202" s="6" t="n"/>
+      <c r="F202" s="5" t="n"/>
+      <c r="G202" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G202" s="6" t="inlineStr">
+      <c r="H202" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(19670, 55, 3000)
 ! im alten Code ein einziger Part mit den folgenden 1</t>
@@ -2868,9 +3093,10 @@
       <c r="B203" s="5" t="n"/>
       <c r="C203" s="6" t="n"/>
       <c r="D203" s="6" t="n"/>
-      <c r="E203" s="5" t="n"/>
+      <c r="E203" s="6" t="n"/>
       <c r="F203" s="5" t="n"/>
-      <c r="G203" s="6" t="n"/>
+      <c r="G203" s="5" t="n"/>
+      <c r="H203" s="6" t="n"/>
     </row>
     <row r="204" hidden="1" outlineLevel="2">
       <c r="A204" s="4" t="n">
@@ -2879,9 +3105,10 @@
       <c r="B204" s="5" t="n"/>
       <c r="C204" s="6" t="n"/>
       <c r="D204" s="6" t="n"/>
-      <c r="E204" s="5" t="n"/>
+      <c r="E204" s="6" t="n"/>
       <c r="F204" s="5" t="n"/>
-      <c r="G204" s="6" t="n"/>
+      <c r="G204" s="5" t="n"/>
+      <c r="H204" s="6" t="n"/>
     </row>
     <row r="205" hidden="1" outlineLevel="2">
       <c r="A205" s="4" t="n">
@@ -2890,9 +3117,10 @@
       <c r="B205" s="5" t="n"/>
       <c r="C205" s="6" t="n"/>
       <c r="D205" s="6" t="n"/>
-      <c r="E205" s="5" t="n"/>
+      <c r="E205" s="6" t="n"/>
       <c r="F205" s="5" t="n"/>
-      <c r="G205" s="6" t="n"/>
+      <c r="G205" s="5" t="n"/>
+      <c r="H205" s="6" t="n"/>
     </row>
     <row r="206" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A206" s="4" t="n">
@@ -2901,9 +3129,10 @@
       <c r="B206" s="5" t="n"/>
       <c r="C206" s="6" t="n"/>
       <c r="D206" s="6" t="n"/>
-      <c r="E206" s="5" t="n"/>
+      <c r="E206" s="6" t="n"/>
       <c r="F206" s="5" t="n"/>
-      <c r="G206" s="6" t="n"/>
+      <c r="G206" s="5" t="n"/>
+      <c r="H206" s="6" t="n"/>
     </row>
     <row r="207" hidden="1" outlineLevel="2">
       <c r="A207" s="4" t="n">
@@ -2912,9 +3141,10 @@
       <c r="B207" s="5" t="n"/>
       <c r="C207" s="6" t="n"/>
       <c r="D207" s="6" t="n"/>
-      <c r="E207" s="5" t="n"/>
+      <c r="E207" s="6" t="n"/>
       <c r="F207" s="5" t="n"/>
-      <c r="G207" s="6" t="n"/>
+      <c r="G207" s="5" t="n"/>
+      <c r="H207" s="6" t="n"/>
     </row>
     <row r="208" hidden="1" outlineLevel="2">
       <c r="A208" s="4" t="n">
@@ -2923,9 +3153,10 @@
       <c r="B208" s="5" t="n"/>
       <c r="C208" s="6" t="n"/>
       <c r="D208" s="6" t="n"/>
-      <c r="E208" s="5" t="n"/>
+      <c r="E208" s="6" t="n"/>
       <c r="F208" s="5" t="n"/>
-      <c r="G208" s="6" t="n"/>
+      <c r="G208" s="5" t="n"/>
+      <c r="H208" s="6" t="n"/>
     </row>
     <row r="209" hidden="1" outlineLevel="2">
       <c r="A209" s="4" t="n">
@@ -2934,9 +3165,10 @@
       <c r="B209" s="5" t="n"/>
       <c r="C209" s="6" t="n"/>
       <c r="D209" s="6" t="n"/>
-      <c r="E209" s="5" t="n"/>
+      <c r="E209" s="6" t="n"/>
       <c r="F209" s="5" t="n"/>
-      <c r="G209" s="6" t="n"/>
+      <c r="G209" s="5" t="n"/>
+      <c r="H209" s="6" t="n"/>
     </row>
     <row r="210" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A210" s="4" t="n">
@@ -2945,9 +3177,10 @@
       <c r="B210" s="5" t="n"/>
       <c r="C210" s="6" t="n"/>
       <c r="D210" s="6" t="n"/>
-      <c r="E210" s="5" t="n"/>
+      <c r="E210" s="6" t="n"/>
       <c r="F210" s="5" t="n"/>
-      <c r="G210" s="6" t="n"/>
+      <c r="G210" s="5" t="n"/>
+      <c r="H210" s="6" t="n"/>
     </row>
     <row r="211" hidden="1" outlineLevel="2">
       <c r="A211" s="4" t="n">
@@ -2956,9 +3189,10 @@
       <c r="B211" s="5" t="n"/>
       <c r="C211" s="6" t="n"/>
       <c r="D211" s="6" t="n"/>
-      <c r="E211" s="5" t="n"/>
+      <c r="E211" s="6" t="n"/>
       <c r="F211" s="5" t="n"/>
-      <c r="G211" s="6" t="n"/>
+      <c r="G211" s="5" t="n"/>
+      <c r="H211" s="6" t="n"/>
     </row>
     <row r="212" hidden="1" outlineLevel="2">
       <c r="A212" s="4" t="n">
@@ -2967,9 +3201,10 @@
       <c r="B212" s="5" t="n"/>
       <c r="C212" s="6" t="n"/>
       <c r="D212" s="6" t="n"/>
-      <c r="E212" s="5" t="n"/>
+      <c r="E212" s="6" t="n"/>
       <c r="F212" s="5" t="n"/>
-      <c r="G212" s="6" t="n"/>
+      <c r="G212" s="5" t="n"/>
+      <c r="H212" s="6" t="n"/>
     </row>
     <row r="213" hidden="1" outlineLevel="2">
       <c r="A213" s="4" t="n">
@@ -2978,9 +3213,10 @@
       <c r="B213" s="5" t="n"/>
       <c r="C213" s="6" t="n"/>
       <c r="D213" s="6" t="n"/>
-      <c r="E213" s="5" t="n"/>
+      <c r="E213" s="6" t="n"/>
       <c r="F213" s="5" t="n"/>
-      <c r="G213" s="6" t="n"/>
+      <c r="G213" s="5" t="n"/>
+      <c r="H213" s="6" t="n"/>
     </row>
     <row r="214" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A214" s="4" t="n">
@@ -2989,9 +3225,10 @@
       <c r="B214" s="5" t="n"/>
       <c r="C214" s="6" t="n"/>
       <c r="D214" s="6" t="n"/>
-      <c r="E214" s="5" t="n"/>
+      <c r="E214" s="6" t="n"/>
       <c r="F214" s="5" t="n"/>
-      <c r="G214" s="6" t="n"/>
+      <c r="G214" s="5" t="n"/>
+      <c r="H214" s="6" t="n"/>
     </row>
     <row r="215" hidden="1" outlineLevel="2">
       <c r="A215" s="4" t="n">
@@ -3000,9 +3237,10 @@
       <c r="B215" s="5" t="n"/>
       <c r="C215" s="6" t="n"/>
       <c r="D215" s="6" t="n"/>
-      <c r="E215" s="5" t="n"/>
+      <c r="E215" s="6" t="n"/>
       <c r="F215" s="5" t="n"/>
-      <c r="G215" s="6" t="n"/>
+      <c r="G215" s="5" t="n"/>
+      <c r="H215" s="6" t="n"/>
     </row>
     <row r="216" hidden="1" outlineLevel="2">
       <c r="A216" s="4" t="n">
@@ -3011,9 +3249,10 @@
       <c r="B216" s="5" t="n"/>
       <c r="C216" s="6" t="n"/>
       <c r="D216" s="6" t="n"/>
-      <c r="E216" s="5" t="n"/>
+      <c r="E216" s="6" t="n"/>
       <c r="F216" s="5" t="n"/>
-      <c r="G216" s="6" t="n"/>
+      <c r="G216" s="5" t="n"/>
+      <c r="H216" s="6" t="n"/>
     </row>
     <row r="217" hidden="1" outlineLevel="2">
       <c r="A217" s="4" t="n">
@@ -3022,9 +3261,10 @@
       <c r="B217" s="5" t="n"/>
       <c r="C217" s="6" t="n"/>
       <c r="D217" s="6" t="n"/>
-      <c r="E217" s="5" t="n"/>
+      <c r="E217" s="6" t="n"/>
       <c r="F217" s="5" t="n"/>
-      <c r="G217" s="6" t="n"/>
+      <c r="G217" s="5" t="n"/>
+      <c r="H217" s="6" t="n"/>
     </row>
     <row r="218" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A218" s="4" t="n">
@@ -3033,9 +3273,10 @@
       <c r="B218" s="5" t="n"/>
       <c r="C218" s="6" t="n"/>
       <c r="D218" s="6" t="n"/>
-      <c r="E218" s="5" t="n"/>
+      <c r="E218" s="6" t="n"/>
       <c r="F218" s="5" t="n"/>
-      <c r="G218" s="6" t="n"/>
+      <c r="G218" s="5" t="n"/>
+      <c r="H218" s="6" t="n"/>
     </row>
     <row r="219" hidden="1" outlineLevel="2">
       <c r="A219" s="4" t="n">
@@ -3044,9 +3285,10 @@
       <c r="B219" s="5" t="n"/>
       <c r="C219" s="6" t="n"/>
       <c r="D219" s="6" t="n"/>
-      <c r="E219" s="5" t="n"/>
+      <c r="E219" s="6" t="n"/>
       <c r="F219" s="5" t="n"/>
-      <c r="G219" s="6" t="n"/>
+      <c r="G219" s="5" t="n"/>
+      <c r="H219" s="6" t="n"/>
     </row>
     <row r="220" hidden="1" outlineLevel="2">
       <c r="A220" s="4" t="n">
@@ -3055,9 +3297,10 @@
       <c r="B220" s="5" t="n"/>
       <c r="C220" s="6" t="n"/>
       <c r="D220" s="6" t="n"/>
-      <c r="E220" s="5" t="n"/>
+      <c r="E220" s="6" t="n"/>
       <c r="F220" s="5" t="n"/>
-      <c r="G220" s="6" t="n"/>
+      <c r="G220" s="5" t="n"/>
+      <c r="H220" s="6" t="n"/>
     </row>
     <row r="221" hidden="1" outlineLevel="2">
       <c r="A221" s="4" t="n">
@@ -3066,9 +3309,10 @@
       <c r="B221" s="5" t="n"/>
       <c r="C221" s="6" t="n"/>
       <c r="D221" s="6" t="n"/>
-      <c r="E221" s="5" t="n"/>
+      <c r="E221" s="6" t="n"/>
       <c r="F221" s="5" t="n"/>
-      <c r="G221" s="6" t="n"/>
+      <c r="G221" s="5" t="n"/>
+      <c r="H221" s="6" t="n"/>
     </row>
     <row r="222" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A222" s="4" t="n">
@@ -3077,9 +3321,10 @@
       <c r="B222" s="5" t="n"/>
       <c r="C222" s="6" t="n"/>
       <c r="D222" s="6" t="n"/>
-      <c r="E222" s="5" t="n"/>
+      <c r="E222" s="6" t="n"/>
       <c r="F222" s="5" t="n"/>
-      <c r="G222" s="6" t="n"/>
+      <c r="G222" s="5" t="n"/>
+      <c r="H222" s="6" t="n"/>
     </row>
     <row r="223" hidden="1" outlineLevel="2">
       <c r="A223" s="4" t="n">
@@ -3088,9 +3333,10 @@
       <c r="B223" s="5" t="n"/>
       <c r="C223" s="6" t="n"/>
       <c r="D223" s="6" t="n"/>
-      <c r="E223" s="5" t="n"/>
+      <c r="E223" s="6" t="n"/>
       <c r="F223" s="5" t="n"/>
-      <c r="G223" s="6" t="n"/>
+      <c r="G223" s="5" t="n"/>
+      <c r="H223" s="6" t="n"/>
     </row>
     <row r="224" hidden="1" outlineLevel="2">
       <c r="A224" s="4" t="n">
@@ -3099,9 +3345,10 @@
       <c r="B224" s="5" t="n"/>
       <c r="C224" s="6" t="n"/>
       <c r="D224" s="6" t="n"/>
-      <c r="E224" s="5" t="n"/>
+      <c r="E224" s="6" t="n"/>
       <c r="F224" s="5" t="n"/>
-      <c r="G224" s="6" t="n"/>
+      <c r="G224" s="5" t="n"/>
+      <c r="H224" s="6" t="n"/>
     </row>
     <row r="225" hidden="1" outlineLevel="2">
       <c r="A225" s="4" t="n">
@@ -3110,9 +3357,10 @@
       <c r="B225" s="5" t="n"/>
       <c r="C225" s="6" t="n"/>
       <c r="D225" s="6" t="n"/>
-      <c r="E225" s="5" t="n"/>
+      <c r="E225" s="6" t="n"/>
       <c r="F225" s="5" t="n"/>
-      <c r="G225" s="6" t="n"/>
+      <c r="G225" s="5" t="n"/>
+      <c r="H225" s="6" t="n"/>
     </row>
     <row r="226" collapsed="1">
       <c r="A226" s="4" t="n">
@@ -3130,12 +3378,13 @@
         </is>
       </c>
       <c r="D226" s="6" t="n"/>
-      <c r="E226" s="5" t="n"/>
-      <c r="F226" s="5">
+      <c r="E226" s="6" t="n"/>
+      <c r="F226" s="5" t="n"/>
+      <c r="G226" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G226" s="6" t="n"/>
+      <c r="H226" s="6" t="n"/>
     </row>
     <row r="227" hidden="1" outlineLevel="2">
       <c r="A227" s="4" t="n">
@@ -3144,9 +3393,10 @@
       <c r="B227" s="5" t="n"/>
       <c r="C227" s="6" t="n"/>
       <c r="D227" s="6" t="n"/>
-      <c r="E227" s="5" t="n"/>
+      <c r="E227" s="6" t="n"/>
       <c r="F227" s="5" t="n"/>
-      <c r="G227" s="6" t="n"/>
+      <c r="G227" s="5" t="n"/>
+      <c r="H227" s="6" t="n"/>
     </row>
     <row r="228" hidden="1" outlineLevel="2">
       <c r="A228" s="4" t="n">
@@ -3155,9 +3405,10 @@
       <c r="B228" s="5" t="n"/>
       <c r="C228" s="6" t="n"/>
       <c r="D228" s="6" t="n"/>
-      <c r="E228" s="5" t="n"/>
+      <c r="E228" s="6" t="n"/>
       <c r="F228" s="5" t="n"/>
-      <c r="G228" s="6" t="n"/>
+      <c r="G228" s="5" t="n"/>
+      <c r="H228" s="6" t="n"/>
     </row>
     <row r="229" hidden="1" outlineLevel="2">
       <c r="A229" s="4" t="n">
@@ -3166,9 +3417,10 @@
       <c r="B229" s="5" t="n"/>
       <c r="C229" s="6" t="n"/>
       <c r="D229" s="6" t="n"/>
-      <c r="E229" s="5" t="n"/>
+      <c r="E229" s="6" t="n"/>
       <c r="F229" s="5" t="n"/>
-      <c r="G229" s="6" t="n"/>
+      <c r="G229" s="5" t="n"/>
+      <c r="H229" s="6" t="n"/>
     </row>
     <row r="230" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A230" s="4" t="n">
@@ -3177,9 +3429,10 @@
       <c r="B230" s="5" t="n"/>
       <c r="C230" s="6" t="n"/>
       <c r="D230" s="6" t="n"/>
-      <c r="E230" s="5" t="n"/>
+      <c r="E230" s="6" t="n"/>
       <c r="F230" s="5" t="n"/>
-      <c r="G230" s="6" t="n"/>
+      <c r="G230" s="5" t="n"/>
+      <c r="H230" s="6" t="n"/>
     </row>
     <row r="231" hidden="1" outlineLevel="2">
       <c r="A231" s="4" t="n">
@@ -3188,9 +3441,10 @@
       <c r="B231" s="5" t="n"/>
       <c r="C231" s="6" t="n"/>
       <c r="D231" s="6" t="n"/>
-      <c r="E231" s="5" t="n"/>
+      <c r="E231" s="6" t="n"/>
       <c r="F231" s="5" t="n"/>
-      <c r="G231" s="6" t="n"/>
+      <c r="G231" s="5" t="n"/>
+      <c r="H231" s="6" t="n"/>
     </row>
     <row r="232" hidden="1" outlineLevel="2">
       <c r="A232" s="4" t="n">
@@ -3199,9 +3453,10 @@
       <c r="B232" s="5" t="n"/>
       <c r="C232" s="6" t="n"/>
       <c r="D232" s="6" t="n"/>
-      <c r="E232" s="5" t="n"/>
+      <c r="E232" s="6" t="n"/>
       <c r="F232" s="5" t="n"/>
-      <c r="G232" s="6" t="n"/>
+      <c r="G232" s="5" t="n"/>
+      <c r="H232" s="6" t="n"/>
     </row>
     <row r="233" hidden="1" outlineLevel="2">
       <c r="A233" s="4" t="n">
@@ -3210,9 +3465,10 @@
       <c r="B233" s="5" t="n"/>
       <c r="C233" s="6" t="n"/>
       <c r="D233" s="6" t="n"/>
-      <c r="E233" s="5" t="n"/>
+      <c r="E233" s="6" t="n"/>
       <c r="F233" s="5" t="n"/>
-      <c r="G233" s="6" t="n"/>
+      <c r="G233" s="5" t="n"/>
+      <c r="H233" s="6" t="n"/>
     </row>
     <row r="234" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A234" s="4" t="n">
@@ -3221,9 +3477,10 @@
       <c r="B234" s="5" t="n"/>
       <c r="C234" s="6" t="n"/>
       <c r="D234" s="6" t="n"/>
-      <c r="E234" s="5" t="n"/>
+      <c r="E234" s="6" t="n"/>
       <c r="F234" s="5" t="n"/>
-      <c r="G234" s="6" t="n"/>
+      <c r="G234" s="5" t="n"/>
+      <c r="H234" s="6" t="n"/>
     </row>
     <row r="235" hidden="1" outlineLevel="2">
       <c r="A235" s="4" t="n">
@@ -3232,9 +3489,10 @@
       <c r="B235" s="5" t="n"/>
       <c r="C235" s="6" t="n"/>
       <c r="D235" s="6" t="n"/>
-      <c r="E235" s="5" t="n"/>
+      <c r="E235" s="6" t="n"/>
       <c r="F235" s="5" t="n"/>
-      <c r="G235" s="6" t="n"/>
+      <c r="G235" s="5" t="n"/>
+      <c r="H235" s="6" t="n"/>
     </row>
     <row r="236" hidden="1" outlineLevel="2">
       <c r="A236" s="4" t="n">
@@ -3243,9 +3501,10 @@
       <c r="B236" s="5" t="n"/>
       <c r="C236" s="6" t="n"/>
       <c r="D236" s="6" t="n"/>
-      <c r="E236" s="5" t="n"/>
+      <c r="E236" s="6" t="n"/>
       <c r="F236" s="5" t="n"/>
-      <c r="G236" s="6" t="n"/>
+      <c r="G236" s="5" t="n"/>
+      <c r="H236" s="6" t="n"/>
     </row>
     <row r="237" hidden="1" outlineLevel="2">
       <c r="A237" s="4" t="n">
@@ -3254,9 +3513,10 @@
       <c r="B237" s="5" t="n"/>
       <c r="C237" s="6" t="n"/>
       <c r="D237" s="6" t="n"/>
-      <c r="E237" s="5" t="n"/>
+      <c r="E237" s="6" t="n"/>
       <c r="F237" s="5" t="n"/>
-      <c r="G237" s="6" t="n"/>
+      <c r="G237" s="5" t="n"/>
+      <c r="H237" s="6" t="n"/>
     </row>
     <row r="238" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A238" s="4" t="n">
@@ -3265,9 +3525,10 @@
       <c r="B238" s="5" t="n"/>
       <c r="C238" s="6" t="n"/>
       <c r="D238" s="6" t="n"/>
-      <c r="E238" s="5" t="n"/>
+      <c r="E238" s="6" t="n"/>
       <c r="F238" s="5" t="n"/>
-      <c r="G238" s="6" t="n"/>
+      <c r="G238" s="5" t="n"/>
+      <c r="H238" s="6" t="n"/>
     </row>
     <row r="239" hidden="1" outlineLevel="2">
       <c r="A239" s="4" t="n">
@@ -3276,9 +3537,10 @@
       <c r="B239" s="5" t="n"/>
       <c r="C239" s="6" t="n"/>
       <c r="D239" s="6" t="n"/>
-      <c r="E239" s="5" t="n"/>
+      <c r="E239" s="6" t="n"/>
       <c r="F239" s="5" t="n"/>
-      <c r="G239" s="6" t="n"/>
+      <c r="G239" s="5" t="n"/>
+      <c r="H239" s="6" t="n"/>
     </row>
     <row r="240" hidden="1" outlineLevel="2">
       <c r="A240" s="4" t="n">
@@ -3287,9 +3549,10 @@
       <c r="B240" s="5" t="n"/>
       <c r="C240" s="6" t="n"/>
       <c r="D240" s="6" t="n"/>
-      <c r="E240" s="5" t="n"/>
+      <c r="E240" s="6" t="n"/>
       <c r="F240" s="5" t="n"/>
-      <c r="G240" s="6" t="n"/>
+      <c r="G240" s="5" t="n"/>
+      <c r="H240" s="6" t="n"/>
     </row>
     <row r="241" hidden="1" outlineLevel="2">
       <c r="A241" s="4" t="n">
@@ -3298,9 +3561,10 @@
       <c r="B241" s="5" t="n"/>
       <c r="C241" s="6" t="n"/>
       <c r="D241" s="6" t="n"/>
-      <c r="E241" s="5" t="n"/>
+      <c r="E241" s="6" t="n"/>
       <c r="F241" s="5" t="n"/>
-      <c r="G241" s="6" t="n"/>
+      <c r="G241" s="5" t="n"/>
+      <c r="H241" s="6" t="n"/>
     </row>
     <row r="242" collapsed="1">
       <c r="A242" s="4" t="n">
@@ -3318,12 +3582,13 @@
         </is>
       </c>
       <c r="D242" s="6" t="n"/>
-      <c r="E242" s="5" t="n"/>
-      <c r="F242" s="5">
+      <c r="E242" s="6" t="n"/>
+      <c r="F242" s="5" t="n"/>
+      <c r="G242" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G242" s="6" t="inlineStr">
+      <c r="H242" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(15735, 60, 26)</t>
         </is>
@@ -3336,9 +3601,10 @@
       <c r="B243" s="5" t="n"/>
       <c r="C243" s="6" t="n"/>
       <c r="D243" s="6" t="n"/>
-      <c r="E243" s="5" t="n"/>
+      <c r="E243" s="6" t="n"/>
       <c r="F243" s="5" t="n"/>
-      <c r="G243" s="6" t="n"/>
+      <c r="G243" s="5" t="n"/>
+      <c r="H243" s="6" t="n"/>
     </row>
     <row r="244" hidden="1" outlineLevel="2">
       <c r="A244" s="4" t="n">
@@ -3347,9 +3613,10 @@
       <c r="B244" s="5" t="n"/>
       <c r="C244" s="6" t="n"/>
       <c r="D244" s="6" t="n"/>
-      <c r="E244" s="5" t="n"/>
+      <c r="E244" s="6" t="n"/>
       <c r="F244" s="5" t="n"/>
-      <c r="G244" s="6" t="n"/>
+      <c r="G244" s="5" t="n"/>
+      <c r="H244" s="6" t="n"/>
     </row>
     <row r="245" hidden="1" outlineLevel="2">
       <c r="A245" s="4" t="n">
@@ -3358,9 +3625,10 @@
       <c r="B245" s="5" t="n"/>
       <c r="C245" s="6" t="n"/>
       <c r="D245" s="6" t="n"/>
-      <c r="E245" s="5" t="n"/>
+      <c r="E245" s="6" t="n"/>
       <c r="F245" s="5" t="n"/>
-      <c r="G245" s="6" t="n"/>
+      <c r="G245" s="5" t="n"/>
+      <c r="H245" s="6" t="n"/>
     </row>
     <row r="246" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A246" s="4" t="n">
@@ -3369,9 +3637,10 @@
       <c r="B246" s="5" t="n"/>
       <c r="C246" s="6" t="n"/>
       <c r="D246" s="6" t="n"/>
-      <c r="E246" s="5" t="n"/>
+      <c r="E246" s="6" t="n"/>
       <c r="F246" s="5" t="n"/>
-      <c r="G246" s="6" t="n"/>
+      <c r="G246" s="5" t="n"/>
+      <c r="H246" s="6" t="n"/>
     </row>
     <row r="247" hidden="1" outlineLevel="2">
       <c r="A247" s="4" t="n">
@@ -3380,9 +3649,10 @@
       <c r="B247" s="5" t="n"/>
       <c r="C247" s="6" t="n"/>
       <c r="D247" s="6" t="n"/>
-      <c r="E247" s="5" t="n"/>
+      <c r="E247" s="6" t="n"/>
       <c r="F247" s="5" t="n"/>
-      <c r="G247" s="6" t="n"/>
+      <c r="G247" s="5" t="n"/>
+      <c r="H247" s="6" t="n"/>
     </row>
     <row r="248" hidden="1" outlineLevel="2">
       <c r="A248" s="4" t="n">
@@ -3391,9 +3661,10 @@
       <c r="B248" s="5" t="n"/>
       <c r="C248" s="6" t="n"/>
       <c r="D248" s="6" t="n"/>
-      <c r="E248" s="5" t="n"/>
+      <c r="E248" s="6" t="n"/>
       <c r="F248" s="5" t="n"/>
-      <c r="G248" s="6" t="n"/>
+      <c r="G248" s="5" t="n"/>
+      <c r="H248" s="6" t="n"/>
     </row>
     <row r="249" hidden="1" outlineLevel="2">
       <c r="A249" s="4" t="n">
@@ -3402,9 +3673,10 @@
       <c r="B249" s="5" t="n"/>
       <c r="C249" s="6" t="n"/>
       <c r="D249" s="6" t="n"/>
-      <c r="E249" s="5" t="n"/>
+      <c r="E249" s="6" t="n"/>
       <c r="F249" s="5" t="n"/>
-      <c r="G249" s="6" t="n"/>
+      <c r="G249" s="5" t="n"/>
+      <c r="H249" s="6" t="n"/>
     </row>
     <row r="250" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A250" s="4" t="n">
@@ -3413,9 +3685,10 @@
       <c r="B250" s="5" t="n"/>
       <c r="C250" s="6" t="n"/>
       <c r="D250" s="6" t="n"/>
-      <c r="E250" s="5" t="n"/>
+      <c r="E250" s="6" t="n"/>
       <c r="F250" s="5" t="n"/>
-      <c r="G250" s="6" t="n"/>
+      <c r="G250" s="5" t="n"/>
+      <c r="H250" s="6" t="n"/>
     </row>
     <row r="251" hidden="1" outlineLevel="2">
       <c r="A251" s="4" t="n">
@@ -3424,9 +3697,10 @@
       <c r="B251" s="5" t="n"/>
       <c r="C251" s="6" t="n"/>
       <c r="D251" s="6" t="n"/>
-      <c r="E251" s="5" t="n"/>
+      <c r="E251" s="6" t="n"/>
       <c r="F251" s="5" t="n"/>
-      <c r="G251" s="6" t="n"/>
+      <c r="G251" s="5" t="n"/>
+      <c r="H251" s="6" t="n"/>
     </row>
     <row r="252" hidden="1" outlineLevel="2">
       <c r="A252" s="4" t="n">
@@ -3435,9 +3709,10 @@
       <c r="B252" s="5" t="n"/>
       <c r="C252" s="6" t="n"/>
       <c r="D252" s="6" t="n"/>
-      <c r="E252" s="5" t="n"/>
+      <c r="E252" s="6" t="n"/>
       <c r="F252" s="5" t="n"/>
-      <c r="G252" s="6" t="n"/>
+      <c r="G252" s="5" t="n"/>
+      <c r="H252" s="6" t="n"/>
     </row>
     <row r="253" hidden="1" outlineLevel="2">
       <c r="A253" s="4" t="n">
@@ -3446,9 +3721,10 @@
       <c r="B253" s="5" t="n"/>
       <c r="C253" s="6" t="n"/>
       <c r="D253" s="6" t="n"/>
-      <c r="E253" s="5" t="n"/>
+      <c r="E253" s="6" t="n"/>
       <c r="F253" s="5" t="n"/>
-      <c r="G253" s="6" t="n"/>
+      <c r="G253" s="5" t="n"/>
+      <c r="H253" s="6" t="n"/>
     </row>
     <row r="254" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A254" s="4" t="n">
@@ -3457,9 +3733,10 @@
       <c r="B254" s="5" t="n"/>
       <c r="C254" s="6" t="n"/>
       <c r="D254" s="6" t="n"/>
-      <c r="E254" s="5" t="n"/>
+      <c r="E254" s="6" t="n"/>
       <c r="F254" s="5" t="n"/>
-      <c r="G254" s="6" t="n"/>
+      <c r="G254" s="5" t="n"/>
+      <c r="H254" s="6" t="n"/>
     </row>
     <row r="255" hidden="1" outlineLevel="2">
       <c r="A255" s="4" t="n">
@@ -3468,9 +3745,10 @@
       <c r="B255" s="5" t="n"/>
       <c r="C255" s="6" t="n"/>
       <c r="D255" s="6" t="n"/>
-      <c r="E255" s="5" t="n"/>
+      <c r="E255" s="6" t="n"/>
       <c r="F255" s="5" t="n"/>
-      <c r="G255" s="6" t="n"/>
+      <c r="G255" s="5" t="n"/>
+      <c r="H255" s="6" t="n"/>
     </row>
     <row r="256" hidden="1" outlineLevel="2">
       <c r="A256" s="4" t="n">
@@ -3479,9 +3757,10 @@
       <c r="B256" s="5" t="n"/>
       <c r="C256" s="6" t="n"/>
       <c r="D256" s="6" t="n"/>
-      <c r="E256" s="5" t="n"/>
+      <c r="E256" s="6" t="n"/>
       <c r="F256" s="5" t="n"/>
-      <c r="G256" s="6" t="n"/>
+      <c r="G256" s="5" t="n"/>
+      <c r="H256" s="6" t="n"/>
     </row>
     <row r="257" hidden="1" outlineLevel="2">
       <c r="A257" s="4" t="n">
@@ -3490,9 +3769,10 @@
       <c r="B257" s="5" t="n"/>
       <c r="C257" s="6" t="n"/>
       <c r="D257" s="6" t="n"/>
-      <c r="E257" s="5" t="n"/>
+      <c r="E257" s="6" t="n"/>
       <c r="F257" s="5" t="n"/>
-      <c r="G257" s="6" t="n"/>
+      <c r="G257" s="5" t="n"/>
+      <c r="H257" s="6" t="n"/>
     </row>
     <row r="258" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A258" s="4" t="n">
@@ -3501,9 +3781,10 @@
       <c r="B258" s="5" t="n"/>
       <c r="C258" s="6" t="n"/>
       <c r="D258" s="6" t="n"/>
-      <c r="E258" s="5" t="n"/>
+      <c r="E258" s="6" t="n"/>
       <c r="F258" s="5" t="n"/>
-      <c r="G258" s="6" t="n"/>
+      <c r="G258" s="5" t="n"/>
+      <c r="H258" s="6" t="n"/>
     </row>
     <row r="259" hidden="1" outlineLevel="2">
       <c r="A259" s="4" t="n">
@@ -3512,9 +3793,10 @@
       <c r="B259" s="5" t="n"/>
       <c r="C259" s="6" t="n"/>
       <c r="D259" s="6" t="n"/>
-      <c r="E259" s="5" t="n"/>
+      <c r="E259" s="6" t="n"/>
       <c r="F259" s="5" t="n"/>
-      <c r="G259" s="6" t="n"/>
+      <c r="G259" s="5" t="n"/>
+      <c r="H259" s="6" t="n"/>
     </row>
     <row r="260" hidden="1" outlineLevel="2">
       <c r="A260" s="4" t="n">
@@ -3523,9 +3805,10 @@
       <c r="B260" s="5" t="n"/>
       <c r="C260" s="6" t="n"/>
       <c r="D260" s="6" t="n"/>
-      <c r="E260" s="5" t="n"/>
+      <c r="E260" s="6" t="n"/>
       <c r="F260" s="5" t="n"/>
-      <c r="G260" s="6" t="n"/>
+      <c r="G260" s="5" t="n"/>
+      <c r="H260" s="6" t="n"/>
     </row>
     <row r="261" hidden="1" outlineLevel="2">
       <c r="A261" s="4" t="n">
@@ -3534,9 +3817,10 @@
       <c r="B261" s="5" t="n"/>
       <c r="C261" s="6" t="n"/>
       <c r="D261" s="6" t="n"/>
-      <c r="E261" s="5" t="n"/>
+      <c r="E261" s="6" t="n"/>
       <c r="F261" s="5" t="n"/>
-      <c r="G261" s="6" t="n"/>
+      <c r="G261" s="5" t="n"/>
+      <c r="H261" s="6" t="n"/>
     </row>
     <row r="262" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A262" s="4" t="n">
@@ -3545,9 +3829,10 @@
       <c r="B262" s="5" t="n"/>
       <c r="C262" s="6" t="n"/>
       <c r="D262" s="6" t="n"/>
-      <c r="E262" s="5" t="n"/>
+      <c r="E262" s="6" t="n"/>
       <c r="F262" s="5" t="n"/>
-      <c r="G262" s="6" t="n"/>
+      <c r="G262" s="5" t="n"/>
+      <c r="H262" s="6" t="n"/>
     </row>
     <row r="263" hidden="1" outlineLevel="2">
       <c r="A263" s="4" t="n">
@@ -3556,9 +3841,10 @@
       <c r="B263" s="5" t="n"/>
       <c r="C263" s="6" t="n"/>
       <c r="D263" s="6" t="n"/>
-      <c r="E263" s="5" t="n"/>
+      <c r="E263" s="6" t="n"/>
       <c r="F263" s="5" t="n"/>
-      <c r="G263" s="6" t="n"/>
+      <c r="G263" s="5" t="n"/>
+      <c r="H263" s="6" t="n"/>
     </row>
     <row r="264" hidden="1" outlineLevel="2">
       <c r="A264" s="4" t="n">
@@ -3567,9 +3853,10 @@
       <c r="B264" s="5" t="n"/>
       <c r="C264" s="6" t="n"/>
       <c r="D264" s="6" t="n"/>
-      <c r="E264" s="5" t="n"/>
+      <c r="E264" s="6" t="n"/>
       <c r="F264" s="5" t="n"/>
-      <c r="G264" s="6" t="n"/>
+      <c r="G264" s="5" t="n"/>
+      <c r="H264" s="6" t="n"/>
     </row>
     <row r="265" hidden="1" outlineLevel="2">
       <c r="A265" s="4" t="n">
@@ -3578,9 +3865,10 @@
       <c r="B265" s="5" t="n"/>
       <c r="C265" s="6" t="n"/>
       <c r="D265" s="6" t="n"/>
-      <c r="E265" s="5" t="n"/>
+      <c r="E265" s="6" t="n"/>
       <c r="F265" s="5" t="n"/>
-      <c r="G265" s="6" t="n"/>
+      <c r="G265" s="5" t="n"/>
+      <c r="H265" s="6" t="n"/>
     </row>
     <row r="266" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A266" s="4" t="n">
@@ -3589,9 +3877,10 @@
       <c r="B266" s="5" t="n"/>
       <c r="C266" s="6" t="n"/>
       <c r="D266" s="6" t="n"/>
-      <c r="E266" s="5" t="n"/>
+      <c r="E266" s="6" t="n"/>
       <c r="F266" s="5" t="n"/>
-      <c r="G266" s="6" t="n"/>
+      <c r="G266" s="5" t="n"/>
+      <c r="H266" s="6" t="n"/>
     </row>
     <row r="267" hidden="1" outlineLevel="2">
       <c r="A267" s="4" t="n">
@@ -3600,9 +3889,10 @@
       <c r="B267" s="5" t="n"/>
       <c r="C267" s="6" t="n"/>
       <c r="D267" s="6" t="n"/>
-      <c r="E267" s="5" t="n"/>
+      <c r="E267" s="6" t="n"/>
       <c r="F267" s="5" t="n"/>
-      <c r="G267" s="6" t="n"/>
+      <c r="G267" s="5" t="n"/>
+      <c r="H267" s="6" t="n"/>
     </row>
     <row r="268" hidden="1" outlineLevel="2">
       <c r="A268" s="4" t="n">
@@ -3611,9 +3901,10 @@
       <c r="B268" s="5" t="n"/>
       <c r="C268" s="6" t="n"/>
       <c r="D268" s="6" t="n"/>
-      <c r="E268" s="5" t="n"/>
+      <c r="E268" s="6" t="n"/>
       <c r="F268" s="5" t="n"/>
-      <c r="G268" s="6" t="n"/>
+      <c r="G268" s="5" t="n"/>
+      <c r="H268" s="6" t="n"/>
     </row>
     <row r="269" hidden="1" outlineLevel="2">
       <c r="A269" s="4" t="n">
@@ -3622,9 +3913,10 @@
       <c r="B269" s="5" t="n"/>
       <c r="C269" s="6" t="n"/>
       <c r="D269" s="6" t="n"/>
-      <c r="E269" s="5" t="n"/>
+      <c r="E269" s="6" t="n"/>
       <c r="F269" s="5" t="n"/>
-      <c r="G269" s="6" t="n"/>
+      <c r="G269" s="5" t="n"/>
+      <c r="H269" s="6" t="n"/>
     </row>
     <row r="270" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A270" s="4" t="n">
@@ -3633,9 +3925,10 @@
       <c r="B270" s="5" t="n"/>
       <c r="C270" s="6" t="n"/>
       <c r="D270" s="6" t="n"/>
-      <c r="E270" s="5" t="n"/>
+      <c r="E270" s="6" t="n"/>
       <c r="F270" s="5" t="n"/>
-      <c r="G270" s="6" t="n"/>
+      <c r="G270" s="5" t="n"/>
+      <c r="H270" s="6" t="n"/>
     </row>
     <row r="271" hidden="1" outlineLevel="2">
       <c r="A271" s="4" t="n">
@@ -3644,9 +3937,10 @@
       <c r="B271" s="5" t="n"/>
       <c r="C271" s="6" t="n"/>
       <c r="D271" s="6" t="n"/>
-      <c r="E271" s="5" t="n"/>
+      <c r="E271" s="6" t="n"/>
       <c r="F271" s="5" t="n"/>
-      <c r="G271" s="6" t="n"/>
+      <c r="G271" s="5" t="n"/>
+      <c r="H271" s="6" t="n"/>
     </row>
     <row r="272" hidden="1" outlineLevel="2">
       <c r="A272" s="4" t="n">
@@ -3655,9 +3949,10 @@
       <c r="B272" s="5" t="n"/>
       <c r="C272" s="6" t="n"/>
       <c r="D272" s="6" t="n"/>
-      <c r="E272" s="5" t="n"/>
+      <c r="E272" s="6" t="n"/>
       <c r="F272" s="5" t="n"/>
-      <c r="G272" s="6" t="n"/>
+      <c r="G272" s="5" t="n"/>
+      <c r="H272" s="6" t="n"/>
     </row>
     <row r="273" hidden="1" outlineLevel="2">
       <c r="A273" s="4" t="n">
@@ -3666,9 +3961,10 @@
       <c r="B273" s="5" t="n"/>
       <c r="C273" s="6" t="n"/>
       <c r="D273" s="6" t="n"/>
-      <c r="E273" s="5" t="n"/>
+      <c r="E273" s="6" t="n"/>
       <c r="F273" s="5" t="n"/>
-      <c r="G273" s="6" t="n"/>
+      <c r="G273" s="5" t="n"/>
+      <c r="H273" s="6" t="n"/>
     </row>
     <row r="274" collapsed="1">
       <c r="A274" s="4" t="n">
@@ -3686,12 +3982,13 @@
         </is>
       </c>
       <c r="D274" s="6" t="n"/>
-      <c r="E274" s="5" t="n"/>
-      <c r="F274" s="5">
+      <c r="E274" s="6" t="n"/>
+      <c r="F274" s="5" t="n"/>
+      <c r="G274" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G274" s="6" t="inlineStr">
+      <c r="H274" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(7870, 490, 65, 5, 26, 5, true, 3)</t>
         </is>
@@ -3704,9 +4001,10 @@
       <c r="B275" s="5" t="n"/>
       <c r="C275" s="6" t="n"/>
       <c r="D275" s="6" t="n"/>
-      <c r="E275" s="5" t="n"/>
+      <c r="E275" s="6" t="n"/>
       <c r="F275" s="5" t="n"/>
-      <c r="G275" s="6" t="n"/>
+      <c r="G275" s="5" t="n"/>
+      <c r="H275" s="6" t="n"/>
     </row>
     <row r="276" hidden="1" outlineLevel="2">
       <c r="A276" s="4" t="n">
@@ -3715,9 +4013,10 @@
       <c r="B276" s="5" t="n"/>
       <c r="C276" s="6" t="n"/>
       <c r="D276" s="6" t="n"/>
-      <c r="E276" s="5" t="n"/>
+      <c r="E276" s="6" t="n"/>
       <c r="F276" s="5" t="n"/>
-      <c r="G276" s="6" t="n"/>
+      <c r="G276" s="5" t="n"/>
+      <c r="H276" s="6" t="n"/>
     </row>
     <row r="277" hidden="1" outlineLevel="2">
       <c r="A277" s="4" t="n">
@@ -3726,9 +4025,10 @@
       <c r="B277" s="5" t="n"/>
       <c r="C277" s="6" t="n"/>
       <c r="D277" s="6" t="n"/>
-      <c r="E277" s="5" t="n"/>
+      <c r="E277" s="6" t="n"/>
       <c r="F277" s="5" t="n"/>
-      <c r="G277" s="6" t="n"/>
+      <c r="G277" s="5" t="n"/>
+      <c r="H277" s="6" t="n"/>
     </row>
     <row r="278" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A278" s="4" t="n">
@@ -3737,9 +4037,10 @@
       <c r="B278" s="5" t="n"/>
       <c r="C278" s="6" t="n"/>
       <c r="D278" s="6" t="n"/>
-      <c r="E278" s="5" t="n"/>
+      <c r="E278" s="6" t="n"/>
       <c r="F278" s="5" t="n"/>
-      <c r="G278" s="6" t="n"/>
+      <c r="G278" s="5" t="n"/>
+      <c r="H278" s="6" t="n"/>
     </row>
     <row r="279" hidden="1" outlineLevel="2">
       <c r="A279" s="4" t="n">
@@ -3748,9 +4049,10 @@
       <c r="B279" s="5" t="n"/>
       <c r="C279" s="6" t="n"/>
       <c r="D279" s="6" t="n"/>
-      <c r="E279" s="5" t="n"/>
+      <c r="E279" s="6" t="n"/>
       <c r="F279" s="5" t="n"/>
-      <c r="G279" s="6" t="n"/>
+      <c r="G279" s="5" t="n"/>
+      <c r="H279" s="6" t="n"/>
     </row>
     <row r="280" hidden="1" outlineLevel="2">
       <c r="A280" s="4" t="n">
@@ -3759,9 +4061,10 @@
       <c r="B280" s="5" t="n"/>
       <c r="C280" s="6" t="n"/>
       <c r="D280" s="6" t="n"/>
-      <c r="E280" s="5" t="n"/>
+      <c r="E280" s="6" t="n"/>
       <c r="F280" s="5" t="n"/>
-      <c r="G280" s="6" t="n"/>
+      <c r="G280" s="5" t="n"/>
+      <c r="H280" s="6" t="n"/>
     </row>
     <row r="281" hidden="1" outlineLevel="2">
       <c r="A281" s="4" t="n">
@@ -3770,9 +4073,10 @@
       <c r="B281" s="5" t="n"/>
       <c r="C281" s="6" t="n"/>
       <c r="D281" s="6" t="n"/>
-      <c r="E281" s="5" t="n"/>
+      <c r="E281" s="6" t="n"/>
       <c r="F281" s="5" t="n"/>
-      <c r="G281" s="6" t="n"/>
+      <c r="G281" s="5" t="n"/>
+      <c r="H281" s="6" t="n"/>
     </row>
     <row r="282" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A282" s="4" t="n">
@@ -3781,9 +4085,10 @@
       <c r="B282" s="5" t="n"/>
       <c r="C282" s="6" t="n"/>
       <c r="D282" s="6" t="n"/>
-      <c r="E282" s="5" t="n"/>
+      <c r="E282" s="6" t="n"/>
       <c r="F282" s="5" t="n"/>
-      <c r="G282" s="6" t="n"/>
+      <c r="G282" s="5" t="n"/>
+      <c r="H282" s="6" t="n"/>
     </row>
     <row r="283" hidden="1" outlineLevel="2">
       <c r="A283" s="4" t="n">
@@ -3792,9 +4097,10 @@
       <c r="B283" s="5" t="n"/>
       <c r="C283" s="6" t="n"/>
       <c r="D283" s="6" t="n"/>
-      <c r="E283" s="5" t="n"/>
+      <c r="E283" s="6" t="n"/>
       <c r="F283" s="5" t="n"/>
-      <c r="G283" s="6" t="n"/>
+      <c r="G283" s="5" t="n"/>
+      <c r="H283" s="6" t="n"/>
     </row>
     <row r="284" hidden="1" outlineLevel="2">
       <c r="A284" s="4" t="n">
@@ -3803,9 +4109,10 @@
       <c r="B284" s="5" t="n"/>
       <c r="C284" s="6" t="n"/>
       <c r="D284" s="6" t="n"/>
-      <c r="E284" s="5" t="n"/>
+      <c r="E284" s="6" t="n"/>
       <c r="F284" s="5" t="n"/>
-      <c r="G284" s="6" t="n"/>
+      <c r="G284" s="5" t="n"/>
+      <c r="H284" s="6" t="n"/>
     </row>
     <row r="285" hidden="1" outlineLevel="2">
       <c r="A285" s="4" t="n">
@@ -3814,9 +4121,10 @@
       <c r="B285" s="5" t="n"/>
       <c r="C285" s="6" t="n"/>
       <c r="D285" s="6" t="n"/>
-      <c r="E285" s="5" t="n"/>
+      <c r="E285" s="6" t="n"/>
       <c r="F285" s="5" t="n"/>
-      <c r="G285" s="6" t="n"/>
+      <c r="G285" s="5" t="n"/>
+      <c r="H285" s="6" t="n"/>
     </row>
     <row r="286" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A286" s="4" t="n">
@@ -3825,9 +4133,10 @@
       <c r="B286" s="5" t="n"/>
       <c r="C286" s="6" t="n"/>
       <c r="D286" s="6" t="n"/>
-      <c r="E286" s="5" t="n"/>
+      <c r="E286" s="6" t="n"/>
       <c r="F286" s="5" t="n"/>
-      <c r="G286" s="6" t="n"/>
+      <c r="G286" s="5" t="n"/>
+      <c r="H286" s="6" t="n"/>
     </row>
     <row r="287" hidden="1" outlineLevel="2">
       <c r="A287" s="4" t="n">
@@ -3836,9 +4145,10 @@
       <c r="B287" s="5" t="n"/>
       <c r="C287" s="6" t="n"/>
       <c r="D287" s="6" t="n"/>
-      <c r="E287" s="5" t="n"/>
+      <c r="E287" s="6" t="n"/>
       <c r="F287" s="5" t="n"/>
-      <c r="G287" s="6" t="n"/>
+      <c r="G287" s="5" t="n"/>
+      <c r="H287" s="6" t="n"/>
     </row>
     <row r="288" hidden="1" outlineLevel="2">
       <c r="A288" s="4" t="n">
@@ -3847,9 +4157,10 @@
       <c r="B288" s="5" t="n"/>
       <c r="C288" s="6" t="n"/>
       <c r="D288" s="6" t="n"/>
-      <c r="E288" s="5" t="n"/>
+      <c r="E288" s="6" t="n"/>
       <c r="F288" s="5" t="n"/>
-      <c r="G288" s="6" t="n"/>
+      <c r="G288" s="5" t="n"/>
+      <c r="H288" s="6" t="n"/>
     </row>
     <row r="289" hidden="1" outlineLevel="2">
       <c r="A289" s="4" t="n">
@@ -3858,9 +4169,10 @@
       <c r="B289" s="5" t="n"/>
       <c r="C289" s="6" t="n"/>
       <c r="D289" s="6" t="n"/>
-      <c r="E289" s="5" t="n"/>
+      <c r="E289" s="6" t="n"/>
       <c r="F289" s="5" t="n"/>
-      <c r="G289" s="6" t="n"/>
+      <c r="G289" s="5" t="n"/>
+      <c r="H289" s="6" t="n"/>
     </row>
     <row r="290" collapsed="1">
       <c r="A290" s="4" t="n">
@@ -3878,12 +4190,13 @@
         </is>
       </c>
       <c r="D290" s="6" t="n"/>
-      <c r="E290" s="5" t="n"/>
-      <c r="F290" s="5">
+      <c r="E290" s="6" t="n"/>
+      <c r="F290" s="5" t="n"/>
+      <c r="G290" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G290" s="6" t="inlineStr">
+      <c r="H290" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(7870, 4, 70)</t>
         </is>
@@ -3896,9 +4209,10 @@
       <c r="B291" s="5" t="n"/>
       <c r="C291" s="6" t="n"/>
       <c r="D291" s="6" t="n"/>
-      <c r="E291" s="5" t="n"/>
+      <c r="E291" s="6" t="n"/>
       <c r="F291" s="5" t="n"/>
-      <c r="G291" s="6" t="n"/>
+      <c r="G291" s="5" t="n"/>
+      <c r="H291" s="6" t="n"/>
     </row>
     <row r="292" hidden="1" outlineLevel="2">
       <c r="A292" s="4" t="n">
@@ -3907,9 +4221,10 @@
       <c r="B292" s="5" t="n"/>
       <c r="C292" s="6" t="n"/>
       <c r="D292" s="6" t="n"/>
-      <c r="E292" s="5" t="n"/>
+      <c r="E292" s="6" t="n"/>
       <c r="F292" s="5" t="n"/>
-      <c r="G292" s="6" t="n"/>
+      <c r="G292" s="5" t="n"/>
+      <c r="H292" s="6" t="n"/>
     </row>
     <row r="293" hidden="1" outlineLevel="2">
       <c r="A293" s="4" t="n">
@@ -3918,9 +4233,10 @@
       <c r="B293" s="5" t="n"/>
       <c r="C293" s="6" t="n"/>
       <c r="D293" s="6" t="n"/>
-      <c r="E293" s="5" t="n"/>
+      <c r="E293" s="6" t="n"/>
       <c r="F293" s="5" t="n"/>
-      <c r="G293" s="6" t="n"/>
+      <c r="G293" s="5" t="n"/>
+      <c r="H293" s="6" t="n"/>
     </row>
     <row r="294" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A294" s="4" t="n">
@@ -3929,9 +4245,10 @@
       <c r="B294" s="5" t="n"/>
       <c r="C294" s="6" t="n"/>
       <c r="D294" s="6" t="n"/>
-      <c r="E294" s="5" t="n"/>
+      <c r="E294" s="6" t="n"/>
       <c r="F294" s="5" t="n"/>
-      <c r="G294" s="6" t="n"/>
+      <c r="G294" s="5" t="n"/>
+      <c r="H294" s="6" t="n"/>
     </row>
     <row r="295" hidden="1" outlineLevel="2">
       <c r="A295" s="4" t="n">
@@ -3940,9 +4257,10 @@
       <c r="B295" s="5" t="n"/>
       <c r="C295" s="6" t="n"/>
       <c r="D295" s="6" t="n"/>
-      <c r="E295" s="5" t="n"/>
+      <c r="E295" s="6" t="n"/>
       <c r="F295" s="5" t="n"/>
-      <c r="G295" s="6" t="n"/>
+      <c r="G295" s="5" t="n"/>
+      <c r="H295" s="6" t="n"/>
     </row>
     <row r="296" hidden="1" outlineLevel="2">
       <c r="A296" s="4" t="n">
@@ -3951,9 +4269,10 @@
       <c r="B296" s="5" t="n"/>
       <c r="C296" s="6" t="n"/>
       <c r="D296" s="6" t="n"/>
-      <c r="E296" s="5" t="n"/>
+      <c r="E296" s="6" t="n"/>
       <c r="F296" s="5" t="n"/>
-      <c r="G296" s="6" t="n"/>
+      <c r="G296" s="5" t="n"/>
+      <c r="H296" s="6" t="n"/>
     </row>
     <row r="297" hidden="1" outlineLevel="2">
       <c r="A297" s="4" t="n">
@@ -3962,9 +4281,10 @@
       <c r="B297" s="5" t="n"/>
       <c r="C297" s="6" t="n"/>
       <c r="D297" s="6" t="n"/>
-      <c r="E297" s="5" t="n"/>
+      <c r="E297" s="6" t="n"/>
       <c r="F297" s="5" t="n"/>
-      <c r="G297" s="6" t="n"/>
+      <c r="G297" s="5" t="n"/>
+      <c r="H297" s="6" t="n"/>
     </row>
     <row r="298" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A298" s="4" t="n">
@@ -3973,9 +4293,10 @@
       <c r="B298" s="5" t="n"/>
       <c r="C298" s="6" t="n"/>
       <c r="D298" s="6" t="n"/>
-      <c r="E298" s="5" t="n"/>
+      <c r="E298" s="6" t="n"/>
       <c r="F298" s="5" t="n"/>
-      <c r="G298" s="6" t="n"/>
+      <c r="G298" s="5" t="n"/>
+      <c r="H298" s="6" t="n"/>
     </row>
     <row r="299" hidden="1" outlineLevel="2">
       <c r="A299" s="4" t="n">
@@ -3984,9 +4305,10 @@
       <c r="B299" s="5" t="n"/>
       <c r="C299" s="6" t="n"/>
       <c r="D299" s="6" t="n"/>
-      <c r="E299" s="5" t="n"/>
+      <c r="E299" s="6" t="n"/>
       <c r="F299" s="5" t="n"/>
-      <c r="G299" s="6" t="n"/>
+      <c r="G299" s="5" t="n"/>
+      <c r="H299" s="6" t="n"/>
     </row>
     <row r="300" hidden="1" outlineLevel="2">
       <c r="A300" s="4" t="n">
@@ -3995,9 +4317,10 @@
       <c r="B300" s="5" t="n"/>
       <c r="C300" s="6" t="n"/>
       <c r="D300" s="6" t="n"/>
-      <c r="E300" s="5" t="n"/>
+      <c r="E300" s="6" t="n"/>
       <c r="F300" s="5" t="n"/>
-      <c r="G300" s="6" t="n"/>
+      <c r="G300" s="5" t="n"/>
+      <c r="H300" s="6" t="n"/>
     </row>
     <row r="301" hidden="1" outlineLevel="2">
       <c r="A301" s="4" t="n">
@@ -4006,9 +4329,10 @@
       <c r="B301" s="5" t="n"/>
       <c r="C301" s="6" t="n"/>
       <c r="D301" s="6" t="n"/>
-      <c r="E301" s="5" t="n"/>
+      <c r="E301" s="6" t="n"/>
       <c r="F301" s="5" t="n"/>
-      <c r="G301" s="6" t="n"/>
+      <c r="G301" s="5" t="n"/>
+      <c r="H301" s="6" t="n"/>
     </row>
     <row r="302" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A302" s="4" t="n">
@@ -4017,9 +4341,10 @@
       <c r="B302" s="5" t="n"/>
       <c r="C302" s="6" t="n"/>
       <c r="D302" s="6" t="n"/>
-      <c r="E302" s="5" t="n"/>
+      <c r="E302" s="6" t="n"/>
       <c r="F302" s="5" t="n"/>
-      <c r="G302" s="6" t="n"/>
+      <c r="G302" s="5" t="n"/>
+      <c r="H302" s="6" t="n"/>
     </row>
     <row r="303" hidden="1" outlineLevel="2">
       <c r="A303" s="4" t="n">
@@ -4028,9 +4353,10 @@
       <c r="B303" s="5" t="n"/>
       <c r="C303" s="6" t="n"/>
       <c r="D303" s="6" t="n"/>
-      <c r="E303" s="5" t="n"/>
+      <c r="E303" s="6" t="n"/>
       <c r="F303" s="5" t="n"/>
-      <c r="G303" s="6" t="n"/>
+      <c r="G303" s="5" t="n"/>
+      <c r="H303" s="6" t="n"/>
     </row>
     <row r="304" hidden="1" outlineLevel="2">
       <c r="A304" s="4" t="n">
@@ -4039,9 +4365,10 @@
       <c r="B304" s="5" t="n"/>
       <c r="C304" s="6" t="n"/>
       <c r="D304" s="6" t="n"/>
-      <c r="E304" s="5" t="n"/>
+      <c r="E304" s="6" t="n"/>
       <c r="F304" s="5" t="n"/>
-      <c r="G304" s="6" t="n"/>
+      <c r="G304" s="5" t="n"/>
+      <c r="H304" s="6" t="n"/>
     </row>
     <row r="305" hidden="1" outlineLevel="2">
       <c r="A305" s="4" t="n">
@@ -4050,9 +4377,10 @@
       <c r="B305" s="5" t="n"/>
       <c r="C305" s="6" t="n"/>
       <c r="D305" s="6" t="n"/>
-      <c r="E305" s="5" t="n"/>
+      <c r="E305" s="6" t="n"/>
       <c r="F305" s="5" t="n"/>
-      <c r="G305" s="6" t="n"/>
+      <c r="G305" s="5" t="n"/>
+      <c r="H305" s="6" t="n"/>
     </row>
     <row r="306" collapsed="1">
       <c r="A306" s="4" t="n">
@@ -4070,12 +4398,13 @@
         </is>
       </c>
       <c r="D306" s="6" t="n"/>
-      <c r="E306" s="5" t="n"/>
-      <c r="F306" s="5">
+      <c r="E306" s="6" t="n"/>
+      <c r="F306" s="5" t="n"/>
+      <c r="G306" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G306" s="6" t="inlineStr">
+      <c r="H306" s="6" t="inlineStr">
         <is>
           <t>progPalette(15740, 9, 75)</t>
         </is>
@@ -4088,9 +4417,10 @@
       <c r="B307" s="5" t="n"/>
       <c r="C307" s="6" t="n"/>
       <c r="D307" s="6" t="n"/>
-      <c r="E307" s="5" t="n"/>
+      <c r="E307" s="6" t="n"/>
       <c r="F307" s="5" t="n"/>
-      <c r="G307" s="6" t="n"/>
+      <c r="G307" s="5" t="n"/>
+      <c r="H307" s="6" t="n"/>
     </row>
     <row r="308" hidden="1" outlineLevel="2">
       <c r="A308" s="4" t="n">
@@ -4099,9 +4429,10 @@
       <c r="B308" s="5" t="n"/>
       <c r="C308" s="6" t="n"/>
       <c r="D308" s="6" t="n"/>
-      <c r="E308" s="5" t="n"/>
+      <c r="E308" s="6" t="n"/>
       <c r="F308" s="5" t="n"/>
-      <c r="G308" s="6" t="n"/>
+      <c r="G308" s="5" t="n"/>
+      <c r="H308" s="6" t="n"/>
     </row>
     <row r="309" hidden="1" outlineLevel="2">
       <c r="A309" s="4" t="n">
@@ -4110,9 +4441,10 @@
       <c r="B309" s="5" t="n"/>
       <c r="C309" s="6" t="n"/>
       <c r="D309" s="6" t="n"/>
-      <c r="E309" s="5" t="n"/>
+      <c r="E309" s="6" t="n"/>
       <c r="F309" s="5" t="n"/>
-      <c r="G309" s="6" t="n"/>
+      <c r="G309" s="5" t="n"/>
+      <c r="H309" s="6" t="n"/>
     </row>
     <row r="310" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A310" s="4" t="n">
@@ -4121,9 +4453,10 @@
       <c r="B310" s="5" t="n"/>
       <c r="C310" s="6" t="n"/>
       <c r="D310" s="6" t="n"/>
-      <c r="E310" s="5" t="n"/>
+      <c r="E310" s="6" t="n"/>
       <c r="F310" s="5" t="n"/>
-      <c r="G310" s="6" t="n"/>
+      <c r="G310" s="5" t="n"/>
+      <c r="H310" s="6" t="n"/>
     </row>
     <row r="311" hidden="1" outlineLevel="2">
       <c r="A311" s="4" t="n">
@@ -4132,9 +4465,10 @@
       <c r="B311" s="5" t="n"/>
       <c r="C311" s="6" t="n"/>
       <c r="D311" s="6" t="n"/>
-      <c r="E311" s="5" t="n"/>
+      <c r="E311" s="6" t="n"/>
       <c r="F311" s="5" t="n"/>
-      <c r="G311" s="6" t="n"/>
+      <c r="G311" s="5" t="n"/>
+      <c r="H311" s="6" t="n"/>
     </row>
     <row r="312" hidden="1" outlineLevel="2">
       <c r="A312" s="4" t="n">
@@ -4143,9 +4477,10 @@
       <c r="B312" s="5" t="n"/>
       <c r="C312" s="6" t="n"/>
       <c r="D312" s="6" t="n"/>
-      <c r="E312" s="5" t="n"/>
+      <c r="E312" s="6" t="n"/>
       <c r="F312" s="5" t="n"/>
-      <c r="G312" s="6" t="n"/>
+      <c r="G312" s="5" t="n"/>
+      <c r="H312" s="6" t="n"/>
     </row>
     <row r="313" hidden="1" outlineLevel="2">
       <c r="A313" s="4" t="n">
@@ -4154,9 +4489,10 @@
       <c r="B313" s="5" t="n"/>
       <c r="C313" s="6" t="n"/>
       <c r="D313" s="6" t="n"/>
-      <c r="E313" s="5" t="n"/>
+      <c r="E313" s="6" t="n"/>
       <c r="F313" s="5" t="n"/>
-      <c r="G313" s="6" t="n"/>
+      <c r="G313" s="5" t="n"/>
+      <c r="H313" s="6" t="n"/>
     </row>
     <row r="314" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A314" s="4" t="n">
@@ -4165,9 +4501,10 @@
       <c r="B314" s="5" t="n"/>
       <c r="C314" s="6" t="n"/>
       <c r="D314" s="6" t="n"/>
-      <c r="E314" s="5" t="n"/>
+      <c r="E314" s="6" t="n"/>
       <c r="F314" s="5" t="n"/>
-      <c r="G314" s="6" t="n"/>
+      <c r="G314" s="5" t="n"/>
+      <c r="H314" s="6" t="n"/>
     </row>
     <row r="315" hidden="1" outlineLevel="2">
       <c r="A315" s="4" t="n">
@@ -4176,9 +4513,10 @@
       <c r="B315" s="5" t="n"/>
       <c r="C315" s="6" t="n"/>
       <c r="D315" s="6" t="n"/>
-      <c r="E315" s="5" t="n"/>
+      <c r="E315" s="6" t="n"/>
       <c r="F315" s="5" t="n"/>
-      <c r="G315" s="6" t="n"/>
+      <c r="G315" s="5" t="n"/>
+      <c r="H315" s="6" t="n"/>
     </row>
     <row r="316" hidden="1" outlineLevel="2">
       <c r="A316" s="4" t="n">
@@ -4187,9 +4525,10 @@
       <c r="B316" s="5" t="n"/>
       <c r="C316" s="6" t="n"/>
       <c r="D316" s="6" t="n"/>
-      <c r="E316" s="5" t="n"/>
+      <c r="E316" s="6" t="n"/>
       <c r="F316" s="5" t="n"/>
-      <c r="G316" s="6" t="n"/>
+      <c r="G316" s="5" t="n"/>
+      <c r="H316" s="6" t="n"/>
     </row>
     <row r="317" hidden="1" outlineLevel="2">
       <c r="A317" s="4" t="n">
@@ -4198,9 +4537,10 @@
       <c r="B317" s="5" t="n"/>
       <c r="C317" s="6" t="n"/>
       <c r="D317" s="6" t="n"/>
-      <c r="E317" s="5" t="n"/>
+      <c r="E317" s="6" t="n"/>
       <c r="F317" s="5" t="n"/>
-      <c r="G317" s="6" t="n"/>
+      <c r="G317" s="5" t="n"/>
+      <c r="H317" s="6" t="n"/>
     </row>
     <row r="318" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A318" s="4" t="n">
@@ -4209,9 +4549,10 @@
       <c r="B318" s="5" t="n"/>
       <c r="C318" s="6" t="n"/>
       <c r="D318" s="6" t="n"/>
-      <c r="E318" s="5" t="n"/>
+      <c r="E318" s="6" t="n"/>
       <c r="F318" s="5" t="n"/>
-      <c r="G318" s="6" t="n"/>
+      <c r="G318" s="5" t="n"/>
+      <c r="H318" s="6" t="n"/>
     </row>
     <row r="319" hidden="1" outlineLevel="2">
       <c r="A319" s="4" t="n">
@@ -4220,9 +4561,10 @@
       <c r="B319" s="5" t="n"/>
       <c r="C319" s="6" t="n"/>
       <c r="D319" s="6" t="n"/>
-      <c r="E319" s="5" t="n"/>
+      <c r="E319" s="6" t="n"/>
       <c r="F319" s="5" t="n"/>
-      <c r="G319" s="6" t="n"/>
+      <c r="G319" s="5" t="n"/>
+      <c r="H319" s="6" t="n"/>
     </row>
     <row r="320" hidden="1" outlineLevel="2">
       <c r="A320" s="4" t="n">
@@ -4231,9 +4573,10 @@
       <c r="B320" s="5" t="n"/>
       <c r="C320" s="6" t="n"/>
       <c r="D320" s="6" t="n"/>
-      <c r="E320" s="5" t="n"/>
+      <c r="E320" s="6" t="n"/>
       <c r="F320" s="5" t="n"/>
-      <c r="G320" s="6" t="n"/>
+      <c r="G320" s="5" t="n"/>
+      <c r="H320" s="6" t="n"/>
     </row>
     <row r="321" hidden="1" outlineLevel="2">
       <c r="A321" s="4" t="n">
@@ -4242,9 +4585,10 @@
       <c r="B321" s="5" t="n"/>
       <c r="C321" s="6" t="n"/>
       <c r="D321" s="6" t="n"/>
-      <c r="E321" s="5" t="n"/>
+      <c r="E321" s="6" t="n"/>
       <c r="F321" s="5" t="n"/>
-      <c r="G321" s="6" t="n"/>
+      <c r="G321" s="5" t="n"/>
+      <c r="H321" s="6" t="n"/>
     </row>
     <row r="322" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A322" s="4" t="n">
@@ -4253,9 +4597,10 @@
       <c r="B322" s="5" t="n"/>
       <c r="C322" s="6" t="n"/>
       <c r="D322" s="6" t="n"/>
-      <c r="E322" s="5" t="n"/>
+      <c r="E322" s="6" t="n"/>
       <c r="F322" s="5" t="n"/>
-      <c r="G322" s="6" t="n"/>
+      <c r="G322" s="5" t="n"/>
+      <c r="H322" s="6" t="n"/>
     </row>
     <row r="323" hidden="1" outlineLevel="2">
       <c r="A323" s="4" t="n">
@@ -4264,9 +4609,10 @@
       <c r="B323" s="5" t="n"/>
       <c r="C323" s="6" t="n"/>
       <c r="D323" s="6" t="n"/>
-      <c r="E323" s="5" t="n"/>
+      <c r="E323" s="6" t="n"/>
       <c r="F323" s="5" t="n"/>
-      <c r="G323" s="6" t="n"/>
+      <c r="G323" s="5" t="n"/>
+      <c r="H323" s="6" t="n"/>
     </row>
     <row r="324" hidden="1" outlineLevel="2">
       <c r="A324" s="4" t="n">
@@ -4275,9 +4621,10 @@
       <c r="B324" s="5" t="n"/>
       <c r="C324" s="6" t="n"/>
       <c r="D324" s="6" t="n"/>
-      <c r="E324" s="5" t="n"/>
+      <c r="E324" s="6" t="n"/>
       <c r="F324" s="5" t="n"/>
-      <c r="G324" s="6" t="n"/>
+      <c r="G324" s="5" t="n"/>
+      <c r="H324" s="6" t="n"/>
     </row>
     <row r="325" hidden="1" outlineLevel="2">
       <c r="A325" s="4" t="n">
@@ -4286,9 +4633,10 @@
       <c r="B325" s="5" t="n"/>
       <c r="C325" s="6" t="n"/>
       <c r="D325" s="6" t="n"/>
-      <c r="E325" s="5" t="n"/>
+      <c r="E325" s="6" t="n"/>
       <c r="F325" s="5" t="n"/>
-      <c r="G325" s="6" t="n"/>
+      <c r="G325" s="5" t="n"/>
+      <c r="H325" s="6" t="n"/>
     </row>
     <row r="326" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A326" s="4" t="n">
@@ -4297,9 +4645,10 @@
       <c r="B326" s="5" t="n"/>
       <c r="C326" s="6" t="n"/>
       <c r="D326" s="6" t="n"/>
-      <c r="E326" s="5" t="n"/>
+      <c r="E326" s="6" t="n"/>
       <c r="F326" s="5" t="n"/>
-      <c r="G326" s="6" t="n"/>
+      <c r="G326" s="5" t="n"/>
+      <c r="H326" s="6" t="n"/>
     </row>
     <row r="327" hidden="1" outlineLevel="2">
       <c r="A327" s="4" t="n">
@@ -4308,9 +4657,10 @@
       <c r="B327" s="5" t="n"/>
       <c r="C327" s="6" t="n"/>
       <c r="D327" s="6" t="n"/>
-      <c r="E327" s="5" t="n"/>
+      <c r="E327" s="6" t="n"/>
       <c r="F327" s="5" t="n"/>
-      <c r="G327" s="6" t="n"/>
+      <c r="G327" s="5" t="n"/>
+      <c r="H327" s="6" t="n"/>
     </row>
     <row r="328" hidden="1" outlineLevel="2">
       <c r="A328" s="4" t="n">
@@ -4319,9 +4669,10 @@
       <c r="B328" s="5" t="n"/>
       <c r="C328" s="6" t="n"/>
       <c r="D328" s="6" t="n"/>
-      <c r="E328" s="5" t="n"/>
+      <c r="E328" s="6" t="n"/>
       <c r="F328" s="5" t="n"/>
-      <c r="G328" s="6" t="n"/>
+      <c r="G328" s="5" t="n"/>
+      <c r="H328" s="6" t="n"/>
     </row>
     <row r="329" hidden="1" outlineLevel="2">
       <c r="A329" s="4" t="n">
@@ -4330,9 +4681,10 @@
       <c r="B329" s="5" t="n"/>
       <c r="C329" s="6" t="n"/>
       <c r="D329" s="6" t="n"/>
-      <c r="E329" s="5" t="n"/>
+      <c r="E329" s="6" t="n"/>
       <c r="F329" s="5" t="n"/>
-      <c r="G329" s="6" t="n"/>
+      <c r="G329" s="5" t="n"/>
+      <c r="H329" s="6" t="n"/>
     </row>
     <row r="330" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A330" s="4" t="n">
@@ -4341,9 +4693,10 @@
       <c r="B330" s="5" t="n"/>
       <c r="C330" s="6" t="n"/>
       <c r="D330" s="6" t="n"/>
-      <c r="E330" s="5" t="n"/>
+      <c r="E330" s="6" t="n"/>
       <c r="F330" s="5" t="n"/>
-      <c r="G330" s="6" t="n"/>
+      <c r="G330" s="5" t="n"/>
+      <c r="H330" s="6" t="n"/>
     </row>
     <row r="331" hidden="1" outlineLevel="2">
       <c r="A331" s="4" t="n">
@@ -4352,9 +4705,10 @@
       <c r="B331" s="5" t="n"/>
       <c r="C331" s="6" t="n"/>
       <c r="D331" s="6" t="n"/>
-      <c r="E331" s="5" t="n"/>
+      <c r="E331" s="6" t="n"/>
       <c r="F331" s="5" t="n"/>
-      <c r="G331" s="6" t="n"/>
+      <c r="G331" s="5" t="n"/>
+      <c r="H331" s="6" t="n"/>
     </row>
     <row r="332" hidden="1" outlineLevel="2">
       <c r="A332" s="4" t="n">
@@ -4363,9 +4717,10 @@
       <c r="B332" s="5" t="n"/>
       <c r="C332" s="6" t="n"/>
       <c r="D332" s="6" t="n"/>
-      <c r="E332" s="5" t="n"/>
+      <c r="E332" s="6" t="n"/>
       <c r="F332" s="5" t="n"/>
-      <c r="G332" s="6" t="n"/>
+      <c r="G332" s="5" t="n"/>
+      <c r="H332" s="6" t="n"/>
     </row>
     <row r="333" hidden="1" outlineLevel="2">
       <c r="A333" s="4" t="n">
@@ -4374,9 +4729,10 @@
       <c r="B333" s="5" t="n"/>
       <c r="C333" s="6" t="n"/>
       <c r="D333" s="6" t="n"/>
-      <c r="E333" s="5" t="n"/>
+      <c r="E333" s="6" t="n"/>
       <c r="F333" s="5" t="n"/>
-      <c r="G333" s="6" t="n"/>
+      <c r="G333" s="5" t="n"/>
+      <c r="H333" s="6" t="n"/>
     </row>
     <row r="334" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A334" s="4" t="n">
@@ -4385,9 +4741,10 @@
       <c r="B334" s="5" t="n"/>
       <c r="C334" s="6" t="n"/>
       <c r="D334" s="6" t="n"/>
-      <c r="E334" s="5" t="n"/>
+      <c r="E334" s="6" t="n"/>
       <c r="F334" s="5" t="n"/>
-      <c r="G334" s="6" t="n"/>
+      <c r="G334" s="5" t="n"/>
+      <c r="H334" s="6" t="n"/>
     </row>
     <row r="335" hidden="1" outlineLevel="2">
       <c r="A335" s="4" t="n">
@@ -4396,9 +4753,10 @@
       <c r="B335" s="5" t="n"/>
       <c r="C335" s="6" t="n"/>
       <c r="D335" s="6" t="n"/>
-      <c r="E335" s="5" t="n"/>
+      <c r="E335" s="6" t="n"/>
       <c r="F335" s="5" t="n"/>
-      <c r="G335" s="6" t="n"/>
+      <c r="G335" s="5" t="n"/>
+      <c r="H335" s="6" t="n"/>
     </row>
     <row r="336" hidden="1" outlineLevel="2">
       <c r="A336" s="4" t="n">
@@ -4407,9 +4765,10 @@
       <c r="B336" s="5" t="n"/>
       <c r="C336" s="6" t="n"/>
       <c r="D336" s="6" t="n"/>
-      <c r="E336" s="5" t="n"/>
+      <c r="E336" s="6" t="n"/>
       <c r="F336" s="5" t="n"/>
-      <c r="G336" s="6" t="n"/>
+      <c r="G336" s="5" t="n"/>
+      <c r="H336" s="6" t="n"/>
     </row>
     <row r="337" hidden="1" outlineLevel="2">
       <c r="A337" s="4" t="n">
@@ -4418,9 +4777,10 @@
       <c r="B337" s="5" t="n"/>
       <c r="C337" s="6" t="n"/>
       <c r="D337" s="6" t="n"/>
-      <c r="E337" s="5" t="n"/>
+      <c r="E337" s="6" t="n"/>
       <c r="F337" s="5" t="n"/>
-      <c r="G337" s="6" t="n"/>
+      <c r="G337" s="5" t="n"/>
+      <c r="H337" s="6" t="n"/>
     </row>
     <row r="338" collapsed="1">
       <c r="A338" s="4" t="n">
@@ -4439,12 +4799,13 @@
         </is>
       </c>
       <c r="D338" s="6" t="n"/>
-      <c r="E338" s="5" t="n"/>
-      <c r="F338" s="5">
+      <c r="E338" s="6" t="n"/>
+      <c r="F338" s="5" t="n"/>
+      <c r="G338" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G338" s="6" t="inlineStr">
+      <c r="H338" s="6" t="inlineStr">
         <is>
           <t>matrixMovieFX(15735, 80, 100, 6)</t>
         </is>
@@ -4457,9 +4818,10 @@
       <c r="B339" s="5" t="n"/>
       <c r="C339" s="6" t="n"/>
       <c r="D339" s="6" t="n"/>
-      <c r="E339" s="5" t="n"/>
+      <c r="E339" s="6" t="n"/>
       <c r="F339" s="5" t="n"/>
-      <c r="G339" s="6" t="n"/>
+      <c r="G339" s="5" t="n"/>
+      <c r="H339" s="6" t="n"/>
     </row>
     <row r="340" hidden="1" outlineLevel="2">
       <c r="A340" s="4" t="n">
@@ -4468,9 +4830,10 @@
       <c r="B340" s="5" t="n"/>
       <c r="C340" s="6" t="n"/>
       <c r="D340" s="6" t="n"/>
-      <c r="E340" s="5" t="n"/>
+      <c r="E340" s="6" t="n"/>
       <c r="F340" s="5" t="n"/>
-      <c r="G340" s="6" t="n"/>
+      <c r="G340" s="5" t="n"/>
+      <c r="H340" s="6" t="n"/>
     </row>
     <row r="341" hidden="1" outlineLevel="2">
       <c r="A341" s="4" t="n">
@@ -4479,9 +4842,10 @@
       <c r="B341" s="5" t="n"/>
       <c r="C341" s="6" t="n"/>
       <c r="D341" s="6" t="n"/>
-      <c r="E341" s="5" t="n"/>
+      <c r="E341" s="6" t="n"/>
       <c r="F341" s="5" t="n"/>
-      <c r="G341" s="6" t="n"/>
+      <c r="G341" s="5" t="n"/>
+      <c r="H341" s="6" t="n"/>
     </row>
     <row r="342" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A342" s="4" t="n">
@@ -4490,9 +4854,10 @@
       <c r="B342" s="5" t="n"/>
       <c r="C342" s="6" t="n"/>
       <c r="D342" s="6" t="n"/>
-      <c r="E342" s="5" t="n"/>
+      <c r="E342" s="6" t="n"/>
       <c r="F342" s="5" t="n"/>
-      <c r="G342" s="6" t="n"/>
+      <c r="G342" s="5" t="n"/>
+      <c r="H342" s="6" t="n"/>
     </row>
     <row r="343" hidden="1" outlineLevel="2">
       <c r="A343" s="4" t="n">
@@ -4501,9 +4866,10 @@
       <c r="B343" s="5" t="n"/>
       <c r="C343" s="6" t="n"/>
       <c r="D343" s="6" t="n"/>
-      <c r="E343" s="5" t="n"/>
+      <c r="E343" s="6" t="n"/>
       <c r="F343" s="5" t="n"/>
-      <c r="G343" s="6" t="n"/>
+      <c r="G343" s="5" t="n"/>
+      <c r="H343" s="6" t="n"/>
     </row>
     <row r="344" hidden="1" outlineLevel="2">
       <c r="A344" s="4" t="n">
@@ -4512,9 +4878,10 @@
       <c r="B344" s="5" t="n"/>
       <c r="C344" s="6" t="n"/>
       <c r="D344" s="6" t="n"/>
-      <c r="E344" s="5" t="n"/>
+      <c r="E344" s="6" t="n"/>
       <c r="F344" s="5" t="n"/>
-      <c r="G344" s="6" t="n"/>
+      <c r="G344" s="5" t="n"/>
+      <c r="H344" s="6" t="n"/>
     </row>
     <row r="345" hidden="1" outlineLevel="2">
       <c r="A345" s="4" t="n">
@@ -4523,9 +4890,10 @@
       <c r="B345" s="5" t="n"/>
       <c r="C345" s="6" t="n"/>
       <c r="D345" s="6" t="n"/>
-      <c r="E345" s="5" t="n"/>
+      <c r="E345" s="6" t="n"/>
       <c r="F345" s="5" t="n"/>
-      <c r="G345" s="6" t="n"/>
+      <c r="G345" s="5" t="n"/>
+      <c r="H345" s="6" t="n"/>
     </row>
     <row r="346" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A346" s="4" t="n">
@@ -4534,9 +4902,10 @@
       <c r="B346" s="5" t="n"/>
       <c r="C346" s="6" t="n"/>
       <c r="D346" s="6" t="n"/>
-      <c r="E346" s="5" t="n"/>
+      <c r="E346" s="6" t="n"/>
       <c r="F346" s="5" t="n"/>
-      <c r="G346" s="6" t="n"/>
+      <c r="G346" s="5" t="n"/>
+      <c r="H346" s="6" t="n"/>
     </row>
     <row r="347" hidden="1" outlineLevel="2">
       <c r="A347" s="4" t="n">
@@ -4545,9 +4914,10 @@
       <c r="B347" s="5" t="n"/>
       <c r="C347" s="6" t="n"/>
       <c r="D347" s="6" t="n"/>
-      <c r="E347" s="5" t="n"/>
+      <c r="E347" s="6" t="n"/>
       <c r="F347" s="5" t="n"/>
-      <c r="G347" s="6" t="n"/>
+      <c r="G347" s="5" t="n"/>
+      <c r="H347" s="6" t="n"/>
     </row>
     <row r="348" hidden="1" outlineLevel="2">
       <c r="A348" s="4" t="n">
@@ -4556,9 +4926,10 @@
       <c r="B348" s="5" t="n"/>
       <c r="C348" s="6" t="n"/>
       <c r="D348" s="6" t="n"/>
-      <c r="E348" s="5" t="n"/>
+      <c r="E348" s="6" t="n"/>
       <c r="F348" s="5" t="n"/>
-      <c r="G348" s="6" t="n"/>
+      <c r="G348" s="5" t="n"/>
+      <c r="H348" s="6" t="n"/>
     </row>
     <row r="349" hidden="1" outlineLevel="2">
       <c r="A349" s="4" t="n">
@@ -4567,9 +4938,10 @@
       <c r="B349" s="5" t="n"/>
       <c r="C349" s="6" t="n"/>
       <c r="D349" s="6" t="n"/>
-      <c r="E349" s="5" t="n"/>
+      <c r="E349" s="6" t="n"/>
       <c r="F349" s="5" t="n"/>
-      <c r="G349" s="6" t="n"/>
+      <c r="G349" s="5" t="n"/>
+      <c r="H349" s="6" t="n"/>
     </row>
     <row r="350" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A350" s="4" t="n">
@@ -4578,9 +4950,10 @@
       <c r="B350" s="5" t="n"/>
       <c r="C350" s="6" t="n"/>
       <c r="D350" s="6" t="n"/>
-      <c r="E350" s="5" t="n"/>
+      <c r="E350" s="6" t="n"/>
       <c r="F350" s="5" t="n"/>
-      <c r="G350" s="6" t="n"/>
+      <c r="G350" s="5" t="n"/>
+      <c r="H350" s="6" t="n"/>
     </row>
     <row r="351" hidden="1" outlineLevel="2">
       <c r="A351" s="4" t="n">
@@ -4589,9 +4962,10 @@
       <c r="B351" s="5" t="n"/>
       <c r="C351" s="6" t="n"/>
       <c r="D351" s="6" t="n"/>
-      <c r="E351" s="5" t="n"/>
+      <c r="E351" s="6" t="n"/>
       <c r="F351" s="5" t="n"/>
-      <c r="G351" s="6" t="n"/>
+      <c r="G351" s="5" t="n"/>
+      <c r="H351" s="6" t="n"/>
     </row>
     <row r="352" hidden="1" outlineLevel="2">
       <c r="A352" s="4" t="n">
@@ -4600,9 +4974,10 @@
       <c r="B352" s="5" t="n"/>
       <c r="C352" s="6" t="n"/>
       <c r="D352" s="6" t="n"/>
-      <c r="E352" s="5" t="n"/>
+      <c r="E352" s="6" t="n"/>
       <c r="F352" s="5" t="n"/>
-      <c r="G352" s="6" t="n"/>
+      <c r="G352" s="5" t="n"/>
+      <c r="H352" s="6" t="n"/>
     </row>
     <row r="353" hidden="1" outlineLevel="2">
       <c r="A353" s="4" t="n">
@@ -4611,9 +4986,10 @@
       <c r="B353" s="5" t="n"/>
       <c r="C353" s="6" t="n"/>
       <c r="D353" s="6" t="n"/>
-      <c r="E353" s="5" t="n"/>
+      <c r="E353" s="6" t="n"/>
       <c r="F353" s="5" t="n"/>
-      <c r="G353" s="6" t="n"/>
+      <c r="G353" s="5" t="n"/>
+      <c r="H353" s="6" t="n"/>
     </row>
     <row r="354" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A354" s="4" t="n">
@@ -4622,9 +4998,10 @@
       <c r="B354" s="5" t="n"/>
       <c r="C354" s="6" t="n"/>
       <c r="D354" s="6" t="n"/>
-      <c r="E354" s="5" t="n"/>
+      <c r="E354" s="6" t="n"/>
       <c r="F354" s="5" t="n"/>
-      <c r="G354" s="6" t="n"/>
+      <c r="G354" s="5" t="n"/>
+      <c r="H354" s="6" t="n"/>
     </row>
     <row r="355" hidden="1" outlineLevel="2">
       <c r="A355" s="4" t="n">
@@ -4633,9 +5010,10 @@
       <c r="B355" s="5" t="n"/>
       <c r="C355" s="6" t="n"/>
       <c r="D355" s="6" t="n"/>
-      <c r="E355" s="5" t="n"/>
+      <c r="E355" s="6" t="n"/>
       <c r="F355" s="5" t="n"/>
-      <c r="G355" s="6" t="n"/>
+      <c r="G355" s="5" t="n"/>
+      <c r="H355" s="6" t="n"/>
     </row>
     <row r="356" hidden="1" outlineLevel="2">
       <c r="A356" s="4" t="n">
@@ -4644,9 +5022,10 @@
       <c r="B356" s="5" t="n"/>
       <c r="C356" s="6" t="n"/>
       <c r="D356" s="6" t="n"/>
-      <c r="E356" s="5" t="n"/>
+      <c r="E356" s="6" t="n"/>
       <c r="F356" s="5" t="n"/>
-      <c r="G356" s="6" t="n"/>
+      <c r="G356" s="5" t="n"/>
+      <c r="H356" s="6" t="n"/>
     </row>
     <row r="357" hidden="1" outlineLevel="2">
       <c r="A357" s="4" t="n">
@@ -4655,9 +5034,10 @@
       <c r="B357" s="5" t="n"/>
       <c r="C357" s="6" t="n"/>
       <c r="D357" s="6" t="n"/>
-      <c r="E357" s="5" t="n"/>
+      <c r="E357" s="6" t="n"/>
       <c r="F357" s="5" t="n"/>
-      <c r="G357" s="6" t="n"/>
+      <c r="G357" s="5" t="n"/>
+      <c r="H357" s="6" t="n"/>
     </row>
     <row r="358" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A358" s="4" t="n">
@@ -4666,9 +5046,10 @@
       <c r="B358" s="5" t="n"/>
       <c r="C358" s="6" t="n"/>
       <c r="D358" s="6" t="n"/>
-      <c r="E358" s="5" t="n"/>
+      <c r="E358" s="6" t="n"/>
       <c r="F358" s="5" t="n"/>
-      <c r="G358" s="6" t="n"/>
+      <c r="G358" s="5" t="n"/>
+      <c r="H358" s="6" t="n"/>
     </row>
     <row r="359" hidden="1" outlineLevel="2">
       <c r="A359" s="4" t="n">
@@ -4677,9 +5058,10 @@
       <c r="B359" s="5" t="n"/>
       <c r="C359" s="6" t="n"/>
       <c r="D359" s="6" t="n"/>
-      <c r="E359" s="5" t="n"/>
+      <c r="E359" s="6" t="n"/>
       <c r="F359" s="5" t="n"/>
-      <c r="G359" s="6" t="n"/>
+      <c r="G359" s="5" t="n"/>
+      <c r="H359" s="6" t="n"/>
     </row>
     <row r="360" hidden="1" outlineLevel="2">
       <c r="A360" s="4" t="n">
@@ -4688,9 +5070,10 @@
       <c r="B360" s="5" t="n"/>
       <c r="C360" s="6" t="n"/>
       <c r="D360" s="6" t="n"/>
-      <c r="E360" s="5" t="n"/>
+      <c r="E360" s="6" t="n"/>
       <c r="F360" s="5" t="n"/>
-      <c r="G360" s="6" t="n"/>
+      <c r="G360" s="5" t="n"/>
+      <c r="H360" s="6" t="n"/>
     </row>
     <row r="361" hidden="1" outlineLevel="2">
       <c r="A361" s="4" t="n">
@@ -4699,9 +5082,10 @@
       <c r="B361" s="5" t="n"/>
       <c r="C361" s="6" t="n"/>
       <c r="D361" s="6" t="n"/>
-      <c r="E361" s="5" t="n"/>
+      <c r="E361" s="6" t="n"/>
       <c r="F361" s="5" t="n"/>
-      <c r="G361" s="6" t="n"/>
+      <c r="G361" s="5" t="n"/>
+      <c r="H361" s="6" t="n"/>
     </row>
     <row r="362" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A362" s="4" t="n">
@@ -4710,9 +5094,10 @@
       <c r="B362" s="5" t="n"/>
       <c r="C362" s="6" t="n"/>
       <c r="D362" s="6" t="n"/>
-      <c r="E362" s="5" t="n"/>
+      <c r="E362" s="6" t="n"/>
       <c r="F362" s="5" t="n"/>
-      <c r="G362" s="6" t="n"/>
+      <c r="G362" s="5" t="n"/>
+      <c r="H362" s="6" t="n"/>
     </row>
     <row r="363" hidden="1" outlineLevel="2">
       <c r="A363" s="4" t="n">
@@ -4721,9 +5106,10 @@
       <c r="B363" s="5" t="n"/>
       <c r="C363" s="6" t="n"/>
       <c r="D363" s="6" t="n"/>
-      <c r="E363" s="5" t="n"/>
+      <c r="E363" s="6" t="n"/>
       <c r="F363" s="5" t="n"/>
-      <c r="G363" s="6" t="n"/>
+      <c r="G363" s="5" t="n"/>
+      <c r="H363" s="6" t="n"/>
     </row>
     <row r="364" hidden="1" outlineLevel="2">
       <c r="A364" s="4" t="n">
@@ -4732,9 +5118,10 @@
       <c r="B364" s="5" t="n"/>
       <c r="C364" s="6" t="n"/>
       <c r="D364" s="6" t="n"/>
-      <c r="E364" s="5" t="n"/>
+      <c r="E364" s="6" t="n"/>
       <c r="F364" s="5" t="n"/>
-      <c r="G364" s="6" t="n"/>
+      <c r="G364" s="5" t="n"/>
+      <c r="H364" s="6" t="n"/>
     </row>
     <row r="365" hidden="1" outlineLevel="2">
       <c r="A365" s="4" t="n">
@@ -4743,9 +5130,10 @@
       <c r="B365" s="5" t="n"/>
       <c r="C365" s="6" t="n"/>
       <c r="D365" s="6" t="n"/>
-      <c r="E365" s="5" t="n"/>
+      <c r="E365" s="6" t="n"/>
       <c r="F365" s="5" t="n"/>
-      <c r="G365" s="6" t="n"/>
+      <c r="G365" s="5" t="n"/>
+      <c r="H365" s="6" t="n"/>
     </row>
     <row r="366" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A366" s="4" t="n">
@@ -4754,9 +5142,10 @@
       <c r="B366" s="5" t="n"/>
       <c r="C366" s="6" t="n"/>
       <c r="D366" s="6" t="n"/>
-      <c r="E366" s="5" t="n"/>
+      <c r="E366" s="6" t="n"/>
       <c r="F366" s="5" t="n"/>
-      <c r="G366" s="6" t="n"/>
+      <c r="G366" s="5" t="n"/>
+      <c r="H366" s="6" t="n"/>
     </row>
     <row r="367" hidden="1" outlineLevel="2">
       <c r="A367" s="4" t="n">
@@ -4765,9 +5154,10 @@
       <c r="B367" s="5" t="n"/>
       <c r="C367" s="6" t="n"/>
       <c r="D367" s="6" t="n"/>
-      <c r="E367" s="5" t="n"/>
+      <c r="E367" s="6" t="n"/>
       <c r="F367" s="5" t="n"/>
-      <c r="G367" s="6" t="n"/>
+      <c r="G367" s="5" t="n"/>
+      <c r="H367" s="6" t="n"/>
     </row>
     <row r="368" hidden="1" outlineLevel="2">
       <c r="A368" s="4" t="n">
@@ -4776,9 +5166,10 @@
       <c r="B368" s="5" t="n"/>
       <c r="C368" s="6" t="n"/>
       <c r="D368" s="6" t="n"/>
-      <c r="E368" s="5" t="n"/>
+      <c r="E368" s="6" t="n"/>
       <c r="F368" s="5" t="n"/>
-      <c r="G368" s="6" t="n"/>
+      <c r="G368" s="5" t="n"/>
+      <c r="H368" s="6" t="n"/>
     </row>
     <row r="369" hidden="1" outlineLevel="2">
       <c r="A369" s="4" t="n">
@@ -4787,9 +5178,10 @@
       <c r="B369" s="5" t="n"/>
       <c r="C369" s="6" t="n"/>
       <c r="D369" s="6" t="n"/>
-      <c r="E369" s="5" t="n"/>
+      <c r="E369" s="6" t="n"/>
       <c r="F369" s="5" t="n"/>
-      <c r="G369" s="6" t="n"/>
+      <c r="G369" s="5" t="n"/>
+      <c r="H369" s="6" t="n"/>
     </row>
     <row r="370" collapsed="1">
       <c r="A370" s="4" t="n">
@@ -4807,12 +5199,13 @@
         </is>
       </c>
       <c r="D370" s="6" t="n"/>
-      <c r="E370" s="5" t="n"/>
-      <c r="F370" s="5">
+      <c r="E370" s="6" t="n"/>
+      <c r="F370" s="5" t="n"/>
+      <c r="G370" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G370" s="6" t="inlineStr">
+      <c r="H370" s="6" t="inlineStr">
         <is>
           <t>progBlack(5900, 85)</t>
         </is>
@@ -4825,9 +5218,10 @@
       <c r="B371" s="5" t="n"/>
       <c r="C371" s="6" t="n"/>
       <c r="D371" s="6" t="n"/>
-      <c r="E371" s="5" t="n"/>
+      <c r="E371" s="6" t="n"/>
       <c r="F371" s="5" t="n"/>
-      <c r="G371" s="6" t="n"/>
+      <c r="G371" s="5" t="n"/>
+      <c r="H371" s="6" t="n"/>
     </row>
     <row r="372" hidden="1" outlineLevel="2">
       <c r="A372" s="4" t="n">
@@ -4836,9 +5230,10 @@
       <c r="B372" s="5" t="n"/>
       <c r="C372" s="6" t="n"/>
       <c r="D372" s="6" t="n"/>
-      <c r="E372" s="5" t="n"/>
+      <c r="E372" s="6" t="n"/>
       <c r="F372" s="5" t="n"/>
-      <c r="G372" s="6" t="n"/>
+      <c r="G372" s="5" t="n"/>
+      <c r="H372" s="6" t="n"/>
     </row>
     <row r="373" hidden="1" outlineLevel="2">
       <c r="A373" s="4" t="n">
@@ -4847,9 +5242,10 @@
       <c r="B373" s="5" t="n"/>
       <c r="C373" s="6" t="n"/>
       <c r="D373" s="6" t="n"/>
-      <c r="E373" s="5" t="n"/>
+      <c r="E373" s="6" t="n"/>
       <c r="F373" s="5" t="n"/>
-      <c r="G373" s="6" t="n"/>
+      <c r="G373" s="5" t="n"/>
+      <c r="H373" s="6" t="n"/>
     </row>
     <row r="374" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A374" s="4" t="n">
@@ -4858,9 +5254,10 @@
       <c r="B374" s="5" t="n"/>
       <c r="C374" s="6" t="n"/>
       <c r="D374" s="6" t="n"/>
-      <c r="E374" s="5" t="n"/>
+      <c r="E374" s="6" t="n"/>
       <c r="F374" s="5" t="n"/>
-      <c r="G374" s="6" t="n"/>
+      <c r="G374" s="5" t="n"/>
+      <c r="H374" s="6" t="n"/>
     </row>
     <row r="375" hidden="1" outlineLevel="2">
       <c r="A375" s="4" t="n">
@@ -4869,9 +5266,10 @@
       <c r="B375" s="5" t="n"/>
       <c r="C375" s="6" t="n"/>
       <c r="D375" s="6" t="n"/>
-      <c r="E375" s="5" t="n"/>
+      <c r="E375" s="6" t="n"/>
       <c r="F375" s="5" t="n"/>
-      <c r="G375" s="6" t="n"/>
+      <c r="G375" s="5" t="n"/>
+      <c r="H375" s="6" t="n"/>
     </row>
     <row r="376" hidden="1" outlineLevel="2">
       <c r="A376" s="4" t="n">
@@ -4880,9 +5278,10 @@
       <c r="B376" s="5" t="n"/>
       <c r="C376" s="6" t="n"/>
       <c r="D376" s="6" t="n"/>
-      <c r="E376" s="5" t="n"/>
+      <c r="E376" s="6" t="n"/>
       <c r="F376" s="5" t="n"/>
-      <c r="G376" s="6" t="n"/>
+      <c r="G376" s="5" t="n"/>
+      <c r="H376" s="6" t="n"/>
     </row>
     <row r="377" hidden="1" outlineLevel="2">
       <c r="A377" s="4" t="n">
@@ -4891,9 +5290,10 @@
       <c r="B377" s="5" t="n"/>
       <c r="C377" s="6" t="n"/>
       <c r="D377" s="6" t="n"/>
-      <c r="E377" s="5" t="n"/>
+      <c r="E377" s="6" t="n"/>
       <c r="F377" s="5" t="n"/>
-      <c r="G377" s="6" t="n"/>
+      <c r="G377" s="5" t="n"/>
+      <c r="H377" s="6" t="n"/>
     </row>
     <row r="378" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A378" s="4" t="n">
@@ -4902,9 +5302,10 @@
       <c r="B378" s="5" t="n"/>
       <c r="C378" s="6" t="n"/>
       <c r="D378" s="6" t="n"/>
-      <c r="E378" s="5" t="n"/>
+      <c r="E378" s="6" t="n"/>
       <c r="F378" s="5" t="n"/>
-      <c r="G378" s="6" t="n"/>
+      <c r="G378" s="5" t="n"/>
+      <c r="H378" s="6" t="n"/>
     </row>
     <row r="379" hidden="1" outlineLevel="2">
       <c r="A379" s="4" t="n">
@@ -4913,9 +5314,10 @@
       <c r="B379" s="5" t="n"/>
       <c r="C379" s="6" t="n"/>
       <c r="D379" s="6" t="n"/>
-      <c r="E379" s="5" t="n"/>
+      <c r="E379" s="6" t="n"/>
       <c r="F379" s="5" t="n"/>
-      <c r="G379" s="6" t="n"/>
+      <c r="G379" s="5" t="n"/>
+      <c r="H379" s="6" t="n"/>
     </row>
     <row r="380" hidden="1" outlineLevel="2">
       <c r="A380" s="4" t="n">
@@ -4924,9 +5326,10 @@
       <c r="B380" s="5" t="n"/>
       <c r="C380" s="6" t="n"/>
       <c r="D380" s="6" t="n"/>
-      <c r="E380" s="5" t="n"/>
+      <c r="E380" s="6" t="n"/>
       <c r="F380" s="5" t="n"/>
-      <c r="G380" s="6" t="n"/>
+      <c r="G380" s="5" t="n"/>
+      <c r="H380" s="6" t="n"/>
     </row>
     <row r="381" hidden="1" outlineLevel="2">
       <c r="A381" s="4" t="n">
@@ -4935,9 +5338,10 @@
       <c r="B381" s="5" t="n"/>
       <c r="C381" s="6" t="n"/>
       <c r="D381" s="6" t="n"/>
-      <c r="E381" s="5" t="n"/>
+      <c r="E381" s="6" t="n"/>
       <c r="F381" s="5" t="n"/>
-      <c r="G381" s="6" t="n"/>
+      <c r="G381" s="5" t="n"/>
+      <c r="H381" s="6" t="n"/>
     </row>
     <row r="382" collapsed="1">
       <c r="A382" s="4" t="n">
@@ -4955,12 +5359,13 @@
         </is>
       </c>
       <c r="D382" s="6" t="n"/>
-      <c r="E382" s="5" t="n"/>
-      <c r="F382" s="5">
+      <c r="E382" s="6" t="n"/>
+      <c r="F382" s="5" t="n"/>
+      <c r="G382" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G382" s="6" t="inlineStr">
+      <c r="H382" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1970, 90, 50, getRandomCRGB())</t>
         </is>
@@ -4973,9 +5378,10 @@
       <c r="B383" s="5" t="n"/>
       <c r="C383" s="6" t="n"/>
       <c r="D383" s="6" t="n"/>
-      <c r="E383" s="5" t="n"/>
+      <c r="E383" s="6" t="n"/>
       <c r="F383" s="5" t="n"/>
-      <c r="G383" s="6" t="n"/>
+      <c r="G383" s="5" t="n"/>
+      <c r="H383" s="6" t="n"/>
     </row>
     <row r="384" hidden="1" outlineLevel="2">
       <c r="A384" s="4" t="n">
@@ -4984,9 +5390,10 @@
       <c r="B384" s="5" t="n"/>
       <c r="C384" s="6" t="n"/>
       <c r="D384" s="6" t="n"/>
-      <c r="E384" s="5" t="n"/>
+      <c r="E384" s="6" t="n"/>
       <c r="F384" s="5" t="n"/>
-      <c r="G384" s="6" t="n"/>
+      <c r="G384" s="5" t="n"/>
+      <c r="H384" s="6" t="n"/>
     </row>
     <row r="385" hidden="1" outlineLevel="2">
       <c r="A385" s="4" t="n">
@@ -4995,9 +5402,10 @@
       <c r="B385" s="5" t="n"/>
       <c r="C385" s="6" t="n"/>
       <c r="D385" s="6" t="n"/>
-      <c r="E385" s="5" t="n"/>
+      <c r="E385" s="6" t="n"/>
       <c r="F385" s="5" t="n"/>
-      <c r="G385" s="6" t="n"/>
+      <c r="G385" s="5" t="n"/>
+      <c r="H385" s="6" t="n"/>
     </row>
     <row r="386" collapsed="1">
       <c r="A386" s="4" t="n">
@@ -5015,12 +5423,13 @@
         </is>
       </c>
       <c r="D386" s="6" t="n"/>
-      <c r="E386" s="5" t="n"/>
-      <c r="F386" s="5">
+      <c r="E386" s="6" t="n"/>
+      <c r="F386" s="5" t="n"/>
+      <c r="G386" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G386" s="6" t="inlineStr">
+      <c r="H386" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(7870, 95, 50, true, true)</t>
         </is>
@@ -5033,9 +5442,10 @@
       <c r="B387" s="5" t="n"/>
       <c r="C387" s="6" t="n"/>
       <c r="D387" s="6" t="n"/>
-      <c r="E387" s="5" t="n"/>
+      <c r="E387" s="6" t="n"/>
       <c r="F387" s="5" t="n"/>
-      <c r="G387" s="6" t="n"/>
+      <c r="G387" s="5" t="n"/>
+      <c r="H387" s="6" t="n"/>
     </row>
     <row r="388" hidden="1" outlineLevel="2">
       <c r="A388" s="4" t="n">
@@ -5044,9 +5454,10 @@
       <c r="B388" s="5" t="n"/>
       <c r="C388" s="6" t="n"/>
       <c r="D388" s="6" t="n"/>
-      <c r="E388" s="5" t="n"/>
+      <c r="E388" s="6" t="n"/>
       <c r="F388" s="5" t="n"/>
-      <c r="G388" s="6" t="n"/>
+      <c r="G388" s="5" t="n"/>
+      <c r="H388" s="6" t="n"/>
     </row>
     <row r="389" hidden="1" outlineLevel="2">
       <c r="A389" s="4" t="n">
@@ -5055,9 +5466,10 @@
       <c r="B389" s="5" t="n"/>
       <c r="C389" s="6" t="n"/>
       <c r="D389" s="6" t="n"/>
-      <c r="E389" s="5" t="n"/>
+      <c r="E389" s="6" t="n"/>
       <c r="F389" s="5" t="n"/>
-      <c r="G389" s="6" t="n"/>
+      <c r="G389" s="5" t="n"/>
+      <c r="H389" s="6" t="n"/>
     </row>
     <row r="390" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A390" s="4" t="n">
@@ -5066,9 +5478,10 @@
       <c r="B390" s="5" t="n"/>
       <c r="C390" s="6" t="n"/>
       <c r="D390" s="6" t="n"/>
-      <c r="E390" s="5" t="n"/>
+      <c r="E390" s="6" t="n"/>
       <c r="F390" s="5" t="n"/>
-      <c r="G390" s="6" t="n"/>
+      <c r="G390" s="5" t="n"/>
+      <c r="H390" s="6" t="n"/>
     </row>
     <row r="391" hidden="1" outlineLevel="2">
       <c r="A391" s="4" t="n">
@@ -5077,9 +5490,10 @@
       <c r="B391" s="5" t="n"/>
       <c r="C391" s="6" t="n"/>
       <c r="D391" s="6" t="n"/>
-      <c r="E391" s="5" t="n"/>
+      <c r="E391" s="6" t="n"/>
       <c r="F391" s="5" t="n"/>
-      <c r="G391" s="6" t="n"/>
+      <c r="G391" s="5" t="n"/>
+      <c r="H391" s="6" t="n"/>
     </row>
     <row r="392" hidden="1" outlineLevel="2">
       <c r="A392" s="4" t="n">
@@ -5088,9 +5502,10 @@
       <c r="B392" s="5" t="n"/>
       <c r="C392" s="6" t="n"/>
       <c r="D392" s="6" t="n"/>
-      <c r="E392" s="5" t="n"/>
+      <c r="E392" s="6" t="n"/>
       <c r="F392" s="5" t="n"/>
-      <c r="G392" s="6" t="n"/>
+      <c r="G392" s="5" t="n"/>
+      <c r="H392" s="6" t="n"/>
     </row>
     <row r="393" hidden="1" outlineLevel="2">
       <c r="A393" s="4" t="n">
@@ -5099,9 +5514,10 @@
       <c r="B393" s="5" t="n"/>
       <c r="C393" s="6" t="n"/>
       <c r="D393" s="6" t="n"/>
-      <c r="E393" s="5" t="n"/>
+      <c r="E393" s="6" t="n"/>
       <c r="F393" s="5" t="n"/>
-      <c r="G393" s="6" t="n"/>
+      <c r="G393" s="5" t="n"/>
+      <c r="H393" s="6" t="n"/>
     </row>
     <row r="394" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A394" s="4" t="n">
@@ -5110,9 +5526,10 @@
       <c r="B394" s="5" t="n"/>
       <c r="C394" s="6" t="n"/>
       <c r="D394" s="6" t="n"/>
-      <c r="E394" s="5" t="n"/>
+      <c r="E394" s="6" t="n"/>
       <c r="F394" s="5" t="n"/>
-      <c r="G394" s="6" t="n"/>
+      <c r="G394" s="5" t="n"/>
+      <c r="H394" s="6" t="n"/>
     </row>
     <row r="395" hidden="1" outlineLevel="2">
       <c r="A395" s="4" t="n">
@@ -5121,9 +5538,10 @@
       <c r="B395" s="5" t="n"/>
       <c r="C395" s="6" t="n"/>
       <c r="D395" s="6" t="n"/>
-      <c r="E395" s="5" t="n"/>
+      <c r="E395" s="6" t="n"/>
       <c r="F395" s="5" t="n"/>
-      <c r="G395" s="6" t="n"/>
+      <c r="G395" s="5" t="n"/>
+      <c r="H395" s="6" t="n"/>
     </row>
     <row r="396" hidden="1" outlineLevel="2">
       <c r="A396" s="4" t="n">
@@ -5132,9 +5550,10 @@
       <c r="B396" s="5" t="n"/>
       <c r="C396" s="6" t="n"/>
       <c r="D396" s="6" t="n"/>
-      <c r="E396" s="5" t="n"/>
+      <c r="E396" s="6" t="n"/>
       <c r="F396" s="5" t="n"/>
-      <c r="G396" s="6" t="n"/>
+      <c r="G396" s="5" t="n"/>
+      <c r="H396" s="6" t="n"/>
     </row>
     <row r="397" hidden="1" outlineLevel="2">
       <c r="A397" s="4" t="n">
@@ -5143,9 +5562,10 @@
       <c r="B397" s="5" t="n"/>
       <c r="C397" s="6" t="n"/>
       <c r="D397" s="6" t="n"/>
-      <c r="E397" s="5" t="n"/>
+      <c r="E397" s="6" t="n"/>
       <c r="F397" s="5" t="n"/>
-      <c r="G397" s="6" t="n"/>
+      <c r="G397" s="5" t="n"/>
+      <c r="H397" s="6" t="n"/>
     </row>
     <row r="398" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A398" s="4" t="n">
@@ -5154,9 +5574,10 @@
       <c r="B398" s="5" t="n"/>
       <c r="C398" s="6" t="n"/>
       <c r="D398" s="6" t="n"/>
-      <c r="E398" s="5" t="n"/>
+      <c r="E398" s="6" t="n"/>
       <c r="F398" s="5" t="n"/>
-      <c r="G398" s="6" t="n"/>
+      <c r="G398" s="5" t="n"/>
+      <c r="H398" s="6" t="n"/>
     </row>
     <row r="399" hidden="1" outlineLevel="2">
       <c r="A399" s="4" t="n">
@@ -5165,9 +5586,10 @@
       <c r="B399" s="5" t="n"/>
       <c r="C399" s="6" t="n"/>
       <c r="D399" s="6" t="n"/>
-      <c r="E399" s="5" t="n"/>
+      <c r="E399" s="6" t="n"/>
       <c r="F399" s="5" t="n"/>
-      <c r="G399" s="6" t="n"/>
+      <c r="G399" s="5" t="n"/>
+      <c r="H399" s="6" t="n"/>
     </row>
     <row r="400" hidden="1" outlineLevel="2">
       <c r="A400" s="4" t="n">
@@ -5176,9 +5598,10 @@
       <c r="B400" s="5" t="n"/>
       <c r="C400" s="6" t="n"/>
       <c r="D400" s="6" t="n"/>
-      <c r="E400" s="5" t="n"/>
+      <c r="E400" s="6" t="n"/>
       <c r="F400" s="5" t="n"/>
-      <c r="G400" s="6" t="n"/>
+      <c r="G400" s="5" t="n"/>
+      <c r="H400" s="6" t="n"/>
     </row>
     <row r="401" hidden="1" outlineLevel="2">
       <c r="A401" s="4" t="n">
@@ -5187,9 +5610,10 @@
       <c r="B401" s="5" t="n"/>
       <c r="C401" s="6" t="n"/>
       <c r="D401" s="6" t="n"/>
-      <c r="E401" s="5" t="n"/>
+      <c r="E401" s="6" t="n"/>
       <c r="F401" s="5" t="n"/>
-      <c r="G401" s="6" t="n"/>
+      <c r="G401" s="5" t="n"/>
+      <c r="H401" s="6" t="n"/>
     </row>
     <row r="402" collapsed="1">
       <c r="A402" s="4" t="n">
@@ -5207,12 +5631,13 @@
         </is>
       </c>
       <c r="D402" s="6" t="n"/>
-      <c r="E402" s="5" t="n"/>
-      <c r="F402" s="5">
+      <c r="E402" s="6" t="n"/>
+      <c r="F402" s="5" t="n"/>
+      <c r="G402" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G402" s="6" t="inlineStr">
+      <c r="H402" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(7865, 4, 100)</t>
         </is>
@@ -5225,9 +5650,10 @@
       <c r="B403" s="5" t="n"/>
       <c r="C403" s="6" t="n"/>
       <c r="D403" s="6" t="n"/>
-      <c r="E403" s="5" t="n"/>
+      <c r="E403" s="6" t="n"/>
       <c r="F403" s="5" t="n"/>
-      <c r="G403" s="6" t="n"/>
+      <c r="G403" s="5" t="n"/>
+      <c r="H403" s="6" t="n"/>
     </row>
     <row r="404" hidden="1" outlineLevel="2">
       <c r="A404" s="4" t="n">
@@ -5236,9 +5662,10 @@
       <c r="B404" s="5" t="n"/>
       <c r="C404" s="6" t="n"/>
       <c r="D404" s="6" t="n"/>
-      <c r="E404" s="5" t="n"/>
+      <c r="E404" s="6" t="n"/>
       <c r="F404" s="5" t="n"/>
-      <c r="G404" s="6" t="n"/>
+      <c r="G404" s="5" t="n"/>
+      <c r="H404" s="6" t="n"/>
     </row>
     <row r="405" hidden="1" outlineLevel="2">
       <c r="A405" s="4" t="n">
@@ -5247,9 +5674,10 @@
       <c r="B405" s="5" t="n"/>
       <c r="C405" s="6" t="n"/>
       <c r="D405" s="6" t="n"/>
-      <c r="E405" s="5" t="n"/>
+      <c r="E405" s="6" t="n"/>
       <c r="F405" s="5" t="n"/>
-      <c r="G405" s="6" t="n"/>
+      <c r="G405" s="5" t="n"/>
+      <c r="H405" s="6" t="n"/>
     </row>
     <row r="406" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A406" s="4" t="n">
@@ -5258,9 +5686,10 @@
       <c r="B406" s="5" t="n"/>
       <c r="C406" s="6" t="n"/>
       <c r="D406" s="6" t="n"/>
-      <c r="E406" s="5" t="n"/>
+      <c r="E406" s="6" t="n"/>
       <c r="F406" s="5" t="n"/>
-      <c r="G406" s="6" t="n"/>
+      <c r="G406" s="5" t="n"/>
+      <c r="H406" s="6" t="n"/>
     </row>
     <row r="407" hidden="1" outlineLevel="2">
       <c r="A407" s="4" t="n">
@@ -5269,9 +5698,10 @@
       <c r="B407" s="5" t="n"/>
       <c r="C407" s="6" t="n"/>
       <c r="D407" s="6" t="n"/>
-      <c r="E407" s="5" t="n"/>
+      <c r="E407" s="6" t="n"/>
       <c r="F407" s="5" t="n"/>
-      <c r="G407" s="6" t="n"/>
+      <c r="G407" s="5" t="n"/>
+      <c r="H407" s="6" t="n"/>
     </row>
     <row r="408" hidden="1" outlineLevel="2">
       <c r="A408" s="4" t="n">
@@ -5280,9 +5710,10 @@
       <c r="B408" s="5" t="n"/>
       <c r="C408" s="6" t="n"/>
       <c r="D408" s="6" t="n"/>
-      <c r="E408" s="5" t="n"/>
+      <c r="E408" s="6" t="n"/>
       <c r="F408" s="5" t="n"/>
-      <c r="G408" s="6" t="n"/>
+      <c r="G408" s="5" t="n"/>
+      <c r="H408" s="6" t="n"/>
     </row>
     <row r="409" hidden="1" outlineLevel="2">
       <c r="A409" s="4" t="n">
@@ -5291,9 +5722,10 @@
       <c r="B409" s="5" t="n"/>
       <c r="C409" s="6" t="n"/>
       <c r="D409" s="6" t="n"/>
-      <c r="E409" s="5" t="n"/>
+      <c r="E409" s="6" t="n"/>
       <c r="F409" s="5" t="n"/>
-      <c r="G409" s="6" t="n"/>
+      <c r="G409" s="5" t="n"/>
+      <c r="H409" s="6" t="n"/>
     </row>
     <row r="410" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A410" s="4" t="n">
@@ -5302,9 +5734,10 @@
       <c r="B410" s="5" t="n"/>
       <c r="C410" s="6" t="n"/>
       <c r="D410" s="6" t="n"/>
-      <c r="E410" s="5" t="n"/>
+      <c r="E410" s="6" t="n"/>
       <c r="F410" s="5" t="n"/>
-      <c r="G410" s="6" t="n"/>
+      <c r="G410" s="5" t="n"/>
+      <c r="H410" s="6" t="n"/>
     </row>
     <row r="411" hidden="1" outlineLevel="2">
       <c r="A411" s="4" t="n">
@@ -5313,9 +5746,10 @@
       <c r="B411" s="5" t="n"/>
       <c r="C411" s="6" t="n"/>
       <c r="D411" s="6" t="n"/>
-      <c r="E411" s="5" t="n"/>
+      <c r="E411" s="6" t="n"/>
       <c r="F411" s="5" t="n"/>
-      <c r="G411" s="6" t="n"/>
+      <c r="G411" s="5" t="n"/>
+      <c r="H411" s="6" t="n"/>
     </row>
     <row r="412" hidden="1" outlineLevel="2">
       <c r="A412" s="4" t="n">
@@ -5324,9 +5758,10 @@
       <c r="B412" s="5" t="n"/>
       <c r="C412" s="6" t="n"/>
       <c r="D412" s="6" t="n"/>
-      <c r="E412" s="5" t="n"/>
+      <c r="E412" s="6" t="n"/>
       <c r="F412" s="5" t="n"/>
-      <c r="G412" s="6" t="n"/>
+      <c r="G412" s="5" t="n"/>
+      <c r="H412" s="6" t="n"/>
     </row>
     <row r="413" hidden="1" outlineLevel="2">
       <c r="A413" s="4" t="n">
@@ -5335,9 +5770,10 @@
       <c r="B413" s="5" t="n"/>
       <c r="C413" s="6" t="n"/>
       <c r="D413" s="6" t="n"/>
-      <c r="E413" s="5" t="n"/>
+      <c r="E413" s="6" t="n"/>
       <c r="F413" s="5" t="n"/>
-      <c r="G413" s="6" t="n"/>
+      <c r="G413" s="5" t="n"/>
+      <c r="H413" s="6" t="n"/>
     </row>
     <row r="414" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A414" s="4" t="n">
@@ -5346,9 +5782,10 @@
       <c r="B414" s="5" t="n"/>
       <c r="C414" s="6" t="n"/>
       <c r="D414" s="6" t="n"/>
-      <c r="E414" s="5" t="n"/>
+      <c r="E414" s="6" t="n"/>
       <c r="F414" s="5" t="n"/>
-      <c r="G414" s="6" t="n"/>
+      <c r="G414" s="5" t="n"/>
+      <c r="H414" s="6" t="n"/>
     </row>
     <row r="415" hidden="1" outlineLevel="2">
       <c r="A415" s="4" t="n">
@@ -5357,9 +5794,10 @@
       <c r="B415" s="5" t="n"/>
       <c r="C415" s="6" t="n"/>
       <c r="D415" s="6" t="n"/>
-      <c r="E415" s="5" t="n"/>
+      <c r="E415" s="6" t="n"/>
       <c r="F415" s="5" t="n"/>
-      <c r="G415" s="6" t="n"/>
+      <c r="G415" s="5" t="n"/>
+      <c r="H415" s="6" t="n"/>
     </row>
     <row r="416" hidden="1" outlineLevel="2">
       <c r="A416" s="4" t="n">
@@ -5368,9 +5806,10 @@
       <c r="B416" s="5" t="n"/>
       <c r="C416" s="6" t="n"/>
       <c r="D416" s="6" t="n"/>
-      <c r="E416" s="5" t="n"/>
+      <c r="E416" s="6" t="n"/>
       <c r="F416" s="5" t="n"/>
-      <c r="G416" s="6" t="n"/>
+      <c r="G416" s="5" t="n"/>
+      <c r="H416" s="6" t="n"/>
     </row>
     <row r="417" hidden="1" outlineLevel="2">
       <c r="A417" s="4" t="n">
@@ -5379,9 +5818,10 @@
       <c r="B417" s="5" t="n"/>
       <c r="C417" s="6" t="n"/>
       <c r="D417" s="6" t="n"/>
-      <c r="E417" s="5" t="n"/>
+      <c r="E417" s="6" t="n"/>
       <c r="F417" s="5" t="n"/>
-      <c r="G417" s="6" t="n"/>
+      <c r="G417" s="5" t="n"/>
+      <c r="H417" s="6" t="n"/>
     </row>
     <row r="418" collapsed="1">
       <c r="A418" s="4" t="n">
@@ -5399,12 +5839,13 @@
         </is>
       </c>
       <c r="D418" s="6" t="n"/>
-      <c r="E418" s="5" t="n"/>
-      <c r="F418" s="5">
+      <c r="E418" s="6" t="n"/>
+      <c r="F418" s="5" t="n"/>
+      <c r="G418" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G418" s="6" t="inlineStr">
+      <c r="H418" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(15740, 490, 105, 5, 26, 5, false, 4)</t>
         </is>
@@ -5417,9 +5858,10 @@
       <c r="B419" s="5" t="n"/>
       <c r="C419" s="6" t="n"/>
       <c r="D419" s="6" t="n"/>
-      <c r="E419" s="5" t="n"/>
+      <c r="E419" s="6" t="n"/>
       <c r="F419" s="5" t="n"/>
-      <c r="G419" s="6" t="n"/>
+      <c r="G419" s="5" t="n"/>
+      <c r="H419" s="6" t="n"/>
     </row>
     <row r="420" hidden="1" outlineLevel="2">
       <c r="A420" s="4" t="n">
@@ -5428,9 +5870,10 @@
       <c r="B420" s="5" t="n"/>
       <c r="C420" s="6" t="n"/>
       <c r="D420" s="6" t="n"/>
-      <c r="E420" s="5" t="n"/>
+      <c r="E420" s="6" t="n"/>
       <c r="F420" s="5" t="n"/>
-      <c r="G420" s="6" t="n"/>
+      <c r="G420" s="5" t="n"/>
+      <c r="H420" s="6" t="n"/>
     </row>
     <row r="421" hidden="1" outlineLevel="2">
       <c r="A421" s="4" t="n">
@@ -5439,9 +5882,10 @@
       <c r="B421" s="5" t="n"/>
       <c r="C421" s="6" t="n"/>
       <c r="D421" s="6" t="n"/>
-      <c r="E421" s="5" t="n"/>
+      <c r="E421" s="6" t="n"/>
       <c r="F421" s="5" t="n"/>
-      <c r="G421" s="6" t="n"/>
+      <c r="G421" s="5" t="n"/>
+      <c r="H421" s="6" t="n"/>
     </row>
     <row r="422" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A422" s="4" t="n">
@@ -5450,9 +5894,10 @@
       <c r="B422" s="5" t="n"/>
       <c r="C422" s="6" t="n"/>
       <c r="D422" s="6" t="n"/>
-      <c r="E422" s="5" t="n"/>
+      <c r="E422" s="6" t="n"/>
       <c r="F422" s="5" t="n"/>
-      <c r="G422" s="6" t="n"/>
+      <c r="G422" s="5" t="n"/>
+      <c r="H422" s="6" t="n"/>
     </row>
     <row r="423" hidden="1" outlineLevel="2">
       <c r="A423" s="4" t="n">
@@ -5461,9 +5906,10 @@
       <c r="B423" s="5" t="n"/>
       <c r="C423" s="6" t="n"/>
       <c r="D423" s="6" t="n"/>
-      <c r="E423" s="5" t="n"/>
+      <c r="E423" s="6" t="n"/>
       <c r="F423" s="5" t="n"/>
-      <c r="G423" s="6" t="n"/>
+      <c r="G423" s="5" t="n"/>
+      <c r="H423" s="6" t="n"/>
     </row>
     <row r="424" hidden="1" outlineLevel="2">
       <c r="A424" s="4" t="n">
@@ -5472,9 +5918,10 @@
       <c r="B424" s="5" t="n"/>
       <c r="C424" s="6" t="n"/>
       <c r="D424" s="6" t="n"/>
-      <c r="E424" s="5" t="n"/>
+      <c r="E424" s="6" t="n"/>
       <c r="F424" s="5" t="n"/>
-      <c r="G424" s="6" t="n"/>
+      <c r="G424" s="5" t="n"/>
+      <c r="H424" s="6" t="n"/>
     </row>
     <row r="425" hidden="1" outlineLevel="2">
       <c r="A425" s="4" t="n">
@@ -5483,9 +5930,10 @@
       <c r="B425" s="5" t="n"/>
       <c r="C425" s="6" t="n"/>
       <c r="D425" s="6" t="n"/>
-      <c r="E425" s="5" t="n"/>
+      <c r="E425" s="6" t="n"/>
       <c r="F425" s="5" t="n"/>
-      <c r="G425" s="6" t="n"/>
+      <c r="G425" s="5" t="n"/>
+      <c r="H425" s="6" t="n"/>
     </row>
     <row r="426" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A426" s="4" t="n">
@@ -5494,9 +5942,10 @@
       <c r="B426" s="5" t="n"/>
       <c r="C426" s="6" t="n"/>
       <c r="D426" s="6" t="n"/>
-      <c r="E426" s="5" t="n"/>
+      <c r="E426" s="6" t="n"/>
       <c r="F426" s="5" t="n"/>
-      <c r="G426" s="6" t="n"/>
+      <c r="G426" s="5" t="n"/>
+      <c r="H426" s="6" t="n"/>
     </row>
     <row r="427" hidden="1" outlineLevel="2">
       <c r="A427" s="4" t="n">
@@ -5505,9 +5954,10 @@
       <c r="B427" s="5" t="n"/>
       <c r="C427" s="6" t="n"/>
       <c r="D427" s="6" t="n"/>
-      <c r="E427" s="5" t="n"/>
+      <c r="E427" s="6" t="n"/>
       <c r="F427" s="5" t="n"/>
-      <c r="G427" s="6" t="n"/>
+      <c r="G427" s="5" t="n"/>
+      <c r="H427" s="6" t="n"/>
     </row>
     <row r="428" hidden="1" outlineLevel="2">
       <c r="A428" s="4" t="n">
@@ -5516,9 +5966,10 @@
       <c r="B428" s="5" t="n"/>
       <c r="C428" s="6" t="n"/>
       <c r="D428" s="6" t="n"/>
-      <c r="E428" s="5" t="n"/>
+      <c r="E428" s="6" t="n"/>
       <c r="F428" s="5" t="n"/>
-      <c r="G428" s="6" t="n"/>
+      <c r="G428" s="5" t="n"/>
+      <c r="H428" s="6" t="n"/>
     </row>
     <row r="429" hidden="1" outlineLevel="2">
       <c r="A429" s="4" t="n">
@@ -5527,9 +5978,10 @@
       <c r="B429" s="5" t="n"/>
       <c r="C429" s="6" t="n"/>
       <c r="D429" s="6" t="n"/>
-      <c r="E429" s="5" t="n"/>
+      <c r="E429" s="6" t="n"/>
       <c r="F429" s="5" t="n"/>
-      <c r="G429" s="6" t="n"/>
+      <c r="G429" s="5" t="n"/>
+      <c r="H429" s="6" t="n"/>
     </row>
     <row r="430" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A430" s="4" t="n">
@@ -5538,9 +5990,10 @@
       <c r="B430" s="5" t="n"/>
       <c r="C430" s="6" t="n"/>
       <c r="D430" s="6" t="n"/>
-      <c r="E430" s="5" t="n"/>
+      <c r="E430" s="6" t="n"/>
       <c r="F430" s="5" t="n"/>
-      <c r="G430" s="6" t="n"/>
+      <c r="G430" s="5" t="n"/>
+      <c r="H430" s="6" t="n"/>
     </row>
     <row r="431" hidden="1" outlineLevel="2">
       <c r="A431" s="4" t="n">
@@ -5549,9 +6002,10 @@
       <c r="B431" s="5" t="n"/>
       <c r="C431" s="6" t="n"/>
       <c r="D431" s="6" t="n"/>
-      <c r="E431" s="5" t="n"/>
+      <c r="E431" s="6" t="n"/>
       <c r="F431" s="5" t="n"/>
-      <c r="G431" s="6" t="n"/>
+      <c r="G431" s="5" t="n"/>
+      <c r="H431" s="6" t="n"/>
     </row>
     <row r="432" hidden="1" outlineLevel="2">
       <c r="A432" s="4" t="n">
@@ -5560,9 +6014,10 @@
       <c r="B432" s="5" t="n"/>
       <c r="C432" s="6" t="n"/>
       <c r="D432" s="6" t="n"/>
-      <c r="E432" s="5" t="n"/>
+      <c r="E432" s="6" t="n"/>
       <c r="F432" s="5" t="n"/>
-      <c r="G432" s="6" t="n"/>
+      <c r="G432" s="5" t="n"/>
+      <c r="H432" s="6" t="n"/>
     </row>
     <row r="433" hidden="1" outlineLevel="2">
       <c r="A433" s="4" t="n">
@@ -5571,9 +6026,10 @@
       <c r="B433" s="5" t="n"/>
       <c r="C433" s="6" t="n"/>
       <c r="D433" s="6" t="n"/>
-      <c r="E433" s="5" t="n"/>
+      <c r="E433" s="6" t="n"/>
       <c r="F433" s="5" t="n"/>
-      <c r="G433" s="6" t="n"/>
+      <c r="G433" s="5" t="n"/>
+      <c r="H433" s="6" t="n"/>
     </row>
     <row r="434" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A434" s="4" t="n">
@@ -5582,9 +6038,10 @@
       <c r="B434" s="5" t="n"/>
       <c r="C434" s="6" t="n"/>
       <c r="D434" s="6" t="n"/>
-      <c r="E434" s="5" t="n"/>
+      <c r="E434" s="6" t="n"/>
       <c r="F434" s="5" t="n"/>
-      <c r="G434" s="6" t="n"/>
+      <c r="G434" s="5" t="n"/>
+      <c r="H434" s="6" t="n"/>
     </row>
     <row r="435" hidden="1" outlineLevel="2">
       <c r="A435" s="4" t="n">
@@ -5593,9 +6050,10 @@
       <c r="B435" s="5" t="n"/>
       <c r="C435" s="6" t="n"/>
       <c r="D435" s="6" t="n"/>
-      <c r="E435" s="5" t="n"/>
+      <c r="E435" s="6" t="n"/>
       <c r="F435" s="5" t="n"/>
-      <c r="G435" s="6" t="n"/>
+      <c r="G435" s="5" t="n"/>
+      <c r="H435" s="6" t="n"/>
     </row>
     <row r="436" hidden="1" outlineLevel="2">
       <c r="A436" s="4" t="n">
@@ -5604,9 +6062,10 @@
       <c r="B436" s="5" t="n"/>
       <c r="C436" s="6" t="n"/>
       <c r="D436" s="6" t="n"/>
-      <c r="E436" s="5" t="n"/>
+      <c r="E436" s="6" t="n"/>
       <c r="F436" s="5" t="n"/>
-      <c r="G436" s="6" t="n"/>
+      <c r="G436" s="5" t="n"/>
+      <c r="H436" s="6" t="n"/>
     </row>
     <row r="437" hidden="1" outlineLevel="2">
       <c r="A437" s="4" t="n">
@@ -5615,9 +6074,10 @@
       <c r="B437" s="5" t="n"/>
       <c r="C437" s="6" t="n"/>
       <c r="D437" s="6" t="n"/>
-      <c r="E437" s="5" t="n"/>
+      <c r="E437" s="6" t="n"/>
       <c r="F437" s="5" t="n"/>
-      <c r="G437" s="6" t="n"/>
+      <c r="G437" s="5" t="n"/>
+      <c r="H437" s="6" t="n"/>
     </row>
     <row r="438" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A438" s="4" t="n">
@@ -5626,9 +6086,10 @@
       <c r="B438" s="5" t="n"/>
       <c r="C438" s="6" t="n"/>
       <c r="D438" s="6" t="n"/>
-      <c r="E438" s="5" t="n"/>
+      <c r="E438" s="6" t="n"/>
       <c r="F438" s="5" t="n"/>
-      <c r="G438" s="6" t="n"/>
+      <c r="G438" s="5" t="n"/>
+      <c r="H438" s="6" t="n"/>
     </row>
     <row r="439" hidden="1" outlineLevel="2">
       <c r="A439" s="4" t="n">
@@ -5637,9 +6098,10 @@
       <c r="B439" s="5" t="n"/>
       <c r="C439" s="6" t="n"/>
       <c r="D439" s="6" t="n"/>
-      <c r="E439" s="5" t="n"/>
+      <c r="E439" s="6" t="n"/>
       <c r="F439" s="5" t="n"/>
-      <c r="G439" s="6" t="n"/>
+      <c r="G439" s="5" t="n"/>
+      <c r="H439" s="6" t="n"/>
     </row>
     <row r="440" hidden="1" outlineLevel="2">
       <c r="A440" s="4" t="n">
@@ -5648,9 +6110,10 @@
       <c r="B440" s="5" t="n"/>
       <c r="C440" s="6" t="n"/>
       <c r="D440" s="6" t="n"/>
-      <c r="E440" s="5" t="n"/>
+      <c r="E440" s="6" t="n"/>
       <c r="F440" s="5" t="n"/>
-      <c r="G440" s="6" t="n"/>
+      <c r="G440" s="5" t="n"/>
+      <c r="H440" s="6" t="n"/>
     </row>
     <row r="441" hidden="1" outlineLevel="2">
       <c r="A441" s="4" t="n">
@@ -5659,9 +6122,10 @@
       <c r="B441" s="5" t="n"/>
       <c r="C441" s="6" t="n"/>
       <c r="D441" s="6" t="n"/>
-      <c r="E441" s="5" t="n"/>
+      <c r="E441" s="6" t="n"/>
       <c r="F441" s="5" t="n"/>
-      <c r="G441" s="6" t="n"/>
+      <c r="G441" s="5" t="n"/>
+      <c r="H441" s="6" t="n"/>
     </row>
     <row r="442" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A442" s="4" t="n">
@@ -5670,9 +6134,10 @@
       <c r="B442" s="5" t="n"/>
       <c r="C442" s="6" t="n"/>
       <c r="D442" s="6" t="n"/>
-      <c r="E442" s="5" t="n"/>
+      <c r="E442" s="6" t="n"/>
       <c r="F442" s="5" t="n"/>
-      <c r="G442" s="6" t="n"/>
+      <c r="G442" s="5" t="n"/>
+      <c r="H442" s="6" t="n"/>
     </row>
     <row r="443" hidden="1" outlineLevel="2">
       <c r="A443" s="4" t="n">
@@ -5681,9 +6146,10 @@
       <c r="B443" s="5" t="n"/>
       <c r="C443" s="6" t="n"/>
       <c r="D443" s="6" t="n"/>
-      <c r="E443" s="5" t="n"/>
+      <c r="E443" s="6" t="n"/>
       <c r="F443" s="5" t="n"/>
-      <c r="G443" s="6" t="n"/>
+      <c r="G443" s="5" t="n"/>
+      <c r="H443" s="6" t="n"/>
     </row>
     <row r="444" hidden="1" outlineLevel="2">
       <c r="A444" s="4" t="n">
@@ -5692,9 +6158,10 @@
       <c r="B444" s="5" t="n"/>
       <c r="C444" s="6" t="n"/>
       <c r="D444" s="6" t="n"/>
-      <c r="E444" s="5" t="n"/>
+      <c r="E444" s="6" t="n"/>
       <c r="F444" s="5" t="n"/>
-      <c r="G444" s="6" t="n"/>
+      <c r="G444" s="5" t="n"/>
+      <c r="H444" s="6" t="n"/>
     </row>
     <row r="445" hidden="1" outlineLevel="2">
       <c r="A445" s="4" t="n">
@@ -5703,9 +6170,10 @@
       <c r="B445" s="5" t="n"/>
       <c r="C445" s="6" t="n"/>
       <c r="D445" s="6" t="n"/>
-      <c r="E445" s="5" t="n"/>
+      <c r="E445" s="6" t="n"/>
       <c r="F445" s="5" t="n"/>
-      <c r="G445" s="6" t="n"/>
+      <c r="G445" s="5" t="n"/>
+      <c r="H445" s="6" t="n"/>
     </row>
     <row r="446" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A446" s="4" t="n">
@@ -5714,9 +6182,10 @@
       <c r="B446" s="5" t="n"/>
       <c r="C446" s="6" t="n"/>
       <c r="D446" s="6" t="n"/>
-      <c r="E446" s="5" t="n"/>
+      <c r="E446" s="6" t="n"/>
       <c r="F446" s="5" t="n"/>
-      <c r="G446" s="6" t="n"/>
+      <c r="G446" s="5" t="n"/>
+      <c r="H446" s="6" t="n"/>
     </row>
     <row r="447" hidden="1" outlineLevel="2">
       <c r="A447" s="4" t="n">
@@ -5725,9 +6194,10 @@
       <c r="B447" s="5" t="n"/>
       <c r="C447" s="6" t="n"/>
       <c r="D447" s="6" t="n"/>
-      <c r="E447" s="5" t="n"/>
+      <c r="E447" s="6" t="n"/>
       <c r="F447" s="5" t="n"/>
-      <c r="G447" s="6" t="n"/>
+      <c r="G447" s="5" t="n"/>
+      <c r="H447" s="6" t="n"/>
     </row>
     <row r="448" hidden="1" outlineLevel="2">
       <c r="A448" s="4" t="n">
@@ -5736,9 +6206,10 @@
       <c r="B448" s="5" t="n"/>
       <c r="C448" s="6" t="n"/>
       <c r="D448" s="6" t="n"/>
-      <c r="E448" s="5" t="n"/>
+      <c r="E448" s="6" t="n"/>
       <c r="F448" s="5" t="n"/>
-      <c r="G448" s="6" t="n"/>
+      <c r="G448" s="5" t="n"/>
+      <c r="H448" s="6" t="n"/>
     </row>
     <row r="449" hidden="1" outlineLevel="2">
       <c r="A449" s="4" t="n">
@@ -5747,9 +6218,10 @@
       <c r="B449" s="5" t="n"/>
       <c r="C449" s="6" t="n"/>
       <c r="D449" s="6" t="n"/>
-      <c r="E449" s="5" t="n"/>
+      <c r="E449" s="6" t="n"/>
       <c r="F449" s="5" t="n"/>
-      <c r="G449" s="6" t="n"/>
+      <c r="G449" s="5" t="n"/>
+      <c r="H449" s="6" t="n"/>
     </row>
     <row r="450" collapsed="1">
       <c r="A450" s="4" t="n">
@@ -5767,12 +6239,13 @@
         </is>
       </c>
       <c r="D450" s="6" t="n"/>
-      <c r="E450" s="5" t="n"/>
-      <c r="F450" s="5">
+      <c r="E450" s="6" t="n"/>
+      <c r="F450" s="5" t="n"/>
+      <c r="G450" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G450" s="6" t="inlineStr">
+      <c r="H450" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(7870, 4, 110)</t>
         </is>
@@ -5785,9 +6258,10 @@
       <c r="B451" s="5" t="n"/>
       <c r="C451" s="6" t="n"/>
       <c r="D451" s="6" t="n"/>
-      <c r="E451" s="5" t="n"/>
+      <c r="E451" s="6" t="n"/>
       <c r="F451" s="5" t="n"/>
-      <c r="G451" s="6" t="n"/>
+      <c r="G451" s="5" t="n"/>
+      <c r="H451" s="6" t="n"/>
     </row>
     <row r="452" hidden="1" outlineLevel="2">
       <c r="A452" s="4" t="n">
@@ -5796,9 +6270,10 @@
       <c r="B452" s="5" t="n"/>
       <c r="C452" s="6" t="n"/>
       <c r="D452" s="6" t="n"/>
-      <c r="E452" s="5" t="n"/>
+      <c r="E452" s="6" t="n"/>
       <c r="F452" s="5" t="n"/>
-      <c r="G452" s="6" t="n"/>
+      <c r="G452" s="5" t="n"/>
+      <c r="H452" s="6" t="n"/>
     </row>
     <row r="453" hidden="1" outlineLevel="2">
       <c r="A453" s="4" t="n">
@@ -5807,9 +6282,10 @@
       <c r="B453" s="5" t="n"/>
       <c r="C453" s="6" t="n"/>
       <c r="D453" s="6" t="n"/>
-      <c r="E453" s="5" t="n"/>
+      <c r="E453" s="6" t="n"/>
       <c r="F453" s="5" t="n"/>
-      <c r="G453" s="6" t="n"/>
+      <c r="G453" s="5" t="n"/>
+      <c r="H453" s="6" t="n"/>
     </row>
     <row r="454" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A454" s="4" t="n">
@@ -5818,9 +6294,10 @@
       <c r="B454" s="5" t="n"/>
       <c r="C454" s="6" t="n"/>
       <c r="D454" s="6" t="n"/>
-      <c r="E454" s="5" t="n"/>
+      <c r="E454" s="6" t="n"/>
       <c r="F454" s="5" t="n"/>
-      <c r="G454" s="6" t="n"/>
+      <c r="G454" s="5" t="n"/>
+      <c r="H454" s="6" t="n"/>
     </row>
     <row r="455" hidden="1" outlineLevel="2">
       <c r="A455" s="4" t="n">
@@ -5829,9 +6306,10 @@
       <c r="B455" s="5" t="n"/>
       <c r="C455" s="6" t="n"/>
       <c r="D455" s="6" t="n"/>
-      <c r="E455" s="5" t="n"/>
+      <c r="E455" s="6" t="n"/>
       <c r="F455" s="5" t="n"/>
-      <c r="G455" s="6" t="n"/>
+      <c r="G455" s="5" t="n"/>
+      <c r="H455" s="6" t="n"/>
     </row>
     <row r="456" hidden="1" outlineLevel="2">
       <c r="A456" s="4" t="n">
@@ -5840,9 +6318,10 @@
       <c r="B456" s="5" t="n"/>
       <c r="C456" s="6" t="n"/>
       <c r="D456" s="6" t="n"/>
-      <c r="E456" s="5" t="n"/>
+      <c r="E456" s="6" t="n"/>
       <c r="F456" s="5" t="n"/>
-      <c r="G456" s="6" t="n"/>
+      <c r="G456" s="5" t="n"/>
+      <c r="H456" s="6" t="n"/>
     </row>
     <row r="457" hidden="1" outlineLevel="2">
       <c r="A457" s="4" t="n">
@@ -5851,9 +6330,10 @@
       <c r="B457" s="5" t="n"/>
       <c r="C457" s="6" t="n"/>
       <c r="D457" s="6" t="n"/>
-      <c r="E457" s="5" t="n"/>
+      <c r="E457" s="6" t="n"/>
       <c r="F457" s="5" t="n"/>
-      <c r="G457" s="6" t="n"/>
+      <c r="G457" s="5" t="n"/>
+      <c r="H457" s="6" t="n"/>
     </row>
     <row r="458" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A458" s="4" t="n">
@@ -5862,9 +6342,10 @@
       <c r="B458" s="5" t="n"/>
       <c r="C458" s="6" t="n"/>
       <c r="D458" s="6" t="n"/>
-      <c r="E458" s="5" t="n"/>
+      <c r="E458" s="6" t="n"/>
       <c r="F458" s="5" t="n"/>
-      <c r="G458" s="6" t="n"/>
+      <c r="G458" s="5" t="n"/>
+      <c r="H458" s="6" t="n"/>
     </row>
     <row r="459" hidden="1" outlineLevel="2">
       <c r="A459" s="4" t="n">
@@ -5873,9 +6354,10 @@
       <c r="B459" s="5" t="n"/>
       <c r="C459" s="6" t="n"/>
       <c r="D459" s="6" t="n"/>
-      <c r="E459" s="5" t="n"/>
+      <c r="E459" s="6" t="n"/>
       <c r="F459" s="5" t="n"/>
-      <c r="G459" s="6" t="n"/>
+      <c r="G459" s="5" t="n"/>
+      <c r="H459" s="6" t="n"/>
     </row>
     <row r="460" hidden="1" outlineLevel="2">
       <c r="A460" s="4" t="n">
@@ -5884,9 +6366,10 @@
       <c r="B460" s="5" t="n"/>
       <c r="C460" s="6" t="n"/>
       <c r="D460" s="6" t="n"/>
-      <c r="E460" s="5" t="n"/>
+      <c r="E460" s="6" t="n"/>
       <c r="F460" s="5" t="n"/>
-      <c r="G460" s="6" t="n"/>
+      <c r="G460" s="5" t="n"/>
+      <c r="H460" s="6" t="n"/>
     </row>
     <row r="461" hidden="1" outlineLevel="2">
       <c r="A461" s="4" t="n">
@@ -5895,9 +6378,10 @@
       <c r="B461" s="5" t="n"/>
       <c r="C461" s="6" t="n"/>
       <c r="D461" s="6" t="n"/>
-      <c r="E461" s="5" t="n"/>
+      <c r="E461" s="6" t="n"/>
       <c r="F461" s="5" t="n"/>
-      <c r="G461" s="6" t="n"/>
+      <c r="G461" s="5" t="n"/>
+      <c r="H461" s="6" t="n"/>
     </row>
     <row r="462" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A462" s="4" t="n">
@@ -5906,9 +6390,10 @@
       <c r="B462" s="5" t="n"/>
       <c r="C462" s="6" t="n"/>
       <c r="D462" s="6" t="n"/>
-      <c r="E462" s="5" t="n"/>
+      <c r="E462" s="6" t="n"/>
       <c r="F462" s="5" t="n"/>
-      <c r="G462" s="6" t="n"/>
+      <c r="G462" s="5" t="n"/>
+      <c r="H462" s="6" t="n"/>
     </row>
     <row r="463" hidden="1" outlineLevel="2">
       <c r="A463" s="4" t="n">
@@ -5917,9 +6402,10 @@
       <c r="B463" s="5" t="n"/>
       <c r="C463" s="6" t="n"/>
       <c r="D463" s="6" t="n"/>
-      <c r="E463" s="5" t="n"/>
+      <c r="E463" s="6" t="n"/>
       <c r="F463" s="5" t="n"/>
-      <c r="G463" s="6" t="n"/>
+      <c r="G463" s="5" t="n"/>
+      <c r="H463" s="6" t="n"/>
     </row>
     <row r="464" hidden="1" outlineLevel="2">
       <c r="A464" s="4" t="n">
@@ -5928,9 +6414,10 @@
       <c r="B464" s="5" t="n"/>
       <c r="C464" s="6" t="n"/>
       <c r="D464" s="6" t="n"/>
-      <c r="E464" s="5" t="n"/>
+      <c r="E464" s="6" t="n"/>
       <c r="F464" s="5" t="n"/>
-      <c r="G464" s="6" t="n"/>
+      <c r="G464" s="5" t="n"/>
+      <c r="H464" s="6" t="n"/>
     </row>
     <row r="465" hidden="1" outlineLevel="2">
       <c r="A465" s="4" t="n">
@@ -5939,9 +6426,10 @@
       <c r="B465" s="5" t="n"/>
       <c r="C465" s="6" t="n"/>
       <c r="D465" s="6" t="n"/>
-      <c r="E465" s="5" t="n"/>
+      <c r="E465" s="6" t="n"/>
       <c r="F465" s="5" t="n"/>
-      <c r="G465" s="6" t="n"/>
+      <c r="G465" s="5" t="n"/>
+      <c r="H465" s="6" t="n"/>
     </row>
     <row r="466" collapsed="1">
       <c r="A466" s="4" t="n">
@@ -5959,12 +6447,13 @@
         </is>
       </c>
       <c r="D466" s="6" t="n"/>
-      <c r="E466" s="5" t="n"/>
-      <c r="F466" s="5">
+      <c r="E466" s="6" t="n"/>
+      <c r="F466" s="5" t="n"/>
+      <c r="G466" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G466" s="6" t="inlineStr">
+      <c r="H466" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(7865, 490, 115, 5, 26, 5, true, 3)</t>
         </is>
@@ -5977,9 +6466,10 @@
       <c r="B467" s="5" t="n"/>
       <c r="C467" s="6" t="n"/>
       <c r="D467" s="6" t="n"/>
-      <c r="E467" s="5" t="n"/>
+      <c r="E467" s="6" t="n"/>
       <c r="F467" s="5" t="n"/>
-      <c r="G467" s="6" t="n"/>
+      <c r="G467" s="5" t="n"/>
+      <c r="H467" s="6" t="n"/>
     </row>
     <row r="468" hidden="1" outlineLevel="2">
       <c r="A468" s="4" t="n">
@@ -5988,9 +6478,10 @@
       <c r="B468" s="5" t="n"/>
       <c r="C468" s="6" t="n"/>
       <c r="D468" s="6" t="n"/>
-      <c r="E468" s="5" t="n"/>
+      <c r="E468" s="6" t="n"/>
       <c r="F468" s="5" t="n"/>
-      <c r="G468" s="6" t="n"/>
+      <c r="G468" s="5" t="n"/>
+      <c r="H468" s="6" t="n"/>
     </row>
     <row r="469" hidden="1" outlineLevel="2">
       <c r="A469" s="4" t="n">
@@ -5999,9 +6490,10 @@
       <c r="B469" s="5" t="n"/>
       <c r="C469" s="6" t="n"/>
       <c r="D469" s="6" t="n"/>
-      <c r="E469" s="5" t="n"/>
+      <c r="E469" s="6" t="n"/>
       <c r="F469" s="5" t="n"/>
-      <c r="G469" s="6" t="n"/>
+      <c r="G469" s="5" t="n"/>
+      <c r="H469" s="6" t="n"/>
     </row>
     <row r="470" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A470" s="4" t="n">
@@ -6010,9 +6502,10 @@
       <c r="B470" s="5" t="n"/>
       <c r="C470" s="6" t="n"/>
       <c r="D470" s="6" t="n"/>
-      <c r="E470" s="5" t="n"/>
+      <c r="E470" s="6" t="n"/>
       <c r="F470" s="5" t="n"/>
-      <c r="G470" s="6" t="n"/>
+      <c r="G470" s="5" t="n"/>
+      <c r="H470" s="6" t="n"/>
     </row>
     <row r="471" hidden="1" outlineLevel="2">
       <c r="A471" s="4" t="n">
@@ -6021,9 +6514,10 @@
       <c r="B471" s="5" t="n"/>
       <c r="C471" s="6" t="n"/>
       <c r="D471" s="6" t="n"/>
-      <c r="E471" s="5" t="n"/>
+      <c r="E471" s="6" t="n"/>
       <c r="F471" s="5" t="n"/>
-      <c r="G471" s="6" t="n"/>
+      <c r="G471" s="5" t="n"/>
+      <c r="H471" s="6" t="n"/>
     </row>
     <row r="472" hidden="1" outlineLevel="2">
       <c r="A472" s="4" t="n">
@@ -6032,9 +6526,10 @@
       <c r="B472" s="5" t="n"/>
       <c r="C472" s="6" t="n"/>
       <c r="D472" s="6" t="n"/>
-      <c r="E472" s="5" t="n"/>
+      <c r="E472" s="6" t="n"/>
       <c r="F472" s="5" t="n"/>
-      <c r="G472" s="6" t="n"/>
+      <c r="G472" s="5" t="n"/>
+      <c r="H472" s="6" t="n"/>
     </row>
     <row r="473" hidden="1" outlineLevel="2">
       <c r="A473" s="4" t="n">
@@ -6043,9 +6538,10 @@
       <c r="B473" s="5" t="n"/>
       <c r="C473" s="6" t="n"/>
       <c r="D473" s="6" t="n"/>
-      <c r="E473" s="5" t="n"/>
+      <c r="E473" s="6" t="n"/>
       <c r="F473" s="5" t="n"/>
-      <c r="G473" s="6" t="n"/>
+      <c r="G473" s="5" t="n"/>
+      <c r="H473" s="6" t="n"/>
     </row>
     <row r="474" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A474" s="4" t="n">
@@ -6054,9 +6550,10 @@
       <c r="B474" s="5" t="n"/>
       <c r="C474" s="6" t="n"/>
       <c r="D474" s="6" t="n"/>
-      <c r="E474" s="5" t="n"/>
+      <c r="E474" s="6" t="n"/>
       <c r="F474" s="5" t="n"/>
-      <c r="G474" s="6" t="n"/>
+      <c r="G474" s="5" t="n"/>
+      <c r="H474" s="6" t="n"/>
     </row>
     <row r="475" hidden="1" outlineLevel="2">
       <c r="A475" s="4" t="n">
@@ -6065,9 +6562,10 @@
       <c r="B475" s="5" t="n"/>
       <c r="C475" s="6" t="n"/>
       <c r="D475" s="6" t="n"/>
-      <c r="E475" s="5" t="n"/>
+      <c r="E475" s="6" t="n"/>
       <c r="F475" s="5" t="n"/>
-      <c r="G475" s="6" t="n"/>
+      <c r="G475" s="5" t="n"/>
+      <c r="H475" s="6" t="n"/>
     </row>
     <row r="476" hidden="1" outlineLevel="2">
       <c r="A476" s="4" t="n">
@@ -6076,9 +6574,10 @@
       <c r="B476" s="5" t="n"/>
       <c r="C476" s="6" t="n"/>
       <c r="D476" s="6" t="n"/>
-      <c r="E476" s="5" t="n"/>
+      <c r="E476" s="6" t="n"/>
       <c r="F476" s="5" t="n"/>
-      <c r="G476" s="6" t="n"/>
+      <c r="G476" s="5" t="n"/>
+      <c r="H476" s="6" t="n"/>
     </row>
     <row r="477" hidden="1" outlineLevel="2">
       <c r="A477" s="4" t="n">
@@ -6087,9 +6586,10 @@
       <c r="B477" s="5" t="n"/>
       <c r="C477" s="6" t="n"/>
       <c r="D477" s="6" t="n"/>
-      <c r="E477" s="5" t="n"/>
+      <c r="E477" s="6" t="n"/>
       <c r="F477" s="5" t="n"/>
-      <c r="G477" s="6" t="n"/>
+      <c r="G477" s="5" t="n"/>
+      <c r="H477" s="6" t="n"/>
     </row>
     <row r="478" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A478" s="4" t="n">
@@ -6098,9 +6598,10 @@
       <c r="B478" s="5" t="n"/>
       <c r="C478" s="6" t="n"/>
       <c r="D478" s="6" t="n"/>
-      <c r="E478" s="5" t="n"/>
+      <c r="E478" s="6" t="n"/>
       <c r="F478" s="5" t="n"/>
-      <c r="G478" s="6" t="n"/>
+      <c r="G478" s="5" t="n"/>
+      <c r="H478" s="6" t="n"/>
     </row>
     <row r="479" hidden="1" outlineLevel="2">
       <c r="A479" s="4" t="n">
@@ -6109,9 +6610,10 @@
       <c r="B479" s="5" t="n"/>
       <c r="C479" s="6" t="n"/>
       <c r="D479" s="6" t="n"/>
-      <c r="E479" s="5" t="n"/>
+      <c r="E479" s="6" t="n"/>
       <c r="F479" s="5" t="n"/>
-      <c r="G479" s="6" t="n"/>
+      <c r="G479" s="5" t="n"/>
+      <c r="H479" s="6" t="n"/>
     </row>
     <row r="480" hidden="1" outlineLevel="2">
       <c r="A480" s="4" t="n">
@@ -6120,9 +6622,10 @@
       <c r="B480" s="5" t="n"/>
       <c r="C480" s="6" t="n"/>
       <c r="D480" s="6" t="n"/>
-      <c r="E480" s="5" t="n"/>
+      <c r="E480" s="6" t="n"/>
       <c r="F480" s="5" t="n"/>
-      <c r="G480" s="6" t="n"/>
+      <c r="G480" s="5" t="n"/>
+      <c r="H480" s="6" t="n"/>
     </row>
     <row r="481" hidden="1" outlineLevel="2">
       <c r="A481" s="4" t="n">
@@ -6131,9 +6634,10 @@
       <c r="B481" s="5" t="n"/>
       <c r="C481" s="6" t="n"/>
       <c r="D481" s="6" t="n"/>
-      <c r="E481" s="5" t="n"/>
+      <c r="E481" s="6" t="n"/>
       <c r="F481" s="5" t="n"/>
-      <c r="G481" s="6" t="n"/>
+      <c r="G481" s="5" t="n"/>
+      <c r="H481" s="6" t="n"/>
     </row>
     <row r="482" collapsed="1">
       <c r="A482" s="4" t="n">
@@ -6153,12 +6657,13 @@
         </is>
       </c>
       <c r="D482" s="6" t="n"/>
-      <c r="E482" s="5" t="n"/>
-      <c r="F482" s="5">
+      <c r="E482" s="6" t="n"/>
+      <c r="F482" s="5" t="n"/>
+      <c r="G482" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G482" s="6" t="inlineStr">
+      <c r="H482" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(15740, 8, 120)</t>
         </is>
@@ -6171,9 +6676,10 @@
       <c r="B483" s="5" t="n"/>
       <c r="C483" s="6" t="n"/>
       <c r="D483" s="6" t="n"/>
-      <c r="E483" s="5" t="n"/>
+      <c r="E483" s="6" t="n"/>
       <c r="F483" s="5" t="n"/>
-      <c r="G483" s="6" t="n"/>
+      <c r="G483" s="5" t="n"/>
+      <c r="H483" s="6" t="n"/>
     </row>
     <row r="484" hidden="1" outlineLevel="2">
       <c r="A484" s="4" t="n">
@@ -6182,9 +6688,10 @@
       <c r="B484" s="5" t="n"/>
       <c r="C484" s="6" t="n"/>
       <c r="D484" s="6" t="n"/>
-      <c r="E484" s="5" t="n"/>
+      <c r="E484" s="6" t="n"/>
       <c r="F484" s="5" t="n"/>
-      <c r="G484" s="6" t="n"/>
+      <c r="G484" s="5" t="n"/>
+      <c r="H484" s="6" t="n"/>
     </row>
     <row r="485" hidden="1" outlineLevel="2">
       <c r="A485" s="4" t="n">
@@ -6193,9 +6700,10 @@
       <c r="B485" s="5" t="n"/>
       <c r="C485" s="6" t="n"/>
       <c r="D485" s="6" t="n"/>
-      <c r="E485" s="5" t="n"/>
+      <c r="E485" s="6" t="n"/>
       <c r="F485" s="5" t="n"/>
-      <c r="G485" s="6" t="n"/>
+      <c r="G485" s="5" t="n"/>
+      <c r="H485" s="6" t="n"/>
     </row>
     <row r="486" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A486" s="4" t="n">
@@ -6204,9 +6712,10 @@
       <c r="B486" s="5" t="n"/>
       <c r="C486" s="6" t="n"/>
       <c r="D486" s="6" t="n"/>
-      <c r="E486" s="5" t="n"/>
+      <c r="E486" s="6" t="n"/>
       <c r="F486" s="5" t="n"/>
-      <c r="G486" s="6" t="n"/>
+      <c r="G486" s="5" t="n"/>
+      <c r="H486" s="6" t="n"/>
     </row>
     <row r="487" hidden="1" outlineLevel="2">
       <c r="A487" s="4" t="n">
@@ -6215,9 +6724,10 @@
       <c r="B487" s="5" t="n"/>
       <c r="C487" s="6" t="n"/>
       <c r="D487" s="6" t="n"/>
-      <c r="E487" s="5" t="n"/>
+      <c r="E487" s="6" t="n"/>
       <c r="F487" s="5" t="n"/>
-      <c r="G487" s="6" t="n"/>
+      <c r="G487" s="5" t="n"/>
+      <c r="H487" s="6" t="n"/>
     </row>
     <row r="488" hidden="1" outlineLevel="2">
       <c r="A488" s="4" t="n">
@@ -6226,9 +6736,10 @@
       <c r="B488" s="5" t="n"/>
       <c r="C488" s="6" t="n"/>
       <c r="D488" s="6" t="n"/>
-      <c r="E488" s="5" t="n"/>
+      <c r="E488" s="6" t="n"/>
       <c r="F488" s="5" t="n"/>
-      <c r="G488" s="6" t="n"/>
+      <c r="G488" s="5" t="n"/>
+      <c r="H488" s="6" t="n"/>
     </row>
     <row r="489" hidden="1" outlineLevel="2">
       <c r="A489" s="4" t="n">
@@ -6237,9 +6748,10 @@
       <c r="B489" s="5" t="n"/>
       <c r="C489" s="6" t="n"/>
       <c r="D489" s="6" t="n"/>
-      <c r="E489" s="5" t="n"/>
+      <c r="E489" s="6" t="n"/>
       <c r="F489" s="5" t="n"/>
-      <c r="G489" s="6" t="n"/>
+      <c r="G489" s="5" t="n"/>
+      <c r="H489" s="6" t="n"/>
     </row>
     <row r="490" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A490" s="4" t="n">
@@ -6248,9 +6760,10 @@
       <c r="B490" s="5" t="n"/>
       <c r="C490" s="6" t="n"/>
       <c r="D490" s="6" t="n"/>
-      <c r="E490" s="5" t="n"/>
+      <c r="E490" s="6" t="n"/>
       <c r="F490" s="5" t="n"/>
-      <c r="G490" s="6" t="n"/>
+      <c r="G490" s="5" t="n"/>
+      <c r="H490" s="6" t="n"/>
     </row>
     <row r="491" hidden="1" outlineLevel="2">
       <c r="A491" s="4" t="n">
@@ -6259,9 +6772,10 @@
       <c r="B491" s="5" t="n"/>
       <c r="C491" s="6" t="n"/>
       <c r="D491" s="6" t="n"/>
-      <c r="E491" s="5" t="n"/>
+      <c r="E491" s="6" t="n"/>
       <c r="F491" s="5" t="n"/>
-      <c r="G491" s="6" t="n"/>
+      <c r="G491" s="5" t="n"/>
+      <c r="H491" s="6" t="n"/>
     </row>
     <row r="492" hidden="1" outlineLevel="2">
       <c r="A492" s="4" t="n">
@@ -6270,9 +6784,10 @@
       <c r="B492" s="5" t="n"/>
       <c r="C492" s="6" t="n"/>
       <c r="D492" s="6" t="n"/>
-      <c r="E492" s="5" t="n"/>
+      <c r="E492" s="6" t="n"/>
       <c r="F492" s="5" t="n"/>
-      <c r="G492" s="6" t="n"/>
+      <c r="G492" s="5" t="n"/>
+      <c r="H492" s="6" t="n"/>
     </row>
     <row r="493" hidden="1" outlineLevel="2">
       <c r="A493" s="4" t="n">
@@ -6281,9 +6796,10 @@
       <c r="B493" s="5" t="n"/>
       <c r="C493" s="6" t="n"/>
       <c r="D493" s="6" t="n"/>
-      <c r="E493" s="5" t="n"/>
+      <c r="E493" s="6" t="n"/>
       <c r="F493" s="5" t="n"/>
-      <c r="G493" s="6" t="n"/>
+      <c r="G493" s="5" t="n"/>
+      <c r="H493" s="6" t="n"/>
     </row>
     <row r="494" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A494" s="4" t="n">
@@ -6292,9 +6808,10 @@
       <c r="B494" s="5" t="n"/>
       <c r="C494" s="6" t="n"/>
       <c r="D494" s="6" t="n"/>
-      <c r="E494" s="5" t="n"/>
+      <c r="E494" s="6" t="n"/>
       <c r="F494" s="5" t="n"/>
-      <c r="G494" s="6" t="n"/>
+      <c r="G494" s="5" t="n"/>
+      <c r="H494" s="6" t="n"/>
     </row>
     <row r="495" hidden="1" outlineLevel="2">
       <c r="A495" s="4" t="n">
@@ -6303,9 +6820,10 @@
       <c r="B495" s="5" t="n"/>
       <c r="C495" s="6" t="n"/>
       <c r="D495" s="6" t="n"/>
-      <c r="E495" s="5" t="n"/>
+      <c r="E495" s="6" t="n"/>
       <c r="F495" s="5" t="n"/>
-      <c r="G495" s="6" t="n"/>
+      <c r="G495" s="5" t="n"/>
+      <c r="H495" s="6" t="n"/>
     </row>
     <row r="496" hidden="1" outlineLevel="2">
       <c r="A496" s="4" t="n">
@@ -6314,9 +6832,10 @@
       <c r="B496" s="5" t="n"/>
       <c r="C496" s="6" t="n"/>
       <c r="D496" s="6" t="n"/>
-      <c r="E496" s="5" t="n"/>
+      <c r="E496" s="6" t="n"/>
       <c r="F496" s="5" t="n"/>
-      <c r="G496" s="6" t="n"/>
+      <c r="G496" s="5" t="n"/>
+      <c r="H496" s="6" t="n"/>
     </row>
     <row r="497" hidden="1" outlineLevel="2">
       <c r="A497" s="4" t="n">
@@ -6325,9 +6844,10 @@
       <c r="B497" s="5" t="n"/>
       <c r="C497" s="6" t="n"/>
       <c r="D497" s="6" t="n"/>
-      <c r="E497" s="5" t="n"/>
+      <c r="E497" s="6" t="n"/>
       <c r="F497" s="5" t="n"/>
-      <c r="G497" s="6" t="n"/>
+      <c r="G497" s="5" t="n"/>
+      <c r="H497" s="6" t="n"/>
     </row>
     <row r="498" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A498" s="4" t="n">
@@ -6336,9 +6856,10 @@
       <c r="B498" s="5" t="n"/>
       <c r="C498" s="6" t="n"/>
       <c r="D498" s="6" t="n"/>
-      <c r="E498" s="5" t="n"/>
+      <c r="E498" s="6" t="n"/>
       <c r="F498" s="5" t="n"/>
-      <c r="G498" s="6" t="n"/>
+      <c r="G498" s="5" t="n"/>
+      <c r="H498" s="6" t="n"/>
     </row>
     <row r="499" hidden="1" outlineLevel="2">
       <c r="A499" s="4" t="n">
@@ -6347,9 +6868,10 @@
       <c r="B499" s="5" t="n"/>
       <c r="C499" s="6" t="n"/>
       <c r="D499" s="6" t="n"/>
-      <c r="E499" s="5" t="n"/>
+      <c r="E499" s="6" t="n"/>
       <c r="F499" s="5" t="n"/>
-      <c r="G499" s="6" t="n"/>
+      <c r="G499" s="5" t="n"/>
+      <c r="H499" s="6" t="n"/>
     </row>
     <row r="500" hidden="1" outlineLevel="2">
       <c r="A500" s="4" t="n">
@@ -6358,9 +6880,10 @@
       <c r="B500" s="5" t="n"/>
       <c r="C500" s="6" t="n"/>
       <c r="D500" s="6" t="n"/>
-      <c r="E500" s="5" t="n"/>
+      <c r="E500" s="6" t="n"/>
       <c r="F500" s="5" t="n"/>
-      <c r="G500" s="6" t="n"/>
+      <c r="G500" s="5" t="n"/>
+      <c r="H500" s="6" t="n"/>
     </row>
     <row r="501" hidden="1" outlineLevel="2">
       <c r="A501" s="4" t="n">
@@ -6369,9 +6892,10 @@
       <c r="B501" s="5" t="n"/>
       <c r="C501" s="6" t="n"/>
       <c r="D501" s="6" t="n"/>
-      <c r="E501" s="5" t="n"/>
+      <c r="E501" s="6" t="n"/>
       <c r="F501" s="5" t="n"/>
-      <c r="G501" s="6" t="n"/>
+      <c r="G501" s="5" t="n"/>
+      <c r="H501" s="6" t="n"/>
     </row>
     <row r="502" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A502" s="4" t="n">
@@ -6380,9 +6904,10 @@
       <c r="B502" s="5" t="n"/>
       <c r="C502" s="6" t="n"/>
       <c r="D502" s="6" t="n"/>
-      <c r="E502" s="5" t="n"/>
+      <c r="E502" s="6" t="n"/>
       <c r="F502" s="5" t="n"/>
-      <c r="G502" s="6" t="n"/>
+      <c r="G502" s="5" t="n"/>
+      <c r="H502" s="6" t="n"/>
     </row>
     <row r="503" hidden="1" outlineLevel="2">
       <c r="A503" s="4" t="n">
@@ -6391,9 +6916,10 @@
       <c r="B503" s="5" t="n"/>
       <c r="C503" s="6" t="n"/>
       <c r="D503" s="6" t="n"/>
-      <c r="E503" s="5" t="n"/>
+      <c r="E503" s="6" t="n"/>
       <c r="F503" s="5" t="n"/>
-      <c r="G503" s="6" t="n"/>
+      <c r="G503" s="5" t="n"/>
+      <c r="H503" s="6" t="n"/>
     </row>
     <row r="504" hidden="1" outlineLevel="2">
       <c r="A504" s="4" t="n">
@@ -6402,9 +6928,10 @@
       <c r="B504" s="5" t="n"/>
       <c r="C504" s="6" t="n"/>
       <c r="D504" s="6" t="n"/>
-      <c r="E504" s="5" t="n"/>
+      <c r="E504" s="6" t="n"/>
       <c r="F504" s="5" t="n"/>
-      <c r="G504" s="6" t="n"/>
+      <c r="G504" s="5" t="n"/>
+      <c r="H504" s="6" t="n"/>
     </row>
     <row r="505" hidden="1" outlineLevel="2">
       <c r="A505" s="4" t="n">
@@ -6413,9 +6940,10 @@
       <c r="B505" s="5" t="n"/>
       <c r="C505" s="6" t="n"/>
       <c r="D505" s="6" t="n"/>
-      <c r="E505" s="5" t="n"/>
+      <c r="E505" s="6" t="n"/>
       <c r="F505" s="5" t="n"/>
-      <c r="G505" s="6" t="n"/>
+      <c r="G505" s="5" t="n"/>
+      <c r="H505" s="6" t="n"/>
     </row>
     <row r="506" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A506" s="4" t="n">
@@ -6424,9 +6952,10 @@
       <c r="B506" s="5" t="n"/>
       <c r="C506" s="6" t="n"/>
       <c r="D506" s="6" t="n"/>
-      <c r="E506" s="5" t="n"/>
+      <c r="E506" s="6" t="n"/>
       <c r="F506" s="5" t="n"/>
-      <c r="G506" s="6" t="n"/>
+      <c r="G506" s="5" t="n"/>
+      <c r="H506" s="6" t="n"/>
     </row>
     <row r="507" hidden="1" outlineLevel="2">
       <c r="A507" s="4" t="n">
@@ -6435,9 +6964,10 @@
       <c r="B507" s="5" t="n"/>
       <c r="C507" s="6" t="n"/>
       <c r="D507" s="6" t="n"/>
-      <c r="E507" s="5" t="n"/>
+      <c r="E507" s="6" t="n"/>
       <c r="F507" s="5" t="n"/>
-      <c r="G507" s="6" t="n"/>
+      <c r="G507" s="5" t="n"/>
+      <c r="H507" s="6" t="n"/>
     </row>
     <row r="508" hidden="1" outlineLevel="2">
       <c r="A508" s="4" t="n">
@@ -6446,9 +6976,10 @@
       <c r="B508" s="5" t="n"/>
       <c r="C508" s="6" t="n"/>
       <c r="D508" s="6" t="n"/>
-      <c r="E508" s="5" t="n"/>
+      <c r="E508" s="6" t="n"/>
       <c r="F508" s="5" t="n"/>
-      <c r="G508" s="6" t="n"/>
+      <c r="G508" s="5" t="n"/>
+      <c r="H508" s="6" t="n"/>
     </row>
     <row r="509" hidden="1" outlineLevel="2">
       <c r="A509" s="4" t="n">
@@ -6457,9 +6988,10 @@
       <c r="B509" s="5" t="n"/>
       <c r="C509" s="6" t="n"/>
       <c r="D509" s="6" t="n"/>
-      <c r="E509" s="5" t="n"/>
+      <c r="E509" s="6" t="n"/>
       <c r="F509" s="5" t="n"/>
-      <c r="G509" s="6" t="n"/>
+      <c r="G509" s="5" t="n"/>
+      <c r="H509" s="6" t="n"/>
     </row>
     <row r="510" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A510" s="4" t="n">
@@ -6468,9 +7000,10 @@
       <c r="B510" s="5" t="n"/>
       <c r="C510" s="6" t="n"/>
       <c r="D510" s="6" t="n"/>
-      <c r="E510" s="5" t="n"/>
+      <c r="E510" s="6" t="n"/>
       <c r="F510" s="5" t="n"/>
-      <c r="G510" s="6" t="n"/>
+      <c r="G510" s="5" t="n"/>
+      <c r="H510" s="6" t="n"/>
     </row>
     <row r="511" hidden="1" outlineLevel="2">
       <c r="A511" s="4" t="n">
@@ -6479,9 +7012,10 @@
       <c r="B511" s="5" t="n"/>
       <c r="C511" s="6" t="n"/>
       <c r="D511" s="6" t="n"/>
-      <c r="E511" s="5" t="n"/>
+      <c r="E511" s="6" t="n"/>
       <c r="F511" s="5" t="n"/>
-      <c r="G511" s="6" t="n"/>
+      <c r="G511" s="5" t="n"/>
+      <c r="H511" s="6" t="n"/>
     </row>
     <row r="512" hidden="1" outlineLevel="2">
       <c r="A512" s="4" t="n">
@@ -6490,9 +7024,10 @@
       <c r="B512" s="5" t="n"/>
       <c r="C512" s="6" t="n"/>
       <c r="D512" s="6" t="n"/>
-      <c r="E512" s="5" t="n"/>
+      <c r="E512" s="6" t="n"/>
       <c r="F512" s="5" t="n"/>
-      <c r="G512" s="6" t="n"/>
+      <c r="G512" s="5" t="n"/>
+      <c r="H512" s="6" t="n"/>
     </row>
     <row r="513" hidden="1" outlineLevel="2">
       <c r="A513" s="4" t="n">
@@ -6501,9 +7036,10 @@
       <c r="B513" s="5" t="n"/>
       <c r="C513" s="6" t="n"/>
       <c r="D513" s="6" t="n"/>
-      <c r="E513" s="5" t="n"/>
+      <c r="E513" s="6" t="n"/>
       <c r="F513" s="5" t="n"/>
-      <c r="G513" s="6" t="n"/>
+      <c r="G513" s="5" t="n"/>
+      <c r="H513" s="6" t="n"/>
     </row>
     <row r="514" collapsed="1">
       <c r="A514" s="4" t="n">
@@ -6521,12 +7057,13 @@
         </is>
       </c>
       <c r="D514" s="6" t="n"/>
-      <c r="E514" s="5" t="n"/>
-      <c r="F514" s="5">
+      <c r="E514" s="6" t="n"/>
+      <c r="F514" s="5" t="n"/>
+      <c r="G514" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G514" s="6" t="inlineStr">
+      <c r="H514" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(15740, 127, 50, true, true)</t>
         </is>
@@ -6539,9 +7076,10 @@
       <c r="B515" s="5" t="n"/>
       <c r="C515" s="6" t="n"/>
       <c r="D515" s="6" t="n"/>
-      <c r="E515" s="5" t="n"/>
+      <c r="E515" s="6" t="n"/>
       <c r="F515" s="5" t="n"/>
-      <c r="G515" s="6" t="n"/>
+      <c r="G515" s="5" t="n"/>
+      <c r="H515" s="6" t="n"/>
     </row>
     <row r="516" hidden="1" outlineLevel="2">
       <c r="A516" s="4" t="n">
@@ -6550,9 +7088,10 @@
       <c r="B516" s="5" t="n"/>
       <c r="C516" s="6" t="n"/>
       <c r="D516" s="6" t="n"/>
-      <c r="E516" s="5" t="n"/>
+      <c r="E516" s="6" t="n"/>
       <c r="F516" s="5" t="n"/>
-      <c r="G516" s="6" t="n"/>
+      <c r="G516" s="5" t="n"/>
+      <c r="H516" s="6" t="n"/>
     </row>
     <row r="517" hidden="1" outlineLevel="2">
       <c r="A517" s="4" t="n">
@@ -6561,9 +7100,10 @@
       <c r="B517" s="5" t="n"/>
       <c r="C517" s="6" t="n"/>
       <c r="D517" s="6" t="n"/>
-      <c r="E517" s="5" t="n"/>
+      <c r="E517" s="6" t="n"/>
       <c r="F517" s="5" t="n"/>
-      <c r="G517" s="6" t="n"/>
+      <c r="G517" s="5" t="n"/>
+      <c r="H517" s="6" t="n"/>
     </row>
     <row r="518" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A518" s="4" t="n">
@@ -6572,9 +7112,10 @@
       <c r="B518" s="5" t="n"/>
       <c r="C518" s="6" t="n"/>
       <c r="D518" s="6" t="n"/>
-      <c r="E518" s="5" t="n"/>
+      <c r="E518" s="6" t="n"/>
       <c r="F518" s="5" t="n"/>
-      <c r="G518" s="6" t="n"/>
+      <c r="G518" s="5" t="n"/>
+      <c r="H518" s="6" t="n"/>
     </row>
     <row r="519" hidden="1" outlineLevel="2">
       <c r="A519" s="4" t="n">
@@ -6583,9 +7124,10 @@
       <c r="B519" s="5" t="n"/>
       <c r="C519" s="6" t="n"/>
       <c r="D519" s="6" t="n"/>
-      <c r="E519" s="5" t="n"/>
+      <c r="E519" s="6" t="n"/>
       <c r="F519" s="5" t="n"/>
-      <c r="G519" s="6" t="n"/>
+      <c r="G519" s="5" t="n"/>
+      <c r="H519" s="6" t="n"/>
     </row>
     <row r="520" hidden="1" outlineLevel="2">
       <c r="A520" s="4" t="n">
@@ -6594,9 +7136,10 @@
       <c r="B520" s="5" t="n"/>
       <c r="C520" s="6" t="n"/>
       <c r="D520" s="6" t="n"/>
-      <c r="E520" s="5" t="n"/>
+      <c r="E520" s="6" t="n"/>
       <c r="F520" s="5" t="n"/>
-      <c r="G520" s="6" t="n"/>
+      <c r="G520" s="5" t="n"/>
+      <c r="H520" s="6" t="n"/>
     </row>
     <row r="521" hidden="1" outlineLevel="2">
       <c r="A521" s="4" t="n">
@@ -6605,9 +7148,10 @@
       <c r="B521" s="5" t="n"/>
       <c r="C521" s="6" t="n"/>
       <c r="D521" s="6" t="n"/>
-      <c r="E521" s="5" t="n"/>
+      <c r="E521" s="6" t="n"/>
       <c r="F521" s="5" t="n"/>
-      <c r="G521" s="6" t="n"/>
+      <c r="G521" s="5" t="n"/>
+      <c r="H521" s="6" t="n"/>
     </row>
     <row r="522" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A522" s="4" t="n">
@@ -6616,9 +7160,10 @@
       <c r="B522" s="5" t="n"/>
       <c r="C522" s="6" t="n"/>
       <c r="D522" s="6" t="n"/>
-      <c r="E522" s="5" t="n"/>
+      <c r="E522" s="6" t="n"/>
       <c r="F522" s="5" t="n"/>
-      <c r="G522" s="6" t="n"/>
+      <c r="G522" s="5" t="n"/>
+      <c r="H522" s="6" t="n"/>
     </row>
     <row r="523" hidden="1" outlineLevel="2">
       <c r="A523" s="4" t="n">
@@ -6627,9 +7172,10 @@
       <c r="B523" s="5" t="n"/>
       <c r="C523" s="6" t="n"/>
       <c r="D523" s="6" t="n"/>
-      <c r="E523" s="5" t="n"/>
+      <c r="E523" s="6" t="n"/>
       <c r="F523" s="5" t="n"/>
-      <c r="G523" s="6" t="n"/>
+      <c r="G523" s="5" t="n"/>
+      <c r="H523" s="6" t="n"/>
     </row>
     <row r="524" hidden="1" outlineLevel="2">
       <c r="A524" s="4" t="n">
@@ -6638,9 +7184,10 @@
       <c r="B524" s="5" t="n"/>
       <c r="C524" s="6" t="n"/>
       <c r="D524" s="6" t="n"/>
-      <c r="E524" s="5" t="n"/>
+      <c r="E524" s="6" t="n"/>
       <c r="F524" s="5" t="n"/>
-      <c r="G524" s="6" t="n"/>
+      <c r="G524" s="5" t="n"/>
+      <c r="H524" s="6" t="n"/>
     </row>
     <row r="525" hidden="1" outlineLevel="2">
       <c r="A525" s="4" t="n">
@@ -6649,9 +7196,10 @@
       <c r="B525" s="5" t="n"/>
       <c r="C525" s="6" t="n"/>
       <c r="D525" s="6" t="n"/>
-      <c r="E525" s="5" t="n"/>
+      <c r="E525" s="6" t="n"/>
       <c r="F525" s="5" t="n"/>
-      <c r="G525" s="6" t="n"/>
+      <c r="G525" s="5" t="n"/>
+      <c r="H525" s="6" t="n"/>
     </row>
     <row r="526" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A526" s="4" t="n">
@@ -6660,9 +7208,10 @@
       <c r="B526" s="5" t="n"/>
       <c r="C526" s="6" t="n"/>
       <c r="D526" s="6" t="n"/>
-      <c r="E526" s="5" t="n"/>
+      <c r="E526" s="6" t="n"/>
       <c r="F526" s="5" t="n"/>
-      <c r="G526" s="6" t="n"/>
+      <c r="G526" s="5" t="n"/>
+      <c r="H526" s="6" t="n"/>
     </row>
     <row r="527" hidden="1" outlineLevel="2">
       <c r="A527" s="4" t="n">
@@ -6671,9 +7220,10 @@
       <c r="B527" s="5" t="n"/>
       <c r="C527" s="6" t="n"/>
       <c r="D527" s="6" t="n"/>
-      <c r="E527" s="5" t="n"/>
+      <c r="E527" s="6" t="n"/>
       <c r="F527" s="5" t="n"/>
-      <c r="G527" s="6" t="n"/>
+      <c r="G527" s="5" t="n"/>
+      <c r="H527" s="6" t="n"/>
     </row>
     <row r="528" hidden="1" outlineLevel="2">
       <c r="A528" s="4" t="n">
@@ -6682,9 +7232,10 @@
       <c r="B528" s="5" t="n"/>
       <c r="C528" s="6" t="n"/>
       <c r="D528" s="6" t="n"/>
-      <c r="E528" s="5" t="n"/>
+      <c r="E528" s="6" t="n"/>
       <c r="F528" s="5" t="n"/>
-      <c r="G528" s="6" t="n"/>
+      <c r="G528" s="5" t="n"/>
+      <c r="H528" s="6" t="n"/>
     </row>
     <row r="529" hidden="1" outlineLevel="2">
       <c r="A529" s="4" t="n">
@@ -6693,9 +7244,10 @@
       <c r="B529" s="5" t="n"/>
       <c r="C529" s="6" t="n"/>
       <c r="D529" s="6" t="n"/>
-      <c r="E529" s="5" t="n"/>
+      <c r="E529" s="6" t="n"/>
       <c r="F529" s="5" t="n"/>
-      <c r="G529" s="6" t="n"/>
+      <c r="G529" s="5" t="n"/>
+      <c r="H529" s="6" t="n"/>
     </row>
     <row r="530" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A530" s="4" t="n">
@@ -6704,9 +7256,10 @@
       <c r="B530" s="5" t="n"/>
       <c r="C530" s="6" t="n"/>
       <c r="D530" s="6" t="n"/>
-      <c r="E530" s="5" t="n"/>
+      <c r="E530" s="6" t="n"/>
       <c r="F530" s="5" t="n"/>
-      <c r="G530" s="6" t="n"/>
+      <c r="G530" s="5" t="n"/>
+      <c r="H530" s="6" t="n"/>
     </row>
     <row r="531" hidden="1" outlineLevel="2">
       <c r="A531" s="4" t="n">
@@ -6715,9 +7268,10 @@
       <c r="B531" s="5" t="n"/>
       <c r="C531" s="6" t="n"/>
       <c r="D531" s="6" t="n"/>
-      <c r="E531" s="5" t="n"/>
+      <c r="E531" s="6" t="n"/>
       <c r="F531" s="5" t="n"/>
-      <c r="G531" s="6" t="n"/>
+      <c r="G531" s="5" t="n"/>
+      <c r="H531" s="6" t="n"/>
     </row>
     <row r="532" hidden="1" outlineLevel="2">
       <c r="A532" s="4" t="n">
@@ -6726,9 +7280,10 @@
       <c r="B532" s="5" t="n"/>
       <c r="C532" s="6" t="n"/>
       <c r="D532" s="6" t="n"/>
-      <c r="E532" s="5" t="n"/>
+      <c r="E532" s="6" t="n"/>
       <c r="F532" s="5" t="n"/>
-      <c r="G532" s="6" t="n"/>
+      <c r="G532" s="5" t="n"/>
+      <c r="H532" s="6" t="n"/>
     </row>
     <row r="533" hidden="1" outlineLevel="2">
       <c r="A533" s="4" t="n">
@@ -6737,9 +7292,10 @@
       <c r="B533" s="5" t="n"/>
       <c r="C533" s="6" t="n"/>
       <c r="D533" s="6" t="n"/>
-      <c r="E533" s="5" t="n"/>
+      <c r="E533" s="6" t="n"/>
       <c r="F533" s="5" t="n"/>
-      <c r="G533" s="6" t="n"/>
+      <c r="G533" s="5" t="n"/>
+      <c r="H533" s="6" t="n"/>
     </row>
     <row r="534" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A534" s="4" t="n">
@@ -6748,9 +7304,10 @@
       <c r="B534" s="5" t="n"/>
       <c r="C534" s="6" t="n"/>
       <c r="D534" s="6" t="n"/>
-      <c r="E534" s="5" t="n"/>
+      <c r="E534" s="6" t="n"/>
       <c r="F534" s="5" t="n"/>
-      <c r="G534" s="6" t="n"/>
+      <c r="G534" s="5" t="n"/>
+      <c r="H534" s="6" t="n"/>
     </row>
     <row r="535" hidden="1" outlineLevel="2">
       <c r="A535" s="4" t="n">
@@ -6759,9 +7316,10 @@
       <c r="B535" s="5" t="n"/>
       <c r="C535" s="6" t="n"/>
       <c r="D535" s="6" t="n"/>
-      <c r="E535" s="5" t="n"/>
+      <c r="E535" s="6" t="n"/>
       <c r="F535" s="5" t="n"/>
-      <c r="G535" s="6" t="n"/>
+      <c r="G535" s="5" t="n"/>
+      <c r="H535" s="6" t="n"/>
     </row>
     <row r="536" hidden="1" outlineLevel="2">
       <c r="A536" s="4" t="n">
@@ -6770,9 +7328,10 @@
       <c r="B536" s="5" t="n"/>
       <c r="C536" s="6" t="n"/>
       <c r="D536" s="6" t="n"/>
-      <c r="E536" s="5" t="n"/>
+      <c r="E536" s="6" t="n"/>
       <c r="F536" s="5" t="n"/>
-      <c r="G536" s="6" t="n"/>
+      <c r="G536" s="5" t="n"/>
+      <c r="H536" s="6" t="n"/>
     </row>
     <row r="537" hidden="1" outlineLevel="2">
       <c r="A537" s="4" t="n">
@@ -6781,9 +7340,10 @@
       <c r="B537" s="5" t="n"/>
       <c r="C537" s="6" t="n"/>
       <c r="D537" s="6" t="n"/>
-      <c r="E537" s="5" t="n"/>
+      <c r="E537" s="6" t="n"/>
       <c r="F537" s="5" t="n"/>
-      <c r="G537" s="6" t="n"/>
+      <c r="G537" s="5" t="n"/>
+      <c r="H537" s="6" t="n"/>
     </row>
     <row r="538" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A538" s="4" t="n">
@@ -6792,9 +7352,10 @@
       <c r="B538" s="5" t="n"/>
       <c r="C538" s="6" t="n"/>
       <c r="D538" s="6" t="n"/>
-      <c r="E538" s="5" t="n"/>
+      <c r="E538" s="6" t="n"/>
       <c r="F538" s="5" t="n"/>
-      <c r="G538" s="6" t="n"/>
+      <c r="G538" s="5" t="n"/>
+      <c r="H538" s="6" t="n"/>
     </row>
     <row r="539" hidden="1" outlineLevel="2">
       <c r="A539" s="4" t="n">
@@ -6803,9 +7364,10 @@
       <c r="B539" s="5" t="n"/>
       <c r="C539" s="6" t="n"/>
       <c r="D539" s="6" t="n"/>
-      <c r="E539" s="5" t="n"/>
+      <c r="E539" s="6" t="n"/>
       <c r="F539" s="5" t="n"/>
-      <c r="G539" s="6" t="n"/>
+      <c r="G539" s="5" t="n"/>
+      <c r="H539" s="6" t="n"/>
     </row>
     <row r="540" hidden="1" outlineLevel="2">
       <c r="A540" s="4" t="n">
@@ -6814,9 +7376,10 @@
       <c r="B540" s="5" t="n"/>
       <c r="C540" s="6" t="n"/>
       <c r="D540" s="6" t="n"/>
-      <c r="E540" s="5" t="n"/>
+      <c r="E540" s="6" t="n"/>
       <c r="F540" s="5" t="n"/>
-      <c r="G540" s="6" t="n"/>
+      <c r="G540" s="5" t="n"/>
+      <c r="H540" s="6" t="n"/>
     </row>
     <row r="541" hidden="1" outlineLevel="2">
       <c r="A541" s="4" t="n">
@@ -6825,9 +7388,10 @@
       <c r="B541" s="5" t="n"/>
       <c r="C541" s="6" t="n"/>
       <c r="D541" s="6" t="n"/>
-      <c r="E541" s="5" t="n"/>
+      <c r="E541" s="6" t="n"/>
       <c r="F541" s="5" t="n"/>
-      <c r="G541" s="6" t="n"/>
+      <c r="G541" s="5" t="n"/>
+      <c r="H541" s="6" t="n"/>
     </row>
     <row r="542" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A542" s="4" t="n">
@@ -6836,9 +7400,10 @@
       <c r="B542" s="5" t="n"/>
       <c r="C542" s="6" t="n"/>
       <c r="D542" s="6" t="n"/>
-      <c r="E542" s="5" t="n"/>
+      <c r="E542" s="6" t="n"/>
       <c r="F542" s="5" t="n"/>
-      <c r="G542" s="6" t="n"/>
+      <c r="G542" s="5" t="n"/>
+      <c r="H542" s="6" t="n"/>
     </row>
     <row r="543" hidden="1" outlineLevel="2">
       <c r="A543" s="4" t="n">
@@ -6847,9 +7412,10 @@
       <c r="B543" s="5" t="n"/>
       <c r="C543" s="6" t="n"/>
       <c r="D543" s="6" t="n"/>
-      <c r="E543" s="5" t="n"/>
+      <c r="E543" s="6" t="n"/>
       <c r="F543" s="5" t="n"/>
-      <c r="G543" s="6" t="n"/>
+      <c r="G543" s="5" t="n"/>
+      <c r="H543" s="6" t="n"/>
     </row>
     <row r="544" hidden="1" outlineLevel="2">
       <c r="A544" s="4" t="n">
@@ -6858,9 +7424,10 @@
       <c r="B544" s="5" t="n"/>
       <c r="C544" s="6" t="n"/>
       <c r="D544" s="6" t="n"/>
-      <c r="E544" s="5" t="n"/>
+      <c r="E544" s="6" t="n"/>
       <c r="F544" s="5" t="n"/>
-      <c r="G544" s="6" t="n"/>
+      <c r="G544" s="5" t="n"/>
+      <c r="H544" s="6" t="n"/>
     </row>
     <row r="545" hidden="1" outlineLevel="2">
       <c r="A545" s="4" t="n">
@@ -6869,9 +7436,10 @@
       <c r="B545" s="5" t="n"/>
       <c r="C545" s="6" t="n"/>
       <c r="D545" s="6" t="n"/>
-      <c r="E545" s="5" t="n"/>
+      <c r="E545" s="6" t="n"/>
       <c r="F545" s="5" t="n"/>
-      <c r="G545" s="6" t="n"/>
+      <c r="G545" s="5" t="n"/>
+      <c r="H545" s="6" t="n"/>
     </row>
     <row r="546" collapsed="1">
       <c r="A546" s="4" t="n">
@@ -6889,12 +7457,13 @@
         </is>
       </c>
       <c r="D546" s="6" t="n"/>
-      <c r="E546" s="5" t="n"/>
-      <c r="F546" s="5">
+      <c r="E546" s="6" t="n"/>
+      <c r="F546" s="5" t="n"/>
+      <c r="G546" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="G546" s="6" t="inlineStr">
+      <c r="H546" s="6" t="inlineStr">
         <is>
           <t>! nur im Excel - der alte Code geht hier schon in Schwarz</t>
         </is>
@@ -6907,9 +7476,10 @@
       <c r="B547" s="5" t="n"/>
       <c r="C547" s="6" t="n"/>
       <c r="D547" s="6" t="n"/>
-      <c r="E547" s="5" t="n"/>
+      <c r="E547" s="6" t="n"/>
       <c r="F547" s="5" t="n"/>
-      <c r="G547" s="6" t="n"/>
+      <c r="G547" s="5" t="n"/>
+      <c r="H547" s="6" t="n"/>
     </row>
     <row r="548" hidden="1" outlineLevel="2">
       <c r="A548" s="4" t="n">
@@ -6918,9 +7488,10 @@
       <c r="B548" s="5" t="n"/>
       <c r="C548" s="6" t="n"/>
       <c r="D548" s="6" t="n"/>
-      <c r="E548" s="5" t="n"/>
+      <c r="E548" s="6" t="n"/>
       <c r="F548" s="5" t="n"/>
-      <c r="G548" s="6" t="n"/>
+      <c r="G548" s="5" t="n"/>
+      <c r="H548" s="6" t="n"/>
     </row>
     <row r="549" hidden="1" outlineLevel="2">
       <c r="A549" s="4" t="n">
@@ -6929,9 +7500,10 @@
       <c r="B549" s="5" t="n"/>
       <c r="C549" s="6" t="n"/>
       <c r="D549" s="6" t="n"/>
-      <c r="E549" s="5" t="n"/>
+      <c r="E549" s="6" t="n"/>
       <c r="F549" s="5" t="n"/>
-      <c r="G549" s="6" t="n"/>
+      <c r="G549" s="5" t="n"/>
+      <c r="H549" s="6" t="n"/>
     </row>
     <row r="550" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A550" s="4" t="n">
@@ -6940,9 +7512,10 @@
       <c r="B550" s="5" t="n"/>
       <c r="C550" s="6" t="n"/>
       <c r="D550" s="6" t="n"/>
-      <c r="E550" s="5" t="n"/>
+      <c r="E550" s="6" t="n"/>
       <c r="F550" s="5" t="n"/>
-      <c r="G550" s="6" t="n"/>
+      <c r="G550" s="5" t="n"/>
+      <c r="H550" s="6" t="n"/>
     </row>
     <row r="551" hidden="1" outlineLevel="2">
       <c r="A551" s="4" t="n">
@@ -6951,9 +7524,10 @@
       <c r="B551" s="5" t="n"/>
       <c r="C551" s="6" t="n"/>
       <c r="D551" s="6" t="n"/>
-      <c r="E551" s="5" t="n"/>
+      <c r="E551" s="6" t="n"/>
       <c r="F551" s="5" t="n"/>
-      <c r="G551" s="6" t="n"/>
+      <c r="G551" s="5" t="n"/>
+      <c r="H551" s="6" t="n"/>
     </row>
     <row r="552" hidden="1" outlineLevel="2">
       <c r="A552" s="4" t="n">
@@ -6962,9 +7536,10 @@
       <c r="B552" s="5" t="n"/>
       <c r="C552" s="6" t="n"/>
       <c r="D552" s="6" t="n"/>
-      <c r="E552" s="5" t="n"/>
+      <c r="E552" s="6" t="n"/>
       <c r="F552" s="5" t="n"/>
-      <c r="G552" s="6" t="n"/>
+      <c r="G552" s="5" t="n"/>
+      <c r="H552" s="6" t="n"/>
     </row>
     <row r="553" hidden="1" outlineLevel="2">
       <c r="A553" s="4" t="n">
@@ -6973,9 +7548,10 @@
       <c r="B553" s="5" t="n"/>
       <c r="C553" s="6" t="n"/>
       <c r="D553" s="6" t="n"/>
-      <c r="E553" s="5" t="n"/>
+      <c r="E553" s="6" t="n"/>
       <c r="F553" s="5" t="n"/>
-      <c r="G553" s="6" t="n"/>
+      <c r="G553" s="5" t="n"/>
+      <c r="H553" s="6" t="n"/>
     </row>
     <row r="554">
       <c r="A554" s="7" t="n">
@@ -6991,10 +7567,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="E554" t="n">
+      <c r="F554" t="n">
         <v>0</v>
       </c>
-      <c r="F554">
+      <c r="G554">
         <f>$C$3</f>
         <v/>
       </c>
